--- a/data/gates/planilla_ILIA2026_SIMPLE.xlsx
+++ b/data/gates/planilla_ILIA2026_SIMPLE.xlsx
@@ -11261,7 +11261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11407,12 +11407,24 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>Qué alimenta el cálculo</t>
+          <t>Qué alimenta el cálculo (metodología CENIA v2)</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>Sub1 (Uso): Tipos de proceso, Etapas de uso, Continuidad/Nivel, Convocante (Público/Privado), Cantidad de iniciativas. Sub2 (Desarrollo, = 2025): Tipo desarrollador, Origen, Tipos de IA.</t>
+          <t>Sub1 (Uso): Tipos de proceso (÷5) · Etapas de uso (÷4) · Continuidad = nivel máximo del país (÷3) · Organización Convocante = 3 sub-componentes (amplitud gubernamental ÷3 + amplitud no gubernamental ÷4 + co-convocatoria por máx. relativo) · Cantidad = nº de iniciativas ELEGIBLES (todas, umbrales fijos). Sub2 (Desarrollo, = 2025): Desarrollador (nacional/internacional × 4 tipos, máx. relativo) · Tipos de IA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>IMPORTANTE — co-convocatoria</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Anotar TODOS los convocantes de cada iniciativa (no solo el principal): si ≥2 tipos co-convocan, forman una 'combinación' que suma al tercer sub-componente de Organización Convocante.</t>
         </is>
       </c>
     </row>

--- a/data/gates/planilla_ILIA2026_SIMPLE.xlsx
+++ b/data/gates/planilla_ILIA2026_SIMPLE.xlsx
@@ -12,6 +12,7 @@
     <sheet name="3 · Excluidos" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="4 · Evidencia y fuentes" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="5 · Instrucciones" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6 · Metodología (CENIA v2)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos (entran+dudosos)'!$A$1:$X$45</definedName>
@@ -26,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +45,15 @@
     <font>
       <b val="1"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="8">
@@ -84,7 +94,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -106,11 +116,44 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -152,6 +195,26 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -11284,7 +11347,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>Planilla con 5 pestañas. 44 casos entran/dudosos · 63 excluidos · 107 en total. Tras dedup e-Cidadania: 43 iniciativas.</t>
+          <t>Planilla con 6 pestañas. 44 casos entran/dudosos · 63 excluidos · 107 en total. Tras dedup e-Cidadania: 43 iniciativas.</t>
         </is>
       </c>
     </row>
@@ -11296,7 +11359,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Pestaña 1 = trabajo y cálculo · 2 = qué decidir a mano · 3 = excluidos (referencia) · 4 = evidencia/citas · 5 = esta guía.</t>
+          <t>Pestaña 1 = trabajo y cálculo · 2 = qué decidir a mano · 3 = excluidos (referencia) · 4 = evidencia/citas · 5 = esta guía · 6 = metodología CENIA v2.</t>
         </is>
       </c>
     </row>
@@ -11431,4 +11494,351 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>METODOLOGÍA FINAL — IA en Participación Ciudadana (CENIA v2 · jun-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Indicador = (Sub-Indicador de Uso + Sub-Indicador de Desarrollo) / 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr"/>
+      <c r="B3" s="13" t="inlineStr"/>
+      <c r="C3" s="13" t="inlineStr"/>
+      <c r="D3" s="13" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Sub-indicador</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Cómo se calcula (normalización)</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Columna en pestaña 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Uso de IA
+(promedio simple
+de 5 variables)</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Tipos de proceso</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>nº de tipos distintos ÷ 5 (máximo absoluto)</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Tipo de proceso</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="n"/>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>Etapas de uso</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>nº de etapas distintas ÷ 4 (máximo absoluto)</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>Etapas uso IA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="n"/>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Continuidad</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>nivel MÁXIMO verificado del país ÷ 3 · un 'anuncio' caduca a los 2 años sin implementación</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>Nivel (0-3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="n"/>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Organización Convocante</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>promedio de 3 sub-componentes co-iguales (ver detalle abajo)</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>Convocante (7-cat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="n"/>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Cantidad de iniciativas</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>nº de TODAS las iniciativas elegibles del país · umbrales fijos 0→0 · 1-3→25 · 4-6→50 · 7-9→75 · 10+→100</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>1 fila = 1 iniciativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Desarrollo de IA
+(idéntico a 2025)</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>nacional / internacional × 4 tipos de actor · máximo relativo</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Tipo desarrollador IA · Origen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="n"/>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Tipos de IA</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>nº de sistemas de IA distintos · máximo relativo</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>Tipos/familia IA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr"/>
+      <c r="B12" s="13" t="inlineStr"/>
+      <c r="C12" s="13" t="inlineStr"/>
+      <c r="D12" s="13" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>ORGANIZACIÓN CONVOCANTE — 3 sub-componentes co-iguales · valor de la variable = (1 + 2 + 3) / 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>1 · Amplitud gubernamental</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>nº de tipos gubernamentales distintos ÷ 3</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>gobierno local · gobierno nacional · otra institución pública</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>2 · Amplitud no gubernamental</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>nº de tipos no gubernamentales distintos ÷ 4</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>empresa · universidad · sociedad civil · organización internacional</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>3 · Co-convocatoria</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>nº de combinaciones distintas (conjuntos de ≥2 tipos que co-convocan una misma iniciativa) ÷ máximo relativo móvil del ciclo</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>combinaciones DEDUPLICADAS · una co-convocatoria de 4 actores = 1 combinación</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr"/>
+      <c r="B17" s="13" t="inlineStr"/>
+      <c r="C17" s="13" t="inlineStr"/>
+      <c r="D17" s="13" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>• Universidades públicas → cuentan como 'Universidad' (no gubernamental), NO como 'otra institución pública'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr"/>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>• Anotar TODOS los convocantes de cada iniciativa (no solo el principal): así se detecta la co-convocatoria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr"/>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>• El máximo relativo de co-convocatoria se recalcula en cada corrida del motor — no se fija a mano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr"/>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>• 'Cantidad' cuenta las iniciativas elegibles; los duplicados (Cuenta como iniciativa = NO) no se suman.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr"/>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>• El Sub-Indicador de Desarrollo es idéntico al de 2025 (no se modificó).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr"/>
+      <c r="B23" s="13" t="inlineStr"/>
+      <c r="C23" s="13" t="inlineStr"/>
+      <c r="D23" s="13" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>metodologia_final_CENIA_v2.xlsx · detalle de conformidad en conformidad_metodologia_CENIA.md</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A5:A9"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="B20:D20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/gates/planilla_ILIA2026_SIMPLE.xlsx
+++ b/data/gates/planilla_ILIA2026_SIMPLE.xlsx
@@ -15,10 +15,10 @@
     <sheet name="6 · Metodología (CENIA v2)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos (entran+dudosos)'!$A$1:$X$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos (entran+dudosos)'!$A$1:$X$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2 · A validar a mano'!$A$1:$G$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 · Excluidos'!$A$1:$E$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 · Evidencia y fuentes'!$A$1:$L$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 · Excluidos'!$A$1:$E$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 · Evidencia y fuentes'!$A$1:$L$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X38"/>
+  <dimension ref="A1:X41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2354,9 +2354,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>➜ DUDA (criterio corregido) — resolver a mano</t>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -2592,9 +2592,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>➜ DUDA (criterio corregido) — resolver a mano</t>
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -3287,9 +3287,9 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>➜ REVISAR — ¿es participación?</t>
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -3524,7 +3524,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>➜ DUDA — revisar posible IA/participación</t>
+        </is>
+      </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>CO</t>
@@ -3532,7 +3536,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>ECHO – HáblameD Medellín</t>
+          <t>DNP - Diálogos Regionales Vinculantes (PND 2022-2026)</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -3540,9 +3544,9 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3552,17 +3556,17 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Participación Digital; Mini públicos</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
@@ -3575,17 +3579,17 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>organización internacional; gobierno local</t>
+          <t>gobierno nacional</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>contenido</t>
+          <t>no-claro</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3595,92 +3599,85 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>Voz a Texto; NLP; LLM</t>
-        </is>
-      </c>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
       <c r="R26" s="2" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>Diálogos Regionales Vinculantes (DRV) convocados por el Gobierno Nacional (Presidencia + DNP) para construir las bases del Plan Nacional de Desarrollo 2022-2026 'Colombia, Potencia Mundial de la Vida'. 51 diálogos regionales, ~250.000 participantes, 2.115 mesas de diálogo, 89.788 propuestas ciudadanas recolectadas y sistematizadas.</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>Departamento Nacional de Planeación (DNP) de Colombia. El análisis cuantitativo lo realizó la 'Unidad de Científicos de Datos' del DNP; el análisis cualitativo se desarrolló de manera conjunta entre el DNP y la Universidad Externado de Colombia (Facultad de Ciencias Sociales y Humanas).</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="V26" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.funcionpublica.gov.co/documents/d/guest/la_rendicion_de_cuentas_y_el_control_social_marco_dialogos_regionales_vinculantes_-drv-
+https://github.com/ucd-dnp/ConTexto</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>CO-dnp-dialogos-regionales-vinculantes-pnd</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>ECHO – HáblameD Medellín</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>IA que capta voz ciudadana en debates guiados y clasifica cada enunciado en metas ODS, generando visualizaciones para la planificación territorial</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
-        </is>
-      </c>
-      <c r="X26" s="2" t="inlineStr">
-        <is>
-          <t>CO-echo-hablamed-medellin</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>➜ RESOLVER DUDA</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>(sin revisar)</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>DUDA(lean SI)</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (múltiples fuentes de prensa independientes; sin verificación técnica del método; cobertura crítica)</t>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Presupuestos Participativos; Gobernanza Colaborativa</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Análisis; Traducción Política</t>
+          <t>Implementación; Análisis</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
@@ -3688,1333 +3685,1686 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>organización internacional; gobierno local</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Mixto</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>Voz a Texto; NLP; LLM</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>IA que capta voz ciudadana en debates guiados y clasifica cada enunciado en metas ODS, generando visualizaciones para la planificación territorial</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>CO-echo-hablamed-medellin</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>➜ RESOLVER DUDA</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>(sin revisar)</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>DUDA(lean SI)</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>MEDIA (múltiples fuentes de prensa independientes; sin verificación técnica del método; cobertura crítica)</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Presupuestos Participativos; Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Análisis; Traducción Política</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>sociedad civil</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Sociedad Civil</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q27" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>LLM; NLP</t>
         </is>
       </c>
-      <c r="R27" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>Plataforma participativa donde jóvenes del resguardo Zenú deciden por votación digital la asignación de presupuestos locales del cabildo y debaten proyectos de ley / proponen iniciativas ciudadanas colectivas.</t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
         <is>
           <t>Resguardo indígena Zenú (Reparo Torrente, Bajo Sinú); creador Carlos Redondo Rincón</t>
         </is>
       </c>
-      <c r="U27" s="2" t="inlineStr">
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="V27" s="5" t="n">
+      <c r="V28" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="W27" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>https://cerosetenta.uniandes.edu.co/
 https://gaitanaia.org/
 https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
         <is>
           <t>CO-gaitana-ia-resguardo-zenu</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-      <c r="B28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Tenemos que hablar de Colombia</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="J28" s="2" t="n">
+      <c r="J29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>universidad; empresa; sociedad civil</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>Mixto</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Sociedad Civil</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>NLP - Tópicos; NLP - Sentiment</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>Plataforma colaborativa de diálogo e incidencia ciudadana para la conversación entre diversos actores de la sociedad colombiana, surgido a partir de eventos de manifestaciones sociales.</t>
         </is>
       </c>
-      <c r="T28" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
         <is>
           <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
         </is>
       </c>
-      <c r="U28" s="2" t="inlineStr">
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="V28" s="4" t="n">
+      <c r="V29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W28" s="2" t="inlineStr">
+      <c r="W29" s="2" t="inlineStr">
         <is>
           <t>https://tenemosquehablarcolombia.co/
 https://tenemosquehablarcolombia.co/resultados/</t>
         </is>
       </c>
-      <c r="X28" s="2" t="inlineStr">
+      <c r="X29" s="2" t="inlineStr">
         <is>
           <t>CO-tenemos-que-hablar-de-colombia</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>➜ DUDA (criterio corregido) — resolver a mano</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>➜ DUDA (frontera) — resolver a mano</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>U-Report Costa Rica – chatbot juvenil</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Participación Digital</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="J29" s="2" t="n">
+      <c r="J30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>organización internacional</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Sociedad Civil; Privado</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>NLP</t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>U-Report es una plataforma global de UNICEF que empodera a adolescentes y jóvenes, permitiéndoles opinar sobre temas sociales cruciales a través de canales que ya utilizan, como WhatsApp, SMS y Facebook Messenger.</t>
         </is>
       </c>
-      <c r="T29" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
         <is>
           <t>Unicef</t>
         </is>
       </c>
-      <c r="U29" s="2" t="inlineStr"/>
-      <c r="V29" s="4" t="n">
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W29" s="2" t="inlineStr">
+      <c r="W30" s="2" t="inlineStr">
         <is>
           <t>https://costarica.ureport.in/
 https://www.unicef.org/costarica/comunicados-prensa/plataforma-mundial-u-report-llega-costa-rica</t>
         </is>
       </c>
-      <c r="X29" s="2" t="inlineStr">
+      <c r="X30" s="2" t="inlineStr">
         <is>
           <t>CR-u-report-costa-rica-chatbot-juvenil</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
-      <c r="B30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>➜ DUDA — revisar posible IA/participación</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>CiudadanIA</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>(sin revisar)</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>SI*</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Plataforma</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>empresa; universidad; gobierno nacional</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Mixto</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>Sistemas de recomendación; LLM</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>Sistema de interacción ciudadana basado en inteligencia artificial, diseñado para recopilar datos representativos que permitan el entrenamiento avanzado de IA en la prestación de servicios públicos. A través de ventanillas ubicadas en puntos estratégicos de alto tránsito, ofrece asistencia, información y recomendaciones personalizadas, fomentando la participación activa de la ciudadanía en el diseño y desarrollo de un sistema de Gobierno Inteligente.</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>GENIA Latinoamérica, en colaboración con la Universidad del Caribe (UNICARIBE), el Ministerio de la Presidencia (MINPRE) y la Oficina Gubernamental de Tecnologías de la Información y Comunicación (OGTIC)</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.genia.ai/paises-miembros
+https://presidencia.gob.do/seccion/inteligencia-artificial</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>DO-ciudadania</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>EC</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PAGA IA </t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="J30" s="2" t="n">
+      <c r="J32" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>gobierno nacional; sociedad civil</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>Mixto</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Sociedad Civil</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>LLM</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto. Analiza datos de planes de acción de gobierno abierto de Ecuador y otros países de Hispanoamérica para sugerir actividades e hitos relacionados con temas propuestos por los usuarios</t>
         </is>
       </c>
-      <c r="T30" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
         <is>
           <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
         </is>
       </c>
-      <c r="U30" s="2" t="inlineStr">
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V30" s="4" t="n">
+      <c r="V32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>https://www.gobiernoabierto.ec/boletin-014-2023/
 https://ia.gobiernoabierto.ec/
 https://ia.gobiernoabierto.ec/acercade</t>
         </is>
       </c>
-      <c r="X30" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
         <is>
           <t>EC-paga-ia</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
-      <c r="B31" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Guatemala Joven Conversa </t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="J31" s="2" t="n">
+      <c r="J33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>organización internacional; sociedad civil</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Mixto</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Gobierno</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
+      <c r="P33" s="2" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr">
+      <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>NLP - Sentiment; NLP - Tópicos</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="R33" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
+      <c r="S33" s="2" t="inlineStr">
         <is>
           <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarrollo y la lucha contra la corrupción.</t>
         </is>
       </c>
-      <c r="T31" s="2" t="inlineStr">
+      <c r="T33" s="2" t="inlineStr">
         <is>
           <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
         </is>
       </c>
-      <c r="U31" s="2" t="inlineStr">
+      <c r="U33" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="V31" s="4" t="n">
+      <c r="V33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="W33" s="2" t="inlineStr">
         <is>
           <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
 https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/?utm_source=chatgpt.com
 https://dppa.un.org/en/using-power-of-ai-to-boost-youth-political-participation-guatemala</t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr">
+      <c r="X33" s="2" t="inlineStr">
         <is>
           <t>GT-guatemala-joven-conversa</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>HN</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RedPública + iVerify </t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="J32" s="2" t="n">
+      <c r="J34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>organización internacional; universidad</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Gobierno; Academia</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>Internacional, Nacional</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>NLP - Tópicos</t>
         </is>
       </c>
-      <c r="R32" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias. Integra iVerify, una herramienta que utiliza aprendizaje automático para detectar y clasificar desinformación electoral antes de su publicación.</t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
         <is>
           <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
         </is>
       </c>
-      <c r="U32" s="2" t="inlineStr">
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V32" s="4" t="n">
+      <c r="V34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W32" s="2" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
         <is>
           <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
         </is>
       </c>
-      <c r="X32" s="2" t="inlineStr">
+      <c r="X34" s="2" t="inlineStr">
         <is>
           <t>HN-redpublica-iverify</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-      <c r="B33" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Gobernanza Colaborativa; Participación Digital</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="J33" s="2" t="n">
+      <c r="J35" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>gobierno local</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O33" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Gobierno</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr">
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>NLP; Otros(no especificado)</t>
         </is>
       </c>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
         <is>
           <t>Elaboración del Programa de Gobierno del Estado de Guanajuato 2024-2030 ('Gobierno de la Gente'), un plan de gobierno construido con participación ciudadana: se recorrió el territorio y se realizaron cuatro talleres regionales (noreste, norte, centro y sur) con representación de los 46 municipios, integrando la voz de más de 26,000 personas mediante talleres y consultas. El contenido fue validado por el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG), conformado por ciudadanía, la Gobernadora, secretarios de cada eje e IPLANEG. Se utilizaron herramientas de inteligencia artificial para procesar y organizar las miles de ideas y propuestas recibidas, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región, transformando el diálogo social en datos para la toma de decisiones que alimentaron los ejes del programa. Adicionalmente existe la asistente virtual 'Esperanza' para consultar el programa ya publicado.</t>
         </is>
       </c>
-      <c r="T33" s="2" t="inlineStr">
+      <c r="T35" s="2" t="inlineStr">
         <is>
           <t>Gobierno del Estado de Guanajuato — Instituto de Planeación, Estadística y Geografía del Estado de Guanajuato (IPLANEG), con validación del COPLADEG. Titular: Gobernadora Libia Dennise García Muñoz Ledo.</t>
         </is>
       </c>
-      <c r="U33" s="2" t="inlineStr">
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="V33" s="5" t="n">
+      <c r="V35" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="W33" s="2" t="inlineStr">
+      <c r="W35" s="2" t="inlineStr">
         <is>
           <t>https://guanajuatointeligente.com/como-hicimos-el-programa/
 https://iplaneg.guanajuato.gob.mx/programagobierno24-30/
 https://iplaneg.guanajuato.gob.mx/wp-content/uploads/03-2.05-Diagnostico-Programa-de-Gobierno-2024-2030-_Diagnostico-Estatal-2025_.pdf</t>
         </is>
       </c>
-      <c r="X33" s="2" t="inlineStr">
+      <c r="X35" s="2" t="inlineStr">
         <is>
           <t>MX-guanajuato-inteligente-2024-2030</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>➜ RESOLVER DUDA</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Jalisco - Consulta ¡Armemos un Plan! (Plan Estatal de Desarrollo y Gobernanza 2024-2030)</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>(sin revisar)</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>DUDA(lean NO)</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="n">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>gobierno local</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" s="2" t="inlineStr"/>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>Consulta ciudadana '¡Armemos un Plan!' convocada por el Gobierno de Jalisco a través de la Secretaría de Planeación y Participación Ciudadana (SPPC) para construir el Plan Estatal de Desarrollo y Gobernanza 2024-2030. Ejercicio abierto e inclusivo del 20 de febrero al 17 de abril de 2025 que registró 675,484 participaciones (aprox. 624,226 participaciones digitales + 25,176 niñas, niños y adolescentes mediante un mecanismo especialmente diseñado). Combinó: una encuesta representativa 'casa por casa' con rigor estadístico y metodológico; consulta digital abierta que recibió 15,899 propuestas ciudadanas escritas (temas: espacios públicos/deportivos/recreativos, medio ambiente y movilidad, agua y territorio, turismo rural, vivienda digna, economías locales); 12 foros regionales y 9 foros temáticos / mesas de trabajo con 5,563 participantes presenciales; 168 mesas regionales y 47 sectoriales donde se identificaron y discutieron 1,349 problemáticas; e instalación de 18 Consejos de Participación y Planeación (1 estatal, 12 regionales, 5 sectoriales). El resultado se estructuró en 5 ejes, 36 temas, 50 objetivos estratégicos, 197-198 proyectos y 82 indicadores de seguimiento.</t>
         </is>
       </c>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
         <is>
           <t>Gobierno del Estado de Jalisco — Secretaría de Planeación y Participación Ciudadana (SPPC). Titular: Cynthia Cantero Pacheco. Apoyo de información estadística/geográfica: Instituto de Información Estadística y Geográfica de Jalisco (IIEG). Gobernador: Pablo Lemus Navarro (administración 2024-2030).</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr">
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="V34" s="5" t="n">
+      <c r="V36" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="W34" s="2" t="inlineStr">
+      <c r="W36" s="2" t="inlineStr">
         <is>
           <t>https://armemosunplan.mx/wp-content/uploads/2025/10/Armemos-un-Plan-Informe-de-Consulta-COLOR-NNA-v2.4.pdf
 https://plan.jalisco.gob.mx/documentos-metodologicos/
 https://iieg.gob.mx/ns/</t>
         </is>
       </c>
-      <c r="X34" s="2" t="inlineStr">
+      <c r="X36" s="2" t="inlineStr">
         <is>
           <t>MX-jalisco-armemos-un-plan</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Presupuesto CRECES</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Presupuestos Participativos</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="J35" s="2" t="n">
+      <c r="J37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>gobierno local</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>Chatbot - Inespecífico</t>
         </is>
       </c>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>Presupuesto participativo del Ayuntamiento de Hermosillo en México. Utiliza un chatbot que a través de IA simplifica y facilita la votación de los presupuestos participativos</t>
         </is>
       </c>
-      <c r="T35" s="2" t="inlineStr">
+      <c r="T37" s="2" t="inlineStr">
         <is>
           <t>Ayundamiento de Hermosilla</t>
         </is>
       </c>
-      <c r="U35" s="2" t="inlineStr">
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="V35" s="5" t="n">
+      <c r="V37" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="W35" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>https://presupuestocreces.hermosillo.gob.mx/</t>
         </is>
       </c>
-      <c r="X35" s="2" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr">
         <is>
           <t>MX-presupuesto-creces</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr"/>
-      <c r="B36" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>Análisis; Traducción Política</t>
         </is>
       </c>
-      <c r="J36" s="2" t="n">
+      <c r="J38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>sociedad civil; gobierno nacional</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Sociedad Civil</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr">
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
         </is>
       </c>
-      <c r="S36" s="2" t="inlineStr">
+      <c r="S38" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea (www.mansaidea.com) es una plataforma digital basada en inteligencia artificial lanzada el 1 de abril de 2024 por la Fundación Panamá Participa (sociedad civil), liderada por Paulina Franceschi. La plataforma organiza y hace navegables más de 175.000 ideas y propuestas ciudadanas generadas durante el Pacto del Bicentenario 'Cerrando Brechas' (proceso participativo nacional convocado por el gobierno de Panamá / Concertación Nacional, presidente Cortizo, 2020-2021), agregando los consensos nacionales y regionales/provinciales por tema en un solo clic. La IA se aplica sobre el CONTENIDO de los aportes ciudadanos (organiza, agrega y sintetiza el corpus de propuestas) para convertirlo en una base de datos navegable. El uso de la IA es un tratamiento PUNTERAL (~2024) de un corpus histórico de un proceso participativo ya cerrado (el Pacto fue 2020-2021), orientado a elevar el nivel de la conversación electoral 2024 y a dotar a candidatos, medios y ciudadanía de una herramienta para alinear planes con las necesidades de la población y monitorear el mandato ciudadano. IMPORTANTE: el proceso participativo original (recolección de aportes) fue convocado por el gobierno; la capa de IA (Mansa Idea) la desarrolla la sociedad civil sobre ese corpus ya recolectado.</t>
         </is>
       </c>
-      <c r="T36" s="2" t="inlineStr">
+      <c r="T38" s="2" t="inlineStr">
         <is>
           <t>Fundación Panamá Participa (sociedad civil, Panamá), iniciativa liderada por Paulina Franceschi. El proceso participativo de origen (Pacto del Bicentenario 'Cerrando Brechas') fue convocado por el Gobierno de Panamá a través del mecanismo de Concertación Nacional para el Desarrollo (presidente Laurentino Cortizo), con apoyo del PNUD.</t>
         </is>
       </c>
-      <c r="U36" s="2" t="inlineStr">
+      <c r="U38" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="V36" s="5" t="n">
+      <c r="V38" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="W36" s="2" t="inlineStr">
+      <c r="W38" s="2" t="inlineStr">
         <is>
           <t>https://mansaidea.com/ (intentar archive.org / cache); buscar 'Mansa Idea metodología inteligencia artificial procesamiento propuestas' y entrevistas técnicas a Paulina Franceschi / Fundación Panamá Participa.
 https://mansaidea.com/ ; buscar 'Mansa Idea 2025' / 'Mansa Idea 2026' / 'Fundación Panamá Participa actividad reciente'.
 https://mansaidea.com/ ; buscar evidencia de actualizaciones periódicas del corpus o nuevas convocatorias.</t>
         </is>
       </c>
-      <c r="X36" s="2" t="inlineStr">
+      <c r="X38" s="2" t="inlineStr">
         <is>
           <t>PA-mansa-idea-pacto-del-bicentenario</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
-      <c r="B37" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="J37" s="2" t="n">
+      <c r="J39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>otra institución pública</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr">
+      <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>NLP - Tópicos; NLP - Sentiment</t>
         </is>
       </c>
-      <c r="R37" s="2" t="inlineStr">
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S37" s="2" t="inlineStr">
+      <c r="S39" s="2" t="inlineStr">
         <is>
           <t>Una consulta pública para recoger opiniones sobre el Proyecto Educativo Nacional 2036, utilizando encuestas en línea, talleres y mesas deliberativas.</t>
         </is>
       </c>
-      <c r="T37" s="2" t="inlineStr">
+      <c r="T39" s="2" t="inlineStr">
         <is>
           <t>Consejo Nacional de Educación del Perú</t>
         </is>
       </c>
-      <c r="U37" s="2" t="inlineStr">
+      <c r="U39" s="2" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="V37" s="4" t="n">
+      <c r="V39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W37" s="2" t="inlineStr">
+      <c r="W39" s="2" t="inlineStr">
         <is>
           <t>https://www.latinno.net/en/case/17232/
 https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional?utm_source=chatgpt.com
 https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080</t>
         </is>
       </c>
-      <c r="X37" s="2" t="inlineStr">
+      <c r="X39" s="2" t="inlineStr">
         <is>
           <t>PE-consulta-ciudadana-sobre-el-proyecto-nac</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
-      <c r="B38" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>➜ DUDA — revisar posible IA/participación</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>DUDA(lean NO)</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Plataforma</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>gobierno nacional</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>no-claro</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>NLP; Resumen automatico; Clasificacion/agrupacion de texto (capacidad de la plataforma sujeta a plan Premium; activacion NO confirmada en TT)</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>no-claro</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>EngageTT (engage.gov.tt) es la plataforma de participacion ciudadana del Ministry of Digital Transformation de Trinidad y Tobago (desde mayo 2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), lanzada en el simposio del NDTS el 12 de febrero de 2025 junto al BID (IDB). Se usa como canal de participacion en el proceso de planificacion nacional del National Digital Transformation Strategy (NDTS) 2024-2027, donde ciudadanos, empresas y partes interesadas reciben actualizaciones y aportan retroalimentacion via encuestas, sondeos (polls), un 'Open Forum' de ideas y el envio de propuestas. La instancia corre sobre el software Go Vocal (antes CitizenLab) -confirmado por la ruta interna 'projects/e-democracy-govocal-internal'-. Go Vocal incorpora un modulo de IA/NLP de 'Sensemaking' (analisis y resumen automatico de aportes), pero ese modulo NO viene activo por defecto: segun la documentacion de soporte de Go Vocal, el acceso a la funcion de AI Analysis/Sensemaking DEPENDE DEL PLAN contratado (Advanced Sensemaking con auto-insights esta en el plan Premium). Tras 2a pasada de investigacion (&gt;=14 busquedas/fetches) NO se halla evidencia alguna de que la instancia de Trinidad active ni use esas funciones de IA sobre el CONTENIDO de los aportes; toda la documentacion describe a EngageTT como recolector (surveys, polls, Open Forum, ideas), es decir plataforma usada como formulario sin analisis automatico confirmado. Existe ademas AskNDTS, un chatbot/PWA de IA conversacional para responder preguntas sobre el NDTS (rol de FAQ informativo, EXCLUIDO del criterio).</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Digital Transformation de Trinidad y Tobago (desde el 23-may-2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), en colaboracion con el Banco Interamericano de Desarrollo (BID/IDB). Plataforma de software: Go Vocal (antes CitizenLab), empresa belga.</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="V40" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
+https://www.govocal.com/plans
+https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>TT-engagett-plataforma-go-vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>UY</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>(sin revisar)</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>MEDIA (fuente primaria + OCDE 2025; fetch primario bloqueado por proxy, citas vía repo/WebSearch)</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="J38" s="2" t="n">
+      <c r="J41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>universidad</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>Sociedad Civil; Academia</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
+      <c r="P41" s="2" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr">
+      <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>Clustering; ML - Inespecífico</t>
         </is>
       </c>
-      <c r="R38" s="2" t="inlineStr">
+      <c r="R41" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S38" s="2" t="inlineStr">
+      <c r="S41" s="2" t="inlineStr">
         <is>
           <t>Referéndum nacional para derogar 135 artículos de la Ley de Urgente Consideración (LUC). Un equipo de la Universidad de la República corrió una conversación Pol.is en paralelo al referéndum del 27/03/2022 (documentado como caso 2021).</t>
         </is>
       </c>
-      <c r="T38" s="2" t="inlineStr">
+      <c r="T41" s="2" t="inlineStr">
         <is>
           <t>Equipo de 13 personas de la Universidad de la República (UdelaR) — ingenieros, comunicadores y científicos de datos; plataforma Pol.is (The Computational Democracy Project)</t>
         </is>
       </c>
-      <c r="U38" s="2" t="inlineStr">
+      <c r="U41" s="2" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="V38" s="5" t="n">
+      <c r="V41" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="W38" s="2" t="inlineStr">
+      <c r="W41" s="2" t="inlineStr">
         <is>
           <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/</t>
         </is>
       </c>
-      <c r="X38" s="2" t="inlineStr">
+      <c r="X41" s="2" t="inlineStr">
         <is>
           <t>UY-polis-referendum-luc</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X38"/>
+  <autoFilter ref="A1:X41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5224,415 +5574,416 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>A. Excluir (criterio corregido)</t>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Confirmar NO (ya fuera del conteo)</t>
+          <t>Confirmar SI</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Presupuesto CRECES</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Presupuesto participativo (Hermosillo); la IA (chatbot) facilita la votación (Implementación).</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>B. Rescatado → ENTRA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar SI</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>LXS 400 - Chile Delibera</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Mini-público del Senado; la IA modera y administra los turnos de palabra (Implementación/Planificación).</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://es.wikipedia.org/wiki/Lxs_400:_Chile_Delibera
+https://www.lxs400.cl/noticias/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>B. Rescatado → ENTRA</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar SI</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Consulta ciudadana; la IA analiza los aportes (Análisis).</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://participacion.digital.gob.cl/es-CL/folders/consultas-ciudadanas</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>B. Rescatado → ENTRA</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar SI</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RedPública + iVerify </t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Plataforma de propuestas de ley ciudadanas (participación legislativa).</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>B. Rescatado → ENTRA</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar SI</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>La voz de los nuevos votantes</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Consulta a nuevos votantes con NLP — proceso ejecutado por el equipo (confirmado).</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>B. Rescatado → ENTRA</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar SI</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Jornada de escucha / diálogo — proceso ejecutado por el equipo (confirmado).</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>B. Rescatado → ENTRA</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar SI</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Chatico</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Tiene módulos de participación (aportes al Plan de Desarrollo de Bogotá) — confirmado por el equipo.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://secretariageneral.gov.co/noticias/chatico-el-agente-virtual-de-servicio-la-ciudadania-supero-los-36-millones-de-conversaciones
+https://bogota.gov.co/mi-ciudad/gestion-publica/distrito-presenta-su-agente-virtual-chatico-que-guia-la-ciudadania</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>C. DUDA — revisar (posible IA)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Abrir URL y decidir SI/NO</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Revisar si hay/planea IA o módulo de participación</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>¿La IA de Go Vocal (Sensemaking) está ACTIVA o PLANEADA? Si está planeada, ENTRA.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
+https://www.govocal.com/plans
+https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>C. DUDA — revisar (posible IA)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Abrir URL y decidir SI/NO</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>DNP - Diálogos Regionales Vinculantes (PND 2022-2026)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Revisar si hay/planea IA o módulo de participación</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>¿Se usó NLP (p. ej. ConTexto del DNP) para sistematizar las 89.788 propuestas?</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.funcionpublica.gov.co/documents/d/guest/la_rendicion_de_cuentas_y_el_control_social_marco_dialogos_regionales_vinculantes_-drv-
+https://github.com/ucd-dnp/ConTexto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>C. DUDA — revisar (posible IA)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Abrir URL y decidir SI/NO</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>CiudadanIA</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>No es un proceso de participación (o sin IA verificada) → excluido</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Ventanillas de asistencia/servicio + recolección de datos: no es participación.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Revisar si hay/planea IA o módulo de participación</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>¿Tiene un módulo de participación (recoger aportes para decisiones), no solo atención/servicio?</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.genia.ai/paises-miembros
 https://presidencia.gob.do/seccion/inteligencia-artificial</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>A. Excluir (criterio corregido)</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Confirmar NO (ya fuera del conteo)</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>DNP - Diálogos Regionales Vinculantes (PND 2022-2026)</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>No es un proceso de participación (o sin IA verificada) → excluido</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Participación genuina PERO sin IA verificada: no cumple el criterio de IA.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.funcionpublica.gov.co/documents/d/guest/la_rendicion_de_cuentas_y_el_control_social_marco_dialogos_regionales_vinculantes_-drv-
-https://github.com/ucd-dnp/ConTexto</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>A. Excluir (criterio corregido)</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Confirmar NO (ya fuera del conteo)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>No es un proceso de participación (o sin IA verificada) → excluido</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Participación genuina PERO módulo de IA no activado: IA no confirmada en el proceso.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
-https://www.govocal.com/plans</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>B. Rescatado → ENTRA</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Confirmar SI</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Presupuesto CRECES</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Presupuesto participativo (Hermosillo); la IA (chatbot) facilita la votación (Implementación).</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>B. Rescatado → ENTRA</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Confirmar SI</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>LXS 400 - Chile Delibera</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Mini-público del Senado; la IA modera y administra los turnos de palabra (Implementación/Planificación).</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>https://es.wikipedia.org/wiki/Lxs_400:_Chile_Delibera
-https://www.lxs400.cl/noticias/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>B. Rescatado → ENTRA</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Confirmar SI</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Consulta ciudadana; la IA analiza los aportes (Análisis).</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>https://participacion.digital.gob.cl/es-CL/folders/consultas-ciudadanas</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>B. Rescatado → ENTRA</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Confirmar SI</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>HN</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RedPública + iVerify </t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma de propuestas de ley ciudadanas (participación legislativa).</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>C. DUDA (criterio corregido)</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Decidir SI o NO</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>C. DUDA — revisar (posible IA)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Abrir URL y decidir SI/NO</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>U-Report Costa Rica – chatbot juvenil</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>¿Es un proceso de participación ciudadana o un sondeo/evento? Decidir</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>¿Proceso de participación o sondeo? Decidir</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Plataforma de opinión juvenil (UNICEF): ¿consulta participativa o civic tech de sondeo?</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://costarica.ureport.in/
 https://www.unicef.org/costarica/comunicados-prensa/plataforma-mundial-u-report-llega-costa-rica</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>C. DUDA (criterio corregido)</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Decidir SI o NO</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>La voz de los nuevos votantes</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>¿Es un proceso de participación ciudadana o un sondeo/evento? Decidir</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Encuesta a nuevos votantes + NLP: ¿consulta participativa o sondeo puntual?</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>C. DUDA (criterio corregido)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Decidir SI o NO</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>¿Es un proceso de participación ciudadana o un sondeo/evento? Decidir</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Jornada de escucha (comunidad académica + stakeholders): ¿participación ciudadana o evento institucional?</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>D. Revisar ¿participación?</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>¿Mantener SI o pasar a NO?</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Chatico</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Parece civic tech/atención; confirmar si es realmente participación</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Atención automatizada (responde consultas sobre 400 temas): parece atención ciudadana, no participación.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>https://secretariageneral.gov.co/noticias/chatico-el-agente-virtual-de-servicio-la-ciudadania-supero-los-36-millones-de-conversaciones
-https://bogota.gov.co/mi-ciudad/gestion-publica/distrito-presenta-su-agente-virtual-chatico-que-guia-la-ciudadania</t>
         </is>
       </c>
     </row>
@@ -5979,7 +6330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6807,7 +7158,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>DNP - Diálogos Regionales Vinculantes (PND 2022-2026)</t>
+          <t>Descongestión de solicitudes diarias del programa Ingreso Solidario</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -6817,12 +7168,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Participación genuina PERO sin IA verificada: no cumple el criterio de IA.</t>
+          <t>Atención ciudadana (triage de 10.000 correos/día): servicio, no participación.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/ucd-dnp</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/inteligencia-artificial-la-herramienta-que-descongestiono-10-000-solicitudes-diarias-de-ingreso-solidario/</t>
         </is>
       </c>
     </row>
@@ -6834,22 +7185,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Descongestión de solicitudes diarias del programa Ingreso Solidario</t>
+          <t>IA para participación en el POT de Bogotá (Control Visible / Auditoría General)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Dudoso</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana (triage de 10.000 correos/día): servicio, no participación.</t>
+          <t>NO ENTRA. El criterio de elegibilidad exige que dentro de un proceso participativo se DESPLIEGUE IA real (institucional) sobre el CONTENIDO de los aportes ciudadanos. El caso documentado es un ARTÍCULO ACADÉMICO (Fundación Universitaria del Área Andina, Maestría en Innovación; publicado en la revist</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/inteligencia-artificial-la-herramienta-que-descongestiono-10-000-solicitudes-diarias-de-ingreso-solidario/</t>
+          <t>https://controlvisible.auditoria.gov.co/index.php/rcf/article/view/63</t>
         </is>
       </c>
     </row>
@@ -6861,22 +7212,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>IA para participación en el POT de Bogotá (Control Visible / Auditoría General)</t>
+          <t>ISIDataInsights / Reto de Ciudad 'Datos con Historia' (SDP Bogotá)</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Dudoso</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>NO ENTRA. El criterio de elegibilidad exige que dentro de un proceso participativo se DESPLIEGUE IA real (institucional) sobre el CONTENIDO de los aportes ciudadanos. El caso documentado es un ARTÍCULO ACADÉMICO (Fundación Universitaria del Área Andina, Maestría en Innovación; publicado en la revist</t>
+          <t>DUDA con inclinación NO (REAFIRMADA en 3ª pasada con búsqueda amplia, jul-2026). Por un lado, la herramienta ISIDataInsights está diseñada para operar sobre el CONTENIDO de información cualitativa de planeación, incluyendo explícitamente 'los aportes ciudadanos' (procesar, validar consistencia, apli</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://controlvisible.auditoria.gov.co/index.php/rcf/article/view/63</t>
+          <t>https://www.sdp.gov.co/noticias/bogota-cuenta-herramienta-innovadora-abordar-los-problemas-urbanos-aporte-de-la-ciudadania</t>
         </is>
       </c>
     </row>
@@ -6888,22 +7239,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ISIDataInsights / Reto de Ciudad 'Datos con Historia' (SDP Bogotá)</t>
+          <t>Mini-Public del diálogo social de la Procuraduría</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Excluido (revisar)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>DUDA con inclinación NO (REAFIRMADA en 3ª pasada con búsqueda amplia, jul-2026). Por un lado, la herramienta ISIDataInsights está diseñada para operar sobre el CONTENIDO de información cualitativa de planeación, incluyendo explícitamente 'los aportes ciudadanos' (procesar, validar consistencia, apli</t>
+          <t xml:space="preserve">Se MANTIENE EXCLUIDO (entra=NO), confirmando el motivo de exclusión de 2025 ('No se encontró información sobre el uso de la IA en la implementación de los Mini Publics'). El proceso es ELEGIBLE por su naturaleza (mini-público / diálogo social deliberativo convocado por la Procuraduría General de la </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.sdp.gov.co/noticias/bogota-cuenta-herramienta-innovadora-abordar-los-problemas-urbanos-aporte-de-la-ciudadania</t>
+          <t>https://ideemos.org/mini-public-del-dialogo-social-de-la-procuraduria/</t>
         </is>
       </c>
     </row>
@@ -6915,7 +7266,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Mini-Public del diálogo social de la Procuraduría</t>
+          <t>Pa' que veás (Cali)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -6925,12 +7276,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se MANTIENE EXCLUIDO (entra=NO), confirmando el motivo de exclusión de 2025 ('No se encontró información sobre el uso de la IA en la implementación de los Mini Publics'). El proceso es ELEGIBLE por su naturaleza (mini-público / diálogo social deliberativo convocado por la Procuraduría General de la </t>
+          <t xml:space="preserve">Se revisa por su analogia con dIAra (bots que recopilan quejas ciudadanas y predicen riesgos en obras). Sin embargo, NO se encontro evidencia de uso de inteligencia artificial sobre el CONTENIDO de los aportes/quejas ciudadanas dentro de un proceso participativo. 'Pa' que veas' es, en su nucleo, un </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://ideemos.org/mini-public-del-dialogo-social-de-la-procuraduria/</t>
+          <t>https://www.iadb.org/en/news/city-cali-launches-platform-monitoring-public-investment-idb-support</t>
         </is>
       </c>
     </row>
@@ -6942,22 +7293,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Pa' que veás (Cali)</t>
+          <t>Plataforma Urna de Cristal</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Excluido (revisar)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se revisa por su analogia con dIAra (bots que recopilan quejas ciudadanas y predicen riesgos en obras). Sin embargo, NO se encontro evidencia de uso de inteligencia artificial sobre el CONTENIDO de los aportes/quejas ciudadanas dentro de un proceso participativo. 'Pa' que veas' es, en su nucleo, un </t>
+          <t>No evidencia de uso de IA</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.iadb.org/en/news/city-cali-launches-platform-monitoring-public-investment-idb-support</t>
+          <t>https://projects.itforchange.net/mavc/wp-content/uploads/2017/09/Voice-or-Chatter_Case-Study_Colombia_August-2017.pdf?utm_source=chatgpt.com</t>
         </is>
       </c>
     </row>
@@ -6969,7 +7320,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Plataforma Urna de Cristal</t>
+          <t>SISBÉN IV</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -6979,12 +7330,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://projects.itforchange.net/mavc/wp-content/uploads/2017/09/Voice-or-Chatter_Case-Study_Colombia_August-2017.pdf?utm_source=chatgpt.com</t>
+          <t>https://fairlac.iadb.org/sisben</t>
         </is>
       </c>
     </row>
@@ -6996,103 +7347,103 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SISBÉN IV</t>
+          <t>iLabs - Laboratorios de Inteligencia Colectiva (Ideemos)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (revisar)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>MANTENER EXCLUIDO. La regla de reingreso exige evidencia de IA aplicada al CONTENIDO de los aportes ciudadanos dentro de un proceso participativo. La fuente primaria (página iLabs de Ideemos y su PDF) describe 'Inteligencia Artificial' y 'Machine Learning' SOLO como parte de un listado de técnicas c</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/sisben</t>
+          <t>https://ideemos.org/ilabs-laboratorios-de-inteligencia-colectiva/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>iLabs - Laboratorios de Inteligencia Colectiva (Ideemos)</t>
+          <t>dIAra</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Excluido (revisar)</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>MANTENER EXCLUIDO. La regla de reingreso exige evidencia de IA aplicada al CONTENIDO de los aportes ciudadanos dentro de un proceso participativo. La fuente primaria (página iLabs de Ideemos y su PDF) describe 'Inteligencia Artificial' y 'Machine Learning' SOLO como parte de un listado de técnicas c</t>
+          <t>Civic tech de fiscalización de obras (control social vía app): no es un proceso participativo.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://ideemos.org/ilabs-laboratorios-de-inteligencia-colectiva/</t>
+          <t>https://www.opengovpartnership.org/the-open-gov-challenge/costa-rica-artificial-intelligence-alerts-citizen-control-public-infrastructure/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CU</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>dIAra</t>
+          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Dudoso</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Civic tech de fiscalización de obras (control social vía app): no es un proceso participativo.</t>
+          <t>Dentro de un proceso participativo formal y de gran escala (consulta popular legislativa nacional sobre el Código de las Familias, feb-abr 2022, ~6,5 millones de participantes y cientos de miles de propuestas) se usó IA sobre el CONTENIDO de los aportes ciudadanos: el sistema GEMA-CEN (basado en GEM</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.opengovpartnership.org/the-open-gov-challenge/costa-rica-artificial-intelligence-alerts-citizen-control-public-infrastructure/</t>
+          <t>http://www.datys.cu/spa/site/product/15</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>CU</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Dudoso</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Dentro de un proceso participativo formal y de gran escala (consulta popular legislativa nacional sobre el Código de las Familias, feb-abr 2022, ~6,5 millones de participantes y cientos de miles de propuestas) se usó IA sobre el CONTENIDO de los aportes ciudadanos: el sistema GEMA-CEN (basado en GEM</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>http://www.datys.cu/spa/site/product/15</t>
+          <t>https://www.undp.org/es/latin-america/comunicados-de-prensa/sara-la-nueva-herramienta-de-inteligencia-artificial-para-combatir-la-violencia-de-genero-en-centroamerica-0</t>
         </is>
       </c>
     </row>
@@ -7104,61 +7455,61 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CiudadanIA</t>
+          <t>TAÍNA: Gobierno Inteligente</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Ventanillas de asistencia/servicio + recolección de datos: no es participación.</t>
+          <t>Atención ciudadana</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.genia.ai/paises-miembros</t>
+          <t>https://www.diariolibre.com/actualidad/nacional/2023/10/11/gobierno-presenta-estrategia-de-inteligencia-artificial/2489157</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Plataforma de modelos generativos de IA de SEGEPLAN + Red Ciudadana (Guatemala)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Descubrimiento</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>El criterio ELEGIBLE exige que la IA generativa se use para SISTEMATIZAR/CLASIFICAR/RESUMIR el CONTENIDO de los aportes de los diagnosticos participativos (Consejos de Desarrollo COCODES/COMUDES) en los Planes de Desarrollo Municipal (PDM). Toda la evidencia primaria y secundaria (nota SEGEPLAN ?p=1</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/latin-america/comunicados-de-prensa/sara-la-nueva-herramienta-de-inteligencia-artificial-para-combatir-la-violencia-de-genero-en-centroamerica-0</t>
+          <t>https://portal.segeplan.gob.gt/segeplan/?p=14176</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>LATAM</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>TAÍNA: Gobierno Inteligente</t>
+          <t>ANTAI Smart CID (Autoridad Nacional de Transparencia y Acceso a la Información + OS City)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -7168,39 +7519,39 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.diariolibre.com/actualidad/nacional/2023/10/11/gobierno-presenta-estrategia-de-inteligencia-artificial/2489157</t>
+          <t>https://www.caf.com/es/actualidad/noticias/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LATAM</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Plataforma de modelos generativos de IA de SEGEPLAN + Red Ciudadana (Guatemala)</t>
+          <t>Botivist</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>El criterio ELEGIBLE exige que la IA generativa se use para SISTEMATIZAR/CLASIFICAR/RESUMIR el CONTENIDO de los aportes de los diagnosticos participativos (Consejos de Desarrollo COCODES/COMUDES) en los Planes de Desarrollo Municipal (PDM). Toda la evidencia primaria y secundaria (nota SEGEPLAN ?p=1</t>
+          <t>No tiene foco en un país específico</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://portal.segeplan.gob.gt/segeplan/?p=14176</t>
+          <t>https://www.microsoft.com/en-us/research/publication/botivist-calling-volunteers-to-action-using-online-bots/</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7563,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ANTAI Smart CID (Autoridad Nacional de Transparencia y Acceso a la Información + OS City)</t>
+          <t>Chatbot DCI (Denuncia Ciudadana Idónea)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -7222,12 +7573,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>No evidencia de uso de IA</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.caf.com/es/actualidad/noticias/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
+          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7590,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Botivist</t>
+          <t>Citibeats: Covid-19 (“Percepciones ciudadanas COVID-19”)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -7249,12 +7600,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>No tiene foco en un país específico</t>
+          <t>Análisis de redes sociales, no es participación</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/research/publication/botivist-calling-volunteers-to-action-using-online-bots/</t>
+          <t>https://forbescentroamerica.com/2021/04/28/civiclytics-el-big-data-apoya-la-recuperacion-economica</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7617,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Chatbot DCI (Denuncia Ciudadana Idónea)</t>
+          <t>Ushahidi "AI for Good"</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -7276,24 +7627,24 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA</t>
+          <t>No se evidencia el uso de IA en los proyectos de participación listados para Latam</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci</t>
+          <t>https://www.ushahidi.com/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Citibeats: Covid-19 (“Percepciones ciudadanas COVID-19”)</t>
+          <t>AMIMgo</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -7303,24 +7654,24 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Análisis de redes sociales, no es participación</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://forbescentroamerica.com/2021/04/28/civiclytics-el-big-data-apoya-la-recuperacion-economica</t>
+          <t>https://amim.mx/noticias/detalle/estrena-amim-chatbot-para-la-atencion-ciudadana</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Ushahidi "AI for Good"</t>
+          <t>ATIC</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -7330,12 +7681,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>No se evidencia el uso de IA en los proyectos de participación listados para Latam</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.ushahidi.com/</t>
+          <t>https://oem.com.mx/la-prensa/metropoli/info-cdmx-implementa-atic-una-herramienta-con-ia-que-facilita-el-acceso-a-la-informacion-13081722</t>
         </is>
       </c>
     </row>
@@ -7347,7 +7698,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>AMIMgo</t>
+          <t>ChatBot “Claudia"</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -7357,12 +7708,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>No es participación</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://amim.mx/noticias/detalle/estrena-amim-chatbot-para-la-atencion-ciudadana</t>
+          <t>https://mexicocomovamos.mx/animal-politico/2024/08/chatbot-claudia-una-herramienta-de-participacion-ciudadana/</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7725,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>ATIC</t>
+          <t>Chatbot "Inés"</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -7384,12 +7735,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No es participación, es informativo</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://oem.com.mx/la-prensa/metropoli/info-cdmx-implementa-atic-una-herramienta-con-ia-que-facilita-el-acceso-a-la-informacion-13081722</t>
+          <t>https://centralelectoral.ine.mx/2024/04/17/nueva-version-del-chatbot-del-ine-en-whatsapp-permitira-verificar-informacion-sobre-elecciones-2024/</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7752,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>ChatBot “Claudia"</t>
+          <t>Chatbot Sam Petrino</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -7411,12 +7762,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>No es participación</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://mexicocomovamos.mx/animal-politico/2024/08/chatbot-claudia-una-herramienta-de-participacion-ciudadana/</t>
+          <t>https://www.civica.digital/historias/chatbot-sam-petrino</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7779,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Chatbot "Inés"</t>
+          <t>Chatbot Victoria</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -7438,12 +7789,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>No es participación, es informativo</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://centralelectoral.ine.mx/2024/04/17/nueva-version-del-chatbot-del-ine-en-whatsapp-permitira-verificar-informacion-sobre-elecciones-2024/</t>
+          <t>Informe de Gobierno</t>
         </is>
       </c>
     </row>
@@ -7455,7 +7806,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Sam Petrino</t>
+          <t>INAOE (Conacyt) – Laboratorio de Tecnologías del Lenguaje</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -7465,12 +7816,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.civica.digital/historias/chatbot-sam-petrino</t>
+          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=para%20identificar%20posibles%20trastornos,de%20las%20dificultades%20de%20%C3%ADndole</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7833,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Victoria</t>
+          <t>Movimex</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -7492,12 +7843,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Informe de Gobierno</t>
+          <t>https://animalpolitico.com/estados/chatbot-movimex-tramites-denuncias-edomex</t>
         </is>
       </c>
     </row>
@@ -7509,7 +7860,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>INAOE (Conacyt) – Laboratorio de Tecnologías del Lenguaje</t>
+          <t>Sistema *0311 Locatel</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -7519,12 +7870,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Atención ciudadana</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=para%20identificar%20posibles%20trastornos,de%20las%20dificultades%20de%20%C3%ADndole</t>
+          <t>https://research.latinxinai.org/papers/naacl/2022/pdf/paper_01.pdf</t>
         </is>
       </c>
     </row>
@@ -7536,22 +7887,22 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Movimex</t>
+          <t>Sufragio seguro</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Baseline 2025</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>EXCLUSIÓN FIRME (recodificación 2026): Exclusión FIRME (recodificación 2026): integridad/proceso electoral, no contenido</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://animalpolitico.com/estados/chatbot-movimex-tramites-denuncias-edomex</t>
+          <t>https://osf.io/cu6w3</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7914,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Sistema *0311 Locatel</t>
+          <t>Violetta</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -7573,51 +7924,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://research.latinxinai.org/papers/naacl/2022/pdf/paper_01.pdf</t>
+          <t>https://holasoyvioletta.com/acerca-de/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Sufragio seguro</t>
+          <t>Dr. ROSA y Dr. NICO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Baseline 2025</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>EXCLUSIÓN FIRME (recodificación 2026): Exclusión FIRME (recodificación 2026): integridad/proceso electoral, no contenido</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://osf.io/cu6w3</t>
+          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=virtual%2Fchatbot%20que%20funciona%20por%20WhatsApp,que%20realice%20una%20observaci%C3%B3n%20f%C3%ADsica</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Violetta</t>
+          <t>JNE WhatsApp Chatbot</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -7627,132 +7978,132 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://holasoyvioletta.com/acerca-de/</t>
+          <t>https://portal.jne.gob.pe/Portal/Pagina/Nota/12783</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Dr. ROSA y Dr. NICO</t>
+          <t>Sistema de cómputo con IA para las Elecciones Generales 2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Conteo electoral (OCR de actas): votación política, no participación.</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=virtual%2Fchatbot%20que%20funciona%20por%20WhatsApp,que%20realice%20una%20observaci%C3%B3n%20f%C3%ADsica</t>
+          <t>https://cheleloyborolas.com/index.php?Itemid=103&amp;catid=10&amp;id=72545%3Ajefe-de-la-onpe-presenta-avances-en-la-organizacion-de-las-elecciones-generales-2026&amp;option=com_content&amp;view=article</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PY</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>JNE WhatsApp Chatbot</t>
+          <t>Consultas ciudadanas sobre IA en Paraguay - PNUD Accelerator Lab (AccLab) + Columbia SIPA + MITIC / insumo del diagnóstico AILA (Atlas de IA)</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Descubrimiento</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>El criterio ELEGIBLE exige que dentro de un proceso participativo convocado se use IA (NLP/ML/clustering/sentimiento) SOBRE EL CONTENIDO de los aportes. Aquí ocurre lo contrario: (1) la IA es el TEMA de la consulta (se pregunta a la ciudadania por su percepcion de la IA), y (2) el ANÁLISIS de los ap</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://portal.jne.gob.pe/Portal/Pagina/Nota/12783</t>
+          <t>https://www.undp.org/es/paraguay/blog/consultas-ciudadanas-sobre-ia-en-paraguay-visiones-diversas-entre-el-campo-y-la-ciudad</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PY</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Sistema de cómputo con IA para las Elecciones Generales 2026</t>
+          <t>ParaEmpleo</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Conteo electoral (OCR de actas): votación política, no participación.</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://cheleloyborolas.com/index.php?Itemid=103&amp;catid=10&amp;id=72545%3Ajefe-de-la-onpe-presenta-avances-en-la-organizacion-de-las-elecciones-generales-2026&amp;option=com_content&amp;view=article</t>
+          <t>https://fairlac.iadb.org/paraempleo</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>PY</t>
+          <t>UY</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Consultas ciudadanas sobre IA en Paraguay - PNUD Accelerator Lab (AccLab) + Columbia SIPA + MITIC / insumo del diagnóstico AILA (Atlas de IA)</t>
+          <t>Chatbot (Asistente virtual entrenado con IA)</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>El criterio ELEGIBLE exige que dentro de un proceso participativo convocado se use IA (NLP/ML/clustering/sentimiento) SOBRE EL CONTENIDO de los aportes. Aquí ocurre lo contrario: (1) la IA es el TEMA de la consulta (se pregunta a la ciudadania por su percepcion de la IA), y (2) el ANÁLISIS de los ap</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/paraguay/blog/consultas-ciudadanas-sobre-ia-en-paraguay-visiones-diversas-entre-el-campo-y-la-ciudad</t>
+          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=El%20chatbot%20virtual%20creado%20por,desarrollo%20de%20soluciones%20de%20IA</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>PY</t>
+          <t>UY</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>ParaEmpleo</t>
+          <t>Consulta Pública de la Estrategia Nacional de Inteligencia Artificial (IA) de Uruguay 2024–2030,</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -7762,152 +8113,71 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>No evidencia de uso de IA</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/paraempleo</t>
+          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030?utm_source=chatgpt.com</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>UY</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
+          <t>Consulta Pública y Participación Multiactores: "Niñas, niños, adolescentes, entornos digitales e inteligencia artificial" (Uruguay, 2026)</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Descubrimiento</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Participación genuina PERO módulo de IA no activado: IA no confirmada en el proceso.</t>
+          <t>NO (lean firme). (1) TEMPORAL: la consulta está ABIERTA hasta el 10/09/2026 y la fase de sistematización/análisis/validación (Fase 3) recién ocurre entre el 10/09 y el 10/10/2026, con informe final el 30/11/2026. A la fecha de evaluación (2026-07-01) la fase de análisis NO se ha ejecutado, por lo qu</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://support.govocal.com/en/articles/8316692-ai-analysis</t>
+          <t>https://www.gub.uy/ministerio-educacion-cultura/comunicacion/noticias/lanzamiento-consulta-publica-sobre-inteligencia-artificial-entornos-digitales</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>UY</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Chatbot (Asistente virtual entrenado con IA)</t>
+          <t>Plan de la Patria 7 Transformaciones (7T) - IA y Big Data en la sistematización de propuestas de la Consulta Popular</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Dudoso</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>NO (resuelto en 2ª pasada, antes DUDA). Hay un proceso participativo claro (consulta/debate nacional para construir el Plan de la Patria 7T, con +63.000 asambleas, 3,4 M de participantes y 34.491 propuestas) cuyo CONTENIDO sí fue recolectado, cargado, sistematizado y agrupado. Pero la 2ª pasada CONF</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=El%20chatbot%20virtual%20creado%20por,desarrollo%20de%20soluciones%20de%20IA</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>UY</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Consulta Pública de la Estrategia Nacional de Inteligencia Artificial (IA) de Uruguay 2024–2030,</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Excluido 2025</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>No evidencia de uso de IA</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030?utm_source=chatgpt.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>UY</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Consulta Pública y Participación Multiactores: "Niñas, niños, adolescentes, entornos digitales e inteligencia artificial" (Uruguay, 2026)</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Descubrimiento</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>NO (lean firme). (1) TEMPORAL: la consulta está ABIERTA hasta el 10/09/2026 y la fase de sistematización/análisis/validación (Fase 3) recién ocurre entre el 10/09 y el 10/10/2026, con informe final el 30/11/2026. A la fecha de evaluación (2026-07-01) la fase de análisis NO se ha ejecutado, por lo qu</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gub.uy/ministerio-educacion-cultura/comunicacion/noticias/lanzamiento-consulta-publica-sobre-inteligencia-artificial-entornos-digitales</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Plan de la Patria 7 Transformaciones (7T) - IA y Big Data en la sistematización de propuestas de la Consulta Popular</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Dudoso</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>NO (resuelto en 2ª pasada, antes DUDA). Hay un proceso participativo claro (consulta/debate nacional para construir el Plan de la Patria 7T, con +63.000 asambleas, 3,4 M de participantes y 34.491 propuestas) cuyo CONTENIDO sí fue recolectado, cargado, sistematizado y agrupado. Pero la 2ª pasada CONF</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
           <t>http://www.correodelorinoco.gob.ve/venezuela-impulsa-el-debate-sobre-inteligencia-artificial-bajo-principios-de-soberania-y-etica/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E71"/>
+  <autoFilter ref="A1:E68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7918,7 +8188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9498,7 +9768,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ECHO – HáblameD Medellín</t>
+          <t>DNP - Diálogos Regionales Vinculantes (PND 2022-2026)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -9508,47 +9778,54 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+          <t>Documentos oficiales del Departamento Nacional de Planeación (DNP - Departamento Nacional de Planeación) de Colombia sobre los Diálogos Regionales Vinculantes para el Plan Nacional de Desarrollo 2022-2026.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Governanza Colaborativa</t>
+          <t>En los 51 Diálogos Regionales Vinculantes, los colombianos expresaron sus necesidades y propuestas en 2.115 mesas de diálogo entre transformacionales y poblacionales, y se entregaron más de 89.000 propuestas que fueron claves para la definición de los pilares y la construcción del Plan Nacional de Desarrollo 2022-2026.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Implementación, Análisis</t>
+          <t>El resultado de esta categorización lo define la lectura de las propuestas y su recurrencia en cada DRV para el análisis cualitativo correspondiente, que determinó, por frecuencia, los cuatro aspectos en los que los participantes enfocan el desarrollo de su territorio. En el segundo capítulo se organizó la información correspondiente al análisis cuantitativo que desarrolló la Unidad de Científicos de Datos del DNP.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>reconfirmado web (institucional): Reconfirmado: la IA del UNFPA clasifica por ODS las conversaciones ciudadanas captadas en campo (5.000+ personas, 16 comunas).</t>
+          <t>Results were officially published on February 6, 2023. The exercise lasted three months [...] The dialogues officially began in mid-September 2022 in Turbaco (Bolívar).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
+          <t>More than 250,000 Colombians participated in 51 Regional Binding Dialogues [...] 89,788 proposals were collected that inspired the construction of the five major transformations of the National Development Plan 2022-2026.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+          <t>The exercise lasted three months with dialogue and listening sessions convened by President Petro [...] The National Planning Department (DNP) presented official results of 51 Regional Binding Dialogues.</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+          <t>Crítica Dejusticia (2ª pasada): 'During the dialogues, there were no officials with computers systematizing information or recording the multiple proposals from participants. Instead, proposals were kept through voice notes on the cellphones of the officials who accompanied the encounters.' / CCONG-Dejusticia: 'the process with which all consolidated demands were systematized was never clearly identified.'</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+          <t>Se analizaron las propuestas y fueron agrupadas en categorías de intervención territorial (17-19 / 18 categorías) articuladas con las cinco transformaciones del PND. El resultado lo define 'la lectura de las propuestas y su recurrencia... que determinó, por frecuencia' los aspectos prioritarios. Presentación mediante nubes de palabras y gráficos de barras (conteo de temas por sector) y un 'visor'. GitHub ucd-dnp (7 repos): única librería NLP/minería de texto es 'ConTexto' ('Librería en Python para minería de texto y NLP'), pero NINGÚN repositorio ni fuente la vincula al procesamiento de las propuestas de los DRV.</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+          <t>https://github.com/ucd-dnp
+https://colaboracion.dnp.gov.co/CDT/PublishingImages/dialogos_regionales/Analisis-cualitativos/DNP_DRV15Colombianos-en-el-Exterior.pdf
+https://www.dejusticia.org/column/la-demagogia-de-los-dialogos-vinculantes/
+https://www.funcionpublica.gov.co/documents/d/guest/la_rendicion_de_cuentas_y_el_control_social_marco_dialogos_regionales_vinculantes_-drv-
+https://sispt.dnp.gov.co/drv/default-drv
+https://bdigital.uexternado.edu.co/entities/publication/6ff4f32f-4e7a-465d-af92-d1c4f67ae153
+https://ideaspaz.org/publicaciones/investigaciones-analisis/2023-03/dialogo-en-el-gobierno-de-gustavo-petro-que-nos-dejan-los-dialogos-regionales-vinculantes-en-la-planeacion-del-desarrollo
+https://www.dnp.gov.co/Prensa_/Noticias/Paginas/dnp-publica-resultados-de-los-dialogos-regionales-vinculantes.aspx</t>
         </is>
       </c>
     </row>
@@ -9560,242 +9837,367 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
+          <t>ECHO – HáblameD Medellín</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Governanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Implementación, Análisis</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>reconfirmado web (institucional): Reconfirmado: la IA del UNFPA clasifica por ODS las conversaciones ciudadanas captadas en campo (5.000+ personas, 16 comunas).</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>DUDA(lean SI)</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>la herramienta de un resguardo indígena (Zenú, Bajo Sinú, Colombia) para llegar al Congreso (La Silla Vacía)</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>a platform for young people in the Zenú community to decide, through digital voting, how they wanted to allocate local budgets</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>The AI summarizes proposals, organizes consensus, and facilitates collective decision-making</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>More than 10,000 users participate in the chatbot at gaitanaia.org, whose discussions feed the community's positions and proposals</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Gaitana IA is a tool created by Carlos Redondo Rincón ... a platform for young people in the Zenú community</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Gaitana is built on the DeepSeek large language model, adapted to the Zenú worldview ... summarizes proposals, organizes consensus</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>artificial intelligence organizes opinions, processes trends and builds consensuses that, if approved, would become legislative initiatives (KienyKe)</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/
 https://www.kienyke.com/</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Tenemos que hablar de Colombia</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Cerrado</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>https://tenemosquehablarcolombia.co/
 https://tenemosquehablarcolombia.co/resultados/</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>U-Report Costa Rica – chatbot juvenil</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Participación Digital</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado 2024-2025: consulta juvenil de UNICEF con 8.404 participantes; resultados analizados para incidir en política pública.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Plataforma</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Unicef</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>La inteligencia artificial de U-Report analiza miles de opiniones enviadas por texto para transformarlas en datos útiles. Utilizando Procesamiento de Lenguaje Natural (PLN), la IA lee y clasifica automáticamente los mensajes de los jóvenes para identificar los temas, tendencias y sentimientos más importantes, convirtiendo sus voces en evidencia clara para la toma de decisiones.</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>La inteligencia artificial de U-Report analiza miles de opiniones enviadas por texto para transformarlas en datos útiles. Utilizando Procesamiento de Lenguaje Natural (PLN), la IA lee y clasifica automáticamente los mensajes de los jóvenes para identificar los temas, tendencias y sentimientos más importantes, convirtiendo sus voces en evidencia clara para la toma de decisiones.</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>https://costarica.ureport.in/
 https://www.unicef.org/costarica/comunicados-prensa/plataforma-mundial-u-report-llega-costa-rica</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>CiudadanIA</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>SI*</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Governanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>reconfirmado web (institucional): Reverificación: actores activos (OGTIC, GENIA, MINPRE) en agenda de IA, sin evidencia nueva específica de la plataforma 2025-2026. Revisar en Fase 2.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Plataforma</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>GENIA Latinoamérica, en colaboración con la Universidad del Caribe (UNICARIBE), el Ministerio de la Presidencia (MINPRE) y la Oficina Gubernamental de Tecnologías de la Información y Comunicación (OGTIC)</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recopilación y análisis de datos ciudadanos para entrenar algoritmos que mejoren la prestación de servicios públicos, ofreciendo recomendaciones personalizadas y fomentando un gobierno proactivo. </t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recopilación y análisis de datos ciudadanos para entrenar algoritmos que mejoren la prestación de servicios públicos, ofreciendo recomendaciones personalizadas y fomentando un gobierno proactivo. </t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.genia.ai/paises-miembros
+https://presidencia.gob.do/seccion/inteligencia-artificial</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>EC</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PAGA IA </t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado: integrada al Tercer Plan de Acción de Estado Abierto 2025-2027; analiza las propuestas ciudadanas y sugiere actividades.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Plataforma</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto
 </t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto
 </t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>https://www.gobiernoabierto.ec/boletin-014-2023/
 https://ia.gobiernoabierto.ec/
@@ -9803,63 +10205,63 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Guatemala Joven Conversa </t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado: diálogos digitales con IA (DPPA ONU + Fundación Esquipulas); 300+ jóvenes; la IA permite intercambios anónimos y votación de aportes para identifi</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
 https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/?utm_source=chatgpt.com
@@ -9867,125 +10269,125 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>HN</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RedPública + iVerify </t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reverificación: plataforma de propuestas ciudadanas con módulo de análisis de tendencias; evidencia de IA central débil, revisar en Fase 2.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Guanajuato hará historia con el primer Programa de Gobierno realizado con IA</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Para integrar la participación ciudadana en este Programa de Gobierno, se realizaron cuatro talleres cubriendo las regiones noreste, norte, centro y sur, con representación de los 46 municipios de Guanajuato.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>El Programa de Gobierno de Guanajuato 2024-2030 es la guía que orienta las acciones del Gobierno de la Gente para lograr un Guanajuato sostenible, equitativo y transparente.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Su diseño incorporó el uso de inteligencia artificial para integrar más de 26 mil voces de distintas regiones y sectores</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>El Programa de Gobierno 2024-2030 hizo historia al ser el primero en realizarse con ayuda de la Inteligencia Artificial (IA), según anunció la Gobernadora Libia Dennise García Muñoz Ledo en el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG).</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía.</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>https://guanajuatointeligente.com/como-hicimos-el-programa/
 https://guanajuatointeligente.com/
@@ -9998,55 +10400,55 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Jalisco - Consulta ¡Armemos un Plan! (Plan Estatal de Desarrollo y Gobernanza 2024-2030)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>DUDA(lean NO)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>'Armemos un Plan' se llevó a cabo de manera abierta e incluyente del 20 de febrero al 17 de abril por el Gobierno de Jalisco, a través de la Secretaría de Planeación y Participación Ciudadana; la consulta digital recibió 15,899 propuestas ciudadanas.</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Jalisco concluyó la primera etapa de la consulta ciudadana 'Armemos un Plan' con una cifra inédita de 675,484 participaciones, base para desarrollar el Plan Estatal de Desarrollo y Gobernanza 2024-2030.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Se realizaron 12 foros regionales y la instalación de un Consejo de Planeación Participativa en cada región de Jalisco; se llevaron a cabo 168 mesas regionales, 47 sectoriales y 9 grandes foros temáticos... donde se identificaron y discutieron 1,349 problemáticas planteadas por la ciudadanía. (Metodología participativa/estadística; sin componente de IA.)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>Gobierno de Jalisco, a través de la Secretaría de Planeación y Participación Ciudadana (coordinación de Cynthia Cantero Pacheco).</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Las propuestas se construyeron a partir de las opiniones y expresiones de la ciudadanía durante la consulta, agrupando ideas similares y redactándolas de forma clara y ordenada, respetando siempre la intención original de quienes participaron. (Descripción metodológica oficial de armemosunplan.mx/propuestas-ciudadanas, recuperada vía WebSearch que indexa la página; no menciona IA/NLP/algoritmos: describe agrupación editorial manual.)</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>GAP: ninguna fuente atribuye a IA/NLP/minería de texto/clustering el análisis o la agrupación de las 15,899 propuestas; la única descripción del método es 'agrupando ideas similares' de forma manual/editorial.</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>https://armemosunplan.mx/propuestas-ciudadanas/
 https://armemosunplan.mx/wp-content/uploads/2025/10/Armemos-un-Plan-Informe-de-Consulta-COLOR-NNA-v2.4.pdf
@@ -10059,121 +10461,121 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Presupuesto CRECES</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Presupuestos Participativos</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Activo</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>Ayundamiento de Hermosilla</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>https://presupuestocreces.hermosillo.gob.mx/</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>La Fundación Panamá Participa lanzó Mansa Idea (www.mansaidea.com), una plataforma basada en inteligencia artificial que recoge miles de propuestas ciudadanas... iniciativa de alcance nacional que se nutre de ideas y propuestas que miles de panameños hicieron durante el desarrollo del Pacto del Bicentenario. (Panamá; fuentes panama24horas.com.pa y laestrella.com.pa)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea, resultado del Pacto del Bicentenario, ofrece acceso fácil y transparente a más de 175 mil ideas y propuestas generadas por ciudadanos de todo el país. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales. (la IA agrega/organiza/sintetiza el contenido de las propuestas por tema y territorio = Análisis + Traducción Política; el método técnico exacto no se detalla en las fuentes).</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G38" s="6" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>La plataforma fue lanzada el 1 de abril de 2024... constituye una herramienta valiosa de participación ciudadana muy relevante para ciudadanos, candidatos a cargos de elección popular y medios durante la campaña electoral y luego como recurso para el monitoreo del mandato ciudadano. (un despliegue concreto de la plataforma, 2024; sin evidencia de ediciones recurrentes).</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>La Fundación Panamá Participa lanzó Mansa Idea... iniciativa liderada por Paulina Franceschi a través de la Fundación Panamá Participa (sociedad civil). El proceso participativo de origen: 'El 26 de noviembre de 2020, el presidente Laurentino Cortizo Cohen lanzó la iniciativa denominada Pacto del Bicentenario Cerrando Brechas' (gobierno nacional / Concertación Nacional).</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. (la IA procesa el contenido de las propuestas del proceso participativo).</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía. (agregación/síntesis de los aportes ciudadanos = rol sobre el contenido).</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>https://www.panama24horas.com.pa/panama/fundacion-panama-participa-lanza-plataforma-de-propuestas-ciudadanas-mansa-idea/
 https://www.laestrella.com.pa/panama/politica/mansa-idea-una-herramienta-digital-con-propuestas-para-candidatos-YD6746221
@@ -10184,63 +10586,63 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (prensa): VERIFICADO (fuente primaria): el CNE usó IBM Watson Discovery + Studio (ML/NLP) sobre 87.991 documentos de aportes ciudadanos de 847 eventos y 49 espacios de di</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>Consejo Nacional de Educación del Perú</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>https://www.latinno.net/en/case/17232/
 https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional?utm_source=chatgpt.com
@@ -10250,59 +10652,133 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Project: National Digital Transformation Strategy | Ministry of Digital Transformation, Trinidad and Tobago (engage.gov.tt/projects/national-digital-transformation-strategy). Ruta interna confirmatoria: engage.gov.tt/projects/e-democracy-govocal-internal (la instancia corre sobre Go Vocal). En 2026: 'Projects | Ministry of Public Administration and Artificial Intelligence' (engage.gov.tt/projects).</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>EngageTT es una plataforma en linea (engage.gov.tt) donde ciudadanos, empresas y partes interesadas pueden recibir actualizaciones en tiempo real sobre iniciativas de transformacion digital y ofrecer retroalimentacion via encuestas y sondeos (polls); el Ministro anima a todos a participar y enviar ideas y comentarios sobre el NDTS, que se disena para evolucionar mediante el compromiso y la colaboracion continuos. Incluye un 'Open Forum' (engage.gov.tt/ideas/open-forum) y 'Input: Submitting Proposals' (engage.gov.tt/ideas/submitting-proposals).</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>The National Strategy for a Digital TT is finalized, and while the Ministry of Digital Transformation is no longer seeking input, they welcome feedback or comments through the citizen engagement digital platform Engage TT. (engage.gov.tt sigue operativo en 2026 bajo MPAAI).</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>The Ministry of Digital Transformation (MDT) officially presented the National Digital Transformation Strategy (NDTS) 2024-2027... launched during a NDTS Symposium in collaboration with the Inter-American Development Bank (IDB) on Wednesday, February 12th 2025. A major highlight... was the introduction of two new digital tools (EngageTT y AskNDTS). (Lanzamiento/anuncio unico en feb-2025; plataforma de uso continuo pero sin &gt;=2 ediciones de proceso participativo documentadas).</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>The Ministry of Digital Transformation (MDT) officially presented the National Digital Transformation Strategy (NDTS) 2024-2027... and introduced the EngageTT website - an online platform where citizens, businesses, and stakeholders can get real-time updates on digital transformation initiatives, and offer feedback via surveys and polls. (Convocante: gobierno nacional / Ministry of Digital Transformation, hoy MPAAI).</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Go Vocal Support Base (AI Analysis): 'Access to this feature depends on your plan. Advanced Sensemaking with auto-insights is available in the Premium plan.' -&gt; la IA/NLP de Go Vocal NO es automatica, depende del plan; y para EngageTT solo se documenta 'feedback via surveys and polls'/Open Forum/ideas, SIN mencion de analisis automatico por IA de los aportes. No se halla evidencia de activacion del NLP sobre el contenido en la instancia TT. 3a PASADA (refuerzo): Oxford Insights, 'The country's AI utilisation for citizens is concentrated in a robust Chatbot programme' (mas 'deployment of large language models for internal development purposes') -&gt; la IA ciudadana de TT es el chatbot, NO el analisis de aportes.</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Sin evidencia de IA aplicada al contenido de los aportes en engage.gov.tt. La unica IA confirmada de cara al ciudadano (AskNDTS/ANANSI) es chatbot de FAQ, excluido del criterio. En 3a pasada, el material de MPAAI 2026 enmarca la IA en el asistente ANANSI y en encuestas de AI-readiness (resultados 'consolidated and reviewed' en talleres), sin mencion de analisis por IA de los aportes del NDTS ni de Go Vocal Sensemaking.</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>https://support.govocal.com/en/articles/8316692-ai-analysis
+https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool
+https://www.govocal.com/plans
+https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
+https://engage.gov.tt/projects/national-digital-transformation-strategy
+https://engage.gov.tt/projects/e-democracy-govocal-internal
+https://engage.gov.tt/projects
+https://mdt.gov.tt/resources/ministry-launches-digital-tools-to-drive-national-digital-transformation-strategy-2024-2027/
+https://engage.gov.tt/pages/faq
+https://www.govocal.com/en-uk/platform-features/sensemaking
+https://www.govocal.com/en-uk/news/citizenlab-rebrands-to-go-vocal
+https://engage.gov.tt/uploads/51c7a0a3-20e6-46aa-8b13-72bd21a4f9c2/idea_file/file/ac51ce34-6291-4c02-a83f-caa33d60915b/National_Digital_Transformation_Strategy__NDTS__2025_-Actionable_Feedback___Implementation_Plan.pdf
+https://www.ttt.live/national-digital-transformation-strategy-2/
+https://oxfordinsights.com/insights/towards-a-digital-society-trinidad-and-tobagos-ai-ambitions/
+https://www.ttparliament.org/wp-content/uploads/2025/11/MPAAI-Budget-Guide-2026.pdf
+https://mpaai.gov.tt/sites/default/files/2025-12/media_release_trinidad-and-tobago-ignites-national-ai-readiness-drive-with-global-partners.pdf
+https://www.govocal.com/case-studies/cambridge-city-council-analyzes-input-50-faster-with-go-vocals-ai-assistant</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>UY</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Polis has been used to facilitate discussion and build consensus ... in Uruguay on a national referendum (OCDE 2025, 'Governing with AI')</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists — ran Polis alongside the referendum</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>The algorithm maps participants' responses and clusters opinions, facilitating the identification of positions that are supported by the majority of participants (OCDE 2025)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>16,499 people cast more than 295,000 votes ... The referendum was lost by less than 1%</t>
         </is>
       </c>
-      <c r="H38" s="6" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="H41" s="6" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>ran Polis alongside the referendum to look for something deeper than "yes or no"</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>Polis revealed that even where public safety divided people, surprising points of consensus broke through on other issues — bridges between groups</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/
 https://www.oecd.org/en/publications/governing-with-artificial-intelligence_795de142-en.html</t>
@@ -10310,7 +10786,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L38"/>
+  <autoFilter ref="A1:L41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10344,7 +10820,7 @@
       </c>
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>Planilla con 6 pestañas (criterio corregido). 37 casos entran/dudosos · 70 excluidos · 107 en total. Tras dedup e-Cidadania: 36 iniciativas.</t>
+          <t>Planilla con 6 pestañas (criterio corregido). 40 casos entran/dudosos · 67 excluidos · 107 en total. Tras dedup e-Cidadania: 39 iniciativas.</t>
         </is>
       </c>
     </row>
@@ -10372,7 +10848,7 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>7 casos ya FUERA bajo el criterio corregido: no son procesos de participación (civic tech / atención / voto electoral) o no tienen IA verificada. Solo confirmar.</t>
+          <t>4 casos ya FUERA: no son procesos de participación — PE conteo electoral · CO Descongestión (atención) · BR ParticipACT y CR dIAra (civic tech). Solo confirmar.</t>
         </is>
       </c>
     </row>
@@ -10384,19 +10860,19 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>4 casos que vuelven a ENTRAR: MX Presupuesto CRECES, CL LXS 400, CL Estrategia Gob. Digital, HN RedPública. Sí son participación con IA en alguna etapa. Confirmar SI.</t>
+          <t>7 casos que ENTRAN: MX Presupuesto CRECES · CL LXS 400 · CL Estrategia Gob. Digital · HN RedPública · CL Voz nuevos votantes · CL Jornada UNAB · CO Chatico. Confirmar SI.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>PASO 3 — Frontera civic-tech (grupos C y D)</t>
+          <t>PASO 3 — DUDAS a revisar con URL (grupos C y D)</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>3 DUDAS nuevas (CR U-Report, CL Voz nuevos votantes, CL Jornada UNAB) + 2 a revisar (CO Chatico, BR Colab). Decidir si son participación o civic tech/sondeo.</t>
+          <t>C: TT EngageTT (¿IA planeada?), CO DNP Diálogos (¿usó NLP/ConTexto?), DO CiudadanIA (¿módulo de participación?), CR U-Report (¿participación o sondeo?). D: BR Colab (¿participación o civic tech?). Abrir la URL y decidir.</t>
         </is>
       </c>
     </row>

--- a/data/gates/planilla_ILIA2026_SIMPLE.xlsx
+++ b/data/gates/planilla_ILIA2026_SIMPLE.xlsx
@@ -5862,7 +5862,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>¿La IA de Go Vocal (Sensemaking) está ACTIVA o PLANEADA? Si está planeada, ENTRA.</t>
+          <t>IA MIXTA: chatbot AskNDTS (IA) activo que ayuda a ENTENDER el NDTS (facilitación/info, no procesa aportes). El módulo Sensemaking de Go Vocal existe pero NO se confirma activado ni anunciado para TT. Ministerio ahora MPAAI (Public Admin + AI). → DUDA: ¿basta el chatbot explicador como 'IA en el proceso'? Ver mdt.gov.tt (EngageTT + AskNDTS).</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>¿Se usó NLP (p. ej. ConTexto del DNP) para sistematizar las 89.788 propuestas?</t>
+          <t>Análisis de fondo MANUAL/cualitativo (lectura + recurrencia, 7 categorías). Solo text-analytics ligero: nubes de palabras + tabulación por sectores (UCD). Sin NLP profundo ni ConTexto confirmado en los DRV → RECOMIENDO NO. Ver dialogosregionales.dnp.gov.co/resultados-dialogos.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>¿Tiene un módulo de participación (recoger aportes para decisiones), no solo atención/servicio?</t>
+          <t>Solo funciones de ATENCIÓN/SERVICIO; la 'participación' que menciona es co-diseñar la IA aportando datos, no consulta/decisión pública. No se halló módulo de participación → RECOMIENDO NO. Ver genia.ai/plataforma.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">

--- a/data/gates/planilla_ILIA2026_SIMPLE.xlsx
+++ b/data/gates/planilla_ILIA2026_SIMPLE.xlsx
@@ -15,10 +15,10 @@
     <sheet name="6 · Metodología (CENIA v2)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos (entran+dudosos)'!$A$1:$X$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos (entran+dudosos)'!$A$1:$X$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2 · A validar a mano'!$A$1:$G$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 · Excluidos'!$A$1:$E$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 · Evidencia y fuentes'!$A$1:$L$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 · Excluidos'!$A$1:$E$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 · Evidencia y fuentes'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X41"/>
+  <dimension ref="A1:X39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3524,11 +3524,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>➜ DUDA — revisar posible IA/participación</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>CO</t>
@@ -3536,7 +3532,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>DNP - Diálogos Regionales Vinculantes (PND 2022-2026)</t>
+          <t>ECHO – HáblameD Medellín</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -3544,9 +3540,9 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3556,17 +3552,17 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital; Mini públicos</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación; Análisis</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
@@ -3579,17 +3575,17 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional</t>
+          <t>organización internacional; gobierno local</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>no-claro</t>
+          <t>contenido</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3599,47 +3595,54 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr"/>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>Voz a Texto; NLP; LLM</t>
+        </is>
+      </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>Diálogos Regionales Vinculantes (DRV) convocados por el Gobierno Nacional (Presidencia + DNP) para construir las bases del Plan Nacional de Desarrollo 2022-2026 'Colombia, Potencia Mundial de la Vida'. 51 diálogos regionales, ~250.000 participantes, 2.115 mesas de diálogo, 89.788 propuestas ciudadanas recolectadas y sistematizadas.</t>
+          <t>IA que capta voz ciudadana en debates guiados y clasifica cada enunciado en metas ODS, generando visualizaciones para la planificación territorial</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>Departamento Nacional de Planeación (DNP) de Colombia. El análisis cuantitativo lo realizó la 'Unidad de Científicos de Datos' del DNP; el análisis cualitativo se desarrolló de manera conjunta entre el DNP y la Universidad Externado de Colombia (Facultad de Ciencias Sociales y Humanas).</t>
+          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="V26" s="5" t="n">
-        <v>2</v>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>https://www.funcionpublica.gov.co/documents/d/guest/la_rendicion_de_cuentas_y_el_control_social_marco_dialogos_regionales_vinculantes_-drv-
-https://github.com/ucd-dnp/ConTexto</t>
+          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>CO-dnp-dialogos-regionales-vinculantes-pnd</t>
+          <t>CO-echo-hablamed-medellin</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>➜ RESOLVER DUDA</t>
+        </is>
+      </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>CO</t>
@@ -3647,17 +3650,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>ECHO – HáblameD Medellín</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>(sin revisar)</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>DUDA(lean SI)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3667,17 +3670,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+          <t>MEDIA (múltiples fuentes de prensa independientes; sin verificación técnica del método; cobertura crítica)</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Presupuestos Participativos; Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Análisis; Traducción Política</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
@@ -3685,19 +3688,15 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>organización internacional; gobierno local</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>Mixto</t>
-        </is>
-      </c>
+          <t>sociedad civil</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
@@ -3705,17 +3704,17 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Voz a Texto; NLP; LLM</t>
+          <t>LLM; NLP</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
@@ -3725,159 +3724,164 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>IA que capta voz ciudadana en debates guiados y clasifica cada enunciado en metas ODS, generando visualizaciones para la planificación territorial</t>
+          <t>Plataforma participativa donde jóvenes del resguardo Zenú deciden por votación digital la asignación de presupuestos locales del cabildo y debaten proyectos de ley / proponen iniciativas ciudadanas colectivas.</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+          <t>Resguardo indígena Zenú (Reparo Torrente, Bajo Sinú); creador Carlos Redondo Rincón</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="V27" s="4" t="n">
-        <v>0</v>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="V27" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
-        </is>
-      </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>CO-echo-hablamed-medellin</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>➜ RESOLVER DUDA</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>(sin revisar)</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>DUDA(lean SI)</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA (múltiples fuentes de prensa independientes; sin verificación técnica del método; cobertura crítica)</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Presupuestos Participativos; Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Análisis; Traducción Política</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>sociedad civil</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>Sociedad Civil</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>LLM; NLP</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma participativa donde jóvenes del resguardo Zenú deciden por votación digital la asignación de presupuestos locales del cabildo y debaten proyectos de ley / proponen iniciativas ciudadanas colectivas.</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>Resguardo indígena Zenú (Reparo Torrente, Bajo Sinú); creador Carlos Redondo Rincón</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="V28" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>https://cerosetenta.uniandes.edu.co/
 https://gaitanaia.org/
 https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/</t>
         </is>
       </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>CO-gaitana-ia-resguardo-zenu</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Tenemos que hablar de Colombia</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>universidad; empresa; sociedad civil</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Mixto</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>Sociedad Civil</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>NLP - Tópicos; NLP - Sentiment</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>Plataforma colaborativa de diálogo e incidencia ciudadana para la conversación entre diversos actores de la sociedad colombiana, surgido a partir de eventos de manifestaciones sociales.</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>https://tenemosquehablarcolombia.co/
+https://tenemosquehablarcolombia.co/resultados/</t>
+        </is>
+      </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>CO-gaitana-ia-resguardo-zenu</t>
+          <t>CO-tenemos-que-hablar-de-colombia</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>➜ DUDA (frontera) — resolver a mano</t>
+        </is>
+      </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Tenemos que hablar de Colombia</t>
+          <t>U-Report Costa Rica – chatbot juvenil</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -3897,12 +3901,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Participación Digital</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3915,17 +3919,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>universidad; empresa; sociedad civil</t>
+          <t>organización internacional</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3935,17 +3939,17 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil</t>
+          <t>Sociedad Civil; Privado</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos; NLP - Sentiment</t>
+          <t>NLP</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
@@ -3955,48 +3959,40 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>Plataforma colaborativa de diálogo e incidencia ciudadana para la conversación entre diversos actores de la sociedad colombiana, surgido a partir de eventos de manifestaciones sociales.</t>
+          <t>U-Report es una plataforma global de UNICEF que empodera a adolescentes y jóvenes, permitiéndoles opinar sobre temas sociales cruciales a través de canales que ya utilizan, como WhatsApp, SMS y Facebook Messenger.</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
+          <t>Unicef</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>https://tenemosquehablarcolombia.co/
-https://tenemosquehablarcolombia.co/resultados/</t>
+          <t>https://costarica.ureport.in/
+https://www.unicef.org/costarica/comunicados-prensa/plataforma-mundial-u-report-llega-costa-rica</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>CO-tenemos-que-hablar-de-colombia</t>
+          <t>CR-u-report-costa-rica-chatbot-juvenil</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>➜ DUDA (frontera) — resolver a mano</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>U-Report Costa Rica – chatbot juvenil</t>
+          <t xml:space="preserve">PAGA IA </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4021,12 +4017,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital</t>
+          <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
@@ -4039,12 +4035,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>organización internacional</t>
+          <t>gobierno nacional; sociedad civil</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -4054,282 +4050,286 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil; Privado</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>NLP</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>U-Report es una plataforma global de UNICEF que empodera a adolescentes y jóvenes, permitiéndoles opinar sobre temas sociales cruciales a través de canales que ya utilizan, como WhatsApp, SMS y Facebook Messenger.</t>
+          <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto. Analiza datos de planes de acción de gobierno abierto de Ecuador y otros países de Hispanoamérica para sugerir actividades e hitos relacionados con temas propuestos por los usuarios</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>Unicef</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr"/>
+          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="V30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>https://costarica.ureport.in/
-https://www.unicef.org/costarica/comunicados-prensa/plataforma-mundial-u-report-llega-costa-rica</t>
-        </is>
-      </c>
-      <c r="X30" s="2" t="inlineStr">
-        <is>
-          <t>CR-u-report-costa-rica-chatbot-juvenil</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>➜ DUDA — revisar posible IA/participación</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>CiudadanIA</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>(sin revisar)</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>SI*</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>empresa; universidad; gobierno nacional</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>Mixto</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>Privado</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>Sistemas de recomendación; LLM</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>Sistema de interacción ciudadana basado en inteligencia artificial, diseñado para recopilar datos representativos que permitan el entrenamiento avanzado de IA en la prestación de servicios públicos. A través de ventanillas ubicadas en puntos estratégicos de alto tránsito, ofrece asistencia, información y recomendaciones personalizadas, fomentando la participación activa de la ciudadanía en el diseño y desarrollo de un sistema de Gobierno Inteligente.</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>GENIA Latinoamérica, en colaboración con la Universidad del Caribe (UNICARIBE), el Ministerio de la Presidencia (MINPRE) y la Oficina Gubernamental de Tecnologías de la Información y Comunicación (OGTIC)</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.genia.ai/paises-miembros
-https://presidencia.gob.do/seccion/inteligencia-artificial</t>
-        </is>
-      </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t>DO-ciudadania</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PAGA IA </t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Referendos e Iniciativas Populares</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>gobierno nacional; sociedad civil</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>Mixto</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>Sociedad Civil</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto. Analiza datos de planes de acción de gobierno abierto de Ecuador y otros países de Hispanoamérica para sugerir actividades e hitos relacionados con temas propuestos por los usuarios</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>https://www.gobiernoabierto.ec/boletin-014-2023/
 https://ia.gobiernoabierto.ec/
 https://ia.gobiernoabierto.ec/acercade</t>
         </is>
       </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>EC-paga-ia</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guatemala Joven Conversa </t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>organización internacional; sociedad civil</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Mixto</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>NLP - Sentiment; NLP - Tópicos</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarrollo y la lucha contra la corrupción.</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
+https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/?utm_source=chatgpt.com
+https://dppa.un.org/en/using-power-of-ai-to-boost-youth-political-participation-guatemala</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>GT-guatemala-joven-conversa</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RedPública + iVerify </t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Referendos e Iniciativas Populares</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>organización internacional; universidad</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno; Academia</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>Internacional, Nacional</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>NLP - Tópicos</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias. Integra iVerify, una herramienta que utiliza aprendizaje automático para detectar y clasificar desinformación electoral antes de su publicación.</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
+        </is>
+      </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>EC-paga-ia</t>
+          <t>HN-redpublica-iverify</t>
         </is>
       </c>
     </row>
@@ -4337,12 +4337,12 @@
       <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guatemala Joven Conversa </t>
+          <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -4362,17 +4362,17 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Gobernanza Colaborativa; Participación Digital</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>organización internacional; sociedad civil</t>
+          <t>gobierno local</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4405,27 +4405,27 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>NLP - Sentiment; NLP - Tópicos</t>
+          <t>NLP; Otros(no especificado)</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>no-claro</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarrollo y la lucha contra la corrupción.</t>
+          <t>Elaboración del Programa de Gobierno del Estado de Guanajuato 2024-2030 ('Gobierno de la Gente'), un plan de gobierno construido con participación ciudadana: se recorrió el territorio y se realizaron cuatro talleres regionales (noreste, norte, centro y sur) con representación de los 46 municipios, integrando la voz de más de 26,000 personas mediante talleres y consultas. El contenido fue validado por el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG), conformado por ciudadanía, la Gobernadora, secretarios de cada eje e IPLANEG. Se utilizaron herramientas de inteligencia artificial para procesar y organizar las miles de ideas y propuestas recibidas, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región, transformando el diálogo social en datos para la toma de decisiones que alimentaron los ejes del programa. Adicionalmente existe la asistente virtual 'Esperanza' para consultar el programa ya publicado.</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
+          <t>Gobierno del Estado de Guanajuato — Instituto de Planeación, Estadística y Geografía del Estado de Guanajuato (IPLANEG), con validación del COPLADEG. Titular: Gobernadora Libia Dennise García Muñoz Ledo.</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4433,587 +4433,585 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="V33" s="4" t="n">
-        <v>0</v>
+      <c r="V33" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
-https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/?utm_source=chatgpt.com
-https://dppa.un.org/en/using-power-of-ai-to-boost-youth-political-participation-guatemala</t>
-        </is>
-      </c>
-      <c r="X33" s="2" t="inlineStr">
-        <is>
-          <t>GT-guatemala-joven-conversa</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>HN</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RedPública + iVerify </t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Referendos e Iniciativas Populares</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>organización internacional; universidad</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno; Academia</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>Internacional, Nacional</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>NLP - Tópicos</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias. Integra iVerify, una herramienta que utiliza aprendizaje automático para detectar y clasificar desinformación electoral antes de su publicación.</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
-        </is>
-      </c>
-      <c r="X34" s="2" t="inlineStr">
-        <is>
-          <t>HN-redpublica-iverify</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Gobernanza Colaborativa; Participación Digital</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>gobierno local</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>NLP; Otros(no especificado)</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>no-claro</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>Elaboración del Programa de Gobierno del Estado de Guanajuato 2024-2030 ('Gobierno de la Gente'), un plan de gobierno construido con participación ciudadana: se recorrió el territorio y se realizaron cuatro talleres regionales (noreste, norte, centro y sur) con representación de los 46 municipios, integrando la voz de más de 26,000 personas mediante talleres y consultas. El contenido fue validado por el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG), conformado por ciudadanía, la Gobernadora, secretarios de cada eje e IPLANEG. Se utilizaron herramientas de inteligencia artificial para procesar y organizar las miles de ideas y propuestas recibidas, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región, transformando el diálogo social en datos para la toma de decisiones que alimentaron los ejes del programa. Adicionalmente existe la asistente virtual 'Esperanza' para consultar el programa ya publicado.</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno del Estado de Guanajuato — Instituto de Planeación, Estadística y Geografía del Estado de Guanajuato (IPLANEG), con validación del COPLADEG. Titular: Gobernadora Libia Dennise García Muñoz Ledo.</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="V35" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
         <is>
           <t>https://guanajuatointeligente.com/como-hicimos-el-programa/
 https://iplaneg.guanajuato.gob.mx/programagobierno24-30/
 https://iplaneg.guanajuato.gob.mx/wp-content/uploads/03-2.05-Diagnostico-Programa-de-Gobierno-2024-2030-_Diagnostico-Estatal-2025_.pdf</t>
         </is>
       </c>
-      <c r="X35" s="2" t="inlineStr">
+      <c r="X33" s="2" t="inlineStr">
         <is>
           <t>MX-guanajuato-inteligente-2024-2030</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>➜ RESOLVER DUDA</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Jalisco - Consulta ¡Armemos un Plan! (Plan Estatal de Desarrollo y Gobernanza 2024-2030)</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>(sin revisar)</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>DUDA(lean NO)</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="n">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>gobierno local</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr"/>
-      <c r="P36" s="2" t="inlineStr"/>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S36" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>Consulta ciudadana '¡Armemos un Plan!' convocada por el Gobierno de Jalisco a través de la Secretaría de Planeación y Participación Ciudadana (SPPC) para construir el Plan Estatal de Desarrollo y Gobernanza 2024-2030. Ejercicio abierto e inclusivo del 20 de febrero al 17 de abril de 2025 que registró 675,484 participaciones (aprox. 624,226 participaciones digitales + 25,176 niñas, niños y adolescentes mediante un mecanismo especialmente diseñado). Combinó: una encuesta representativa 'casa por casa' con rigor estadístico y metodológico; consulta digital abierta que recibió 15,899 propuestas ciudadanas escritas (temas: espacios públicos/deportivos/recreativos, medio ambiente y movilidad, agua y territorio, turismo rural, vivienda digna, economías locales); 12 foros regionales y 9 foros temáticos / mesas de trabajo con 5,563 participantes presenciales; 168 mesas regionales y 47 sectoriales donde se identificaron y discutieron 1,349 problemáticas; e instalación de 18 Consejos de Participación y Planeación (1 estatal, 12 regionales, 5 sectoriales). El resultado se estructuró en 5 ejes, 36 temas, 50 objetivos estratégicos, 197-198 proyectos y 82 indicadores de seguimiento.</t>
         </is>
       </c>
-      <c r="T36" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
         <is>
           <t>Gobierno del Estado de Jalisco — Secretaría de Planeación y Participación Ciudadana (SPPC). Titular: Cynthia Cantero Pacheco. Apoyo de información estadística/geográfica: Instituto de Información Estadística y Geográfica de Jalisco (IIEG). Gobernador: Pablo Lemus Navarro (administración 2024-2030).</t>
         </is>
       </c>
-      <c r="U36" s="2" t="inlineStr">
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="V36" s="5" t="n">
+      <c r="V34" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="W36" s="2" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
         <is>
           <t>https://armemosunplan.mx/wp-content/uploads/2025/10/Armemos-un-Plan-Informe-de-Consulta-COLOR-NNA-v2.4.pdf
 https://plan.jalisco.gob.mx/documentos-metodologicos/
 https://iieg.gob.mx/ns/</t>
         </is>
       </c>
-      <c r="X36" s="2" t="inlineStr">
+      <c r="X34" s="2" t="inlineStr">
         <is>
           <t>MX-jalisco-armemos-un-plan</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Presupuesto CRECES</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Presupuestos Participativos</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="J37" s="2" t="n">
+      <c r="J35" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>gobierno local</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr">
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>Chatbot - Inespecífico</t>
         </is>
       </c>
-      <c r="R37" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S37" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
         <is>
           <t>Presupuesto participativo del Ayuntamiento de Hermosillo en México. Utiliza un chatbot que a través de IA simplifica y facilita la votación de los presupuestos participativos</t>
         </is>
       </c>
-      <c r="T37" s="2" t="inlineStr">
+      <c r="T35" s="2" t="inlineStr">
         <is>
           <t>Ayundamiento de Hermosilla</t>
         </is>
       </c>
-      <c r="U37" s="2" t="inlineStr">
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="V37" s="5" t="n">
+      <c r="V35" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="W37" s="2" t="inlineStr">
+      <c r="W35" s="2" t="inlineStr">
         <is>
           <t>https://presupuestocreces.hermosillo.gob.mx/</t>
         </is>
       </c>
-      <c r="X37" s="2" t="inlineStr">
+      <c r="X35" s="2" t="inlineStr">
         <is>
           <t>MX-presupuesto-creces</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
-      <c r="B38" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>Análisis; Traducción Política</t>
         </is>
       </c>
-      <c r="J38" s="2" t="n">
+      <c r="J36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>sociedad civil; gobierno nacional</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Sociedad Civil</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr">
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
         </is>
       </c>
-      <c r="S38" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea (www.mansaidea.com) es una plataforma digital basada en inteligencia artificial lanzada el 1 de abril de 2024 por la Fundación Panamá Participa (sociedad civil), liderada por Paulina Franceschi. La plataforma organiza y hace navegables más de 175.000 ideas y propuestas ciudadanas generadas durante el Pacto del Bicentenario 'Cerrando Brechas' (proceso participativo nacional convocado por el gobierno de Panamá / Concertación Nacional, presidente Cortizo, 2020-2021), agregando los consensos nacionales y regionales/provinciales por tema en un solo clic. La IA se aplica sobre el CONTENIDO de los aportes ciudadanos (organiza, agrega y sintetiza el corpus de propuestas) para convertirlo en una base de datos navegable. El uso de la IA es un tratamiento PUNTERAL (~2024) de un corpus histórico de un proceso participativo ya cerrado (el Pacto fue 2020-2021), orientado a elevar el nivel de la conversación electoral 2024 y a dotar a candidatos, medios y ciudadanía de una herramienta para alinear planes con las necesidades de la población y monitorear el mandato ciudadano. IMPORTANTE: el proceso participativo original (recolección de aportes) fue convocado por el gobierno; la capa de IA (Mansa Idea) la desarrolla la sociedad civil sobre ese corpus ya recolectado.</t>
         </is>
       </c>
-      <c r="T38" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
         <is>
           <t>Fundación Panamá Participa (sociedad civil, Panamá), iniciativa liderada por Paulina Franceschi. El proceso participativo de origen (Pacto del Bicentenario 'Cerrando Brechas') fue convocado por el Gobierno de Panamá a través del mecanismo de Concertación Nacional para el Desarrollo (presidente Laurentino Cortizo), con apoyo del PNUD.</t>
         </is>
       </c>
-      <c r="U38" s="2" t="inlineStr">
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="V38" s="5" t="n">
+      <c r="V36" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="W38" s="2" t="inlineStr">
+      <c r="W36" s="2" t="inlineStr">
         <is>
           <t>https://mansaidea.com/ (intentar archive.org / cache); buscar 'Mansa Idea metodología inteligencia artificial procesamiento propuestas' y entrevistas técnicas a Paulina Franceschi / Fundación Panamá Participa.
 https://mansaidea.com/ ; buscar 'Mansa Idea 2025' / 'Mansa Idea 2026' / 'Fundación Panamá Participa actividad reciente'.
 https://mansaidea.com/ ; buscar evidencia de actualizaciones periódicas del corpus o nuevas convocatorias.</t>
         </is>
       </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>PA-mansa-idea-pacto-del-bicentenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>otra institución pública</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>NLP - Tópicos; NLP - Sentiment</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>Una consulta pública para recoger opiniones sobre el Proyecto Educativo Nacional 2036, utilizando encuestas en línea, talleres y mesas deliberativas.</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>Consejo Nacional de Educación del Perú</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.latinno.net/en/case/17232/
+https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional?utm_source=chatgpt.com
+https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>PE-consulta-ciudadana-sobre-el-proyecto-nac</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>➜ DUDA — revisar posible IA/participación</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>DUDA(lean NO)</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Plataforma</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>gobierno nacional</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>no-claro</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>NLP; Resumen automatico; Clasificacion/agrupacion de texto (capacidad de la plataforma sujeta a plan Premium; activacion NO confirmada en TT)</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>no-claro</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>EngageTT (engage.gov.tt) es la plataforma de participacion ciudadana del Ministry of Digital Transformation de Trinidad y Tobago (desde mayo 2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), lanzada en el simposio del NDTS el 12 de febrero de 2025 junto al BID (IDB). Se usa como canal de participacion en el proceso de planificacion nacional del National Digital Transformation Strategy (NDTS) 2024-2027, donde ciudadanos, empresas y partes interesadas reciben actualizaciones y aportan retroalimentacion via encuestas, sondeos (polls), un 'Open Forum' de ideas y el envio de propuestas. La instancia corre sobre el software Go Vocal (antes CitizenLab) -confirmado por la ruta interna 'projects/e-democracy-govocal-internal'-. Go Vocal incorpora un modulo de IA/NLP de 'Sensemaking' (analisis y resumen automatico de aportes), pero ese modulo NO viene activo por defecto: segun la documentacion de soporte de Go Vocal, el acceso a la funcion de AI Analysis/Sensemaking DEPENDE DEL PLAN contratado (Advanced Sensemaking con auto-insights esta en el plan Premium). Tras 2a pasada de investigacion (&gt;=14 busquedas/fetches) NO se halla evidencia alguna de que la instancia de Trinidad active ni use esas funciones de IA sobre el CONTENIDO de los aportes; toda la documentacion describe a EngageTT como recolector (surveys, polls, Open Forum, ideas), es decir plataforma usada como formulario sin analisis automatico confirmado. Existe ademas AskNDTS, un chatbot/PWA de IA conversacional para responder preguntas sobre el NDTS (rol de FAQ informativo, EXCLUIDO del criterio).</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Digital Transformation de Trinidad y Tobago (desde el 23-may-2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), en colaboracion con el Banco Interamericano de Desarrollo (BID/IDB). Plataforma de software: Go Vocal (antes CitizenLab), empresa belga.</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="V38" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
+https://www.govocal.com/plans
+https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool</t>
+        </is>
+      </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>PA-mansa-idea-pacto-del-bicentenario</t>
+          <t>TT-engagett-plataforma-go-vocal</t>
         </is>
       </c>
     </row>
@@ -5021,24 +5019,24 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>UY</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
+          <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>(sin revisar)</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
           <t>sí</t>
@@ -5046,12 +5044,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+          <t>MEDIA (fuente primaria + OCDE 2025; fetch primario bloqueado por proxy, citas vía repo/WebSearch)</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -5069,7 +5067,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>otra institución pública</t>
+          <t>universidad</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -5084,7 +5082,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Sociedad Civil; Academia</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5094,7 +5092,7 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos; NLP - Sentiment</t>
+          <t>Clustering; ML - Inespecífico</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
@@ -5104,267 +5102,35 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>Una consulta pública para recoger opiniones sobre el Proyecto Educativo Nacional 2036, utilizando encuestas en línea, talleres y mesas deliberativas.</t>
+          <t>Referéndum nacional para derogar 135 artículos de la Ley de Urgente Consideración (LUC). Un equipo de la Universidad de la República corrió una conversación Pol.is en paralelo al referéndum del 27/03/2022 (documentado como caso 2021).</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>Consejo Nacional de Educación del Perú</t>
+          <t>Equipo de 13 personas de la Universidad de la República (UdelaR) — ingenieros, comunicadores y científicos de datos; plataforma Pol.is (The Computational Democracy Project)</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="V39" s="4" t="n">
-        <v>0</v>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="V39" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>https://www.latinno.net/en/case/17232/
-https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional?utm_source=chatgpt.com
-https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080</t>
+          <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>PE-consulta-ciudadana-sobre-el-proyecto-nac</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>➜ DUDA — revisar posible IA/participación</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>DUDA(lean NO)</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>gobierno nacional</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>no-claro</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>Privado</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>NLP; Resumen automatico; Clasificacion/agrupacion de texto (capacidad de la plataforma sujeta a plan Premium; activacion NO confirmada en TT)</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>no-claro</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>EngageTT (engage.gov.tt) es la plataforma de participacion ciudadana del Ministry of Digital Transformation de Trinidad y Tobago (desde mayo 2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), lanzada en el simposio del NDTS el 12 de febrero de 2025 junto al BID (IDB). Se usa como canal de participacion en el proceso de planificacion nacional del National Digital Transformation Strategy (NDTS) 2024-2027, donde ciudadanos, empresas y partes interesadas reciben actualizaciones y aportan retroalimentacion via encuestas, sondeos (polls), un 'Open Forum' de ideas y el envio de propuestas. La instancia corre sobre el software Go Vocal (antes CitizenLab) -confirmado por la ruta interna 'projects/e-democracy-govocal-internal'-. Go Vocal incorpora un modulo de IA/NLP de 'Sensemaking' (analisis y resumen automatico de aportes), pero ese modulo NO viene activo por defecto: segun la documentacion de soporte de Go Vocal, el acceso a la funcion de AI Analysis/Sensemaking DEPENDE DEL PLAN contratado (Advanced Sensemaking con auto-insights esta en el plan Premium). Tras 2a pasada de investigacion (&gt;=14 busquedas/fetches) NO se halla evidencia alguna de que la instancia de Trinidad active ni use esas funciones de IA sobre el CONTENIDO de los aportes; toda la documentacion describe a EngageTT como recolector (surveys, polls, Open Forum, ideas), es decir plataforma usada como formulario sin analisis automatico confirmado. Existe ademas AskNDTS, un chatbot/PWA de IA conversacional para responder preguntas sobre el NDTS (rol de FAQ informativo, EXCLUIDO del criterio).</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>Ministry of Digital Transformation de Trinidad y Tobago (desde el 23-may-2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), en colaboracion con el Banco Interamericano de Desarrollo (BID/IDB). Plataforma de software: Go Vocal (antes CitizenLab), empresa belga.</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="V40" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
-https://www.govocal.com/plans
-https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool</t>
-        </is>
-      </c>
-      <c r="X40" s="2" t="inlineStr">
-        <is>
-          <t>TT-engagett-plataforma-go-vocal</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr"/>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>UY</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>(sin revisar)</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA (fuente primaria + OCDE 2025; fetch primario bloqueado por proxy, citas vía repo/WebSearch)</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Referendos e Iniciativas Populares</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>universidad</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>Sociedad Civil; Academia</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>Clustering; ML - Inespecífico</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>Referéndum nacional para derogar 135 artículos de la Ley de Urgente Consideración (LUC). Un equipo de la Universidad de la República corrió una conversación Pol.is en paralelo al referéndum del 27/03/2022 (documentado como caso 2021).</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>Equipo de 13 personas de la Universidad de la República (UdelaR) — ingenieros, comunicadores y científicos de datos; plataforma Pol.is (The Computational Democracy Project)</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="V41" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/</t>
-        </is>
-      </c>
-      <c r="X41" s="2" t="inlineStr">
-        <is>
           <t>UY-polis-referendum-luc</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X41"/>
+  <autoFilter ref="A1:X39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5574,154 +5340,156 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>A. Excluir (criterio corregido)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar NO (ya fuera del conteo)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>CiudadanIA</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>No es un proceso de participación (o sin IA verificada) → excluido</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Solo atención/servicio; la 'participación' es co-diseñar la IA aportando datos, no consulta pública. Sin módulo de participación (verificado). Decisión del equipo.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.genia.ai/paises-miembros
+https://presidencia.gob.do/seccion/inteligencia-artificial</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>A. Excluir (criterio corregido)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar NO (ya fuera del conteo)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>DNP - Diálogos Regionales Vinculantes (PND 2022-2026)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>No es un proceso de participación (o sin IA verificada) → excluido</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Participación real, pero el análisis fue manual/cualitativo; solo text-analytics ligero (nubes de palabras + tabulación), sin NLP sobre el contenido (verificado). Decisión del equipo.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.funcionpublica.gov.co/documents/d/guest/la_rendicion_de_cuentas_y_el_control_social_marco_dialogos_regionales_vinculantes_-drv-
+https://github.com/ucd-dnp/ConTexto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Presupuesto CRECES</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Presupuesto participativo (Hermosillo); la IA (chatbot) facilita la votación (Implementación).</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://presupuestocreces.hermosillo.gob.mx/</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>LXS 400 - Chile Delibera</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Mini-público del Senado; la IA modera y administra los turnos de palabra (Implementación/Planificación).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://es.wikipedia.org/wiki/Lxs_400:_Chile_Delibera
 https://www.lxs400.cl/noticias/</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>B. Rescatado → ENTRA</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Confirmar SI</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Consulta ciudadana; la IA analiza los aportes (Análisis).</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>https://participacion.digital.gob.cl/es-CL/folders/consultas-ciudadanas</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>B. Rescatado → ENTRA</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Confirmar SI</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>HN</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RedPública + iVerify </t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma de propuestas de ley ciudadanas (participación legislativa).</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
-        </is>
-      </c>
-    </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
@@ -5740,7 +5508,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>La voz de los nuevos votantes</t>
+          <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -5750,12 +5518,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Consulta a nuevos votantes con NLP — proceso ejecutado por el equipo (confirmado).</t>
+          <t>Consulta ciudadana; la IA analiza los aportes (Análisis).</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf</t>
+          <t>https://participacion.digital.gob.cl/es-CL/folders/consultas-ciudadanas</t>
         </is>
       </c>
     </row>
@@ -5772,12 +5540,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
+          <t xml:space="preserve">RedPública + iVerify </t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -5787,12 +5555,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Jornada de escucha / diálogo — proceso ejecutado por el equipo (confirmado).</t>
+          <t>Plataforma de propuestas de ley ciudadanas (participación legislativa).</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
+          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
         </is>
       </c>
     </row>
@@ -5809,143 +5577,141 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>La voz de los nuevos votantes</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Consulta a nuevos votantes con NLP — proceso ejecutado por el equipo (confirmado).</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>B. Rescatado → ENTRA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar SI</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Jornada de escucha / diálogo — proceso ejecutado por el equipo (confirmado).</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>B. Rescatado → ENTRA</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar SI</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Chatico</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Tiene módulos de participación (aportes al Plan de Desarrollo de Bogotá) — confirmado por el equipo.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://secretariageneral.gov.co/noticias/chatico-el-agente-virtual-de-servicio-la-ciudadania-supero-los-36-millones-de-conversaciones
 https://bogota.gov.co/mi-ciudad/gestion-publica/distrito-presenta-su-agente-virtual-chatico-que-guia-la-ciudadania</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>C. DUDA — revisar (posible IA)</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Abrir URL y decidir SI/NO</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Revisar si hay/planea IA o módulo de participación</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>IA MIXTA: chatbot AskNDTS (IA) activo que ayuda a ENTENDER el NDTS (facilitación/info, no procesa aportes). El módulo Sensemaking de Go Vocal existe pero NO se confirma activado ni anunciado para TT. Ministerio ahora MPAAI (Public Admin + AI). → DUDA: ¿basta el chatbot explicador como 'IA en el proceso'? Ver mdt.gov.tt (EngageTT + AskNDTS).</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
 https://www.govocal.com/plans
 https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>C. DUDA — revisar (posible IA)</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Abrir URL y decidir SI/NO</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>DNP - Diálogos Regionales Vinculantes (PND 2022-2026)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Revisar si hay/planea IA o módulo de participación</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Análisis de fondo MANUAL/cualitativo (lectura + recurrencia, 7 categorías). Solo text-analytics ligero: nubes de palabras + tabulación por sectores (UCD). Sin NLP profundo ni ConTexto confirmado en los DRV → RECOMIENDO NO. Ver dialogosregionales.dnp.gov.co/resultados-dialogos.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.funcionpublica.gov.co/documents/d/guest/la_rendicion_de_cuentas_y_el_control_social_marco_dialogos_regionales_vinculantes_-drv-
-https://github.com/ucd-dnp/ConTexto</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>C. DUDA — revisar (posible IA)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Abrir URL y decidir SI/NO</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>CiudadanIA</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Revisar si hay/planea IA o módulo de participación</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Solo funciones de ATENCIÓN/SERVICIO; la 'participación' que menciona es co-diseñar la IA aportando datos, no consulta/decisión pública. No se halló módulo de participación → RECOMIENDO NO. Ver genia.ai/plataforma.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.genia.ai/paises-miembros
-https://presidencia.gob.do/seccion/inteligencia-artificial</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7158,7 +6924,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Descongestión de solicitudes diarias del programa Ingreso Solidario</t>
+          <t>DNP - Diálogos Regionales Vinculantes (PND 2022-2026)</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -7168,12 +6934,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana (triage de 10.000 correos/día): servicio, no participación.</t>
+          <t>Participación real, pero el análisis fue manual/cualitativo; solo text-analytics ligero (nubes de palabras + tabulación), sin NLP sobre el contenido (verificado). Decisión del equipo.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/inteligencia-artificial-la-herramienta-que-descongestiono-10-000-solicitudes-diarias-de-ingreso-solidario/</t>
+          <t>https://github.com/ucd-dnp</t>
         </is>
       </c>
     </row>
@@ -7185,22 +6951,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>IA para participación en el POT de Bogotá (Control Visible / Auditoría General)</t>
+          <t>Descongestión de solicitudes diarias del programa Ingreso Solidario</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Dudoso</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>NO ENTRA. El criterio de elegibilidad exige que dentro de un proceso participativo se DESPLIEGUE IA real (institucional) sobre el CONTENIDO de los aportes ciudadanos. El caso documentado es un ARTÍCULO ACADÉMICO (Fundación Universitaria del Área Andina, Maestría en Innovación; publicado en la revist</t>
+          <t>Atención ciudadana (triage de 10.000 correos/día): servicio, no participación.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://controlvisible.auditoria.gov.co/index.php/rcf/article/view/63</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/inteligencia-artificial-la-herramienta-que-descongestiono-10-000-solicitudes-diarias-de-ingreso-solidario/</t>
         </is>
       </c>
     </row>
@@ -7212,22 +6978,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ISIDataInsights / Reto de Ciudad 'Datos con Historia' (SDP Bogotá)</t>
+          <t>IA para participación en el POT de Bogotá (Control Visible / Auditoría General)</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Dudoso</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>DUDA con inclinación NO (REAFIRMADA en 3ª pasada con búsqueda amplia, jul-2026). Por un lado, la herramienta ISIDataInsights está diseñada para operar sobre el CONTENIDO de información cualitativa de planeación, incluyendo explícitamente 'los aportes ciudadanos' (procesar, validar consistencia, apli</t>
+          <t>NO ENTRA. El criterio de elegibilidad exige que dentro de un proceso participativo se DESPLIEGUE IA real (institucional) sobre el CONTENIDO de los aportes ciudadanos. El caso documentado es un ARTÍCULO ACADÉMICO (Fundación Universitaria del Área Andina, Maestría en Innovación; publicado en la revist</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.sdp.gov.co/noticias/bogota-cuenta-herramienta-innovadora-abordar-los-problemas-urbanos-aporte-de-la-ciudadania</t>
+          <t>https://controlvisible.auditoria.gov.co/index.php/rcf/article/view/63</t>
         </is>
       </c>
     </row>
@@ -7239,22 +7005,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Mini-Public del diálogo social de la Procuraduría</t>
+          <t>ISIDataInsights / Reto de Ciudad 'Datos con Historia' (SDP Bogotá)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Excluido (revisar)</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se MANTIENE EXCLUIDO (entra=NO), confirmando el motivo de exclusión de 2025 ('No se encontró información sobre el uso de la IA en la implementación de los Mini Publics'). El proceso es ELEGIBLE por su naturaleza (mini-público / diálogo social deliberativo convocado por la Procuraduría General de la </t>
+          <t>DUDA con inclinación NO (REAFIRMADA en 3ª pasada con búsqueda amplia, jul-2026). Por un lado, la herramienta ISIDataInsights está diseñada para operar sobre el CONTENIDO de información cualitativa de planeación, incluyendo explícitamente 'los aportes ciudadanos' (procesar, validar consistencia, apli</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://ideemos.org/mini-public-del-dialogo-social-de-la-procuraduria/</t>
+          <t>https://www.sdp.gov.co/noticias/bogota-cuenta-herramienta-innovadora-abordar-los-problemas-urbanos-aporte-de-la-ciudadania</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7032,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Pa' que veás (Cali)</t>
+          <t>Mini-Public del diálogo social de la Procuraduría</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -7276,12 +7042,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se revisa por su analogia con dIAra (bots que recopilan quejas ciudadanas y predicen riesgos en obras). Sin embargo, NO se encontro evidencia de uso de inteligencia artificial sobre el CONTENIDO de los aportes/quejas ciudadanas dentro de un proceso participativo. 'Pa' que veas' es, en su nucleo, un </t>
+          <t xml:space="preserve">Se MANTIENE EXCLUIDO (entra=NO), confirmando el motivo de exclusión de 2025 ('No se encontró información sobre el uso de la IA en la implementación de los Mini Publics'). El proceso es ELEGIBLE por su naturaleza (mini-público / diálogo social deliberativo convocado por la Procuraduría General de la </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.iadb.org/en/news/city-cali-launches-platform-monitoring-public-investment-idb-support</t>
+          <t>https://ideemos.org/mini-public-del-dialogo-social-de-la-procuraduria/</t>
         </is>
       </c>
     </row>
@@ -7293,22 +7059,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Plataforma Urna de Cristal</t>
+          <t>Pa' que veás (Cali)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (revisar)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA</t>
+          <t xml:space="preserve">Se revisa por su analogia con dIAra (bots que recopilan quejas ciudadanas y predicen riesgos en obras). Sin embargo, NO se encontro evidencia de uso de inteligencia artificial sobre el CONTENIDO de los aportes/quejas ciudadanas dentro de un proceso participativo. 'Pa' que veas' es, en su nucleo, un </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://projects.itforchange.net/mavc/wp-content/uploads/2017/09/Voice-or-Chatter_Case-Study_Colombia_August-2017.pdf?utm_source=chatgpt.com</t>
+          <t>https://www.iadb.org/en/news/city-cali-launches-platform-monitoring-public-investment-idb-support</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7086,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SISBÉN IV</t>
+          <t>Plataforma Urna de Cristal</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -7330,12 +7096,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>No evidencia de uso de IA</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/sisben</t>
+          <t>https://projects.itforchange.net/mavc/wp-content/uploads/2017/09/Voice-or-Chatter_Case-Study_Colombia_August-2017.pdf?utm_source=chatgpt.com</t>
         </is>
       </c>
     </row>
@@ -7347,103 +7113,103 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>iLabs - Laboratorios de Inteligencia Colectiva (Ideemos)</t>
+          <t>SISBÉN IV</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Excluido (revisar)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>MANTENER EXCLUIDO. La regla de reingreso exige evidencia de IA aplicada al CONTENIDO de los aportes ciudadanos dentro de un proceso participativo. La fuente primaria (página iLabs de Ideemos y su PDF) describe 'Inteligencia Artificial' y 'Machine Learning' SOLO como parte de un listado de técnicas c</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://ideemos.org/ilabs-laboratorios-de-inteligencia-colectiva/</t>
+          <t>https://fairlac.iadb.org/sisben</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>dIAra</t>
+          <t>iLabs - Laboratorios de Inteligencia Colectiva (Ideemos)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido (revisar)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Civic tech de fiscalización de obras (control social vía app): no es un proceso participativo.</t>
+          <t>MANTENER EXCLUIDO. La regla de reingreso exige evidencia de IA aplicada al CONTENIDO de los aportes ciudadanos dentro de un proceso participativo. La fuente primaria (página iLabs de Ideemos y su PDF) describe 'Inteligencia Artificial' y 'Machine Learning' SOLO como parte de un listado de técnicas c</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.opengovpartnership.org/the-open-gov-challenge/costa-rica-artificial-intelligence-alerts-citizen-control-public-infrastructure/</t>
+          <t>https://ideemos.org/ilabs-laboratorios-de-inteligencia-colectiva/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>CU</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
+          <t>dIAra</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Dudoso</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Dentro de un proceso participativo formal y de gran escala (consulta popular legislativa nacional sobre el Código de las Familias, feb-abr 2022, ~6,5 millones de participantes y cientos de miles de propuestas) se usó IA sobre el CONTENIDO de los aportes ciudadanos: el sistema GEMA-CEN (basado en GEM</t>
+          <t>Civic tech de fiscalización de obras (control social vía app): no es un proceso participativo.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>http://www.datys.cu/spa/site/product/15</t>
+          <t>https://www.opengovpartnership.org/the-open-gov-challenge/costa-rica-artificial-intelligence-alerts-citizen-control-public-infrastructure/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>CU</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Dudoso</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Dentro de un proceso participativo formal y de gran escala (consulta popular legislativa nacional sobre el Código de las Familias, feb-abr 2022, ~6,5 millones de participantes y cientos de miles de propuestas) se usó IA sobre el CONTENIDO de los aportes ciudadanos: el sistema GEMA-CEN (basado en GEM</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/latin-america/comunicados-de-prensa/sara-la-nueva-herramienta-de-inteligencia-artificial-para-combatir-la-violencia-de-genero-en-centroamerica-0</t>
+          <t>http://www.datys.cu/spa/site/product/15</t>
         </is>
       </c>
     </row>
@@ -7455,61 +7221,61 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>TAÍNA: Gobierno Inteligente</t>
+          <t>CiudadanIA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>Solo atención/servicio; la 'participación' es co-diseñar la IA aportando datos, no consulta pública. Sin módulo de participación (verificado). Decisión del equipo.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.diariolibre.com/actualidad/nacional/2023/10/11/gobierno-presenta-estrategia-de-inteligencia-artificial/2489157</t>
+          <t>https://www.genia.ai/paises-miembros</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Plataforma de modelos generativos de IA de SEGEPLAN + Red Ciudadana (Guatemala)</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>El criterio ELEGIBLE exige que la IA generativa se use para SISTEMATIZAR/CLASIFICAR/RESUMIR el CONTENIDO de los aportes de los diagnosticos participativos (Consejos de Desarrollo COCODES/COMUDES) en los Planes de Desarrollo Municipal (PDM). Toda la evidencia primaria y secundaria (nota SEGEPLAN ?p=1</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://portal.segeplan.gob.gt/segeplan/?p=14176</t>
+          <t>https://www.undp.org/es/latin-america/comunicados-de-prensa/sara-la-nueva-herramienta-de-inteligencia-artificial-para-combatir-la-violencia-de-genero-en-centroamerica-0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LATAM</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>ANTAI Smart CID (Autoridad Nacional de Transparencia y Acceso a la Información + OS City)</t>
+          <t>TAÍNA: Gobierno Inteligente</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -7519,39 +7285,39 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Atención ciudadana</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.caf.com/es/actualidad/noticias/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
+          <t>https://www.diariolibre.com/actualidad/nacional/2023/10/11/gobierno-presenta-estrategia-de-inteligencia-artificial/2489157</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LATAM</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Botivist</t>
+          <t>Plataforma de modelos generativos de IA de SEGEPLAN + Red Ciudadana (Guatemala)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Descubrimiento</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>No tiene foco en un país específico</t>
+          <t>El criterio ELEGIBLE exige que la IA generativa se use para SISTEMATIZAR/CLASIFICAR/RESUMIR el CONTENIDO de los aportes de los diagnosticos participativos (Consejos de Desarrollo COCODES/COMUDES) en los Planes de Desarrollo Municipal (PDM). Toda la evidencia primaria y secundaria (nota SEGEPLAN ?p=1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/research/publication/botivist-calling-volunteers-to-action-using-online-bots/</t>
+          <t>https://portal.segeplan.gob.gt/segeplan/?p=14176</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7329,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Chatbot DCI (Denuncia Ciudadana Idónea)</t>
+          <t>ANTAI Smart CID (Autoridad Nacional de Transparencia y Acceso a la Información + OS City)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -7573,12 +7339,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci</t>
+          <t>https://www.caf.com/es/actualidad/noticias/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7356,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Citibeats: Covid-19 (“Percepciones ciudadanas COVID-19”)</t>
+          <t>Botivist</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -7600,12 +7366,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Análisis de redes sociales, no es participación</t>
+          <t>No tiene foco en un país específico</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://forbescentroamerica.com/2021/04/28/civiclytics-el-big-data-apoya-la-recuperacion-economica</t>
+          <t>https://www.microsoft.com/en-us/research/publication/botivist-calling-volunteers-to-action-using-online-bots/</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7383,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Ushahidi "AI for Good"</t>
+          <t>Chatbot DCI (Denuncia Ciudadana Idónea)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -7627,24 +7393,24 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>No se evidencia el uso de IA en los proyectos de participación listados para Latam</t>
+          <t>No evidencia de uso de IA</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.ushahidi.com/</t>
+          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>LATAM</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>AMIMgo</t>
+          <t>Citibeats: Covid-19 (“Percepciones ciudadanas COVID-19”)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -7654,24 +7420,24 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Análisis de redes sociales, no es participación</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://amim.mx/noticias/detalle/estrena-amim-chatbot-para-la-atencion-ciudadana</t>
+          <t>https://forbescentroamerica.com/2021/04/28/civiclytics-el-big-data-apoya-la-recuperacion-economica</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>LATAM</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>ATIC</t>
+          <t>Ushahidi "AI for Good"</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -7681,12 +7447,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No se evidencia el uso de IA en los proyectos de participación listados para Latam</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://oem.com.mx/la-prensa/metropoli/info-cdmx-implementa-atic-una-herramienta-con-ia-que-facilita-el-acceso-a-la-informacion-13081722</t>
+          <t>https://www.ushahidi.com/</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7464,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>ChatBot “Claudia"</t>
+          <t>AMIMgo</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -7708,12 +7474,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>No es participación</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://mexicocomovamos.mx/animal-politico/2024/08/chatbot-claudia-una-herramienta-de-participacion-ciudadana/</t>
+          <t>https://amim.mx/noticias/detalle/estrena-amim-chatbot-para-la-atencion-ciudadana</t>
         </is>
       </c>
     </row>
@@ -7725,7 +7491,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Chatbot "Inés"</t>
+          <t>ATIC</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -7735,12 +7501,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>No es participación, es informativo</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://centralelectoral.ine.mx/2024/04/17/nueva-version-del-chatbot-del-ine-en-whatsapp-permitira-verificar-informacion-sobre-elecciones-2024/</t>
+          <t>https://oem.com.mx/la-prensa/metropoli/info-cdmx-implementa-atic-una-herramienta-con-ia-que-facilita-el-acceso-a-la-informacion-13081722</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7518,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Sam Petrino</t>
+          <t>ChatBot “Claudia"</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -7762,12 +7528,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No es participación</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.civica.digital/historias/chatbot-sam-petrino</t>
+          <t>https://mexicocomovamos.mx/animal-politico/2024/08/chatbot-claudia-una-herramienta-de-participacion-ciudadana/</t>
         </is>
       </c>
     </row>
@@ -7779,7 +7545,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Victoria</t>
+          <t>Chatbot "Inés"</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -7789,12 +7555,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No es participación, es informativo</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Informe de Gobierno</t>
+          <t>https://centralelectoral.ine.mx/2024/04/17/nueva-version-del-chatbot-del-ine-en-whatsapp-permitira-verificar-informacion-sobre-elecciones-2024/</t>
         </is>
       </c>
     </row>
@@ -7806,7 +7572,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>INAOE (Conacyt) – Laboratorio de Tecnologías del Lenguaje</t>
+          <t>Chatbot Sam Petrino</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -7816,12 +7582,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=para%20identificar%20posibles%20trastornos,de%20las%20dificultades%20de%20%C3%ADndole</t>
+          <t>https://www.civica.digital/historias/chatbot-sam-petrino</t>
         </is>
       </c>
     </row>
@@ -7833,7 +7599,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Movimex</t>
+          <t>Chatbot Victoria</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -7843,12 +7609,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://animalpolitico.com/estados/chatbot-movimex-tramites-denuncias-edomex</t>
+          <t>Informe de Gobierno</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7626,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Sistema *0311 Locatel</t>
+          <t>INAOE (Conacyt) – Laboratorio de Tecnologías del Lenguaje</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -7870,12 +7636,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://research.latinxinai.org/papers/naacl/2022/pdf/paper_01.pdf</t>
+          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=para%20identificar%20posibles%20trastornos,de%20las%20dificultades%20de%20%C3%ADndole</t>
         </is>
       </c>
     </row>
@@ -7887,22 +7653,22 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Sufragio seguro</t>
+          <t>Movimex</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Baseline 2025</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>EXCLUSIÓN FIRME (recodificación 2026): Exclusión FIRME (recodificación 2026): integridad/proceso electoral, no contenido</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://osf.io/cu6w3</t>
+          <t>https://animalpolitico.com/estados/chatbot-movimex-tramites-denuncias-edomex</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7680,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Violetta</t>
+          <t>Sistema *0311 Locatel</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -7924,51 +7690,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Atención ciudadana</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://holasoyvioletta.com/acerca-de/</t>
+          <t>https://research.latinxinai.org/papers/naacl/2022/pdf/paper_01.pdf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Dr. ROSA y Dr. NICO</t>
+          <t>Sufragio seguro</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Baseline 2025</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>EXCLUSIÓN FIRME (recodificación 2026): Exclusión FIRME (recodificación 2026): integridad/proceso electoral, no contenido</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=virtual%2Fchatbot%20que%20funciona%20por%20WhatsApp,que%20realice%20una%20observaci%C3%B3n%20f%C3%ADsica</t>
+          <t>https://osf.io/cu6w3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>JNE WhatsApp Chatbot</t>
+          <t>Violetta</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -7978,132 +7744,132 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://portal.jne.gob.pe/Portal/Pagina/Nota/12783</t>
+          <t>https://holasoyvioletta.com/acerca-de/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Sistema de cómputo con IA para las Elecciones Generales 2026</t>
+          <t>Dr. ROSA y Dr. NICO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Conteo electoral (OCR de actas): votación política, no participación.</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://cheleloyborolas.com/index.php?Itemid=103&amp;catid=10&amp;id=72545%3Ajefe-de-la-onpe-presenta-avances-en-la-organizacion-de-las-elecciones-generales-2026&amp;option=com_content&amp;view=article</t>
+          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=virtual%2Fchatbot%20que%20funciona%20por%20WhatsApp,que%20realice%20una%20observaci%C3%B3n%20f%C3%ADsica</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>PY</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Consultas ciudadanas sobre IA en Paraguay - PNUD Accelerator Lab (AccLab) + Columbia SIPA + MITIC / insumo del diagnóstico AILA (Atlas de IA)</t>
+          <t>JNE WhatsApp Chatbot</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>El criterio ELEGIBLE exige que dentro de un proceso participativo convocado se use IA (NLP/ML/clustering/sentimiento) SOBRE EL CONTENIDO de los aportes. Aquí ocurre lo contrario: (1) la IA es el TEMA de la consulta (se pregunta a la ciudadania por su percepcion de la IA), y (2) el ANÁLISIS de los ap</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/paraguay/blog/consultas-ciudadanas-sobre-ia-en-paraguay-visiones-diversas-entre-el-campo-y-la-ciudad</t>
+          <t>https://portal.jne.gob.pe/Portal/Pagina/Nota/12783</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>PY</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>ParaEmpleo</t>
+          <t>Sistema de cómputo con IA para las Elecciones Generales 2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Conteo electoral (OCR de actas): votación política, no participación.</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/paraempleo</t>
+          <t>https://cheleloyborolas.com/index.php?Itemid=103&amp;catid=10&amp;id=72545%3Ajefe-de-la-onpe-presenta-avances-en-la-organizacion-de-las-elecciones-generales-2026&amp;option=com_content&amp;view=article</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>UY</t>
+          <t>PY</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Chatbot (Asistente virtual entrenado con IA)</t>
+          <t>Consultas ciudadanas sobre IA en Paraguay - PNUD Accelerator Lab (AccLab) + Columbia SIPA + MITIC / insumo del diagnóstico AILA (Atlas de IA)</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Descubrimiento</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>El criterio ELEGIBLE exige que dentro de un proceso participativo convocado se use IA (NLP/ML/clustering/sentimiento) SOBRE EL CONTENIDO de los aportes. Aquí ocurre lo contrario: (1) la IA es el TEMA de la consulta (se pregunta a la ciudadania por su percepcion de la IA), y (2) el ANÁLISIS de los ap</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=El%20chatbot%20virtual%20creado%20por,desarrollo%20de%20soluciones%20de%20IA</t>
+          <t>https://www.undp.org/es/paraguay/blog/consultas-ciudadanas-sobre-ia-en-paraguay-visiones-diversas-entre-el-campo-y-la-ciudad</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>UY</t>
+          <t>PY</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Consulta Pública de la Estrategia Nacional de Inteligencia Artificial (IA) de Uruguay 2024–2030,</t>
+          <t>ParaEmpleo</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -8113,12 +7879,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030?utm_source=chatgpt.com</t>
+          <t>https://fairlac.iadb.org/paraempleo</t>
         </is>
       </c>
     </row>
@@ -8130,54 +7896,108 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Consulta Pública y Participación Multiactores: "Niñas, niños, adolescentes, entornos digitales e inteligencia artificial" (Uruguay, 2026)</t>
+          <t>Chatbot (Asistente virtual entrenado con IA)</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>NO (lean firme). (1) TEMPORAL: la consulta está ABIERTA hasta el 10/09/2026 y la fase de sistematización/análisis/validación (Fase 3) recién ocurre entre el 10/09 y el 10/10/2026, con informe final el 30/11/2026. A la fecha de evaluación (2026-07-01) la fase de análisis NO se ha ejecutado, por lo qu</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.gub.uy/ministerio-educacion-cultura/comunicacion/noticias/lanzamiento-consulta-publica-sobre-inteligencia-artificial-entornos-digitales</t>
+          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=El%20chatbot%20virtual%20creado%20por,desarrollo%20de%20soluciones%20de%20IA</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>UY</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Consulta Pública de la Estrategia Nacional de Inteligencia Artificial (IA) de Uruguay 2024–2030,</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Excluido 2025</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>No evidencia de uso de IA</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030?utm_source=chatgpt.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>UY</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Consulta Pública y Participación Multiactores: "Niñas, niños, adolescentes, entornos digitales e inteligencia artificial" (Uruguay, 2026)</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Descubrimiento</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>NO (lean firme). (1) TEMPORAL: la consulta está ABIERTA hasta el 10/09/2026 y la fase de sistematización/análisis/validación (Fase 3) recién ocurre entre el 10/09 y el 10/10/2026, con informe final el 30/11/2026. A la fecha de evaluación (2026-07-01) la fase de análisis NO se ha ejecutado, por lo qu</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gub.uy/ministerio-educacion-cultura/comunicacion/noticias/lanzamiento-consulta-publica-sobre-inteligencia-artificial-entornos-digitales</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
           <t>VE</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Plan de la Patria 7 Transformaciones (7T) - IA y Big Data en la sistematización de propuestas de la Consulta Popular</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Dudoso</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>NO (resuelto en 2ª pasada, antes DUDA). Hay un proceso participativo claro (consulta/debate nacional para construir el Plan de la Patria 7T, con +63.000 asambleas, 3,4 M de participantes y 34.491 propuestas) cuyo CONTENIDO sí fue recolectado, cargado, sistematizado y agrupado. Pero la 2ª pasada CONF</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>http://www.correodelorinoco.gob.ve/venezuela-impulsa-el-debate-sobre-inteligencia-artificial-bajo-principios-de-soberania-y-etica/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E68"/>
+  <autoFilter ref="A1:E70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8188,7 +8008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9768,7 +9588,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>DNP - Diálogos Regionales Vinculantes (PND 2022-2026)</t>
+          <t>ECHO – HáblameD Medellín</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -9778,54 +9598,47 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Documentos oficiales del Departamento Nacional de Planeación (DNP - Departamento Nacional de Planeación) de Colombia sobre los Diálogos Regionales Vinculantes para el Plan Nacional de Desarrollo 2022-2026.</t>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>En los 51 Diálogos Regionales Vinculantes, los colombianos expresaron sus necesidades y propuestas en 2.115 mesas de diálogo entre transformacionales y poblacionales, y se entregaron más de 89.000 propuestas que fueron claves para la definición de los pilares y la construcción del Plan Nacional de Desarrollo 2022-2026.</t>
+          <t>Governanza Colaborativa</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>El resultado de esta categorización lo define la lectura de las propuestas y su recurrencia en cada DRV para el análisis cualitativo correspondiente, que determinó, por frecuencia, los cuatro aspectos en los que los participantes enfocan el desarrollo de su territorio. En el segundo capítulo se organizó la información correspondiente al análisis cuantitativo que desarrolló la Unidad de Científicos de Datos del DNP.</t>
+          <t>Implementación, Análisis</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Results were officially published on February 6, 2023. The exercise lasted three months [...] The dialogues officially began in mid-September 2022 in Turbaco (Bolívar).</t>
+          <t>reconfirmado web (institucional): Reconfirmado: la IA del UNFPA clasifica por ODS las conversaciones ciudadanas captadas en campo (5.000+ personas, 16 comunas).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>More than 250,000 Colombians participated in 51 Regional Binding Dialogues [...] 89,788 proposals were collected that inspired the construction of the five major transformations of the National Development Plan 2022-2026.</t>
+          <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>The exercise lasted three months with dialogue and listening sessions convened by President Petro [...] The National Planning Department (DNP) presented official results of 51 Regional Binding Dialogues.</t>
+          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Crítica Dejusticia (2ª pasada): 'During the dialogues, there were no officials with computers systematizing information or recording the multiple proposals from participants. Instead, proposals were kept through voice notes on the cellphones of the officials who accompanied the encounters.' / CCONG-Dejusticia: 'the process with which all consolidated demands were systematized was never clearly identified.'</t>
+          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Se analizaron las propuestas y fueron agrupadas en categorías de intervención territorial (17-19 / 18 categorías) articuladas con las cinco transformaciones del PND. El resultado lo define 'la lectura de las propuestas y su recurrencia... que determinó, por frecuencia' los aspectos prioritarios. Presentación mediante nubes de palabras y gráficos de barras (conteo de temas por sector) y un 'visor'. GitHub ucd-dnp (7 repos): única librería NLP/minería de texto es 'ConTexto' ('Librería en Python para minería de texto y NLP'), pero NINGÚN repositorio ni fuente la vincula al procesamiento de las propuestas de los DRV.</t>
+          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/ucd-dnp
-https://colaboracion.dnp.gov.co/CDT/PublishingImages/dialogos_regionales/Analisis-cualitativos/DNP_DRV15Colombianos-en-el-Exterior.pdf
-https://www.dejusticia.org/column/la-demagogia-de-los-dialogos-vinculantes/
-https://www.funcionpublica.gov.co/documents/d/guest/la_rendicion_de_cuentas_y_el_control_social_marco_dialogos_regionales_vinculantes_-drv-
-https://sispt.dnp.gov.co/drv/default-drv
-https://bdigital.uexternado.edu.co/entities/publication/6ff4f32f-4e7a-465d-af92-d1c4f67ae153
-https://ideaspaz.org/publicaciones/investigaciones-analisis/2023-03/dialogo-en-el-gobierno-de-gustavo-petro-que-nos-dejan-los-dialogos-regionales-vinculantes-en-la-planeacion-del-desarrollo
-https://www.dnp.gov.co/Prensa_/Noticias/Paginas/dnp-publica-resultados-de-los-dialogos-regionales-vinculantes.aspx</t>
+          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
         </is>
       </c>
     </row>
@@ -9837,57 +9650,54 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>ECHO – HáblameD Medellín</t>
+          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>DUDA(lean SI)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+          <t>la herramienta de un resguardo indígena (Zenú, Bajo Sinú, Colombia) para llegar al Congreso (La Silla Vacía)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Governanza Colaborativa</t>
+          <t>a platform for young people in the Zenú community to decide, through digital voting, how they wanted to allocate local budgets</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Implementación, Análisis</t>
+          <t>The AI summarizes proposals, organizes consensus, and facilitates collective decision-making</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>reconfirmado web (institucional): Reconfirmado: la IA del UNFPA clasifica por ODS las conversaciones ciudadanas captadas en campo (5.000+ personas, 16 comunas).</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
-        </is>
-      </c>
+          <t>More than 10,000 users participate in the chatbot at gaitanaia.org, whose discussions feed the community's positions and proposals</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+          <t>Gaitana IA is a tool created by Carlos Redondo Rincón ... a platform for young people in the Zenú community</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+          <t>Gaitana is built on the DeepSeek large language model, adapted to the Zenú worldview ... summarizes proposals, organizes consensus</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+          <t>artificial intelligence organizes opinions, processes trends and builds consensuses that, if approved, would become legislative initiatives (KienyKe)</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+          <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/
+https://www.kienyke.com/</t>
         </is>
       </c>
     </row>
@@ -9899,66 +9709,70 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
+          <t>Tenemos que hablar de Colombia</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>DUDA(lean SI)</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>la herramienta de un resguardo indígena (Zenú, Bajo Sinú, Colombia) para llegar al Congreso (La Silla Vacía)</t>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>a platform for young people in the Zenú community to decide, through digital voting, how they wanted to allocate local budgets</t>
+          <t>Governanza Colaborativa</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>The AI summarizes proposals, organizes consensus, and facilitates collective decision-making</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>More than 10,000 users participate in the chatbot at gaitanaia.org, whose discussions feed the community's positions and proposals</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr"/>
+          <t>BBDD 2025: Cerrado</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Gaitana IA is a tool created by Carlos Redondo Rincón ... a platform for young people in the Zenú community</t>
+          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Gaitana is built on the DeepSeek large language model, adapted to the Zenú worldview ... summarizes proposals, organizes consensus</t>
+          <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>artificial intelligence organizes opinions, processes trends and builds consensuses that, if approved, would become legislative initiatives (KienyKe)</t>
+          <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/
-https://www.kienyke.com/</t>
+          <t>https://tenemosquehablarcolombia.co/
+https://tenemosquehablarcolombia.co/resultados/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Tenemos que hablar de Colombia</t>
+          <t>U-Report Costa Rica – chatbot juvenil</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -9973,7 +9787,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Governanza Colaborativa</t>
+          <t>Participación Digital</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -9983,45 +9797,45 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>BBDD 2025: Cerrado</t>
+          <t>reconfirmado web (institucional): Reconfirmado 2024-2025: consulta juvenil de UNICEF con 8.404 participantes; resultados analizados para incidir en política pública.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
+          <t>Continuidad (BBDD 2025): Plataforma</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
+          <t>Unicef</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
+          <t>La inteligencia artificial de U-Report analiza miles de opiniones enviadas por texto para transformarlas en datos útiles. Utilizando Procesamiento de Lenguaje Natural (PLN), la IA lee y clasifica automáticamente los mensajes de los jóvenes para identificar los temas, tendencias y sentimientos más importantes, convirtiendo sus voces en evidencia clara para la toma de decisiones.</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
+          <t>La inteligencia artificial de U-Report analiza miles de opiniones enviadas por texto para transformarlas en datos útiles. Utilizando Procesamiento de Lenguaje Natural (PLN), la IA lee y clasifica automáticamente los mensajes de los jóvenes para identificar los temas, tendencias y sentimientos más importantes, convirtiendo sus voces en evidencia clara para la toma de decisiones.</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://tenemosquehablarcolombia.co/
-https://tenemosquehablarcolombia.co/resultados/</t>
+          <t>https://costarica.ureport.in/
+https://www.unicef.org/costarica/comunicados-prensa/plataforma-mundial-u-report-llega-costa-rica</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>U-Report Costa Rica – chatbot juvenil</t>
+          <t xml:space="preserve">PAGA IA </t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -10036,17 +9850,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital</t>
+          <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>reconfirmado web (institucional): Reconfirmado 2024-2025: consulta juvenil de UNICEF con 8.404 participantes; resultados analizados para incidir en política pública.</t>
+          <t>reconfirmado web (institucional): Reconfirmado: integrada al Tercer Plan de Acción de Estado Abierto 2025-2027; analiza las propuestas ciudadanas y sugiere actividades.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -10056,148 +9870,22 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Unicef</t>
+          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>La inteligencia artificial de U-Report analiza miles de opiniones enviadas por texto para transformarlas en datos útiles. Utilizando Procesamiento de Lenguaje Natural (PLN), la IA lee y clasifica automáticamente los mensajes de los jóvenes para identificar los temas, tendencias y sentimientos más importantes, convirtiendo sus voces en evidencia clara para la toma de decisiones.</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>La inteligencia artificial de U-Report analiza miles de opiniones enviadas por texto para transformarlas en datos útiles. Utilizando Procesamiento de Lenguaje Natural (PLN), la IA lee y clasifica automáticamente los mensajes de los jóvenes para identificar los temas, tendencias y sentimientos más importantes, convirtiendo sus voces en evidencia clara para la toma de decisiones.</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>https://costarica.ureport.in/
-https://www.unicef.org/costarica/comunicados-prensa/plataforma-mundial-u-report-llega-costa-rica</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>CiudadanIA</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>SI*</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Governanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>reconfirmado web (institucional): Reverificación: actores activos (OGTIC, GENIA, MINPRE) en agenda de IA, sin evidencia nueva específica de la plataforma 2025-2026. Revisar en Fase 2.</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Plataforma</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>GENIA Latinoamérica, en colaboración con la Universidad del Caribe (UNICARIBE), el Ministerio de la Presidencia (MINPRE) y la Oficina Gubernamental de Tecnologías de la Información y Comunicación (OGTIC)</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recopilación y análisis de datos ciudadanos para entrenar algoritmos que mejoren la prestación de servicios públicos, ofreciendo recomendaciones personalizadas y fomentando un gobierno proactivo. </t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recopilación y análisis de datos ciudadanos para entrenar algoritmos que mejoren la prestación de servicios públicos, ofreciendo recomendaciones personalizadas y fomentando un gobierno proactivo. </t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.genia.ai/paises-miembros
-https://presidencia.gob.do/seccion/inteligencia-artificial</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PAGA IA </t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Referendos e Iniciativas Populares</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>reconfirmado web (institucional): Reconfirmado: integrada al Tercer Plan de Acción de Estado Abierto 2025-2027; analiza las propuestas ciudadanas y sugiere actividades.</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Plataforma</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto
 </t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto
 </t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>https://www.gobiernoabierto.ec/boletin-014-2023/
 https://ia.gobiernoabierto.ec/
@@ -10205,63 +9893,63 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Guatemala Joven Conversa </t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado: diálogos digitales con IA (DPPA ONU + Fundación Esquipulas); 300+ jóvenes; la IA permite intercambios anónimos y votación de aportes para identifi</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
 https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/?utm_source=chatgpt.com
@@ -10269,125 +9957,125 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>HN</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RedPública + iVerify </t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reverificación: plataforma de propuestas ciudadanas con módulo de análisis de tendencias; evidencia de IA central débil, revisar en Fase 2.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Guanajuato hará historia con el primer Programa de Gobierno realizado con IA</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Para integrar la participación ciudadana en este Programa de Gobierno, se realizaron cuatro talleres cubriendo las regiones noreste, norte, centro y sur, con representación de los 46 municipios de Guanajuato.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>El Programa de Gobierno de Guanajuato 2024-2030 es la guía que orienta las acciones del Gobierno de la Gente para lograr un Guanajuato sostenible, equitativo y transparente.</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Su diseño incorporó el uso de inteligencia artificial para integrar más de 26 mil voces de distintas regiones y sectores</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>El Programa de Gobierno 2024-2030 hizo historia al ser el primero en realizarse con ayuda de la Inteligencia Artificial (IA), según anunció la Gobernadora Libia Dennise García Muñoz Ledo en el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG).</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía.</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>https://guanajuatointeligente.com/como-hicimos-el-programa/
 https://guanajuatointeligente.com/
@@ -10400,55 +10088,55 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Jalisco - Consulta ¡Armemos un Plan! (Plan Estatal de Desarrollo y Gobernanza 2024-2030)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>DUDA(lean NO)</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>'Armemos un Plan' se llevó a cabo de manera abierta e incluyente del 20 de febrero al 17 de abril por el Gobierno de Jalisco, a través de la Secretaría de Planeación y Participación Ciudadana; la consulta digital recibió 15,899 propuestas ciudadanas.</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Jalisco concluyó la primera etapa de la consulta ciudadana 'Armemos un Plan' con una cifra inédita de 675,484 participaciones, base para desarrollar el Plan Estatal de Desarrollo y Gobernanza 2024-2030.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Se realizaron 12 foros regionales y la instalación de un Consejo de Planeación Participativa en cada región de Jalisco; se llevaron a cabo 168 mesas regionales, 47 sectoriales y 9 grandes foros temáticos... donde se identificaron y discutieron 1,349 problemáticas planteadas por la ciudadanía. (Metodología participativa/estadística; sin componente de IA.)</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Gobierno de Jalisco, a través de la Secretaría de Planeación y Participación Ciudadana (coordinación de Cynthia Cantero Pacheco).</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Las propuestas se construyeron a partir de las opiniones y expresiones de la ciudadanía durante la consulta, agrupando ideas similares y redactándolas de forma clara y ordenada, respetando siempre la intención original de quienes participaron. (Descripción metodológica oficial de armemosunplan.mx/propuestas-ciudadanas, recuperada vía WebSearch que indexa la página; no menciona IA/NLP/algoritmos: describe agrupación editorial manual.)</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>GAP: ninguna fuente atribuye a IA/NLP/minería de texto/clustering el análisis o la agrupación de las 15,899 propuestas; la única descripción del método es 'agrupando ideas similares' de forma manual/editorial.</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>https://armemosunplan.mx/propuestas-ciudadanas/
 https://armemosunplan.mx/wp-content/uploads/2025/10/Armemos-un-Plan-Informe-de-Consulta-COLOR-NNA-v2.4.pdf
@@ -10461,121 +10149,121 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Presupuesto CRECES</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Presupuestos Participativos</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Activo</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Ayundamiento de Hermosilla</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>https://presupuestocreces.hermosillo.gob.mx/</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>La Fundación Panamá Participa lanzó Mansa Idea (www.mansaidea.com), una plataforma basada en inteligencia artificial que recoge miles de propuestas ciudadanas... iniciativa de alcance nacional que se nutre de ideas y propuestas que miles de panameños hicieron durante el desarrollo del Pacto del Bicentenario. (Panamá; fuentes panama24horas.com.pa y laestrella.com.pa)</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea, resultado del Pacto del Bicentenario, ofrece acceso fácil y transparente a más de 175 mil ideas y propuestas generadas por ciudadanos de todo el país. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales. (la IA agrega/organiza/sintetiza el contenido de las propuestas por tema y territorio = Análisis + Traducción Política; el método técnico exacto no se detalla en las fuentes).</t>
         </is>
       </c>
-      <c r="G38" s="6" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>La plataforma fue lanzada el 1 de abril de 2024... constituye una herramienta valiosa de participación ciudadana muy relevante para ciudadanos, candidatos a cargos de elección popular y medios durante la campaña electoral y luego como recurso para el monitoreo del mandato ciudadano. (un despliegue concreto de la plataforma, 2024; sin evidencia de ediciones recurrentes).</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>La Fundación Panamá Participa lanzó Mansa Idea... iniciativa liderada por Paulina Franceschi a través de la Fundación Panamá Participa (sociedad civil). El proceso participativo de origen: 'El 26 de noviembre de 2020, el presidente Laurentino Cortizo Cohen lanzó la iniciativa denominada Pacto del Bicentenario Cerrando Brechas' (gobierno nacional / Concertación Nacional).</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. (la IA procesa el contenido de las propuestas del proceso participativo).</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía. (agregación/síntesis de los aportes ciudadanos = rol sobre el contenido).</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>https://www.panama24horas.com.pa/panama/fundacion-panama-participa-lanza-plataforma-de-propuestas-ciudadanas-mansa-idea/
 https://www.laestrella.com.pa/panama/politica/mansa-idea-una-herramienta-digital-con-propuestas-para-candidatos-YD6746221
@@ -10586,63 +10274,63 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (prensa): VERIFICADO (fuente primaria): el CNE usó IBM Watson Discovery + Studio (ML/NLP) sobre 87.991 documentos de aportes ciudadanos de 847 eventos y 49 espacios de di</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>Consejo Nacional de Educación del Perú</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>https://www.latinno.net/en/case/17232/
 https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional?utm_source=chatgpt.com
@@ -10652,59 +10340,59 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Project: National Digital Transformation Strategy | Ministry of Digital Transformation, Trinidad and Tobago (engage.gov.tt/projects/national-digital-transformation-strategy). Ruta interna confirmatoria: engage.gov.tt/projects/e-democracy-govocal-internal (la instancia corre sobre Go Vocal). En 2026: 'Projects | Ministry of Public Administration and Artificial Intelligence' (engage.gov.tt/projects).</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>EngageTT es una plataforma en linea (engage.gov.tt) donde ciudadanos, empresas y partes interesadas pueden recibir actualizaciones en tiempo real sobre iniciativas de transformacion digital y ofrecer retroalimentacion via encuestas y sondeos (polls); el Ministro anima a todos a participar y enviar ideas y comentarios sobre el NDTS, que se disena para evolucionar mediante el compromiso y la colaboracion continuos. Incluye un 'Open Forum' (engage.gov.tt/ideas/open-forum) y 'Input: Submitting Proposals' (engage.gov.tt/ideas/submitting-proposals).</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>The National Strategy for a Digital TT is finalized, and while the Ministry of Digital Transformation is no longer seeking input, they welcome feedback or comments through the citizen engagement digital platform Engage TT. (engage.gov.tt sigue operativo en 2026 bajo MPAAI).</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>The Ministry of Digital Transformation (MDT) officially presented the National Digital Transformation Strategy (NDTS) 2024-2027... launched during a NDTS Symposium in collaboration with the Inter-American Development Bank (IDB) on Wednesday, February 12th 2025. A major highlight... was the introduction of two new digital tools (EngageTT y AskNDTS). (Lanzamiento/anuncio unico en feb-2025; plataforma de uso continuo pero sin &gt;=2 ediciones de proceso participativo documentadas).</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>The Ministry of Digital Transformation (MDT) officially presented the National Digital Transformation Strategy (NDTS) 2024-2027... and introduced the EngageTT website - an online platform where citizens, businesses, and stakeholders can get real-time updates on digital transformation initiatives, and offer feedback via surveys and polls. (Convocante: gobierno nacional / Ministry of Digital Transformation, hoy MPAAI).</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Go Vocal Support Base (AI Analysis): 'Access to this feature depends on your plan. Advanced Sensemaking with auto-insights is available in the Premium plan.' -&gt; la IA/NLP de Go Vocal NO es automatica, depende del plan; y para EngageTT solo se documenta 'feedback via surveys and polls'/Open Forum/ideas, SIN mencion de analisis automatico por IA de los aportes. No se halla evidencia de activacion del NLP sobre el contenido en la instancia TT. 3a PASADA (refuerzo): Oxford Insights, 'The country's AI utilisation for citizens is concentrated in a robust Chatbot programme' (mas 'deployment of large language models for internal development purposes') -&gt; la IA ciudadana de TT es el chatbot, NO el analisis de aportes.</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>Sin evidencia de IA aplicada al contenido de los aportes en engage.gov.tt. La unica IA confirmada de cara al ciudadano (AskNDTS/ANANSI) es chatbot de FAQ, excluido del criterio. En 3a pasada, el material de MPAAI 2026 enmarca la IA en el asistente ANANSI y en encuestas de AI-readiness (resultados 'consolidated and reviewed' en talleres), sin mencion de analisis por IA de los aportes del NDTS ni de Go Vocal Sensemaking.</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>https://support.govocal.com/en/articles/8316692-ai-analysis
 https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool
@@ -10726,59 +10414,59 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>UY</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Polis has been used to facilitate discussion and build consensus ... in Uruguay on a national referendum (OCDE 2025, 'Governing with AI')</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists — ran Polis alongside the referendum</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>The algorithm maps participants' responses and clusters opinions, facilitating the identification of positions that are supported by the majority of participants (OCDE 2025)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>16,499 people cast more than 295,000 votes ... The referendum was lost by less than 1%</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>ran Polis alongside the referendum to look for something deeper than "yes or no"</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>Polis revealed that even where public safety divided people, surprising points of consensus broke through on other issues — bridges between groups</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/
 https://www.oecd.org/en/publications/governing-with-artificial-intelligence_795de142-en.html</t>
@@ -10786,7 +10474,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L41"/>
+  <autoFilter ref="A1:L39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10820,7 +10508,7 @@
       </c>
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>Planilla con 6 pestañas (criterio corregido). 40 casos entran/dudosos · 67 excluidos · 107 en total. Tras dedup e-Cidadania: 39 iniciativas.</t>
+          <t>Planilla con 6 pestañas (criterio corregido). 38 casos entran/dudosos · 69 excluidos · 107 en total. Tras dedup e-Cidadania: 37 iniciativas.</t>
         </is>
       </c>
     </row>

--- a/data/gates/planilla_ILIA2026_SIMPLE.xlsx
+++ b/data/gates/planilla_ILIA2026_SIMPLE.xlsx
@@ -170,16 +170,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -189,6 +186,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1083,7 +1083,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>➜ REVISAR — ¿es participación?</t>
+          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
@@ -2354,7 +2354,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
@@ -2472,7 +2472,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
@@ -2592,7 +2592,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
@@ -2710,7 +2710,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>➜ RESOLVER DUDA</t>
         </is>
@@ -2730,7 +2730,7 @@
           <t>(sin revisar)</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>DUDA(lean NO)</t>
         </is>
@@ -3171,7 +3171,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>➜ RESOLVER DUDA</t>
         </is>
@@ -3191,7 +3191,7 @@
           <t>(sin revisar)</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>DUDA(lean SI)</t>
         </is>
@@ -3287,7 +3287,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
@@ -3638,7 +3638,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>➜ RESOLVER DUDA</t>
         </is>
@@ -3658,7 +3658,7 @@
           <t>(sin revisar)</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>DUDA(lean SI)</t>
         </is>
@@ -3869,7 +3869,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>➜ DUDA (frontera) — resolver a mano</t>
         </is>
@@ -4216,7 +4216,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
@@ -4450,7 +4450,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>➜ RESOLVER DUDA</t>
         </is>
@@ -4470,7 +4470,7 @@
           <t>(sin revisar)</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>DUDA(lean NO)</t>
         </is>
@@ -4554,7 +4554,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
@@ -4900,7 +4900,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>➜ DUDA — revisar posible IA/participación</t>
         </is>
@@ -4920,7 +4920,7 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>DUDA(lean NO)</t>
         </is>
@@ -5191,7 +5191,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>A. Excluir (criterio corregido)</t>
         </is>
@@ -5228,7 +5228,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>A. Excluir (criterio corregido)</t>
         </is>
@@ -5265,7 +5265,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>A. Excluir (criterio corregido)</t>
         </is>
@@ -5302,7 +5302,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>A. Excluir (criterio corregido)</t>
         </is>
@@ -5340,7 +5340,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>A. Excluir (criterio corregido)</t>
         </is>
@@ -5378,7 +5378,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>A. Excluir (criterio corregido)</t>
         </is>
@@ -5416,7 +5416,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
@@ -5453,7 +5453,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
@@ -5491,7 +5491,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
@@ -5528,7 +5528,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
@@ -5565,7 +5565,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
@@ -5602,7 +5602,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
@@ -5639,7 +5639,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
@@ -5677,37 +5677,74 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>B. Rescatado → ENTRA</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar SI</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Colab</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Permite sugerir ideas y votar en decisiones municipales (módulos de participación) — confirmado por el equipo.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.colab.com.br/sou-cidadao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>C. DUDA — revisar (posible IA)</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Abrir URL y decidir SI/NO</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Revisar si hay/planea IA o módulo de participación</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>IA MIXTA: chatbot AskNDTS (IA) activo que ayuda a ENTENDER el NDTS (facilitación/info, no procesa aportes). El módulo Sensemaking de Go Vocal existe pero NO se confirma activado ni anunciado para TT. Ministerio ahora MPAAI (Public Admin + AI). → DUDA: ¿basta el chatbot explicador como 'IA en el proceso'? Ver mdt.gov.tt (EngageTT + AskNDTS).</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
 https://www.govocal.com/plans
@@ -5715,83 +5752,46 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>C. DUDA — revisar (posible IA)</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Abrir URL y decidir SI/NO</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>U-Report Costa Rica – chatbot juvenil</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>¿Proceso de participación o sondeo? Decidir</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Plataforma de opinión juvenil (UNICEF): ¿consulta participativa o civic tech de sondeo?</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://costarica.ureport.in/
 https://www.unicef.org/costarica/comunicados-prensa/plataforma-mundial-u-report-llega-costa-rica</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>D. Revisar ¿participación?</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>¿Mantener SI o pasar a NO?</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Colab</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Parece civic tech/atención; confirmar si es realmente participación</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>GovTech de reporte urbano + servicios (IA para gestión/servicios): ¿participación o civic tech?</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.colab.com.br/sou-cidadao/</t>
-        </is>
-      </c>
-    </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>E. Resolver DUDA de campo</t>
         </is>
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>E. Resolver DUDA de campo</t>
         </is>
@@ -5867,7 +5867,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>E. Resolver DUDA de campo</t>
         </is>
@@ -5905,7 +5905,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>E. Resolver DUDA de campo</t>
         </is>
@@ -5943,7 +5943,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>F. Posible reingreso</t>
         </is>
@@ -5981,7 +5981,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>F. Posible reingreso</t>
         </is>
@@ -8395,7 +8395,7 @@
           <t>José Carlos Vaz, from the USP Public Policy Management course / professor at the University of São Paulo's School of Arts, Sciences and Humanities (EACH) ... coordinates GETIP. (snippet; convocante = universidad USP)</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr"/>
+      <c r="J6" s="12" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>AI could help generate proposals based on knowledge databases and transform them into legally viable drafts / a IA o ajuda a escrever essa proposta. (snippet; rol sobre el contenido del aporte, pero en marco de investigación)</t>
@@ -8437,11 +8437,11 @@
           <t>OPA é o Orçamento Participativo 100% digital do Governo do Estado do Piauí... Após analisar a viabilidade das propostas, o Governo do Estado disponibilizará uma votação por meio da Colab para que qualquer cidadão acima de 16 anos com CPF possa votar no que considera mais importante para o seu município. (Colab)</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
+      <c r="F7" s="12" t="inlineStr"/>
+      <c r="G7" s="12" t="inlineStr"/>
+      <c r="H7" s="12" t="inlineStr"/>
+      <c r="I7" s="12" t="inlineStr"/>
+      <c r="J7" s="12" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Todo esse processo é realizado por meio da plataforma Colab Gov... O sistema utiliza tecnologia da AWS, referência mundial em segurança digital. (la IA/tecnología se presenta como soporte operativo, de eficiencia y de seguridad del flujo, no como análisis del contenido de las propuestas → rol de apoyo)</t>
@@ -9075,7 +9075,7 @@
           <t>The platform used an AI tool to keep time and distribute speaking rights equitably, allowing participants to form speaking queues and discuss in small groups with timed agendas. (OCDE 2025) / El Centro de Microdatos de la Universidad de Chile, usando tecnologia basada en Inteligencia Artificial (IA), selecciono esta muestra representativa.</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr"/>
+      <c r="G17" s="12" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Lxs 400: Chile Delibera... es un evento de participacion ciudadana de escala nacional realizado en Chile desde el 9 de diciembre de 2020, con su evento principal a fines de marzo de 2021. (Wikipedia ES) [Evento puntual de una edicion 2020-2021; no se hallaron ediciones posteriores recurrentes].</t>
@@ -9196,20 +9196,20 @@
           <t>La alcaldía de la comuna de Pudahuel implementó un nuevo modelo de gestión presupuestaria deliberativa y vinculante ... presupuesto municipal 2023 ... más de 1.200 participantes y sobre 150 iniciativas de proyectos</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
           <t>plataforma de participación activa (participa.mpudahuel.cl)</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr"/>
+      <c r="H19" s="12" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
           <t>La alcaldía de la comuna de Pudahuel</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="J19" s="12" t="inlineStr"/>
+      <c r="K19" s="12" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
           <t>https://participa.mpudahuel.cl/
@@ -9432,20 +9432,20 @@
           <t>Following devastating wildfires, Go Vocal fueled community-driven recovery by empowering residents to redesign public spaces (caso Viña del Mar)</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr"/>
+      <c r="F23" s="12" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Primer Presupuesto Participativo Viña del Mar 2024 (guía alojada en vinadecide.cl)</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr"/>
+      <c r="H23" s="12" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Municipalidad de Viña del Mar (Primer Presupuesto Participativo 2024)</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr"/>
-      <c r="K23" s="6" t="inlineStr"/>
+      <c r="J23" s="12" t="inlineStr"/>
+      <c r="K23" s="12" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t>https://www.govocal.com/
@@ -9548,7 +9548,7 @@
           <t>Citibeats utiliza algoritmos que combinan NLP (Procesamiento de Lenguaje Natural) y ML (Machine Learning), filtrando contenido relevante de distintas fuentes de datos abiertas (Twitter, Facebook, Instagram, foros, blogs, noticias y comentarios de video), clasificando las opiniones e información de los usuarios en categorías y extrayendo conocimiento y patrones de forma automática, en tiempo real.</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr"/>
+      <c r="G25" s="12" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>El PNUD Colombia está experimentando con Citibeats, una plataforma de inteligencia artificial (IA) ética y responsable. (proyecto descrito como experimentación/piloto del Laboratorio de Aceleración, diciembre 2021).</t>
@@ -9678,7 +9678,7 @@
           <t>More than 10,000 users participate in the chatbot at gaitanaia.org, whose discussions feed the community's positions and proposals</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr"/>
+      <c r="H27" s="12" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Gaitana IA is a tool created by Carlos Redondo Rincón ... a platform for young people in the Zenú community</t>
@@ -10104,13 +10104,13 @@
           <t>DUDA(lean NO)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr"/>
+      <c r="D34" s="12" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
           <t>'Armemos un Plan' se llevó a cabo de manera abierta e incluyente del 20 de febrero al 17 de abril por el Gobierno de Jalisco, a través de la Secretaría de Planeación y Participación Ciudadana; la consulta digital recibió 15,899 propuestas ciudadanas.</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr"/>
+      <c r="F34" s="12" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Jalisco concluyó la primera etapa de la consulta ciudadana 'Armemos un Plan' con una cifra inédita de 675,484 participaciones, base para desarrollar el Plan Estatal de Desarrollo y Gobernanza 2024-2030.</t>
@@ -10242,7 +10242,7 @@
           <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales. (la IA agrega/organiza/sintetiza el contenido de las propuestas por tema y territorio = Análisis + Traducción Política; el método técnico exacto no se detalla en las fuentes).</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr"/>
+      <c r="G36" s="12" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>La plataforma fue lanzada el 1 de abril de 2024... constituye una herramienta valiosa de participación ciudadana muy relevante para ciudadanos, candidatos a cargos de elección popular y medios durante la campaña electoral y luego como recurso para el monitoreo del mandato ciudadano. (un despliegue concreto de la plataforma, 2024; sin evidencia de ediciones recurrentes).</t>
@@ -10366,7 +10366,7 @@
           <t>EngageTT es una plataforma en linea (engage.gov.tt) donde ciudadanos, empresas y partes interesadas pueden recibir actualizaciones en tiempo real sobre iniciativas de transformacion digital y ofrecer retroalimentacion via encuestas y sondeos (polls); el Ministro anima a todos a participar y enviar ideas y comentarios sobre el NDTS, que se disena para evolucionar mediante el compromiso y la colaboracion continuos. Incluye un 'Open Forum' (engage.gov.tt/ideas/open-forum) y 'Input: Submitting Proposals' (engage.gov.tt/ideas/submitting-proposals).</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr"/>
+      <c r="F38" s="12" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>The National Strategy for a Digital TT is finalized, and while the Ministry of Digital Transformation is no longer seeking input, they welcome feedback or comments through the citizen engagement digital platform Engage TT. (engage.gov.tt sigue operativo en 2026 bajo MPAAI).</t>
@@ -10450,7 +10450,7 @@
           <t>16,499 people cast more than 295,000 votes ... The referendum was lost by less than 1%</t>
         </is>
       </c>
-      <c r="H39" s="6" t="inlineStr"/>
+      <c r="H39" s="12" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists</t>

--- a/data/gates/planilla_ILIA2026_SIMPLE.xlsx
+++ b/data/gates/planilla_ILIA2026_SIMPLE.xlsx
@@ -4900,9 +4900,9 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>➜ DUDA — revisar posible IA/participación</t>
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -5714,14 +5714,14 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>C. DUDA — revisar (posible IA)</t>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Abrir URL y decidir SI/NO</t>
+          <t>Confirmar SI</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -5736,19 +5736,18 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Revisar si hay/planea IA o módulo de participación</t>
+          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>IA MIXTA: chatbot AskNDTS (IA) activo que ayuda a ENTENDER el NDTS (facilitación/info, no procesa aportes). El módulo Sensemaking de Go Vocal existe pero NO se confirma activado ni anunciado para TT. Ministerio ahora MPAAI (Public Admin + AI). → DUDA: ¿basta el chatbot explicador como 'IA en el proceso'? Ver mdt.gov.tt (EngageTT + AskNDTS).</t>
+          <t>Caso borde: el chatbot AskNDTS (IA) informa/apoya la implementación del proceso NDTS y el módulo Go Vocal Sensemaking está planeado (existe). → ENTRA como apoyo a la implementación. Decisión del equipo.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
-https://www.govocal.com/plans
-https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool</t>
+https://www.govocal.com/plans</t>
         </is>
       </c>
     </row>

--- a/data/gates/planilla_ILIA2026_SIMPLE.xlsx
+++ b/data/gates/planilla_ILIA2026_SIMPLE.xlsx
@@ -15,10 +15,10 @@
     <sheet name="6 · Metodología (CENIA v2)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos (entran+dudosos)'!$A$1:$X$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos (entran+dudosos)'!$A$1:$X$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2 · A validar a mano'!$A$1:$G$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 · Excluidos'!$A$1:$E$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 · Evidencia y fuentes'!$A$1:$L$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 · Excluidos'!$A$1:$E$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 · Evidencia y fuentes'!$A$1:$L$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X39"/>
+  <dimension ref="A1:X38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3869,19 +3869,15 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>➜ DUDA (frontera) — resolver a mano</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>U-Report Costa Rica – chatbot juvenil</t>
+          <t xml:space="preserve">PAGA IA </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -3906,12 +3902,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital</t>
+          <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
@@ -3924,12 +3920,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>organización internacional</t>
+          <t>gobierno nacional; sociedad civil</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3939,47 +3935,52 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil; Privado</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>NLP</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>U-Report es una plataforma global de UNICEF que empodera a adolescentes y jóvenes, permitiéndoles opinar sobre temas sociales cruciales a través de canales que ya utilizan, como WhatsApp, SMS y Facebook Messenger.</t>
+          <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto. Analiza datos de planes de acción de gobierno abierto de Ecuador y otros países de Hispanoamérica para sugerir actividades e hitos relacionados con temas propuestos por los usuarios</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>Unicef</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr"/>
+          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="V29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>https://costarica.ureport.in/
-https://www.unicef.org/costarica/comunicados-prensa/plataforma-mundial-u-report-llega-costa-rica</t>
+          <t>https://www.gobiernoabierto.ec/boletin-014-2023/
+https://ia.gobiernoabierto.ec/
+https://ia.gobiernoabierto.ec/acercade</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>CR-u-report-costa-rica-chatbot-juvenil</t>
+          <t>EC-paga-ia</t>
         </is>
       </c>
     </row>
@@ -3987,12 +3988,12 @@
       <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAGA IA </t>
+          <t xml:space="preserve">Guatemala Joven Conversa </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4017,7 +4018,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Referendos e Iniciativas Populares</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4030,12 +4031,12 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional; sociedad civil</t>
+          <t>organización internacional; sociedad civil</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -4050,185 +4051,183 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil</t>
+          <t>Gobierno</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>NLP - Sentiment; NLP - Tópicos</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto. Analiza datos de planes de acción de gobierno abierto de Ecuador y otros países de Hispanoamérica para sugerir actividades e hitos relacionados con temas propuestos por los usuarios</t>
+          <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarrollo y la lucha contra la corrupción.</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
+          <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="V30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gobiernoabierto.ec/boletin-014-2023/
-https://ia.gobiernoabierto.ec/
-https://ia.gobiernoabierto.ec/acercade</t>
-        </is>
-      </c>
-      <c r="X30" s="2" t="inlineStr">
-        <is>
-          <t>EC-paga-ia</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>GT</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Guatemala Joven Conversa </t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>organización internacional; sociedad civil</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>Mixto</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>NLP - Sentiment; NLP - Tópicos</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarrollo y la lucha contra la corrupción.</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="V31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
         <is>
           <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
 https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/?utm_source=chatgpt.com
 https://dppa.un.org/en/using-power-of-ai-to-boost-youth-political-participation-guatemala</t>
         </is>
       </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>GT-guatemala-joven-conversa</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RedPública + iVerify </t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Referendos e Iniciativas Populares</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>organización internacional; universidad</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno; Academia</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>Internacional, Nacional</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>NLP - Tópicos</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias. Integra iVerify, una herramienta que utiliza aprendizaje automático para detectar y clasificar desinformación electoral antes de su publicación.</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
+        </is>
+      </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>GT-guatemala-joven-conversa</t>
+          <t>HN-redpublica-iverify</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RedPública + iVerify </t>
+          <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -4248,12 +4247,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Referendos e Iniciativas Populares</t>
+          <t>Gobernanza Colaborativa; Participación Digital</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4271,7 +4270,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>organización internacional; universidad</t>
+          <t>gobierno local</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -4286,287 +4285,287 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Gobierno; Academia</t>
+          <t>Gobierno</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Internacional, Nacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos</t>
+          <t>NLP; Otros(no especificado)</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>no-claro</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias. Integra iVerify, una herramienta que utiliza aprendizaje automático para detectar y clasificar desinformación electoral antes de su publicación.</t>
+          <t>Elaboración del Programa de Gobierno del Estado de Guanajuato 2024-2030 ('Gobierno de la Gente'), un plan de gobierno construido con participación ciudadana: se recorrió el territorio y se realizaron cuatro talleres regionales (noreste, norte, centro y sur) con representación de los 46 municipios, integrando la voz de más de 26,000 personas mediante talleres y consultas. El contenido fue validado por el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG), conformado por ciudadanía, la Gobernadora, secretarios de cada eje e IPLANEG. Se utilizaron herramientas de inteligencia artificial para procesar y organizar las miles de ideas y propuestas recibidas, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región, transformando el diálogo social en datos para la toma de decisiones que alimentaron los ejes del programa. Adicionalmente existe la asistente virtual 'Esperanza' para consultar el programa ya publicado.</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
+          <t>Gobierno del Estado de Guanajuato — Instituto de Planeación, Estadística y Geografía del Estado de Guanajuato (IPLANEG), con validación del COPLADEG. Titular: Gobernadora Libia Dennise García Muñoz Ledo.</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>0</v>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="V32" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
-        </is>
-      </c>
-      <c r="X32" s="2" t="inlineStr">
-        <is>
-          <t>HN-redpublica-iverify</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Gobernanza Colaborativa; Participación Digital</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>gobierno local</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>NLP; Otros(no especificado)</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>no-claro</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>Elaboración del Programa de Gobierno del Estado de Guanajuato 2024-2030 ('Gobierno de la Gente'), un plan de gobierno construido con participación ciudadana: se recorrió el territorio y se realizaron cuatro talleres regionales (noreste, norte, centro y sur) con representación de los 46 municipios, integrando la voz de más de 26,000 personas mediante talleres y consultas. El contenido fue validado por el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG), conformado por ciudadanía, la Gobernadora, secretarios de cada eje e IPLANEG. Se utilizaron herramientas de inteligencia artificial para procesar y organizar las miles de ideas y propuestas recibidas, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región, transformando el diálogo social en datos para la toma de decisiones que alimentaron los ejes del programa. Adicionalmente existe la asistente virtual 'Esperanza' para consultar el programa ya publicado.</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno del Estado de Guanajuato — Instituto de Planeación, Estadística y Geografía del Estado de Guanajuato (IPLANEG), con validación del COPLADEG. Titular: Gobernadora Libia Dennise García Muñoz Ledo.</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="V33" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="W33" s="2" t="inlineStr">
         <is>
           <t>https://guanajuatointeligente.com/como-hicimos-el-programa/
 https://iplaneg.guanajuato.gob.mx/programagobierno24-30/
 https://iplaneg.guanajuato.gob.mx/wp-content/uploads/03-2.05-Diagnostico-Programa-de-Gobierno-2024-2030-_Diagnostico-Estatal-2025_.pdf</t>
         </is>
       </c>
-      <c r="X33" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
         <is>
           <t>MX-guanajuato-inteligente-2024-2030</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>➜ RESOLVER DUDA</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Jalisco - Consulta ¡Armemos un Plan! (Plan Estatal de Desarrollo y Gobernanza 2024-2030)</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>(sin revisar)</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>DUDA(lean NO)</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="n">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>gobierno local</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" s="2" t="inlineStr"/>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr">
+      <c r="S33" s="2" t="inlineStr">
         <is>
           <t>Consulta ciudadana '¡Armemos un Plan!' convocada por el Gobierno de Jalisco a través de la Secretaría de Planeación y Participación Ciudadana (SPPC) para construir el Plan Estatal de Desarrollo y Gobernanza 2024-2030. Ejercicio abierto e inclusivo del 20 de febrero al 17 de abril de 2025 que registró 675,484 participaciones (aprox. 624,226 participaciones digitales + 25,176 niñas, niños y adolescentes mediante un mecanismo especialmente diseñado). Combinó: una encuesta representativa 'casa por casa' con rigor estadístico y metodológico; consulta digital abierta que recibió 15,899 propuestas ciudadanas escritas (temas: espacios públicos/deportivos/recreativos, medio ambiente y movilidad, agua y territorio, turismo rural, vivienda digna, economías locales); 12 foros regionales y 9 foros temáticos / mesas de trabajo con 5,563 participantes presenciales; 168 mesas regionales y 47 sectoriales donde se identificaron y discutieron 1,349 problemáticas; e instalación de 18 Consejos de Participación y Planeación (1 estatal, 12 regionales, 5 sectoriales). El resultado se estructuró en 5 ejes, 36 temas, 50 objetivos estratégicos, 197-198 proyectos y 82 indicadores de seguimiento.</t>
         </is>
       </c>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="T33" s="2" t="inlineStr">
         <is>
           <t>Gobierno del Estado de Jalisco — Secretaría de Planeación y Participación Ciudadana (SPPC). Titular: Cynthia Cantero Pacheco. Apoyo de información estadística/geográfica: Instituto de Información Estadística y Geográfica de Jalisco (IIEG). Gobernador: Pablo Lemus Navarro (administración 2024-2030).</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr">
+      <c r="U33" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="V34" s="5" t="n">
+      <c r="V33" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="W34" s="2" t="inlineStr">
+      <c r="W33" s="2" t="inlineStr">
         <is>
           <t>https://armemosunplan.mx/wp-content/uploads/2025/10/Armemos-un-Plan-Informe-de-Consulta-COLOR-NNA-v2.4.pdf
 https://plan.jalisco.gob.mx/documentos-metodologicos/
 https://iieg.gob.mx/ns/</t>
         </is>
       </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>MX-jalisco-armemos-un-plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Presupuesto CRECES</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Presupuestos Participativos</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>gobierno local</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>Chatbot - Inespecífico</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>Presupuesto participativo del Ayuntamiento de Hermosillo en México. Utiliza un chatbot que a través de IA simplifica y facilita la votación de los presupuestos participativos</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>Ayundamiento de Hermosilla</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="V34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
+        </is>
+      </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>MX-jalisco-armemos-un-plan</t>
+          <t>MX-presupuesto-creces</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Presupuesto CRECES</t>
+          <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -4586,17 +4585,17 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Presupuestos Participativos</t>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Análisis; Traducción Política</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
@@ -4604,17 +4603,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>gobierno local</t>
+          <t>sociedad civil; gobierno nacional</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4624,7 +4623,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4632,42 +4631,40 @@
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>Chatbot - Inespecífico</t>
-        </is>
-      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>no-claro</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>Presupuesto participativo del Ayuntamiento de Hermosillo en México. Utiliza un chatbot que a través de IA simplifica y facilita la votación de los presupuestos participativos</t>
+          <t>Mansa Idea (www.mansaidea.com) es una plataforma digital basada en inteligencia artificial lanzada el 1 de abril de 2024 por la Fundación Panamá Participa (sociedad civil), liderada por Paulina Franceschi. La plataforma organiza y hace navegables más de 175.000 ideas y propuestas ciudadanas generadas durante el Pacto del Bicentenario 'Cerrando Brechas' (proceso participativo nacional convocado por el gobierno de Panamá / Concertación Nacional, presidente Cortizo, 2020-2021), agregando los consensos nacionales y regionales/provinciales por tema en un solo clic. La IA se aplica sobre el CONTENIDO de los aportes ciudadanos (organiza, agrega y sintetiza el corpus de propuestas) para convertirlo en una base de datos navegable. El uso de la IA es un tratamiento PUNTERAL (~2024) de un corpus histórico de un proceso participativo ya cerrado (el Pacto fue 2020-2021), orientado a elevar el nivel de la conversación electoral 2024 y a dotar a candidatos, medios y ciudadanía de una herramienta para alinear planes con las necesidades de la población y monitorear el mandato ciudadano. IMPORTANTE: el proceso participativo original (recolección de aportes) fue convocado por el gobierno; la capa de IA (Mansa Idea) la desarrolla la sociedad civil sobre ese corpus ya recolectado.</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>Ayundamiento de Hermosilla</t>
+          <t>Fundación Panamá Participa (sociedad civil, Panamá), iniciativa liderada por Paulina Franceschi. El proceso participativo de origen (Pacto del Bicentenario 'Cerrando Brechas') fue convocado por el Gobierno de Panamá a través del mecanismo de Concertación Nacional para el Desarrollo (presidente Laurentino Cortizo), con apoyo del PNUD.</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="V35" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
+          <t>https://mansaidea.com/ (intentar archive.org / cache); buscar 'Mansa Idea metodología inteligencia artificial procesamiento propuestas' y entrevistas técnicas a Paulina Franceschi / Fundación Panamá Participa.
+https://mansaidea.com/ ; buscar 'Mansa Idea 2025' / 'Mansa Idea 2026' / 'Fundación Panamá Participa actividad reciente'.
+https://mansaidea.com/ ; buscar evidencia de actualizaciones periódicas del corpus o nuevas convocatorias.</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>MX-presupuesto-creces</t>
+          <t>PA-mansa-idea-pacto-del-bicentenario</t>
         </is>
       </c>
     </row>
@@ -4675,12 +4672,12 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
+          <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -4700,17 +4697,17 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Análisis; Traducción Política</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
@@ -4718,419 +4715,307 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>sociedad civil; gobierno nacional</t>
+          <t>otra institución pública</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>Sociedad Civil</t>
-        </is>
-      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr"/>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>NLP - Tópicos; NLP - Sentiment</t>
+        </is>
+      </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>no-claro</t>
+          <t>no</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>Mansa Idea (www.mansaidea.com) es una plataforma digital basada en inteligencia artificial lanzada el 1 de abril de 2024 por la Fundación Panamá Participa (sociedad civil), liderada por Paulina Franceschi. La plataforma organiza y hace navegables más de 175.000 ideas y propuestas ciudadanas generadas durante el Pacto del Bicentenario 'Cerrando Brechas' (proceso participativo nacional convocado por el gobierno de Panamá / Concertación Nacional, presidente Cortizo, 2020-2021), agregando los consensos nacionales y regionales/provinciales por tema en un solo clic. La IA se aplica sobre el CONTENIDO de los aportes ciudadanos (organiza, agrega y sintetiza el corpus de propuestas) para convertirlo en una base de datos navegable. El uso de la IA es un tratamiento PUNTERAL (~2024) de un corpus histórico de un proceso participativo ya cerrado (el Pacto fue 2020-2021), orientado a elevar el nivel de la conversación electoral 2024 y a dotar a candidatos, medios y ciudadanía de una herramienta para alinear planes con las necesidades de la población y monitorear el mandato ciudadano. IMPORTANTE: el proceso participativo original (recolección de aportes) fue convocado por el gobierno; la capa de IA (Mansa Idea) la desarrolla la sociedad civil sobre ese corpus ya recolectado.</t>
+          <t>Una consulta pública para recoger opiniones sobre el Proyecto Educativo Nacional 2036, utilizando encuestas en línea, talleres y mesas deliberativas.</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>Fundación Panamá Participa (sociedad civil, Panamá), iniciativa liderada por Paulina Franceschi. El proceso participativo de origen (Pacto del Bicentenario 'Cerrando Brechas') fue convocado por el Gobierno de Panamá a través del mecanismo de Concertación Nacional para el Desarrollo (presidente Laurentino Cortizo), con apoyo del PNUD.</t>
+          <t>Consejo Nacional de Educación del Perú</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="V36" s="5" t="n">
-        <v>5</v>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>https://mansaidea.com/ (intentar archive.org / cache); buscar 'Mansa Idea metodología inteligencia artificial procesamiento propuestas' y entrevistas técnicas a Paulina Franceschi / Fundación Panamá Participa.
-https://mansaidea.com/ ; buscar 'Mansa Idea 2025' / 'Mansa Idea 2026' / 'Fundación Panamá Participa actividad reciente'.
-https://mansaidea.com/ ; buscar evidencia de actualizaciones periódicas del corpus o nuevas convocatorias.</t>
-        </is>
-      </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
-          <t>PA-mansa-idea-pacto-del-bicentenario</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>PE</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>otra institución pública</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>Privado</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>NLP - Tópicos; NLP - Sentiment</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>Una consulta pública para recoger opiniones sobre el Proyecto Educativo Nacional 2036, utilizando encuestas en línea, talleres y mesas deliberativas.</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>Consejo Nacional de Educación del Perú</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="V37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>https://www.latinno.net/en/case/17232/
 https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional?utm_source=chatgpt.com
 https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080</t>
         </is>
       </c>
-      <c r="X37" s="2" t="inlineStr">
+      <c r="X36" s="2" t="inlineStr">
         <is>
           <t>PE-consulta-ciudadana-sobre-el-proyecto-nac</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>DUDA(lean NO)</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="n">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>gobierno nacional</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr">
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>NLP; Resumen automatico; Clasificacion/agrupacion de texto (capacidad de la plataforma sujeta a plan Premium; activacion NO confirmada en TT)</t>
         </is>
       </c>
-      <c r="R38" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
         </is>
       </c>
-      <c r="S38" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) es la plataforma de participacion ciudadana del Ministry of Digital Transformation de Trinidad y Tobago (desde mayo 2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), lanzada en el simposio del NDTS el 12 de febrero de 2025 junto al BID (IDB). Se usa como canal de participacion en el proceso de planificacion nacional del National Digital Transformation Strategy (NDTS) 2024-2027, donde ciudadanos, empresas y partes interesadas reciben actualizaciones y aportan retroalimentacion via encuestas, sondeos (polls), un 'Open Forum' de ideas y el envio de propuestas. La instancia corre sobre el software Go Vocal (antes CitizenLab) -confirmado por la ruta interna 'projects/e-democracy-govocal-internal'-. Go Vocal incorpora un modulo de IA/NLP de 'Sensemaking' (analisis y resumen automatico de aportes), pero ese modulo NO viene activo por defecto: segun la documentacion de soporte de Go Vocal, el acceso a la funcion de AI Analysis/Sensemaking DEPENDE DEL PLAN contratado (Advanced Sensemaking con auto-insights esta en el plan Premium). Tras 2a pasada de investigacion (&gt;=14 busquedas/fetches) NO se halla evidencia alguna de que la instancia de Trinidad active ni use esas funciones de IA sobre el CONTENIDO de los aportes; toda la documentacion describe a EngageTT como recolector (surveys, polls, Open Forum, ideas), es decir plataforma usada como formulario sin analisis automatico confirmado. Existe ademas AskNDTS, un chatbot/PWA de IA conversacional para responder preguntas sobre el NDTS (rol de FAQ informativo, EXCLUIDO del criterio).</t>
         </is>
       </c>
-      <c r="T38" s="2" t="inlineStr">
+      <c r="T37" s="2" t="inlineStr">
         <is>
           <t>Ministry of Digital Transformation de Trinidad y Tobago (desde el 23-may-2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), en colaboracion con el Banco Interamericano de Desarrollo (BID/IDB). Plataforma de software: Go Vocal (antes CitizenLab), empresa belga.</t>
         </is>
       </c>
-      <c r="U38" s="2" t="inlineStr">
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="V38" s="5" t="n">
+      <c r="V37" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="W38" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
 https://www.govocal.com/plans
 https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool</t>
         </is>
       </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>TT-engagett-plataforma-go-vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>UY</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>(sin revisar)</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>MEDIA (fuente primaria + OCDE 2025; fetch primario bloqueado por proxy, citas vía repo/WebSearch)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Referendos e Iniciativas Populares</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>universidad</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>Sociedad Civil; Academia</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>Clustering; ML - Inespecífico</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>Referéndum nacional para derogar 135 artículos de la Ley de Urgente Consideración (LUC). Un equipo de la Universidad de la República corrió una conversación Pol.is en paralelo al referéndum del 27/03/2022 (documentado como caso 2021).</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>Equipo de 13 personas de la Universidad de la República (UdelaR) — ingenieros, comunicadores y científicos de datos; plataforma Pol.is (The Computational Democracy Project)</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="V38" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/</t>
+        </is>
+      </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>TT-engagett-plataforma-go-vocal</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>UY</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>(sin revisar)</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA (fuente primaria + OCDE 2025; fetch primario bloqueado por proxy, citas vía repo/WebSearch)</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Referendos e Iniciativas Populares</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>universidad</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>Sociedad Civil; Academia</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>Clustering; ML - Inespecífico</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>Referéndum nacional para derogar 135 artículos de la Ley de Urgente Consideración (LUC). Un equipo de la Universidad de la República corrió una conversación Pol.is en paralelo al referéndum del 27/03/2022 (documentado como caso 2021).</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t>Equipo de 13 personas de la Universidad de la República (UdelaR) — ingenieros, comunicadores y científicos de datos; plataforma Pol.is (The Computational Democracy Project)</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="V39" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="W39" s="2" t="inlineStr">
-        <is>
-          <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/</t>
-        </is>
-      </c>
-      <c r="X39" s="2" t="inlineStr">
-        <is>
           <t>UY-polis-referendum-luc</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X39"/>
+  <autoFilter ref="A1:X38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5416,39 +5301,40 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>B. Rescatado → ENTRA</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>A. Excluir (criterio corregido)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Confirmar SI</t>
+          <t>Confirmar NO (ya fuera del conteo)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Presupuesto CRECES</t>
+          <t>U-Report Costa Rica – chatbot juvenil</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
+          <t>No es un proceso de participación (o sin IA verificada) → excluido</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Presupuesto participativo (Hermosillo); la IA (chatbot) facilita la votación (Implementación).</t>
+          <t>UNICEF lo define como 'encuestas de opinión' (panel de sondeo/percepción juvenil anónimo: clima, salud mental, educación); sin proceso participativo estructurado con incidencia concreta (verificado). Solo opinión → fuera. Decisión del equipo.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
+          <t>https://costarica.ureport.in/
+https://www.unicef.org/costarica/comunicados-prensa/plataforma-mundial-u-report-llega-costa-rica</t>
         </is>
       </c>
     </row>
@@ -5465,68 +5351,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Presupuesto CRECES</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Presupuesto participativo (Hermosillo); la IA (chatbot) facilita la votación (Implementación).</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>B. Rescatado → ENTRA</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar SI</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>LXS 400 - Chile Delibera</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Mini-público del Senado; la IA modera y administra los turnos de palabra (Implementación/Planificación).</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://es.wikipedia.org/wiki/Lxs_400:_Chile_Delibera
 https://www.lxs400.cl/noticias/</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>B. Rescatado → ENTRA</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Confirmar SI</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Consulta ciudadana; la IA analiza los aportes (Análisis).</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>https://participacion.digital.gob.cl/es-CL/folders/consultas-ciudadanas</t>
-        </is>
-      </c>
-    </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -5540,12 +5426,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RedPública + iVerify </t>
+          <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -5555,12 +5441,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Plataforma de propuestas de ley ciudadanas (participación legislativa).</t>
+          <t>Consulta ciudadana; la IA analiza los aportes (Análisis).</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
+          <t>https://participacion.digital.gob.cl/es-CL/folders/consultas-ciudadanas</t>
         </is>
       </c>
     </row>
@@ -5577,12 +5463,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>La voz de los nuevos votantes</t>
+          <t xml:space="preserve">RedPública + iVerify </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -5592,12 +5478,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Consulta a nuevos votantes con NLP — proceso ejecutado por el equipo (confirmado).</t>
+          <t>Plataforma de propuestas de ley ciudadanas (participación legislativa).</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf</t>
+          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5505,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
+          <t>La voz de los nuevos votantes</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -5629,12 +5515,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Jornada de escucha / diálogo — proceso ejecutado por el equipo (confirmado).</t>
+          <t>Consulta a nuevos votantes con NLP — proceso ejecutado por el equipo (confirmado).</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
+          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf</t>
         </is>
       </c>
     </row>
@@ -5651,68 +5537,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Jornada de escucha / diálogo — proceso ejecutado por el equipo (confirmado).</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>B. Rescatado → ENTRA</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar SI</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Chatico</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Tiene módulos de participación (aportes al Plan de Desarrollo de Bogotá) — confirmado por el equipo.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://secretariageneral.gov.co/noticias/chatico-el-agente-virtual-de-servicio-la-ciudadania-supero-los-36-millones-de-conversaciones
 https://bogota.gov.co/mi-ciudad/gestion-publica/distrito-presenta-su-agente-virtual-chatico-que-guia-la-ciudadania</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>B. Rescatado → ENTRA</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Confirmar SI</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Colab</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Permite sugerir ideas y votar en decisiones municipales (módulos de participación) — confirmado por el equipo.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.colab.com.br/sou-cidadao/</t>
-        </is>
-      </c>
-    </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
@@ -5726,66 +5612,65 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Colab</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Permite sugerir ideas y votar en decisiones municipales (módulos de participación) — confirmado por el equipo.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.colab.com.br/sou-cidadao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>B. Rescatado → ENTRA</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar SI</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Caso borde: el chatbot AskNDTS (IA) informa/apoya la implementación del proceso NDTS y el módulo Go Vocal Sensemaking está planeado (existe). → ENTRA como apoyo a la implementación. Decisión del equipo.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
 https://www.govocal.com/plans</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>C. DUDA — revisar (posible IA)</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Abrir URL y decidir SI/NO</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>U-Report Costa Rica – chatbot juvenil</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>¿Proceso de participación o sondeo? Decidir</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma de opinión juvenil (UNICEF): ¿consulta participativa o civic tech de sondeo?</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>https://costarica.ureport.in/
-https://www.unicef.org/costarica/comunicados-prensa/plataforma-mundial-u-report-llega-costa-rica</t>
         </is>
       </c>
     </row>
@@ -6095,7 +5980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7166,7 +7051,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>dIAra</t>
+          <t>U-Report Costa Rica – chatbot juvenil</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -7176,66 +7061,66 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Civic tech de fiscalización de obras (control social vía app): no es un proceso participativo.</t>
+          <t>UNICEF lo define como 'encuestas de opinión' (panel de sondeo/percepción juvenil anónimo: clima, salud mental, educación); sin proceso participativo estructurado con incidencia concreta (verificado). Solo opinión → fuera. Decisión del equipo.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.opengovpartnership.org/the-open-gov-challenge/costa-rica-artificial-intelligence-alerts-citizen-control-public-infrastructure/</t>
+          <t>https://costarica.ureport.in/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>CU</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
+          <t>dIAra</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Dudoso</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Dentro de un proceso participativo formal y de gran escala (consulta popular legislativa nacional sobre el Código de las Familias, feb-abr 2022, ~6,5 millones de participantes y cientos de miles de propuestas) se usó IA sobre el CONTENIDO de los aportes ciudadanos: el sistema GEMA-CEN (basado en GEM</t>
+          <t>Civic tech de fiscalización de obras (control social vía app): no es un proceso participativo.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>http://www.datys.cu/spa/site/product/15</t>
+          <t>https://www.opengovpartnership.org/the-open-gov-challenge/costa-rica-artificial-intelligence-alerts-citizen-control-public-infrastructure/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>CU</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CiudadanIA</t>
+          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Dudoso</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Solo atención/servicio; la 'participación' es co-diseñar la IA aportando datos, no consulta pública. Sin módulo de participación (verificado). Decisión del equipo.</t>
+          <t>Dentro de un proceso participativo formal y de gran escala (consulta popular legislativa nacional sobre el Código de las Familias, feb-abr 2022, ~6,5 millones de participantes y cientos de miles de propuestas) se usó IA sobre el CONTENIDO de los aportes ciudadanos: el sistema GEMA-CEN (basado en GEM</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.genia.ai/paises-miembros</t>
+          <t>http://www.datys.cu/spa/site/product/15</t>
         </is>
       </c>
     </row>
@@ -7247,22 +7132,22 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>CiudadanIA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Solo atención/servicio; la 'participación' es co-diseñar la IA aportando datos, no consulta pública. Sin módulo de participación (verificado). Decisión del equipo.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/latin-america/comunicados-de-prensa/sara-la-nueva-herramienta-de-inteligencia-artificial-para-combatir-la-violencia-de-genero-en-centroamerica-0</t>
+          <t>https://www.genia.ai/paises-miembros</t>
         </is>
       </c>
     </row>
@@ -7274,7 +7159,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>TAÍNA: Gobierno Inteligente</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -7284,66 +7169,66 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.diariolibre.com/actualidad/nacional/2023/10/11/gobierno-presenta-estrategia-de-inteligencia-artificial/2489157</t>
+          <t>https://www.undp.org/es/latin-america/comunicados-de-prensa/sara-la-nueva-herramienta-de-inteligencia-artificial-para-combatir-la-violencia-de-genero-en-centroamerica-0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Plataforma de modelos generativos de IA de SEGEPLAN + Red Ciudadana (Guatemala)</t>
+          <t>TAÍNA: Gobierno Inteligente</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>El criterio ELEGIBLE exige que la IA generativa se use para SISTEMATIZAR/CLASIFICAR/RESUMIR el CONTENIDO de los aportes de los diagnosticos participativos (Consejos de Desarrollo COCODES/COMUDES) en los Planes de Desarrollo Municipal (PDM). Toda la evidencia primaria y secundaria (nota SEGEPLAN ?p=1</t>
+          <t>Atención ciudadana</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://portal.segeplan.gob.gt/segeplan/?p=14176</t>
+          <t>https://www.diariolibre.com/actualidad/nacional/2023/10/11/gobierno-presenta-estrategia-de-inteligencia-artificial/2489157</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LATAM</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ANTAI Smart CID (Autoridad Nacional de Transparencia y Acceso a la Información + OS City)</t>
+          <t>Plataforma de modelos generativos de IA de SEGEPLAN + Red Ciudadana (Guatemala)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Descubrimiento</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>El criterio ELEGIBLE exige que la IA generativa se use para SISTEMATIZAR/CLASIFICAR/RESUMIR el CONTENIDO de los aportes de los diagnosticos participativos (Consejos de Desarrollo COCODES/COMUDES) en los Planes de Desarrollo Municipal (PDM). Toda la evidencia primaria y secundaria (nota SEGEPLAN ?p=1</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.caf.com/es/actualidad/noticias/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
+          <t>https://portal.segeplan.gob.gt/segeplan/?p=14176</t>
         </is>
       </c>
     </row>
@@ -7355,7 +7240,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Botivist</t>
+          <t>ANTAI Smart CID (Autoridad Nacional de Transparencia y Acceso a la Información + OS City)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -7365,12 +7250,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>No tiene foco en un país específico</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/research/publication/botivist-calling-volunteers-to-action-using-online-bots/</t>
+          <t>https://www.caf.com/es/actualidad/noticias/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7267,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Chatbot DCI (Denuncia Ciudadana Idónea)</t>
+          <t>Botivist</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -7392,12 +7277,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA</t>
+          <t>No tiene foco en un país específico</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci</t>
+          <t>https://www.microsoft.com/en-us/research/publication/botivist-calling-volunteers-to-action-using-online-bots/</t>
         </is>
       </c>
     </row>
@@ -7409,7 +7294,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Citibeats: Covid-19 (“Percepciones ciudadanas COVID-19”)</t>
+          <t>Chatbot DCI (Denuncia Ciudadana Idónea)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -7419,12 +7304,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Análisis de redes sociales, no es participación</t>
+          <t>No evidencia de uso de IA</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://forbescentroamerica.com/2021/04/28/civiclytics-el-big-data-apoya-la-recuperacion-economica</t>
+          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7321,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Ushahidi "AI for Good"</t>
+          <t>Citibeats: Covid-19 (“Percepciones ciudadanas COVID-19”)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -7446,24 +7331,24 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>No se evidencia el uso de IA en los proyectos de participación listados para Latam</t>
+          <t>Análisis de redes sociales, no es participación</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.ushahidi.com/</t>
+          <t>https://forbescentroamerica.com/2021/04/28/civiclytics-el-big-data-apoya-la-recuperacion-economica</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>LATAM</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>AMIMgo</t>
+          <t>Ushahidi "AI for Good"</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -7473,12 +7358,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>No se evidencia el uso de IA en los proyectos de participación listados para Latam</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://amim.mx/noticias/detalle/estrena-amim-chatbot-para-la-atencion-ciudadana</t>
+          <t>https://www.ushahidi.com/</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7375,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>ATIC</t>
+          <t>AMIMgo</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -7500,12 +7385,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://oem.com.mx/la-prensa/metropoli/info-cdmx-implementa-atic-una-herramienta-con-ia-que-facilita-el-acceso-a-la-informacion-13081722</t>
+          <t>https://amim.mx/noticias/detalle/estrena-amim-chatbot-para-la-atencion-ciudadana</t>
         </is>
       </c>
     </row>
@@ -7517,7 +7402,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>ChatBot “Claudia"</t>
+          <t>ATIC</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -7527,12 +7412,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>No es participación</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://mexicocomovamos.mx/animal-politico/2024/08/chatbot-claudia-una-herramienta-de-participacion-ciudadana/</t>
+          <t>https://oem.com.mx/la-prensa/metropoli/info-cdmx-implementa-atic-una-herramienta-con-ia-que-facilita-el-acceso-a-la-informacion-13081722</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7429,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Chatbot "Inés"</t>
+          <t>ChatBot “Claudia"</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -7554,12 +7439,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>No es participación, es informativo</t>
+          <t>No es participación</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://centralelectoral.ine.mx/2024/04/17/nueva-version-del-chatbot-del-ine-en-whatsapp-permitira-verificar-informacion-sobre-elecciones-2024/</t>
+          <t>https://mexicocomovamos.mx/animal-politico/2024/08/chatbot-claudia-una-herramienta-de-participacion-ciudadana/</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7456,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Sam Petrino</t>
+          <t>Chatbot "Inés"</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -7581,12 +7466,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No es participación, es informativo</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.civica.digital/historias/chatbot-sam-petrino</t>
+          <t>https://centralelectoral.ine.mx/2024/04/17/nueva-version-del-chatbot-del-ine-en-whatsapp-permitira-verificar-informacion-sobre-elecciones-2024/</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7483,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Victoria</t>
+          <t>Chatbot Sam Petrino</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -7613,7 +7498,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Informe de Gobierno</t>
+          <t>https://www.civica.digital/historias/chatbot-sam-petrino</t>
         </is>
       </c>
     </row>
@@ -7625,7 +7510,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>INAOE (Conacyt) – Laboratorio de Tecnologías del Lenguaje</t>
+          <t>Chatbot Victoria</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -7635,12 +7520,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=para%20identificar%20posibles%20trastornos,de%20las%20dificultades%20de%20%C3%ADndole</t>
+          <t>Informe de Gobierno</t>
         </is>
       </c>
     </row>
@@ -7652,7 +7537,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Movimex</t>
+          <t>INAOE (Conacyt) – Laboratorio de Tecnologías del Lenguaje</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -7667,7 +7552,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://animalpolitico.com/estados/chatbot-movimex-tramites-denuncias-edomex</t>
+          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=para%20identificar%20posibles%20trastornos,de%20las%20dificultades%20de%20%C3%ADndole</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7564,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Sistema *0311 Locatel</t>
+          <t>Movimex</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -7689,12 +7574,12 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://research.latinxinai.org/papers/naacl/2022/pdf/paper_01.pdf</t>
+          <t>https://animalpolitico.com/estados/chatbot-movimex-tramites-denuncias-edomex</t>
         </is>
       </c>
     </row>
@@ -7706,22 +7591,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Sufragio seguro</t>
+          <t>Sistema *0311 Locatel</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Baseline 2025</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>EXCLUSIÓN FIRME (recodificación 2026): Exclusión FIRME (recodificación 2026): integridad/proceso electoral, no contenido</t>
+          <t>Atención ciudadana</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://osf.io/cu6w3</t>
+          <t>https://research.latinxinai.org/papers/naacl/2022/pdf/paper_01.pdf</t>
         </is>
       </c>
     </row>
@@ -7733,34 +7618,34 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Violetta</t>
+          <t>Sufragio seguro</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Baseline 2025</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>EXCLUSIÓN FIRME (recodificación 2026): Exclusión FIRME (recodificación 2026): integridad/proceso electoral, no contenido</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://holasoyvioletta.com/acerca-de/</t>
+          <t>https://osf.io/cu6w3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Dr. ROSA y Dr. NICO</t>
+          <t>Violetta</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -7770,24 +7655,24 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=virtual%2Fchatbot%20que%20funciona%20por%20WhatsApp,que%20realice%20una%20observaci%C3%B3n%20f%C3%ADsica</t>
+          <t>https://holasoyvioletta.com/acerca-de/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>JNE WhatsApp Chatbot</t>
+          <t>Dr. ROSA y Dr. NICO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -7802,7 +7687,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://portal.jne.gob.pe/Portal/Pagina/Nota/12783</t>
+          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=virtual%2Fchatbot%20que%20funciona%20por%20WhatsApp,que%20realice%20una%20observaci%C3%B3n%20f%C3%ADsica</t>
         </is>
       </c>
     </row>
@@ -7814,49 +7699,49 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Sistema de cómputo con IA para las Elecciones Generales 2026</t>
+          <t>JNE WhatsApp Chatbot</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Conteo electoral (OCR de actas): votación política, no participación.</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://cheleloyborolas.com/index.php?Itemid=103&amp;catid=10&amp;id=72545%3Ajefe-de-la-onpe-presenta-avances-en-la-organizacion-de-las-elecciones-generales-2026&amp;option=com_content&amp;view=article</t>
+          <t>https://portal.jne.gob.pe/Portal/Pagina/Nota/12783</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>PY</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Consultas ciudadanas sobre IA en Paraguay - PNUD Accelerator Lab (AccLab) + Columbia SIPA + MITIC / insumo del diagnóstico AILA (Atlas de IA)</t>
+          <t>Sistema de cómputo con IA para las Elecciones Generales 2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>El criterio ELEGIBLE exige que dentro de un proceso participativo convocado se use IA (NLP/ML/clustering/sentimiento) SOBRE EL CONTENIDO de los aportes. Aquí ocurre lo contrario: (1) la IA es el TEMA de la consulta (se pregunta a la ciudadania por su percepcion de la IA), y (2) el ANÁLISIS de los ap</t>
+          <t>Conteo electoral (OCR de actas): votación política, no participación.</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/paraguay/blog/consultas-ciudadanas-sobre-ia-en-paraguay-visiones-diversas-entre-el-campo-y-la-ciudad</t>
+          <t>https://cheleloyborolas.com/index.php?Itemid=103&amp;catid=10&amp;id=72545%3Ajefe-de-la-onpe-presenta-avances-en-la-organizacion-de-las-elecciones-generales-2026&amp;option=com_content&amp;view=article</t>
         </is>
       </c>
     </row>
@@ -7868,34 +7753,34 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>ParaEmpleo</t>
+          <t>Consultas ciudadanas sobre IA en Paraguay - PNUD Accelerator Lab (AccLab) + Columbia SIPA + MITIC / insumo del diagnóstico AILA (Atlas de IA)</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Descubrimiento</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>El criterio ELEGIBLE exige que dentro de un proceso participativo convocado se use IA (NLP/ML/clustering/sentimiento) SOBRE EL CONTENIDO de los aportes. Aquí ocurre lo contrario: (1) la IA es el TEMA de la consulta (se pregunta a la ciudadania por su percepcion de la IA), y (2) el ANÁLISIS de los ap</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/paraempleo</t>
+          <t>https://www.undp.org/es/paraguay/blog/consultas-ciudadanas-sobre-ia-en-paraguay-visiones-diversas-entre-el-campo-y-la-ciudad</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>UY</t>
+          <t>PY</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Chatbot (Asistente virtual entrenado con IA)</t>
+          <t>ParaEmpleo</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -7905,12 +7790,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=El%20chatbot%20virtual%20creado%20por,desarrollo%20de%20soluciones%20de%20IA</t>
+          <t>https://fairlac.iadb.org/paraempleo</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7807,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Consulta Pública de la Estrategia Nacional de Inteligencia Artificial (IA) de Uruguay 2024–2030,</t>
+          <t>Chatbot (Asistente virtual entrenado con IA)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -7932,12 +7817,12 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030?utm_source=chatgpt.com</t>
+          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=El%20chatbot%20virtual%20creado%20por,desarrollo%20de%20soluciones%20de%20IA</t>
         </is>
       </c>
     </row>
@@ -7949,54 +7834,81 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Consulta Pública y Participación Multiactores: "Niñas, niños, adolescentes, entornos digitales e inteligencia artificial" (Uruguay, 2026)</t>
+          <t>Consulta Pública de la Estrategia Nacional de Inteligencia Artificial (IA) de Uruguay 2024–2030,</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>NO (lean firme). (1) TEMPORAL: la consulta está ABIERTA hasta el 10/09/2026 y la fase de sistematización/análisis/validación (Fase 3) recién ocurre entre el 10/09 y el 10/10/2026, con informe final el 30/11/2026. A la fecha de evaluación (2026-07-01) la fase de análisis NO se ha ejecutado, por lo qu</t>
+          <t>No evidencia de uso de IA</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.gub.uy/ministerio-educacion-cultura/comunicacion/noticias/lanzamiento-consulta-publica-sobre-inteligencia-artificial-entornos-digitales</t>
+          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030?utm_source=chatgpt.com</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>UY</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Consulta Pública y Participación Multiactores: "Niñas, niños, adolescentes, entornos digitales e inteligencia artificial" (Uruguay, 2026)</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Descubrimiento</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>NO (lean firme). (1) TEMPORAL: la consulta está ABIERTA hasta el 10/09/2026 y la fase de sistematización/análisis/validación (Fase 3) recién ocurre entre el 10/09 y el 10/10/2026, con informe final el 30/11/2026. A la fecha de evaluación (2026-07-01) la fase de análisis NO se ha ejecutado, por lo qu</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gub.uy/ministerio-educacion-cultura/comunicacion/noticias/lanzamiento-consulta-publica-sobre-inteligencia-artificial-entornos-digitales</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
           <t>VE</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Plan de la Patria 7 Transformaciones (7T) - IA y Big Data en la sistematización de propuestas de la Consulta Popular</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Dudoso</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>NO (resuelto en 2ª pasada, antes DUDA). Hay un proceso participativo claro (consulta/debate nacional para construir el Plan de la Patria 7T, con +63.000 asambleas, 3,4 M de participantes y 34.491 propuestas) cuyo CONTENIDO sí fue recolectado, cargado, sistematizado y agrupado. Pero la 2ª pasada CONF</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>http://www.correodelorinoco.gob.ve/venezuela-impulsa-el-debate-sobre-inteligencia-artificial-bajo-principios-de-soberania-y-etica/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E70"/>
+  <autoFilter ref="A1:E71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8007,7 +7919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9766,12 +9678,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>U-Report Costa Rica – chatbot juvenil</t>
+          <t xml:space="preserve">PAGA IA </t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -9786,17 +9698,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital</t>
+          <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>reconfirmado web (institucional): Reconfirmado 2024-2025: consulta juvenil de UNICEF con 8.404 participantes; resultados analizados para incidir en política pública.</t>
+          <t>reconfirmado web (institucional): Reconfirmado: integrada al Tercer Plan de Acción de Estado Abierto 2025-2027; analiza las propuestas ciudadanas y sugiere actividades.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -9806,85 +9718,22 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Unicef</t>
+          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>La inteligencia artificial de U-Report analiza miles de opiniones enviadas por texto para transformarlas en datos útiles. Utilizando Procesamiento de Lenguaje Natural (PLN), la IA lee y clasifica automáticamente los mensajes de los jóvenes para identificar los temas, tendencias y sentimientos más importantes, convirtiendo sus voces en evidencia clara para la toma de decisiones.</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>La inteligencia artificial de U-Report analiza miles de opiniones enviadas por texto para transformarlas en datos útiles. Utilizando Procesamiento de Lenguaje Natural (PLN), la IA lee y clasifica automáticamente los mensajes de los jóvenes para identificar los temas, tendencias y sentimientos más importantes, convirtiendo sus voces en evidencia clara para la toma de decisiones.</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>https://costarica.ureport.in/
-https://www.unicef.org/costarica/comunicados-prensa/plataforma-mundial-u-report-llega-costa-rica</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PAGA IA </t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Referendos e Iniciativas Populares</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>reconfirmado web (institucional): Reconfirmado: integrada al Tercer Plan de Acción de Estado Abierto 2025-2027; analiza las propuestas ciudadanas y sugiere actividades.</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Plataforma</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto
 </t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto
 </t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>https://www.gobiernoabierto.ec/boletin-014-2023/
 https://ia.gobiernoabierto.ec/
@@ -9892,63 +9741,63 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Guatemala Joven Conversa </t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado: diálogos digitales con IA (DPPA ONU + Fundación Esquipulas); 300+ jóvenes; la IA permite intercambios anónimos y votación de aportes para identifi</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
 https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/?utm_source=chatgpt.com
@@ -9956,15 +9805,77 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RedPública + iVerify </t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Referendos e Iniciativas Populares</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>reconfirmado web (institucional): Reverificación: plataforma de propuestas ciudadanas con módulo de análisis de tendencias; evidencia de IA central débil, revisar en Fase 2.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RedPública + iVerify </t>
+          <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -9974,107 +9885,45 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+          <t>Guanajuato hará historia con el primer Programa de Gobierno realizado con IA</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Referendos e Iniciativas Populares</t>
+          <t>Para integrar la participación ciudadana en este Programa de Gobierno, se realizaron cuatro talleres cubriendo las regiones noreste, norte, centro y sur, con representación de los 46 municipios de Guanajuato.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>reconfirmado web (institucional): Reverificación: plataforma de propuestas ciudadanas con módulo de análisis de tendencias; evidencia de IA central débil, revisar en Fase 2.</t>
+          <t>El Programa de Gobierno de Guanajuato 2024-2030 es la guía que orienta las acciones del Gobierno de la Gente para lograr un Guanajuato sostenible, equitativo y transparente.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
+          <t>Su diseño incorporó el uso de inteligencia artificial para integrar más de 26 mil voces de distintas regiones y sectores</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
+          <t>El Programa de Gobierno 2024-2030 hizo historia al ser el primero en realizarse con ayuda de la Inteligencia Artificial (IA), según anunció la Gobernadora Libia Dennise García Muñoz Ledo en el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG).</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
+          <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
+          <t>Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Guanajuato hará historia con el primer Programa de Gobierno realizado con IA</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Para integrar la participación ciudadana en este Programa de Gobierno, se realizaron cuatro talleres cubriendo las regiones noreste, norte, centro y sur, con representación de los 46 municipios de Guanajuato.</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>El Programa de Gobierno de Guanajuato 2024-2030 es la guía que orienta las acciones del Gobierno de la Gente para lograr un Guanajuato sostenible, equitativo y transparente.</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Su diseño incorporó el uso de inteligencia artificial para integrar más de 26 mil voces de distintas regiones y sectores</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>El Programa de Gobierno 2024-2030 hizo historia al ser el primero en realizarse con ayuda de la Inteligencia Artificial (IA), según anunció la Gobernadora Libia Dennise García Muñoz Ledo en el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG).</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía.</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>https://guanajuatointeligente.com/como-hicimos-el-programa/
 https://guanajuatointeligente.com/
@@ -10087,55 +9936,55 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Jalisco - Consulta ¡Armemos un Plan! (Plan Estatal de Desarrollo y Gobernanza 2024-2030)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>DUDA(lean NO)</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>'Armemos un Plan' se llevó a cabo de manera abierta e incluyente del 20 de febrero al 17 de abril por el Gobierno de Jalisco, a través de la Secretaría de Planeación y Participación Ciudadana; la consulta digital recibió 15,899 propuestas ciudadanas.</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Jalisco concluyó la primera etapa de la consulta ciudadana 'Armemos un Plan' con una cifra inédita de 675,484 participaciones, base para desarrollar el Plan Estatal de Desarrollo y Gobernanza 2024-2030.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Se realizaron 12 foros regionales y la instalación de un Consejo de Planeación Participativa en cada región de Jalisco; se llevaron a cabo 168 mesas regionales, 47 sectoriales y 9 grandes foros temáticos... donde se identificaron y discutieron 1,349 problemáticas planteadas por la ciudadanía. (Metodología participativa/estadística; sin componente de IA.)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Gobierno de Jalisco, a través de la Secretaría de Planeación y Participación Ciudadana (coordinación de Cynthia Cantero Pacheco).</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Las propuestas se construyeron a partir de las opiniones y expresiones de la ciudadanía durante la consulta, agrupando ideas similares y redactándolas de forma clara y ordenada, respetando siempre la intención original de quienes participaron. (Descripción metodológica oficial de armemosunplan.mx/propuestas-ciudadanas, recuperada vía WebSearch que indexa la página; no menciona IA/NLP/algoritmos: describe agrupación editorial manual.)</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>GAP: ninguna fuente atribuye a IA/NLP/minería de texto/clustering el análisis o la agrupación de las 15,899 propuestas; la única descripción del método es 'agrupando ideas similares' de forma manual/editorial.</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>https://armemosunplan.mx/propuestas-ciudadanas/
 https://armemosunplan.mx/wp-content/uploads/2025/10/Armemos-un-Plan-Informe-de-Consulta-COLOR-NNA-v2.4.pdf
@@ -10148,15 +9997,77 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Presupuesto CRECES</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Presupuestos Participativos</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>BBDD 2025: Activo</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Ayundamiento de Hermosilla</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Presupuesto CRECES</t>
+          <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -10166,103 +10077,41 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+          <t>La Fundación Panamá Participa lanzó Mansa Idea (www.mansaidea.com), una plataforma basada en inteligencia artificial que recoge miles de propuestas ciudadanas... iniciativa de alcance nacional que se nutre de ideas y propuestas que miles de panameños hicieron durante el desarrollo del Pacto del Bicentenario. (Panamá; fuentes panama24horas.com.pa y laestrella.com.pa)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Presupuestos Participativos</t>
+          <t>Mansa Idea, resultado del Pacto del Bicentenario, ofrece acceso fácil y transparente a más de 175 mil ideas y propuestas generadas por ciudadanos de todo el país. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>BBDD 2025: Activo</t>
-        </is>
-      </c>
+          <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales. (la IA agrega/organiza/sintetiza el contenido de las propuestas por tema y territorio = Análisis + Traducción Política; el método técnico exacto no se detalla en las fuentes).</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
+          <t>La plataforma fue lanzada el 1 de abril de 2024... constituye una herramienta valiosa de participación ciudadana muy relevante para ciudadanos, candidatos a cargos de elección popular y medios durante la campaña electoral y luego como recurso para el monitoreo del mandato ciudadano. (un despliegue concreto de la plataforma, 2024; sin evidencia de ediciones recurrentes).</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Ayundamiento de Hermosilla</t>
+          <t>La Fundación Panamá Participa lanzó Mansa Idea... iniciativa liderada por Paulina Franceschi a través de la Fundación Panamá Participa (sociedad civil). El proceso participativo de origen: 'El 26 de noviembre de 2020, el presidente Laurentino Cortizo Cohen lanzó la iniciativa denominada Pacto del Bicentenario Cerrando Brechas' (gobierno nacional / Concertación Nacional).</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
+          <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. (la IA procesa el contenido de las propuestas del proceso participativo).</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
+          <t>La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía. (agregación/síntesis de los aportes ciudadanos = rol sobre el contenido).</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>La Fundación Panamá Participa lanzó Mansa Idea (www.mansaidea.com), una plataforma basada en inteligencia artificial que recoge miles de propuestas ciudadanas... iniciativa de alcance nacional que se nutre de ideas y propuestas que miles de panameños hicieron durante el desarrollo del Pacto del Bicentenario. (Panamá; fuentes panama24horas.com.pa y laestrella.com.pa)</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Mansa Idea, resultado del Pacto del Bicentenario, ofrece acceso fácil y transparente a más de 175 mil ideas y propuestas generadas por ciudadanos de todo el país. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía.</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales. (la IA agrega/organiza/sintetiza el contenido de las propuestas por tema y territorio = Análisis + Traducción Política; el método técnico exacto no se detalla en las fuentes).</t>
-        </is>
-      </c>
-      <c r="G36" s="12" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>La plataforma fue lanzada el 1 de abril de 2024... constituye una herramienta valiosa de participación ciudadana muy relevante para ciudadanos, candidatos a cargos de elección popular y medios durante la campaña electoral y luego como recurso para el monitoreo del mandato ciudadano. (un despliegue concreto de la plataforma, 2024; sin evidencia de ediciones recurrentes).</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>La Fundación Panamá Participa lanzó Mansa Idea... iniciativa liderada por Paulina Franceschi a través de la Fundación Panamá Participa (sociedad civil). El proceso participativo de origen: 'El 26 de noviembre de 2020, el presidente Laurentino Cortizo Cohen lanzó la iniciativa denominada Pacto del Bicentenario Cerrando Brechas' (gobierno nacional / Concertación Nacional).</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. (la IA procesa el contenido de las propuestas del proceso participativo).</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía. (agregación/síntesis de los aportes ciudadanos = rol sobre el contenido).</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>https://www.panama24horas.com.pa/panama/fundacion-panama-participa-lanza-plataforma-de-propuestas-ciudadanas-mansa-idea/
 https://www.laestrella.com.pa/panama/politica/mansa-idea-una-herramienta-digital-con-propuestas-para-candidatos-YD6746221
@@ -10273,63 +10122,63 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (prensa): VERIFICADO (fuente primaria): el CNE usó IBM Watson Discovery + Studio (ML/NLP) sobre 87.991 documentos de aportes ciudadanos de 847 eventos y 49 espacios de di</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>Consejo Nacional de Educación del Perú</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>https://www.latinno.net/en/case/17232/
 https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional?utm_source=chatgpt.com
@@ -10339,59 +10188,59 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Project: National Digital Transformation Strategy | Ministry of Digital Transformation, Trinidad and Tobago (engage.gov.tt/projects/national-digital-transformation-strategy). Ruta interna confirmatoria: engage.gov.tt/projects/e-democracy-govocal-internal (la instancia corre sobre Go Vocal). En 2026: 'Projects | Ministry of Public Administration and Artificial Intelligence' (engage.gov.tt/projects).</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>EngageTT es una plataforma en linea (engage.gov.tt) donde ciudadanos, empresas y partes interesadas pueden recibir actualizaciones en tiempo real sobre iniciativas de transformacion digital y ofrecer retroalimentacion via encuestas y sondeos (polls); el Ministro anima a todos a participar y enviar ideas y comentarios sobre el NDTS, que se disena para evolucionar mediante el compromiso y la colaboracion continuos. Incluye un 'Open Forum' (engage.gov.tt/ideas/open-forum) y 'Input: Submitting Proposals' (engage.gov.tt/ideas/submitting-proposals).</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="F37" s="12" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>The National Strategy for a Digital TT is finalized, and while the Ministry of Digital Transformation is no longer seeking input, they welcome feedback or comments through the citizen engagement digital platform Engage TT. (engage.gov.tt sigue operativo en 2026 bajo MPAAI).</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>The Ministry of Digital Transformation (MDT) officially presented the National Digital Transformation Strategy (NDTS) 2024-2027... launched during a NDTS Symposium in collaboration with the Inter-American Development Bank (IDB) on Wednesday, February 12th 2025. A major highlight... was the introduction of two new digital tools (EngageTT y AskNDTS). (Lanzamiento/anuncio unico en feb-2025; plataforma de uso continuo pero sin &gt;=2 ediciones de proceso participativo documentadas).</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>The Ministry of Digital Transformation (MDT) officially presented the National Digital Transformation Strategy (NDTS) 2024-2027... and introduced the EngageTT website - an online platform where citizens, businesses, and stakeholders can get real-time updates on digital transformation initiatives, and offer feedback via surveys and polls. (Convocante: gobierno nacional / Ministry of Digital Transformation, hoy MPAAI).</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>Go Vocal Support Base (AI Analysis): 'Access to this feature depends on your plan. Advanced Sensemaking with auto-insights is available in the Premium plan.' -&gt; la IA/NLP de Go Vocal NO es automatica, depende del plan; y para EngageTT solo se documenta 'feedback via surveys and polls'/Open Forum/ideas, SIN mencion de analisis automatico por IA de los aportes. No se halla evidencia de activacion del NLP sobre el contenido en la instancia TT. 3a PASADA (refuerzo): Oxford Insights, 'The country's AI utilisation for citizens is concentrated in a robust Chatbot programme' (mas 'deployment of large language models for internal development purposes') -&gt; la IA ciudadana de TT es el chatbot, NO el analisis de aportes.</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>Sin evidencia de IA aplicada al contenido de los aportes en engage.gov.tt. La unica IA confirmada de cara al ciudadano (AskNDTS/ANANSI) es chatbot de FAQ, excluido del criterio. En 3a pasada, el material de MPAAI 2026 enmarca la IA en el asistente ANANSI y en encuestas de AI-readiness (resultados 'consolidated and reviewed' en talleres), sin mencion de analisis por IA de los aportes del NDTS ni de Go Vocal Sensemaking.</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>https://support.govocal.com/en/articles/8316692-ai-analysis
 https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool
@@ -10413,59 +10262,59 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>UY</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Polis has been used to facilitate discussion and build consensus ... in Uruguay on a national referendum (OCDE 2025, 'Governing with AI')</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists — ran Polis alongside the referendum</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>The algorithm maps participants' responses and clusters opinions, facilitating the identification of positions that are supported by the majority of participants (OCDE 2025)</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>16,499 people cast more than 295,000 votes ... The referendum was lost by less than 1%</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="H38" s="12" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>ran Polis alongside the referendum to look for something deeper than "yes or no"</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>Polis revealed that even where public safety divided people, surprising points of consensus broke through on other issues — bridges between groups</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/
 https://www.oecd.org/en/publications/governing-with-artificial-intelligence_795de142-en.html</t>
@@ -10473,7 +10322,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L39"/>
+  <autoFilter ref="A1:L38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10507,7 +10356,7 @@
       </c>
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>Planilla con 6 pestañas (criterio corregido). 38 casos entran/dudosos · 69 excluidos · 107 en total. Tras dedup e-Cidadania: 37 iniciativas.</t>
+          <t>Planilla con 6 pestañas (criterio corregido). 37 casos entran/dudosos · 70 excluidos · 107 en total. Tras dedup e-Cidadania: 36 iniciativas.</t>
         </is>
       </c>
     </row>
@@ -10554,12 +10403,12 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>PASO 3 — DUDAS a revisar con URL (grupos C y D)</t>
+          <t>PASO 3 — Casos frontera (RESUELTOS)</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>C: TT EngageTT (¿IA planeada?), CO DNP Diálogos (¿usó NLP/ConTexto?), DO CiudadanIA (¿módulo de participación?), CR U-Report (¿participación o sondeo?). D: BR Colab (¿participación o civic tech?). Abrir la URL y decidir.</t>
+          <t>Ya decididos con investigación: ENTRAN TT EngageTT, CO Chatico, BR Colab · SALEN DO CiudadanIA, CO DNP, CR U-Report (+ BR ParticipACT, CR dIAra). Ver casos_frontera_ILIA2026.md. No requiere acción.</t>
         </is>
       </c>
     </row>

--- a/data/gates/planilla_ILIA2026_SIMPLE.xlsx
+++ b/data/gates/planilla_ILIA2026_SIMPLE.xlsx
@@ -6175,7 +6175,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>/home/user/ilia26-participacion/data/fichas/BR-brasil-participativo-clustering-semantic_detalle.json</t>
+          <t>https://github.com/ResidenciaTICBrisa/BP-Classificador-de-Propostas</t>
         </is>
       </c>
     </row>

--- a/data/gates/planilla_ILIA2026_SIMPLE.xlsx
+++ b/data/gates/planilla_ILIA2026_SIMPLE.xlsx
@@ -2230,7 +2230,8 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>https://participacion.digital.gob.cl/es-CL/folders/consultas-ciudadanas</t>
+          <t>https://participacion.digital.gob.cl/es-CL/folders/consultas-ciudadanas
+https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
@@ -2344,7 +2345,8 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/estudio-dialogos-percepciones-de-futuro</t>
+          <t>https://fairlac.iadb.org/estudio-dialogos-percepciones-de-futuro
+https://estudiodialogos.cl/</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
@@ -2462,7 +2464,8 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
+          <t>https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3
+https://ipp.unab.cl/</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -2700,7 +2703,8 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf</t>
+          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf
+https://ipp.unab.cl/publicacion/la-voz-de-los-nuevos-votantes-san-bernardo/</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
@@ -5108,7 +5112,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://cheleloyborolas.com/index.php?Itemid=103&amp;catid=10&amp;id=72545%3Ajefe-de-la-onpe-presenta-avances-en-la-organizacion-de-las-elecciones-generales-2026&amp;option=com_content&amp;view=article</t>
+          <t>https://andina.pe/agencia/noticia-onpe-utilizara-un-nuevo-sistema-computo-resultados-incorporara-ia-1021072.aspx</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5450,8 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>https://participacion.digital.gob.cl/es-CL/folders/consultas-ciudadanas</t>
+          <t>https://participacion.digital.gob.cl/es-CL/folders/consultas-ciudadanas
+https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5525,8 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf</t>
+          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf
+https://ipp.unab.cl/publicacion/la-voz-de-los-nuevos-votantes-san-bernardo/</t>
         </is>
       </c>
     </row>
@@ -5557,7 +5563,8 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
+          <t>https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3
+https://ipp.unab.cl/</t>
         </is>
       </c>
     </row>
@@ -6823,7 +6830,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/ucd-dnp</t>
+          <t>https://dialogosregionales.dnp.gov.co/</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7532,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Informe de Gobierno</t>
+          <t>https://adip.cdmx.gob.mx/comunicacion/nota/la-adip-y-el-gobierno-de-la-ciudad-presentan-victoria-el-robot-que-colaborara-en-la-atencion-de-la-ciudadania</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7748,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://cheleloyborolas.com/index.php?Itemid=103&amp;catid=10&amp;id=72545%3Ajefe-de-la-onpe-presenta-avances-en-la-organizacion-de-las-elecciones-generales-2026&amp;option=com_content&amp;view=article</t>
+          <t>https://andina.pe/agencia/noticia-onpe-utilizara-un-nuevo-sistema-computo-resultados-incorporara-ia-1021072.aspx</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8834,8 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://participacion.digital.gob.cl/es-CL/folders/consultas-ciudadanas</t>
+          <t>https://participacion.digital.gob.cl/es-CL/folders/consultas-ciudadanas
+https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030</t>
         </is>
       </c>
     </row>
@@ -8889,7 +8897,8 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/estudio-dialogos-percepciones-de-futuro</t>
+          <t>https://fairlac.iadb.org/estudio-dialogos-percepciones-de-futuro
+https://estudiodialogos.cl/</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8960,8 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
+          <t>https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3
+https://ipp.unab.cl/</t>
         </is>
       </c>
     </row>
@@ -9077,7 +9087,8 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf</t>
+          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf
+https://ipp.unab.cl/publicacion/la-voz-de-los-nuevos-votantes-san-bernardo/</t>
         </is>
       </c>
     </row>

--- a/data/gates/planilla_ILIA2026_SIMPLE.xlsx
+++ b/data/gates/planilla_ILIA2026_SIMPLE.xlsx
@@ -1996,7 +1996,7 @@
         <is>
           <t>https://www.bcn.cl/procesoconstituyente/cabildos2016/
 https://aclanthology.org/W17-5101/
-https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0267443</t>
+https://journals.plos.org/plosone/article?id=10.1371%2Fjournal.pone.0267443</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
@@ -2230,8 +2230,8 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>https://participacion.digital.gob.cl/es-CL/folders/consultas-ciudadanas
-https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030</t>
+          <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030
+https://participacion.digital.gob.cl/folders/consultas-ciudadanas</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
@@ -2345,8 +2345,8 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/estudio-dialogos-percepciones-de-futuro
-https://estudiodialogos.cl/</t>
+          <t>https://estudiodialogos.cl/
+https://fairlac.iadb.org/en/dialogos-study-perceptions-future</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
@@ -2464,8 +2464,8 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3
-https://ipp.unab.cl/</t>
+          <t>https://ipp.unab.cl/
+https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -3977,8 +3977,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>https://www.gobiernoabierto.ec/boletin-014-2023/
-https://ia.gobiernoabierto.ec/
+          <t>https://ia.gobiernoabierto.ec/
 https://ia.gobiernoabierto.ec/acercade</t>
         </is>
       </c>
@@ -4094,7 +4093,7 @@
       <c r="W30" s="2" t="inlineStr">
         <is>
           <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
-https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/?utm_source=chatgpt.com
+https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/
 https://dppa.un.org/en/using-power-of-ai-to-boost-youth-political-participation-guatemala</t>
         </is>
       </c>
@@ -4777,9 +4776,9 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>https://www.latinno.net/en/case/17232/
-https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional?utm_source=chatgpt.com
-https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080</t>
+          <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional
+https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080
+https://andina.pe/agencia/noticia-usan-inteligencia-artificial-para-formular-proyecto-educativo-nacional-al-2036-777369.aspx</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
@@ -5450,8 +5449,8 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>https://participacion.digital.gob.cl/es-CL/folders/consultas-ciudadanas
-https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030</t>
+          <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030
+https://participacion.digital.gob.cl/folders/consultas-ciudadanas</t>
         </is>
       </c>
     </row>
@@ -5563,8 +5562,8 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3
-https://ipp.unab.cl/</t>
+          <t>https://ipp.unab.cl/
+https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6289,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=Jaque%20y%20la%20Gu%C3%ADa%20de,Contiene%20informaci%C3%B3n%2C%20entre</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6586,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.15532?utm_source=chatgpt.com</t>
+          <t>https://arxiv.org/abs/2303.15532</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6991,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://projects.itforchange.net/mavc/wp-content/uploads/2017/09/Voice-or-Chatter_Case-Study_Colombia_August-2017.pdf?utm_source=chatgpt.com</t>
+          <t>https://projects.itforchange.net/mavc/wp-content/uploads/2017/09/Voice-or-Chatter_Case-Study_Colombia_August-2017.pdf</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7180,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/latin-america/comunicados-de-prensa/sara-la-nueva-herramienta-de-inteligencia-artificial-para-combatir-la-violencia-de-genero-en-centroamerica-0</t>
+          <t>https://www.undp.org/es/guatemala/comunicados-de-prensa/sara-la-nueva-herramienta-de-inteligencia-artificial-para-combatir-la-violencia-de-genero-en-centroamerica</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7261,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.caf.com/es/actualidad/noticias/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
+          <t>https://www.caf.com/es/actualidad/noticias/2021/07/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7315,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci</t>
+          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci-1</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7558,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=para%20identificar%20posibles%20trastornos,de%20las%20dificultades%20de%20%C3%ADndole</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7639,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://osf.io/cu6w3</t>
+          <t>https://algoritmoscide.org/proyectos/sufragio-seguro/</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7693,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=virtual%2Fchatbot%20que%20funciona%20por%20WhatsApp,que%20realice%20una%20observaci%C3%B3n%20f%C3%ADsica</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7801,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/paraempleo</t>
+          <t>https://fairlac.iadb.org/en/paraempleo</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7828,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/content/dam/oecd/es/publications/reports/2022/03/the-strategic-and-responsible-use-of-artificial-intelligence-in-the-public-sector-of-latin-america-and-the-caribbean_17c90e5e/5b189cb4-es.pdf#:~:text=El%20chatbot%20virtual%20creado%20por,desarrollo%20de%20soluciones%20de%20IA</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7855,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030?utm_source=chatgpt.com</t>
+          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030</t>
         </is>
       </c>
     </row>
@@ -8194,8 +8193,8 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2511.01545
-https://arxiv.org/abs/2509.21292
+          <t>https://arxiv.org/abs/2509.21292
+https://arxiv.org/abs/2511.01545
 https://github.com/ResidenciaTICBrisa/BP-Classificador-de-Propostas
 https://www.gov.br/secretariageral/pt-br/noticias/2024/dezembro/secretaria-geral-da-presidencia-formaliza-parceria-com-plataforma-decidim
 https://www.gov.br/secretariageral/pt-br/noticias/2025/novembro/brasil-participativo-integra-comite-internacional-de-democracia-digital
@@ -8704,7 +8703,7 @@
         <is>
           <t>https://www.bcn.cl/procesoconstituyente/cabildos2016/
 https://aclanthology.org/W17-5101/
-https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0267443</t>
+https://journals.plos.org/plosone/article?id=10.1371%2Fjournal.pone.0267443</t>
         </is>
       </c>
     </row>
@@ -8834,8 +8833,8 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://participacion.digital.gob.cl/es-CL/folders/consultas-ciudadanas
-https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030</t>
+          <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030
+https://participacion.digital.gob.cl/folders/consultas-ciudadanas</t>
         </is>
       </c>
     </row>
@@ -8897,8 +8896,8 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/estudio-dialogos-percepciones-de-futuro
-https://estudiodialogos.cl/</t>
+          <t>https://estudiodialogos.cl/
+https://fairlac.iadb.org/en/dialogos-study-perceptions-future</t>
         </is>
       </c>
     </row>
@@ -8960,8 +8959,8 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3
-https://ipp.unab.cl/</t>
+          <t>https://ipp.unab.cl/
+https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
         </is>
       </c>
     </row>
@@ -9370,8 +9369,8 @@
       <c r="K23" s="12" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://www.govocal.com/
-https://vinadecide.cl/pages/presupuestoparticipativo</t>
+          <t>https://vinadecide.cl/pages/presupuestoparticipativo
+https://www.govocal.com/</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9745,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://www.gobiernoabierto.ec/boletin-014-2023/
+          <t>https://ia.gobiernoabierto.ec/
 https://ia.gobiernoabierto.ec/
 https://ia.gobiernoabierto.ec/acercade</t>
         </is>
@@ -9811,7 +9810,7 @@
       <c r="L30" s="2" t="inlineStr">
         <is>
           <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
-https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/?utm_source=chatgpt.com
+https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/
 https://dppa.un.org/en/using-power-of-ai-to-boost-youth-political-participation-guatemala</t>
         </is>
       </c>
@@ -10191,8 +10190,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://www.latinno.net/en/case/17232/
-https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional?utm_source=chatgpt.com
+          <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional
 https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080
 https://andina.pe/agencia/noticia-usan-inteligencia-artificial-para-formular-proyecto-educativo-nacional-al-2036-777369.aspx
 https://elperuano.pe/noticia/87397-usan-inteligencia-artificial-para-formular-el-proyecto-educativo-nacional-al-2036</t>

--- a/data/gates/planilla_ILIA2026_SIMPLE.xlsx
+++ b/data/gates/planilla_ILIA2026_SIMPLE.xlsx
@@ -15,10 +15,10 @@
     <sheet name="6 · Metodología (CENIA v2)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos (entran+dudosos)'!$A$1:$X$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos (entran+dudosos)'!$A$1:$X$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2 · A validar a mano'!$A$1:$G$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 · Excluidos'!$A$1:$E$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 · Evidencia y fuentes'!$A$1:$L$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 · Excluidos'!$A$1:$E$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 · Evidencia y fuentes'!$A$1:$L$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -153,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -177,9 +177,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -585,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X38"/>
+  <dimension ref="A1:X35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2714,11 +2711,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>➜ RESOLVER DUDA</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>CL</t>
@@ -2726,17 +2719,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Participa Pudahuel — Presupuesto Participativo deliberativo (plataforma Go Vocal/CitizenLab)</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>(sin revisar)</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>DUDA(lean NO)</t>
+          <t>Participación Ciudadana Proceso Constitucional</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2746,26 +2739,30 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>BAJA (plataforma con capacidad de IA confirmada; uso sobre los aportes no confirmado)</t>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Presupuestos Participativos</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
+          <t>Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="n">
         <v>2</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>gobierno local</t>
+          <t>gobierno nacional</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2775,7 +2772,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>no-claro</t>
+          <t>contenido</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2785,27 +2782,27 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>NLP; Clustering</t>
+          <t>NLP - Tópicos</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>no-claro</t>
+          <t>no</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>Modelo de gestión presupuestaria deliberativa y vinculante de la Municipalidad de Pudahuel (presupuesto municipal 2023): participación virtual abierta + grupos de especial protección; +1.200 participantes y 150+ iniciativas de proyectos.</t>
+          <t>Análisis de los resultados obtenidos de los Diálogos Ciudadanos Autoconvocados dentro del proceso constitucional</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>Municipalidad de Pudahuel</t>
+          <t>Secretaría de Participación Ciudadana</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2813,19 +2810,17 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="V19" s="5" t="n">
-        <v>4</v>
+      <c r="V19" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>https://www.govocal.com/en/cases
-https://participa.mpudahuel.cl/
-https://go-vocal.com/</t>
+          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>CL-participa-pudahuel-presupuesto</t>
+          <t>CL-participacion-ciudadana-proceso-constitu</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2833,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Participación Ciudadana Proceso Constitucional</t>
+          <t>Tenemos que hablar de Chile</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2848,7 +2843,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SI*</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2881,12 +2876,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional</t>
+          <t>universidad</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2896,7 +2891,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2916,17 +2911,17 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>Análisis de los resultados obtenidos de los Diálogos Ciudadanos Autoconvocados dentro del proceso constitucional</t>
+          <t>Iniciativa de diálogo y participación llevada a cabo por la UCH y PUC en el contexto de manifestaciones sociales</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>Secretaría de Participación Ciudadana</t>
+          <t>Universidad de Chile y Pontificia Universidad Católica de Chile</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="V20" s="4" t="n">
@@ -2934,12 +2929,13 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
+          <t>https://www.tenemosquehablardechile.cl/
+https://static1.squarespace.com/static/630d0dbf05b8104ed4d55d7f/t/67f694b2f91e4f228bb941cb/1744213189210/01.+Primer-InformeTQHDCH.pdf</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>CL-participacion-ciudadana-proceso-constitu</t>
+          <t>CL-tenemos-que-hablar-de-chile</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2948,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Tenemos que hablar de Chile</t>
+          <t>Un encuentro para la equidad de género en la movilidad en Chile</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -2962,7 +2958,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>SI*</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -3000,7 +2996,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3010,7 +3006,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3030,500 +3026,499 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>Iniciativa de diálogo y participación llevada a cabo por la UCH y PUC en el contexto de manifestaciones sociales</t>
+          <t>Espacio participativo para levantar opiniones y propuestas de autoridades, miembros de la sociedad civil y académicos sobre la movilidad con perspectiva de género en Chile.</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>Universidad de Chile y Pontificia Universidad Católica de Chile</t>
+          <t>Universidad Andres Bello</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="V21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tenemosquehablardechile.cl/
-https://static1.squarespace.com/static/630d0dbf05b8104ed4d55d7f/t/67f694b2f91e4f228bb941cb/1744213189210/01.+Primer-InformeTQHDCH.pdf</t>
-        </is>
-      </c>
-      <c r="X21" s="2" t="inlineStr">
-        <is>
-          <t>CL-tenemos-que-hablar-de-chile</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Un encuentro para la equidad de género en la movilidad en Chile</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>universidad</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>Privado</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>Privado</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>NLP - Tópicos</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>Espacio participativo para levantar opiniones y propuestas de autoridades, miembros de la sociedad civil y académicos sobre la movilidad con perspectiva de género en Chile.</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>Universidad Andres Bello</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>https://ipp.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/
 https://noticiasrepositorio.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/
 https://public.tableau.com/app/profile/ivania.yovanovic/viz/UnencuentroparalaequidaddegneroenlamovilidadenChile-CIUDHAD/CIUDHADTransporteyGnero</t>
         </is>
       </c>
-      <c r="X22" s="2" t="inlineStr">
+      <c r="X21" s="2" t="inlineStr">
         <is>
           <t>CL-un-encuentro-para-la-equidad-de-genero-e</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>➜ RESOLVER DUDA</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Viña Decide — Primer Presupuesto Participativo de Viña del Mar (plataforma Go Vocal/CitizenLab)</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>(sin revisar)</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>DUDA(lean SI)</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Chatico</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>BAJA (capacidad de plataforma confirmada; uso específico sobre los aportes no confirmado)</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Presupuestos Participativos</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="n">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Referendos e Iniciativas Populares; Presupuestos Participativos</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>gobierno local</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>no-claro</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>Privado</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>NLP; Clustering</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>no-claro</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>Primer Presupuesto Participativo 2024 de la Municipalidad de Viña del Mar ($200M CLP) para la reconstrucción de espacios públicos tras el megaincendio de feb-2024; vecinos (desde 14 años) proponen y votan proyectos en Achupallas, Reñaca Alto, Viña Oriente y Miraflores.</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>Municipalidad de Viña del Mar</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="V23" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.govocal.com/en/cases
-https://vinadecide.cl/pages/presupuestoparticipativo
-https://www.govocal.com/</t>
-        </is>
-      </c>
-      <c r="X23" s="2" t="inlineStr">
-        <is>
-          <t>CL-vina-decide-presupuesto-participativo</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Chatico</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>Privado; Gobierno</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>NLP; LLM</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Referendos e Iniciativas Populares; Presupuestos Participativos</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>gobierno local</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>Privado; Gobierno</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>NLP; LLM</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Atención automatizada mediante procesamiento de lenguaje natural, análisis de datos y algoritmos de inteligencia artificial para responder consultas ciudadanas sobre más de 400 temas de interés.
 </t>
         </is>
       </c>
-      <c r="T24" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
         <is>
           <t>Secretaría General de la Alcaldía Mayor de Bogotá</t>
         </is>
       </c>
-      <c r="U24" s="2" t="inlineStr">
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="V24" s="4" t="n">
+      <c r="V22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>https://secretariageneral.gov.co/noticias/chatico-el-agente-virtual-de-servicio-la-ciudadania-supero-los-36-millones-de-conversaciones
 https://bogota.gov.co/mi-ciudad/gestion-publica/distrito-presenta-su-agente-virtual-chatico-que-guia-la-ciudadania
 https://bogota.gov.co/mi-ciudad/participacion-y-cultura-ciudadana/plan-desarrollo-bogota-camina-segura-tuvo-147-mil-aportes-ciudadanos</t>
         </is>
       </c>
-      <c r="X24" s="2" t="inlineStr">
+      <c r="X22" s="2" t="inlineStr">
         <is>
           <t>CO-chatico</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-      <c r="B25" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Citibeats + PNUD Colombia (analítica de datos para la deliberación pública juvenil)</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Participación Digital</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="J23" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>organización internacional</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>Mixto</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>NLP; Machine Learning; Clasificación de texto; Análisis de sentimiento; Clustering temático</t>
         </is>
       </c>
-      <c r="R25" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>Iniciativa del Laboratorio de Aceleración del PNUD Colombia que, en el contexto del paro nacional de 2021, usó la plataforma de IA Citibeats para monitorear y agrupar en tiempo real las opiniones y propuestas de la juventud colombiana sobre la coyuntura del país, con el fin de 'mejorar la deliberación pública'. La IA filtra y clasifica contenido de fuentes abiertas (Twitter, Facebook, Instagram, foros, blogs, noticias y comentarios de video). En paralelo, el PNUD y aliados como El Avispero generaron espacios presenciales para contrastar lo dicho en las conversaciones en línea; no hay evidencia de que Citibeats procesara los aportes de un proceso participativo formal convocado (consulta, cabildo o deliberación con inputs estructurados), sino principalmente social listening de medios digitales.</t>
         </is>
       </c>
-      <c r="T25" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
         <is>
           <t>PNUD Colombia - Laboratorio de Aceleración (Accelerator Lab), con la plataforma de IA Citibeats (empresa, España)</t>
         </is>
       </c>
-      <c r="U25" s="2" t="inlineStr">
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="V25" s="5" t="n">
+      <c r="V23" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="W25" s="2" t="inlineStr">
+      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>https://www.undp.org/es/colombia/blog/analitica-de-datos-para-mejorar-la-deliberacion-publica-en-colombia
 https://www.undp.org/es/colombia/laboratorio-aceleracion
 https://www.undp.org/es/colombia/blog/data-analytics-improve-public-deliberation-colombia</t>
         </is>
       </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>CO-citibeats-pnud-colombia-deliberacion-pub</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>ECHO – HáblameD Medellín</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Implementación; Análisis</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>organización internacional; gobierno local</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Mixto</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>Voz a Texto; NLP; LLM</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>IA que capta voz ciudadana en debates guiados y clasifica cada enunciado en metas ODS, generando visualizaciones para la planificación territorial</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>CO-echo-hablamed-medellin</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>(sin revisar)</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>DUDA(lean SI)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>MEDIA (múltiples fuentes de prensa independientes; sin verificación técnica del método; cobertura crítica)</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Presupuestos Participativos; Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Análisis; Traducción Política</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Plataforma</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>sociedad civil</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>Sociedad Civil</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>LLM; NLP</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>Plataforma participativa donde jóvenes del resguardo Zenú deciden por votación digital la asignación de presupuestos locales del cabildo y debaten proyectos de ley / proponen iniciativas ciudadanas colectivas.</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>Resguardo indígena Zenú (Reparo Torrente, Bajo Sinú); creador Carlos Redondo Rincón</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>https://cerosetenta.uniandes.edu.co/
+https://gaitanaia.org/
+https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/</t>
+        </is>
+      </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>CO-citibeats-pnud-colombia-deliberacion-pub</t>
+          <t>CO-gaitana-ia-resguardo-zenu</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3531,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>ECHO – HáblameD Medellín</t>
+          <t>Tenemos que hablar de Colombia</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -3556,7 +3551,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3566,7 +3561,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
@@ -3579,7 +3574,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>organización internacional; gobierno local</t>
+          <t>universidad; empresa; sociedad civil</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3594,37 +3589,37 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Voz a Texto; NLP; LLM</t>
+          <t>NLP - Tópicos; NLP - Sentiment</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>IA que capta voz ciudadana en debates guiados y clasifica cada enunciado en metas ODS, generando visualizaciones para la planificación territorial</t>
+          <t>Plataforma colaborativa de diálogo e incidencia ciudadana para la conversación entre diversos actores de la sociedad colombiana, surgido a partir de eventos de manifestaciones sociales.</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="V26" s="4" t="n">
@@ -3632,39 +3627,36 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+          <t>https://tenemosquehablarcolombia.co/
+https://tenemosquehablarcolombia.co/resultados/</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>CO-echo-hablamed-medellin</t>
+          <t>CO-tenemos-que-hablar-de-colombia</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>➜ RESOLVER DUDA</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>(sin revisar)</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>DUDA(lean SI)</t>
+          <t xml:space="preserve">PAGA IA </t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3674,17 +3666,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (múltiples fuentes de prensa independientes; sin verificación técnica del método; cobertura crítica)</t>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Presupuestos Participativos; Gobernanza Colaborativa</t>
+          <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Análisis; Traducción Política</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
@@ -3697,10 +3689,14 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>sociedad civil</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>gobierno nacional; sociedad civil</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Mixto</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
@@ -3718,7 +3714,7 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>LLM; NLP</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
@@ -3728,32 +3724,31 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>Plataforma participativa donde jóvenes del resguardo Zenú deciden por votación digital la asignación de presupuestos locales del cabildo y debaten proyectos de ley / proponen iniciativas ciudadanas colectivas.</t>
+          <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto. Analiza datos de planes de acción de gobierno abierto de Ecuador y otros países de Hispanoamérica para sugerir actividades e hitos relacionados con temas propuestos por los usuarios</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>Resguardo indígena Zenú (Reparo Torrente, Bajo Sinú); creador Carlos Redondo Rincón</t>
+          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="V27" s="5" t="n">
-        <v>3</v>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>https://cerosetenta.uniandes.edu.co/
-https://gaitanaia.org/
-https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/</t>
+          <t>https://ia.gobiernoabierto.ec/
+https://ia.gobiernoabierto.ec/acercade</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>CO-gaitana-ia-resguardo-zenu</t>
+          <t>EC-paga-ia</t>
         </is>
       </c>
     </row>
@@ -3761,12 +3756,12 @@
       <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Tenemos que hablar de Colombia</t>
+          <t xml:space="preserve">Guatemala Joven Conversa </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -3786,7 +3781,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3796,7 +3791,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
@@ -3809,7 +3804,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>universidad; empresa; sociedad civil</t>
+          <t>organización internacional; sociedad civil</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3824,17 +3819,17 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil</t>
+          <t>Gobierno</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos; NLP - Sentiment</t>
+          <t>NLP - Sentiment; NLP - Tópicos</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -3844,17 +3839,17 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>Plataforma colaborativa de diálogo e incidencia ciudadana para la conversación entre diversos actores de la sociedad colombiana, surgido a partir de eventos de manifestaciones sociales.</t>
+          <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarrollo y la lucha contra la corrupción.</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
+          <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="V28" s="4" t="n">
@@ -3862,26 +3857,31 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>https://tenemosquehablarcolombia.co/
-https://tenemosquehablarcolombia.co/resultados/</t>
+          <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
+https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/
+https://dppa.un.org/en/using-power-of-ai-to-boost-youth-political-participation-guatemala</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>CO-tenemos-que-hablar-de-colombia</t>
+          <t>GT-guatemala-joven-conversa</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
+        </is>
+      </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAGA IA </t>
+          <t xml:space="preserve">RedPública + iVerify </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
@@ -3919,17 +3919,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional; sociedad civil</t>
+          <t>organización internacional; universidad</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3939,32 +3939,32 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil</t>
+          <t>Gobierno; Academia</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Internacional, Nacional</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>NLP - Tópicos</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto. Analiza datos de planes de acción de gobierno abierto de Ecuador y otros países de Hispanoamérica para sugerir actividades e hitos relacionados con temas propuestos por los usuarios</t>
+          <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias. Integra iVerify, una herramienta que utiliza aprendizaje automático para detectar y clasificar desinformación electoral antes de su publicación.</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
+          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3977,13 +3977,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>https://ia.gobiernoabierto.ec/
-https://ia.gobiernoabierto.ec/acercade</t>
+          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>EC-paga-ia</t>
+          <t>HN-redpublica-iverify</t>
         </is>
       </c>
     </row>
@@ -3991,12 +3990,12 @@
       <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guatemala Joven Conversa </t>
+          <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4016,17 +4015,17 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Gobernanza Colaborativa; Participación Digital</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
@@ -4039,12 +4038,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>organización internacional; sociedad civil</t>
+          <t>gobierno local</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -4059,27 +4058,27 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>NLP - Sentiment; NLP - Tópicos</t>
+          <t>NLP; Otros(no especificado)</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>no-claro</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarrollo y la lucha contra la corrupción.</t>
+          <t>Elaboración del Programa de Gobierno del Estado de Guanajuato 2024-2030 ('Gobierno de la Gente'), un plan de gobierno construido con participación ciudadana: se recorrió el territorio y se realizaron cuatro talleres regionales (noreste, norte, centro y sur) con representación de los 46 municipios, integrando la voz de más de 26,000 personas mediante talleres y consultas. El contenido fue validado por el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG), conformado por ciudadanía, la Gobernadora, secretarios de cada eje e IPLANEG. Se utilizaron herramientas de inteligencia artificial para procesar y organizar las miles de ideas y propuestas recibidas, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región, transformando el diálogo social en datos para la toma de decisiones que alimentaron los ejes del programa. Adicionalmente existe la asistente virtual 'Esperanza' para consultar el programa ya publicado.</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
+          <t>Gobierno del Estado de Guanajuato — Instituto de Planeación, Estadística y Geografía del Estado de Guanajuato (IPLANEG), con validación del COPLADEG. Titular: Gobernadora Libia Dennise García Muñoz Ledo.</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -4087,19 +4086,19 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="V30" s="4" t="n">
-        <v>0</v>
+      <c r="V30" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
-https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/
-https://dppa.un.org/en/using-power-of-ai-to-boost-youth-political-participation-guatemala</t>
+          <t>https://guanajuatointeligente.com/como-hicimos-el-programa/
+https://iplaneg.guanajuato.gob.mx/programagobierno24-30/
+https://iplaneg.guanajuato.gob.mx/wp-content/uploads/03-2.05-Diagnostico-Programa-de-Gobierno-2024-2030-_Diagnostico-Estatal-2025_.pdf</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>GT-guatemala-joven-conversa</t>
+          <t>MX-guanajuato-inteligente-2024-2030</t>
         </is>
       </c>
     </row>
@@ -4111,12 +4110,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RedPública + iVerify </t>
+          <t>Presupuesto CRECES</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4136,17 +4135,17 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Referendos e Iniciativas Populares</t>
+          <t>Presupuestos Participativos</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
@@ -4159,7 +4158,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>organización internacional; universidad</t>
+          <t>gobierno local</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4174,17 +4173,17 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Gobierno; Academia</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Internacional, Nacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos</t>
+          <t>Chatbot - Inespecífico</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
@@ -4194,30 +4193,30 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias. Integra iVerify, una herramienta que utiliza aprendizaje automático para detectar y clasificar desinformación electoral antes de su publicación.</t>
+          <t>Presupuesto participativo del Ayuntamiento de Hermosillo en México. Utiliza un chatbot que a través de IA simplifica y facilita la votación de los presupuestos participativos</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
+          <t>Ayundamiento de Hermosilla</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V31" s="4" t="n">
-        <v>0</v>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="V31" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
+          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>HN-redpublica-iverify</t>
+          <t>MX-presupuesto-creces</t>
         </is>
       </c>
     </row>
@@ -4225,12 +4224,12 @@
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
+          <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -4250,17 +4249,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa; Participación Digital</t>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Análisis; Traducción Política</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
@@ -4268,176 +4267,184 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
+          <t>Plataforma</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>sociedad civil; gobierno nacional</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>Sociedad Civil</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>no-claro</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>Mansa Idea (www.mansaidea.com) es una plataforma digital basada en inteligencia artificial lanzada el 1 de abril de 2024 por la Fundación Panamá Participa (sociedad civil), liderada por Paulina Franceschi. La plataforma organiza y hace navegables más de 175.000 ideas y propuestas ciudadanas generadas durante el Pacto del Bicentenario 'Cerrando Brechas' (proceso participativo nacional convocado por el gobierno de Panamá / Concertación Nacional, presidente Cortizo, 2020-2021), agregando los consensos nacionales y regionales/provinciales por tema en un solo clic. La IA se aplica sobre el CONTENIDO de los aportes ciudadanos (organiza, agrega y sintetiza el corpus de propuestas) para convertirlo en una base de datos navegable. El uso de la IA es un tratamiento PUNTERAL (~2024) de un corpus histórico de un proceso participativo ya cerrado (el Pacto fue 2020-2021), orientado a elevar el nivel de la conversación electoral 2024 y a dotar a candidatos, medios y ciudadanía de una herramienta para alinear planes con las necesidades de la población y monitorear el mandato ciudadano. IMPORTANTE: el proceso participativo original (recolección de aportes) fue convocado por el gobierno; la capa de IA (Mansa Idea) la desarrolla la sociedad civil sobre ese corpus ya recolectado.</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>Fundación Panamá Participa (sociedad civil, Panamá), iniciativa liderada por Paulina Franceschi. El proceso participativo de origen (Pacto del Bicentenario 'Cerrando Brechas') fue convocado por el Gobierno de Panamá a través del mecanismo de Concertación Nacional para el Desarrollo (presidente Laurentino Cortizo), con apoyo del PNUD.</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="V32" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>https://mansaidea.com/ (intentar archive.org / cache); buscar 'Mansa Idea metodología inteligencia artificial procesamiento propuestas' y entrevistas técnicas a Paulina Franceschi / Fundación Panamá Participa.
+https://mansaidea.com/ ; buscar 'Mansa Idea 2025' / 'Mansa Idea 2026' / 'Fundación Panamá Participa actividad reciente'.
+https://mansaidea.com/ ; buscar evidencia de actualizaciones periódicas del corpus o nuevas convocatorias.</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>PA-mansa-idea-pacto-del-bicentenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>gobierno local</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>otra institución pública</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>NLP; Otros(no especificado)</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>no-claro</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>Elaboración del Programa de Gobierno del Estado de Guanajuato 2024-2030 ('Gobierno de la Gente'), un plan de gobierno construido con participación ciudadana: se recorrió el territorio y se realizaron cuatro talleres regionales (noreste, norte, centro y sur) con representación de los 46 municipios, integrando la voz de más de 26,000 personas mediante talleres y consultas. El contenido fue validado por el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG), conformado por ciudadanía, la Gobernadora, secretarios de cada eje e IPLANEG. Se utilizaron herramientas de inteligencia artificial para procesar y organizar las miles de ideas y propuestas recibidas, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región, transformando el diálogo social en datos para la toma de decisiones que alimentaron los ejes del programa. Adicionalmente existe la asistente virtual 'Esperanza' para consultar el programa ya publicado.</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno del Estado de Guanajuato — Instituto de Planeación, Estadística y Geografía del Estado de Guanajuato (IPLANEG), con validación del COPLADEG. Titular: Gobernadora Libia Dennise García Muñoz Ledo.</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="V32" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>https://guanajuatointeligente.com/como-hicimos-el-programa/
-https://iplaneg.guanajuato.gob.mx/programagobierno24-30/
-https://iplaneg.guanajuato.gob.mx/wp-content/uploads/03-2.05-Diagnostico-Programa-de-Gobierno-2024-2030-_Diagnostico-Estatal-2025_.pdf</t>
-        </is>
-      </c>
-      <c r="X32" s="2" t="inlineStr">
-        <is>
-          <t>MX-guanajuato-inteligente-2024-2030</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>➜ RESOLVER DUDA</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Jalisco - Consulta ¡Armemos un Plan! (Plan Estatal de Desarrollo y Gobernanza 2024-2030)</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>(sin revisar)</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>DUDA(lean NO)</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="n">
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>NLP - Tópicos; NLP - Sentiment</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>Una consulta pública para recoger opiniones sobre el Proyecto Educativo Nacional 2036, utilizando encuestas en línea, talleres y mesas deliberativas.</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>Consejo Nacional de Educación del Perú</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="V33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>gobierno local</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>no-claro</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="2" t="inlineStr"/>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>Consulta ciudadana '¡Armemos un Plan!' convocada por el Gobierno de Jalisco a través de la Secretaría de Planeación y Participación Ciudadana (SPPC) para construir el Plan Estatal de Desarrollo y Gobernanza 2024-2030. Ejercicio abierto e inclusivo del 20 de febrero al 17 de abril de 2025 que registró 675,484 participaciones (aprox. 624,226 participaciones digitales + 25,176 niñas, niños y adolescentes mediante un mecanismo especialmente diseñado). Combinó: una encuesta representativa 'casa por casa' con rigor estadístico y metodológico; consulta digital abierta que recibió 15,899 propuestas ciudadanas escritas (temas: espacios públicos/deportivos/recreativos, medio ambiente y movilidad, agua y territorio, turismo rural, vivienda digna, economías locales); 12 foros regionales y 9 foros temáticos / mesas de trabajo con 5,563 participantes presenciales; 168 mesas regionales y 47 sectoriales donde se identificaron y discutieron 1,349 problemáticas; e instalación de 18 Consejos de Participación y Planeación (1 estatal, 12 regionales, 5 sectoriales). El resultado se estructuró en 5 ejes, 36 temas, 50 objetivos estratégicos, 197-198 proyectos y 82 indicadores de seguimiento.</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno del Estado de Jalisco — Secretaría de Planeación y Participación Ciudadana (SPPC). Titular: Cynthia Cantero Pacheco. Apoyo de información estadística/geográfica: Instituto de Información Estadística y Geográfica de Jalisco (IIEG). Gobernador: Pablo Lemus Navarro (administración 2024-2030).</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="V33" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>https://armemosunplan.mx/wp-content/uploads/2025/10/Armemos-un-Plan-Informe-de-Consulta-COLOR-NNA-v2.4.pdf
-https://plan.jalisco.gob.mx/documentos-metodologicos/
-https://iieg.gob.mx/ns/</t>
+          <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional
+https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080
+https://andina.pe/agencia/noticia-usan-inteligencia-artificial-para-formular-proyecto-educativo-nacional-al-2036-777369.aspx</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>MX-jalisco-armemos-un-plan</t>
+          <t>PE-consulta-ciudadana-sobre-el-proyecto-nac</t>
         </is>
       </c>
     </row>
@@ -4449,12 +4456,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Presupuesto CRECES</t>
+          <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -4462,9 +4469,9 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>DUDA(lean NO)</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4474,30 +4481,26 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Presupuestos Participativos</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>gobierno local</t>
+          <t>gobierno nacional</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -4507,7 +4510,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>contenido</t>
+          <t>no-claro</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4517,27 +4520,27 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>Chatbot - Inespecífico</t>
+          <t>NLP; Resumen automatico; Clasificacion/agrupacion de texto (capacidad de la plataforma sujeta a plan Premium; activacion NO confirmada en TT)</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>no-claro</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Presupuesto participativo del Ayuntamiento de Hermosillo en México. Utiliza un chatbot que a través de IA simplifica y facilita la votación de los presupuestos participativos</t>
+          <t>EngageTT (engage.gov.tt) es la plataforma de participacion ciudadana del Ministry of Digital Transformation de Trinidad y Tobago (desde mayo 2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), lanzada en el simposio del NDTS el 12 de febrero de 2025 junto al BID (IDB). Se usa como canal de participacion en el proceso de planificacion nacional del National Digital Transformation Strategy (NDTS) 2024-2027, donde ciudadanos, empresas y partes interesadas reciben actualizaciones y aportan retroalimentacion via encuestas, sondeos (polls), un 'Open Forum' de ideas y el envio de propuestas. La instancia corre sobre el software Go Vocal (antes CitizenLab) -confirmado por la ruta interna 'projects/e-democracy-govocal-internal'-. Go Vocal incorpora un modulo de IA/NLP de 'Sensemaking' (analisis y resumen automatico de aportes), pero ese modulo NO viene activo por defecto: segun la documentacion de soporte de Go Vocal, el acceso a la funcion de AI Analysis/Sensemaking DEPENDE DEL PLAN contratado (Advanced Sensemaking con auto-insights esta en el plan Premium). Tras 2a pasada de investigacion (&gt;=14 busquedas/fetches) NO se halla evidencia alguna de que la instancia de Trinidad active ni use esas funciones de IA sobre el CONTENIDO de los aportes; toda la documentacion describe a EngageTT como recolector (surveys, polls, Open Forum, ideas), es decir plataforma usada como formulario sin analisis automatico confirmado. Existe ademas AskNDTS, un chatbot/PWA de IA conversacional para responder preguntas sobre el NDTS (rol de FAQ informativo, EXCLUIDO del criterio).</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>Ayundamiento de Hermosilla</t>
+          <t>Ministry of Digital Transformation de Trinidad y Tobago (desde el 23-may-2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), en colaboracion con el Banco Interamericano de Desarrollo (BID/IDB). Plataforma de software: Go Vocal (antes CitizenLab), empresa belga.</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4546,16 +4549,18 @@
         </is>
       </c>
       <c r="V34" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
+          <t>https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
+https://www.govocal.com/plans
+https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>MX-presupuesto-creces</t>
+          <t>TT-engagett-plataforma-go-vocal</t>
         </is>
       </c>
     </row>
@@ -4563,24 +4568,24 @@
       <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>UY</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
+          <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>(sin revisar)</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>sí</t>
@@ -4588,17 +4593,17 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>MEDIA (fuente primaria + OCDE 2025; fetch primario bloqueado por proxy, citas vía repo/WebSearch)</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
+          <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Análisis; Traducción Política</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
@@ -4606,17 +4611,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>sociedad civil; gobierno nacional</t>
+          <t>universidad</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4626,399 +4631,55 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil</t>
+          <t>Sociedad Civil; Academia</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr"/>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>Clustering; ML - Inespecífico</t>
+        </is>
+      </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>no-claro</t>
+          <t>no</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>Mansa Idea (www.mansaidea.com) es una plataforma digital basada en inteligencia artificial lanzada el 1 de abril de 2024 por la Fundación Panamá Participa (sociedad civil), liderada por Paulina Franceschi. La plataforma organiza y hace navegables más de 175.000 ideas y propuestas ciudadanas generadas durante el Pacto del Bicentenario 'Cerrando Brechas' (proceso participativo nacional convocado por el gobierno de Panamá / Concertación Nacional, presidente Cortizo, 2020-2021), agregando los consensos nacionales y regionales/provinciales por tema en un solo clic. La IA se aplica sobre el CONTENIDO de los aportes ciudadanos (organiza, agrega y sintetiza el corpus de propuestas) para convertirlo en una base de datos navegable. El uso de la IA es un tratamiento PUNTERAL (~2024) de un corpus histórico de un proceso participativo ya cerrado (el Pacto fue 2020-2021), orientado a elevar el nivel de la conversación electoral 2024 y a dotar a candidatos, medios y ciudadanía de una herramienta para alinear planes con las necesidades de la población y monitorear el mandato ciudadano. IMPORTANTE: el proceso participativo original (recolección de aportes) fue convocado por el gobierno; la capa de IA (Mansa Idea) la desarrolla la sociedad civil sobre ese corpus ya recolectado.</t>
+          <t>Referéndum nacional para derogar 135 artículos de la Ley de Urgente Consideración (LUC). Un equipo de la Universidad de la República corrió una conversación Pol.is en paralelo al referéndum del 27/03/2022 (documentado como caso 2021).</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>Fundación Panamá Participa (sociedad civil, Panamá), iniciativa liderada por Paulina Franceschi. El proceso participativo de origen (Pacto del Bicentenario 'Cerrando Brechas') fue convocado por el Gobierno de Panamá a través del mecanismo de Concertación Nacional para el Desarrollo (presidente Laurentino Cortizo), con apoyo del PNUD.</t>
+          <t>Equipo de 13 personas de la Universidad de la República (UdelaR) — ingenieros, comunicadores y científicos de datos; plataforma Pol.is (The Computational Democracy Project)</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="V35" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>https://mansaidea.com/ (intentar archive.org / cache); buscar 'Mansa Idea metodología inteligencia artificial procesamiento propuestas' y entrevistas técnicas a Paulina Franceschi / Fundación Panamá Participa.
-https://mansaidea.com/ ; buscar 'Mansa Idea 2025' / 'Mansa Idea 2026' / 'Fundación Panamá Participa actividad reciente'.
-https://mansaidea.com/ ; buscar evidencia de actualizaciones periódicas del corpus o nuevas convocatorias.</t>
+          <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>PA-mansa-idea-pacto-del-bicentenario</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr"/>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>PE</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>otra institución pública</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>Privado</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>NLP - Tópicos; NLP - Sentiment</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>Una consulta pública para recoger opiniones sobre el Proyecto Educativo Nacional 2036, utilizando encuestas en línea, talleres y mesas deliberativas.</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>Consejo Nacional de Educación del Perú</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional
-https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080
-https://andina.pe/agencia/noticia-usan-inteligencia-artificial-para-formular-proyecto-educativo-nacional-al-2036-777369.aspx</t>
-        </is>
-      </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
-          <t>PE-consulta-ciudadana-sobre-el-proyecto-nac</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>DUDA(lean NO)</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>gobierno nacional</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>no-claro</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>Privado</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>NLP; Resumen automatico; Clasificacion/agrupacion de texto (capacidad de la plataforma sujeta a plan Premium; activacion NO confirmada en TT)</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>no-claro</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>EngageTT (engage.gov.tt) es la plataforma de participacion ciudadana del Ministry of Digital Transformation de Trinidad y Tobago (desde mayo 2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), lanzada en el simposio del NDTS el 12 de febrero de 2025 junto al BID (IDB). Se usa como canal de participacion en el proceso de planificacion nacional del National Digital Transformation Strategy (NDTS) 2024-2027, donde ciudadanos, empresas y partes interesadas reciben actualizaciones y aportan retroalimentacion via encuestas, sondeos (polls), un 'Open Forum' de ideas y el envio de propuestas. La instancia corre sobre el software Go Vocal (antes CitizenLab) -confirmado por la ruta interna 'projects/e-democracy-govocal-internal'-. Go Vocal incorpora un modulo de IA/NLP de 'Sensemaking' (analisis y resumen automatico de aportes), pero ese modulo NO viene activo por defecto: segun la documentacion de soporte de Go Vocal, el acceso a la funcion de AI Analysis/Sensemaking DEPENDE DEL PLAN contratado (Advanced Sensemaking con auto-insights esta en el plan Premium). Tras 2a pasada de investigacion (&gt;=14 busquedas/fetches) NO se halla evidencia alguna de que la instancia de Trinidad active ni use esas funciones de IA sobre el CONTENIDO de los aportes; toda la documentacion describe a EngageTT como recolector (surveys, polls, Open Forum, ideas), es decir plataforma usada como formulario sin analisis automatico confirmado. Existe ademas AskNDTS, un chatbot/PWA de IA conversacional para responder preguntas sobre el NDTS (rol de FAQ informativo, EXCLUIDO del criterio).</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>Ministry of Digital Transformation de Trinidad y Tobago (desde el 23-may-2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), en colaboracion con el Banco Interamericano de Desarrollo (BID/IDB). Plataforma de software: Go Vocal (antes CitizenLab), empresa belga.</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="V37" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
-https://www.govocal.com/plans
-https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool</t>
-        </is>
-      </c>
-      <c r="X37" s="2" t="inlineStr">
-        <is>
-          <t>TT-engagett-plataforma-go-vocal</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>UY</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>(sin revisar)</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA (fuente primaria + OCDE 2025; fetch primario bloqueado por proxy, citas vía repo/WebSearch)</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Referendos e Iniciativas Populares</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>universidad</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>Sociedad Civil; Academia</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>Clustering; ML - Inespecífico</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>Referéndum nacional para derogar 135 artículos de la Ley de Urgente Consideración (LUC). Un equipo de la Universidad de la República corrió una conversación Pol.is en paralelo al referéndum del 27/03/2022 (documentado como caso 2021).</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>Equipo de 13 personas de la Universidad de la República (UdelaR) — ingenieros, comunicadores y científicos de datos; plataforma Pol.is (The Computational Democracy Project)</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="V38" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/</t>
-        </is>
-      </c>
-      <c r="X38" s="2" t="inlineStr">
-        <is>
           <t>UY-polis-referendum-luc</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X38"/>
+  <autoFilter ref="A1:X35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5079,7 +4740,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>A. Excluir (criterio corregido)</t>
         </is>
@@ -5116,7 +4777,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>A. Excluir (criterio corregido)</t>
         </is>
@@ -5153,7 +4814,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>A. Excluir (criterio corregido)</t>
         </is>
@@ -5190,7 +4851,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>A. Excluir (criterio corregido)</t>
         </is>
@@ -5228,7 +4889,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>A. Excluir (criterio corregido)</t>
         </is>
@@ -5266,7 +4927,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>A. Excluir (criterio corregido)</t>
         </is>
@@ -5304,7 +4965,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>A. Excluir (criterio corregido)</t>
         </is>
@@ -5342,498 +5003,498 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>A. Excluir (criterio corregido)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar NO (ya fuera del conteo)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Participa Pudahuel — Presupuesto Participativo deliberativo (plataforma Go Vocal/CitizenLab)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>No es un proceso de participación (o sin IA verificada) → excluido</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Presupuesto participativo real, pero solo se confirma que la plataforma (Go Vocal) tiene el módulo de IA/NLP de fábrica; NO hay traza de que Pudahuel lo activara sobre los aportes (usa_IA_en_proceso 'no-claro', sin evidencia). Sin uso de IA verificado → NO. Decisión del equipo.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.govocal.com/en/cases
+https://participa.mpudahuel.cl/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>A. Excluir (criterio corregido)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar NO (ya fuera del conteo)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Viña Decide — Primer Presupuesto Participativo de Viña del Mar (plataforma Go Vocal/CitizenLab)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>No es un proceso de participación (o sin IA verificada) → excluido</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Presupuesto participativo real sobre plataforma Go Vocal, pero no se encontró en el informe ejecutivo ninguna traza de uso de IA sobre los aportes (usa_IA_en_proceso 'no-claro', sin evidencia). Sin uso de IA verificado → NO. Decisión del equipo.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.govocal.com/en/cases
+https://vinadecide.cl/pages/presupuestoparticipativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>A. Excluir (criterio corregido)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar NO (ya fuera del conteo)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Jalisco - Consulta ¡Armemos un Plan! (Plan Estatal de Desarrollo y Gobernanza 2024-2030)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>No es un proceso de participación (o sin IA verificada) → excluido</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Proceso participativo real y masivo (675.484 participaciones; 15.899 propuestas), pero NO hay evidencia de uso de IA para analizar/agrupar/clasificar el contenido de las propuestas (usa_IA_en_proceso 'no'). Sin uso de IA → NO. Decisión del equipo.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://armemosunplan.mx/wp-content/uploads/2025/10/Armemos-un-Plan-Informe-de-Consulta-COLOR-NNA-v2.4.pdf
+https://plan.jalisco.gob.mx/documentos-metodologicos/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Presupuesto CRECES</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Presupuesto participativo (Hermosillo); la IA (chatbot) facilita la votación (Implementación).</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://presupuestocreces.hermosillo.gob.mx/</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>LXS 400 - Chile Delibera</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Mini-público del Senado; la IA modera y administra los turnos de palabra (Implementación/Planificación).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://es.wikipedia.org/wiki/Lxs_400:_Chile_Delibera
 https://www.lxs400.cl/noticias/</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Consulta ciudadana; la IA analiza los aportes (Análisis).</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030
 https://participacion.digital.gob.cl/folders/consultas-ciudadanas</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>HN</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RedPública + iVerify </t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Plataforma de propuestas de ley ciudadanas (participación legislativa).</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>La voz de los nuevos votantes</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Consulta a nuevos votantes con NLP — proceso ejecutado por el equipo (confirmado).</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf
 https://ipp.unab.cl/publicacion/la-voz-de-los-nuevos-votantes-san-bernardo/</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Jornada de escucha / diálogo — proceso ejecutado por el equipo (confirmado).</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://ipp.unab.cl/
 https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Chatico</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Tiene módulos de participación (aportes al Plan de Desarrollo de Bogotá) — confirmado por el equipo.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://secretariageneral.gov.co/noticias/chatico-el-agente-virtual-de-servicio-la-ciudadania-supero-los-36-millones-de-conversaciones
 https://bogota.gov.co/mi-ciudad/gestion-publica/distrito-presenta-su-agente-virtual-chatico-que-guia-la-ciudadania</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Colab</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Permite sugerir ideas y votar en decisiones municipales (módulos de participación) — confirmado por el equipo.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.colab.com.br/sou-cidadao/</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Caso borde: el chatbot AskNDTS (IA) informa/apoya la implementación del proceso NDTS y el módulo Go Vocal Sensemaking está planeado (existe). → ENTRA como apoyo a la implementación. Decisión del equipo.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
 https://www.govocal.com/plans</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>E. Resolver DUDA de campo</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Decidir SI o NO</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Participa Pudahuel — Presupuesto Participativo deliberativo (plataforma Go Vocal/CitizenLab)</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Abrir la URL y confirmar si es participación con IA en alguna etapa</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Presupuesto participativo real sobre plataforma Go Vocal/CitizenLab con capacidad de IA/NLP sobre el contenido de los aportes. DUDA (lean NO): igual que Viña del Mar, no hay cita que confirme el uso efectivo del módulo d</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.govocal.com/en/cases
-https://participa.mpudahuel.cl/</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>E. Resolver DUDA de campo</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Decidir SI o NO</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Viña Decide — Primer Presupuesto Participativo de Viña del Mar (plataforma Go Vocal/CitizenLab)</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Abrir la URL y confirmar si es participación con IA en alguna etapa</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proceso participativo real (presupuesto participativo municipal) sobre plataforma Go Vocal/CitizenLab, que incorpora NLP ('Sensemaking') sobre el CONTENIDO de los aportes. DUDA: no hay cita que confirme que el módulo de </t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.govocal.com/en/cases
-https://vinadecide.cl/pages/presupuestoparticipativo</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>E. Resolver DUDA de campo</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Decidir SI o NO</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>B. Rescatado → ENTRA</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar SI</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Abrir la URL y confirmar si es participación con IA en alguna etapa</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Dentro de un proceso participativo real (presupuesto participativo de un cabildo Zenú + deliberación sobre iniciativas/proyectos de ley) un LLM (DeepSeek) procesa el CONTENIDO de los aportes para resumir, organizar y con</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Un LLM (DeepSeek) resume, organiza y construye CONSENSOS sobre el contenido de los aportes en un proceso participativo real (cabildo Zenú). Procesa el contenido → ENTRA. Decisión del equipo.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://cerosetenta.uniandes.edu.co/
 https://gaitanaia.org/</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>E. Resolver DUDA de campo</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Decidir SI o NO</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Jalisco - Consulta ¡Armemos un Plan! (Plan Estatal de Desarrollo y Gobernanza 2024-2030)</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Abrir la URL y confirmar si es participación con IA en alguna etapa</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO ENTRA. Aunque '¡Armemos un Plan!' es un proceso participativo real y masivo (675,484 participaciones; 15,899 propuestas escritas) para un plan estatal, NO hay evidencia de que el análisis/agrupación/clasificación del </t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>https://armemosunplan.mx/wp-content/uploads/2025/10/Armemos-un-Plan-Informe-de-Consulta-COLOR-NNA-v2.4.pdf
-https://plan.jalisco.gob.mx/documentos-metodologicos/</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>F. Posible reingreso</t>
         </is>
@@ -5871,7 +5532,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>F. Posible reingreso</t>
         </is>
@@ -5986,7 +5647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6598,22 +6259,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Participación Ciudadana Proceso Constitucional</t>
+          <t>Participa Pudahuel — Presupuesto Participativo deliberativo (plataforma Go Vocal/CitizenLab)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Baseline 2025</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Aplica a los dos casos homónimos (autoconvocados y audiencias)</t>
+          <t>Presupuesto participativo real, pero solo se confirma que la plataforma (Go Vocal) tiene el módulo de IA/NLP de fábrica; NO hay traza de que Pudahuel lo activara sobre los aportes (usa_IA_en_proceso 'no-claro', sin evidencia). Sin uso de IA verificado → NO. Decisión del equipo.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
+          <t>https://participa.mpudahuel.cl/</t>
         </is>
       </c>
     </row>
@@ -6625,22 +6286,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Plataforma UCampus - participación 2023 (proceso constitucional)</t>
+          <t>Participación Ciudadana Proceso Constitucional</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Excluido (revisar)</t>
+          <t>Baseline 2025</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>MANTENER EXCLUIDO. Existe un proceso participativo ELEGIBLE (Proceso Constitucional 2023, mecanismos de participación ciudadana con ~280 mil personas, convocado por el Estado de Chile), y UCampus (Universidad de Chile) fue el operador técnico de dos de los cuatro mecanismos (Audiencias Públicas e In</t>
+          <t>Aplica a los dos casos homónimos (autoconvocados y audiencias)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://ucampus.cl/ucampus-es-la-plataforma-digital-del-proceso-constitucional-2023/</t>
+          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
         </is>
       </c>
     </row>
@@ -6652,76 +6313,76 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Senador Virtual / CrowdLaw (GobLab UAI + IMFD)</t>
+          <t>Plataforma UCampus - participación 2023 (proceso constitucional)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Dudoso</t>
+          <t>Excluido (revisar)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2a PASADA (resuelve DUDA -&gt; NO). La plataforma Senador Virtual / Congreso Virtual es un proceso participativo digital del Congreso de Chile (gobierno nacional) plenamente activo y consolidado (&gt;16 anios, &gt;130.000 participantes), pero la plataforma en si NO usa IA sobre el contenido de los aportes y </t>
+          <t>MANTENER EXCLUIDO. Existe un proceso participativo ELEGIBLE (Proceso Constitucional 2023, mecanismos de participación ciudadana con ~280 mil personas, convocado por el Estado de Chile), y UCampus (Universidad de Chile) fue el operador técnico de dos de los cuatro mecanismos (Audiencias Públicas e In</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://goblab.uai.cl/en/16-years-of-crowdlaw-in-the-chilean-parliament/</t>
+          <t>https://ucampus.cl/ucampus-es-la-plataforma-digital-del-proceso-constitucional-2023/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Asamblea Ciudadana Itinerante del Concejo de Bogotá</t>
+          <t>Senador Virtual / CrowdLaw (GobLab UAI + IMFD)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Excluido (revisar)</t>
+          <t>Dudoso</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>El proceso es elegible en su forma (mini-publico deliberativo recurrente convocado por gobierno local: Concejo de Bogota via DemoLab; 3 ediciones 2020/2021/2023). Sin embargo, NO se encontro evidencia de uso de inteligencia artificial sobre el CONTENIDO de los aportes ciudadanos dentro del proceso p</t>
+          <t xml:space="preserve">2a PASADA (resuelve DUDA -&gt; NO). La plataforma Senador Virtual / Congreso Virtual es un proceso participativo digital del Congreso de Chile (gobierno nacional) plenamente activo y consolidado (&gt;16 anios, &gt;130.000 participantes), pero la plataforma en si NO usa IA sobre el contenido de los aportes y </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://concejodebogota.gov.co/llega-al-concejo-de-bogota-la-tercera-asamblea-ciudadana-que-busca/cbogota/2023-05-23/084537.php</t>
+          <t>https://goblab.uai.cl/en/16-years-of-crowdlaw-in-the-chilean-parliament/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Atlántico – Plan de Ordenamiento Departamental (POD) 2025-2050 / plataforma LITA</t>
+          <t>Viña Decide — Primer Presupuesto Participativo de Viña del Mar (plataforma Go Vocal/CitizenLab)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>NO ELEGIBLE. Dentro de un proceso participativo real (POD con mesas/talleres subregionales), la IA (plataforma LITA / base de datos con IA) cumple funciones de ALMACENAMIENTO, PROCESAMIENTO y ESTRUCTURACIÓN de información técnica territorial y CRUCE de datos técnicos/geoespaciales de punta para actu</t>
+          <t>Presupuesto participativo real sobre plataforma Go Vocal, pero no se encontró en el informe ejecutivo ninguna traza de uso de IA sobre los aportes (usa_IA_en_proceso 'no-claro', sin evidencia). Sin uso de IA verificado → NO. Decisión del equipo.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.atlantico.gov.co/index.php/noticias/prensa-planeacion/27250-plan-de-ordenamiento-departamental-toma-forma-en-el-atlantico</t>
+          <t>https://vinadecide.cl/pages/presupuestoparticipativo</t>
         </is>
       </c>
     </row>
@@ -6733,22 +6394,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Chatbot ALBA</t>
+          <t>Asamblea Ciudadana Itinerante del Concejo de Bogotá</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (revisar)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>El proceso es elegible en su forma (mini-publico deliberativo recurrente convocado por gobierno local: Concejo de Bogota via DemoLab; 3 ediciones 2020/2021/2023). Sin embargo, NO se encontro evidencia de uso de inteligencia artificial sobre el CONTENIDO de los aportes ciudadanos dentro del proceso p</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://barranquilla.gov.co/chatbot</t>
+          <t>https://concejodebogota.gov.co/llega-al-concejo-de-bogota-la-tercera-asamblea-ciudadana-que-busca/cbogota/2023-05-23/084537.php</t>
         </is>
       </c>
     </row>
@@ -6760,22 +6421,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Rama Judicial</t>
+          <t>Atlántico – Plan de Ordenamiento Departamental (POD) 2025-2050 / plataforma LITA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Descubrimiento</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>NO ELEGIBLE. Dentro de un proceso participativo real (POD con mesas/talleres subregionales), la IA (plataforma LITA / base de datos con IA) cumple funciones de ALMACENAMIENTO, PROCESAMIENTO y ESTRUCTURACIÓN de información técnica territorial y CRUCE de datos técnicos/geoespaciales de punta para actu</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.ramajudicial.gov.co/web/centro-de-documentacion-judicial/nuevo-chatbot</t>
+          <t>https://www.atlantico.gov.co/index.php/noticias/prensa-planeacion/27250-plan-de-ordenamiento-departamental-toma-forma-en-el-atlantico</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6448,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Rebecca</t>
+          <t>Chatbot ALBA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -6797,12 +6458,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Atención ciudadana</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://bogota.gov.co/mi-ciudad/habitat/bogota-tiene-chatbot-renobo-que-utiliza-inteligencia-artificial</t>
+          <t>https://barranquilla.gov.co/chatbot</t>
         </is>
       </c>
     </row>
@@ -6814,22 +6475,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>DNP - Diálogos Regionales Vinculantes (PND 2022-2026)</t>
+          <t>Chatbot Rama Judicial</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Participación real, pero el análisis fue manual/cualitativo; solo text-analytics ligero (nubes de palabras + tabulación), sin NLP sobre el contenido (verificado). Decisión del equipo.</t>
+          <t>Atención ciudadana</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://dialogosregionales.dnp.gov.co/</t>
+          <t>https://www.ramajudicial.gov.co/web/centro-de-documentacion-judicial/nuevo-chatbot</t>
         </is>
       </c>
     </row>
@@ -6841,22 +6502,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Descongestión de solicitudes diarias del programa Ingreso Solidario</t>
+          <t>Chatbot Rebecca</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana (triage de 10.000 correos/día): servicio, no participación.</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/inteligencia-artificial-la-herramienta-que-descongestiono-10-000-solicitudes-diarias-de-ingreso-solidario/</t>
+          <t>https://bogota.gov.co/mi-ciudad/habitat/bogota-tiene-chatbot-renobo-que-utiliza-inteligencia-artificial</t>
         </is>
       </c>
     </row>
@@ -6868,22 +6529,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>IA para participación en el POT de Bogotá (Control Visible / Auditoría General)</t>
+          <t>DNP - Diálogos Regionales Vinculantes (PND 2022-2026)</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Dudoso</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>NO ENTRA. El criterio de elegibilidad exige que dentro de un proceso participativo se DESPLIEGUE IA real (institucional) sobre el CONTENIDO de los aportes ciudadanos. El caso documentado es un ARTÍCULO ACADÉMICO (Fundación Universitaria del Área Andina, Maestría en Innovación; publicado en la revist</t>
+          <t>Participación real, pero el análisis fue manual/cualitativo; solo text-analytics ligero (nubes de palabras + tabulación), sin NLP sobre el contenido (verificado). Decisión del equipo.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://controlvisible.auditoria.gov.co/index.php/rcf/article/view/63</t>
+          <t>https://dialogosregionales.dnp.gov.co/</t>
         </is>
       </c>
     </row>
@@ -6895,22 +6556,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ISIDataInsights / Reto de Ciudad 'Datos con Historia' (SDP Bogotá)</t>
+          <t>Descongestión de solicitudes diarias del programa Ingreso Solidario</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>DUDA con inclinación NO (REAFIRMADA en 3ª pasada con búsqueda amplia, jul-2026). Por un lado, la herramienta ISIDataInsights está diseñada para operar sobre el CONTENIDO de información cualitativa de planeación, incluyendo explícitamente 'los aportes ciudadanos' (procesar, validar consistencia, apli</t>
+          <t>Atención ciudadana (triage de 10.000 correos/día): servicio, no participación.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.sdp.gov.co/noticias/bogota-cuenta-herramienta-innovadora-abordar-los-problemas-urbanos-aporte-de-la-ciudadania</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/inteligencia-artificial-la-herramienta-que-descongestiono-10-000-solicitudes-diarias-de-ingreso-solidario/</t>
         </is>
       </c>
     </row>
@@ -6922,22 +6583,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Mini-Public del diálogo social de la Procuraduría</t>
+          <t>IA para participación en el POT de Bogotá (Control Visible / Auditoría General)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Excluido (revisar)</t>
+          <t>Dudoso</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se MANTIENE EXCLUIDO (entra=NO), confirmando el motivo de exclusión de 2025 ('No se encontró información sobre el uso de la IA en la implementación de los Mini Publics'). El proceso es ELEGIBLE por su naturaleza (mini-público / diálogo social deliberativo convocado por la Procuraduría General de la </t>
+          <t>NO ENTRA. El criterio de elegibilidad exige que dentro de un proceso participativo se DESPLIEGUE IA real (institucional) sobre el CONTENIDO de los aportes ciudadanos. El caso documentado es un ARTÍCULO ACADÉMICO (Fundación Universitaria del Área Andina, Maestría en Innovación; publicado en la revist</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://ideemos.org/mini-public-del-dialogo-social-de-la-procuraduria/</t>
+          <t>https://controlvisible.auditoria.gov.co/index.php/rcf/article/view/63</t>
         </is>
       </c>
     </row>
@@ -6949,22 +6610,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Pa' que veás (Cali)</t>
+          <t>ISIDataInsights / Reto de Ciudad 'Datos con Historia' (SDP Bogotá)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Excluido (revisar)</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se revisa por su analogia con dIAra (bots que recopilan quejas ciudadanas y predicen riesgos en obras). Sin embargo, NO se encontro evidencia de uso de inteligencia artificial sobre el CONTENIDO de los aportes/quejas ciudadanas dentro de un proceso participativo. 'Pa' que veas' es, en su nucleo, un </t>
+          <t>DUDA con inclinación NO (REAFIRMADA en 3ª pasada con búsqueda amplia, jul-2026). Por un lado, la herramienta ISIDataInsights está diseñada para operar sobre el CONTENIDO de información cualitativa de planeación, incluyendo explícitamente 'los aportes ciudadanos' (procesar, validar consistencia, apli</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.iadb.org/en/news/city-cali-launches-platform-monitoring-public-investment-idb-support</t>
+          <t>https://www.sdp.gov.co/noticias/bogota-cuenta-herramienta-innovadora-abordar-los-problemas-urbanos-aporte-de-la-ciudadania</t>
         </is>
       </c>
     </row>
@@ -6976,22 +6637,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Plataforma Urna de Cristal</t>
+          <t>Mini-Public del diálogo social de la Procuraduría</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (revisar)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA</t>
+          <t xml:space="preserve">Se MANTIENE EXCLUIDO (entra=NO), confirmando el motivo de exclusión de 2025 ('No se encontró información sobre el uso de la IA en la implementación de los Mini Publics'). El proceso es ELEGIBLE por su naturaleza (mini-público / diálogo social deliberativo convocado por la Procuraduría General de la </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://projects.itforchange.net/mavc/wp-content/uploads/2017/09/Voice-or-Chatter_Case-Study_Colombia_August-2017.pdf</t>
+          <t>https://ideemos.org/mini-public-del-dialogo-social-de-la-procuraduria/</t>
         </is>
       </c>
     </row>
@@ -7003,22 +6664,22 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SISBÉN IV</t>
+          <t>Pa' que veás (Cali)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (revisar)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t xml:space="preserve">Se revisa por su analogia con dIAra (bots que recopilan quejas ciudadanas y predicen riesgos en obras). Sin embargo, NO se encontro evidencia de uso de inteligencia artificial sobre el CONTENIDO de los aportes/quejas ciudadanas dentro de un proceso participativo. 'Pa' que veas' es, en su nucleo, un </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/sisben</t>
+          <t>https://www.iadb.org/en/news/city-cali-launches-platform-monitoring-public-investment-idb-support</t>
         </is>
       </c>
     </row>
@@ -7030,115 +6691,115 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>iLabs - Laboratorios de Inteligencia Colectiva (Ideemos)</t>
+          <t>Plataforma Urna de Cristal</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Excluido (revisar)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>MANTENER EXCLUIDO. La regla de reingreso exige evidencia de IA aplicada al CONTENIDO de los aportes ciudadanos dentro de un proceso participativo. La fuente primaria (página iLabs de Ideemos y su PDF) describe 'Inteligencia Artificial' y 'Machine Learning' SOLO como parte de un listado de técnicas c</t>
+          <t>No evidencia de uso de IA</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://ideemos.org/ilabs-laboratorios-de-inteligencia-colectiva/</t>
+          <t>https://projects.itforchange.net/mavc/wp-content/uploads/2017/09/Voice-or-Chatter_Case-Study_Colombia_August-2017.pdf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>U-Report Costa Rica – chatbot juvenil</t>
+          <t>SISBÉN IV</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>UNICEF lo define como 'encuestas de opinión' (panel de sondeo/percepción juvenil anónimo: clima, salud mental, educación); sin proceso participativo estructurado con incidencia concreta (verificado). Solo opinión → fuera. Decisión del equipo.</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://costarica.ureport.in/</t>
+          <t>https://fairlac.iadb.org/sisben</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>dIAra</t>
+          <t>iLabs - Laboratorios de Inteligencia Colectiva (Ideemos)</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido (revisar)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Civic tech de fiscalización de obras (control social vía app): no es un proceso participativo.</t>
+          <t>MANTENER EXCLUIDO. La regla de reingreso exige evidencia de IA aplicada al CONTENIDO de los aportes ciudadanos dentro de un proceso participativo. La fuente primaria (página iLabs de Ideemos y su PDF) describe 'Inteligencia Artificial' y 'Machine Learning' SOLO como parte de un listado de técnicas c</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.opengovpartnership.org/the-open-gov-challenge/costa-rica-artificial-intelligence-alerts-citizen-control-public-infrastructure/</t>
+          <t>https://ideemos.org/ilabs-laboratorios-de-inteligencia-colectiva/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>CU</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
+          <t>U-Report Costa Rica – chatbot juvenil</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Dudoso</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Dentro de un proceso participativo formal y de gran escala (consulta popular legislativa nacional sobre el Código de las Familias, feb-abr 2022, ~6,5 millones de participantes y cientos de miles de propuestas) se usó IA sobre el CONTENIDO de los aportes ciudadanos: el sistema GEMA-CEN (basado en GEM</t>
+          <t>UNICEF lo define como 'encuestas de opinión' (panel de sondeo/percepción juvenil anónimo: clima, salud mental, educación); sin proceso participativo estructurado con incidencia concreta (verificado). Solo opinión → fuera. Decisión del equipo.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>http://www.datys.cu/spa/site/product/15</t>
+          <t>https://costarica.ureport.in/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>CiudadanIA</t>
+          <t>dIAra</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -7148,39 +6809,39 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Solo atención/servicio; la 'participación' es co-diseñar la IA aportando datos, no consulta pública. Sin módulo de participación (verificado). Decisión del equipo.</t>
+          <t>Civic tech de fiscalización de obras (control social vía app): no es un proceso participativo.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.genia.ai/paises-miembros</t>
+          <t>https://www.opengovpartnership.org/the-open-gov-challenge/costa-rica-artificial-intelligence-alerts-citizen-control-public-infrastructure/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>CU</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Dudoso</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Dentro de un proceso participativo formal y de gran escala (consulta popular legislativa nacional sobre el Código de las Familias, feb-abr 2022, ~6,5 millones de participantes y cientos de miles de propuestas) se usó IA sobre el CONTENIDO de los aportes ciudadanos: el sistema GEMA-CEN (basado en GEM</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/guatemala/comunicados-de-prensa/sara-la-nueva-herramienta-de-inteligencia-artificial-para-combatir-la-violencia-de-genero-en-centroamerica</t>
+          <t>http://www.datys.cu/spa/site/product/15</t>
         </is>
       </c>
     </row>
@@ -7192,61 +6853,61 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>TAÍNA: Gobierno Inteligente</t>
+          <t>CiudadanIA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>Solo atención/servicio; la 'participación' es co-diseñar la IA aportando datos, no consulta pública. Sin módulo de participación (verificado). Decisión del equipo.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.diariolibre.com/actualidad/nacional/2023/10/11/gobierno-presenta-estrategia-de-inteligencia-artificial/2489157</t>
+          <t>https://www.genia.ai/paises-miembros</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Plataforma de modelos generativos de IA de SEGEPLAN + Red Ciudadana (Guatemala)</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>El criterio ELEGIBLE exige que la IA generativa se use para SISTEMATIZAR/CLASIFICAR/RESUMIR el CONTENIDO de los aportes de los diagnosticos participativos (Consejos de Desarrollo COCODES/COMUDES) en los Planes de Desarrollo Municipal (PDM). Toda la evidencia primaria y secundaria (nota SEGEPLAN ?p=1</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://portal.segeplan.gob.gt/segeplan/?p=14176</t>
+          <t>https://www.undp.org/es/guatemala/comunicados-de-prensa/sara-la-nueva-herramienta-de-inteligencia-artificial-para-combatir-la-violencia-de-genero-en-centroamerica</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LATAM</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ANTAI Smart CID (Autoridad Nacional de Transparencia y Acceso a la Información + OS City)</t>
+          <t>TAÍNA: Gobierno Inteligente</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -7256,39 +6917,39 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Atención ciudadana</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.caf.com/es/actualidad/noticias/2021/07/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
+          <t>https://www.diariolibre.com/actualidad/nacional/2023/10/11/gobierno-presenta-estrategia-de-inteligencia-artificial/2489157</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LATAM</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Botivist</t>
+          <t>Plataforma de modelos generativos de IA de SEGEPLAN + Red Ciudadana (Guatemala)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Descubrimiento</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>No tiene foco en un país específico</t>
+          <t>El criterio ELEGIBLE exige que la IA generativa se use para SISTEMATIZAR/CLASIFICAR/RESUMIR el CONTENIDO de los aportes de los diagnosticos participativos (Consejos de Desarrollo COCODES/COMUDES) en los Planes de Desarrollo Municipal (PDM). Toda la evidencia primaria y secundaria (nota SEGEPLAN ?p=1</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/research/publication/botivist-calling-volunteers-to-action-using-online-bots/</t>
+          <t>https://portal.segeplan.gob.gt/segeplan/?p=14176</t>
         </is>
       </c>
     </row>
@@ -7300,7 +6961,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Chatbot DCI (Denuncia Ciudadana Idónea)</t>
+          <t>ANTAI Smart CID (Autoridad Nacional de Transparencia y Acceso a la Información + OS City)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -7310,12 +6971,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci-1</t>
+          <t>https://www.caf.com/es/actualidad/noticias/2021/07/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
         </is>
       </c>
     </row>
@@ -7327,7 +6988,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Citibeats: Covid-19 (“Percepciones ciudadanas COVID-19”)</t>
+          <t>Botivist</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -7337,12 +6998,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Análisis de redes sociales, no es participación</t>
+          <t>No tiene foco en un país específico</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://forbescentroamerica.com/2021/04/28/civiclytics-el-big-data-apoya-la-recuperacion-economica</t>
+          <t>https://www.microsoft.com/en-us/research/publication/botivist-calling-volunteers-to-action-using-online-bots/</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7015,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Ushahidi "AI for Good"</t>
+          <t>Chatbot DCI (Denuncia Ciudadana Idónea)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -7364,24 +7025,24 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>No se evidencia el uso de IA en los proyectos de participación listados para Latam</t>
+          <t>No evidencia de uso de IA</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.ushahidi.com/</t>
+          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci-1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>LATAM</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>AMIMgo</t>
+          <t>Citibeats: Covid-19 (“Percepciones ciudadanas COVID-19”)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -7391,24 +7052,24 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Análisis de redes sociales, no es participación</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://amim.mx/noticias/detalle/estrena-amim-chatbot-para-la-atencion-ciudadana</t>
+          <t>https://forbescentroamerica.com/2021/04/28/civiclytics-el-big-data-apoya-la-recuperacion-economica</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>LATAM</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>ATIC</t>
+          <t>Ushahidi "AI for Good"</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -7418,12 +7079,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No se evidencia el uso de IA en los proyectos de participación listados para Latam</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://oem.com.mx/la-prensa/metropoli/info-cdmx-implementa-atic-una-herramienta-con-ia-que-facilita-el-acceso-a-la-informacion-13081722</t>
+          <t>https://www.ushahidi.com/</t>
         </is>
       </c>
     </row>
@@ -7435,7 +7096,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>ChatBot “Claudia"</t>
+          <t>AMIMgo</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -7445,12 +7106,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>No es participación</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://mexicocomovamos.mx/animal-politico/2024/08/chatbot-claudia-una-herramienta-de-participacion-ciudadana/</t>
+          <t>https://amim.mx/noticias/detalle/estrena-amim-chatbot-para-la-atencion-ciudadana</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7123,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Chatbot "Inés"</t>
+          <t>ATIC</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -7472,12 +7133,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>No es participación, es informativo</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://centralelectoral.ine.mx/2024/04/17/nueva-version-del-chatbot-del-ine-en-whatsapp-permitira-verificar-informacion-sobre-elecciones-2024/</t>
+          <t>https://oem.com.mx/la-prensa/metropoli/info-cdmx-implementa-atic-una-herramienta-con-ia-que-facilita-el-acceso-a-la-informacion-13081722</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7150,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Sam Petrino</t>
+          <t>ChatBot “Claudia"</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -7499,12 +7160,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No es participación</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.civica.digital/historias/chatbot-sam-petrino</t>
+          <t>https://mexicocomovamos.mx/animal-politico/2024/08/chatbot-claudia-una-herramienta-de-participacion-ciudadana/</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7177,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Victoria</t>
+          <t>Chatbot "Inés"</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -7526,12 +7187,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No es participación, es informativo</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://adip.cdmx.gob.mx/comunicacion/nota/la-adip-y-el-gobierno-de-la-ciudad-presentan-victoria-el-robot-que-colaborara-en-la-atencion-de-la-ciudadania</t>
+          <t>https://centralelectoral.ine.mx/2024/04/17/nueva-version-del-chatbot-del-ine-en-whatsapp-permitira-verificar-informacion-sobre-elecciones-2024/</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7204,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>INAOE (Conacyt) – Laboratorio de Tecnologías del Lenguaje</t>
+          <t>Chatbot Sam Petrino</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -7553,12 +7214,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
+          <t>https://www.civica.digital/historias/chatbot-sam-petrino</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7231,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Movimex</t>
+          <t>Chatbot Victoria</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -7580,12 +7241,12 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://animalpolitico.com/estados/chatbot-movimex-tramites-denuncias-edomex</t>
+          <t>https://adip.cdmx.gob.mx/comunicacion/nota/la-adip-y-el-gobierno-de-la-ciudad-presentan-victoria-el-robot-que-colaborara-en-la-atencion-de-la-ciudadania</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7258,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Sistema *0311 Locatel</t>
+          <t>INAOE (Conacyt) – Laboratorio de Tecnologías del Lenguaje</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -7607,12 +7268,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://research.latinxinai.org/papers/naacl/2022/pdf/paper_01.pdf</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
     </row>
@@ -7624,22 +7285,22 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Sufragio seguro</t>
+          <t>Jalisco - Consulta ¡Armemos un Plan! (Plan Estatal de Desarrollo y Gobernanza 2024-2030)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Baseline 2025</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>EXCLUSIÓN FIRME (recodificación 2026): Exclusión FIRME (recodificación 2026): integridad/proceso electoral, no contenido</t>
+          <t>Proceso participativo real y masivo (675.484 participaciones; 15.899 propuestas), pero NO hay evidencia de uso de IA para analizar/agrupar/clasificar el contenido de las propuestas (usa_IA_en_proceso 'no'). Sin uso de IA → NO. Decisión del equipo.</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://algoritmoscide.org/proyectos/sufragio-seguro/</t>
+          <t>https://armemosunplan.mx/propuestas-ciudadanas/</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7312,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Violetta</t>
+          <t>Movimex</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -7661,24 +7322,24 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://holasoyvioletta.com/acerca-de/</t>
+          <t>https://animalpolitico.com/estados/chatbot-movimex-tramites-denuncias-edomex</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Dr. ROSA y Dr. NICO</t>
+          <t>Sistema *0311 Locatel</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -7688,105 +7349,105 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Atención ciudadana</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
+          <t>https://research.latinxinai.org/papers/naacl/2022/pdf/paper_01.pdf</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>JNE WhatsApp Chatbot</t>
+          <t>Sufragio seguro</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Baseline 2025</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>EXCLUSIÓN FIRME (recodificación 2026): Exclusión FIRME (recodificación 2026): integridad/proceso electoral, no contenido</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://portal.jne.gob.pe/Portal/Pagina/Nota/12783</t>
+          <t>https://algoritmoscide.org/proyectos/sufragio-seguro/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Sistema de cómputo con IA para las Elecciones Generales 2026</t>
+          <t>Violetta</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Conteo electoral (OCR de actas): votación política, no participación.</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-onpe-utilizara-un-nuevo-sistema-computo-resultados-incorporara-ia-1021072.aspx</t>
+          <t>https://holasoyvioletta.com/acerca-de/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>PY</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Consultas ciudadanas sobre IA en Paraguay - PNUD Accelerator Lab (AccLab) + Columbia SIPA + MITIC / insumo del diagnóstico AILA (Atlas de IA)</t>
+          <t>Dr. ROSA y Dr. NICO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>El criterio ELEGIBLE exige que dentro de un proceso participativo convocado se use IA (NLP/ML/clustering/sentimiento) SOBRE EL CONTENIDO de los aportes. Aquí ocurre lo contrario: (1) la IA es el TEMA de la consulta (se pregunta a la ciudadania por su percepcion de la IA), y (2) el ANÁLISIS de los ap</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/paraguay/blog/consultas-ciudadanas-sobre-ia-en-paraguay-visiones-diversas-entre-el-campo-y-la-ciudad</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>PY</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>ParaEmpleo</t>
+          <t>JNE WhatsApp Chatbot</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -7801,120 +7462,201 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/en/paraempleo</t>
+          <t>https://portal.jne.gob.pe/Portal/Pagina/Nota/12783</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>UY</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Chatbot (Asistente virtual entrenado con IA)</t>
+          <t>Sistema de cómputo con IA para las Elecciones Generales 2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Conteo electoral (OCR de actas): votación política, no participación.</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
+          <t>https://andina.pe/agencia/noticia-onpe-utilizara-un-nuevo-sistema-computo-resultados-incorporara-ia-1021072.aspx</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>UY</t>
+          <t>PY</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Consulta Pública de la Estrategia Nacional de Inteligencia Artificial (IA) de Uruguay 2024–2030,</t>
+          <t>Consultas ciudadanas sobre IA en Paraguay - PNUD Accelerator Lab (AccLab) + Columbia SIPA + MITIC / insumo del diagnóstico AILA (Atlas de IA)</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Descubrimiento</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA</t>
+          <t>El criterio ELEGIBLE exige que dentro de un proceso participativo convocado se use IA (NLP/ML/clustering/sentimiento) SOBRE EL CONTENIDO de los aportes. Aquí ocurre lo contrario: (1) la IA es el TEMA de la consulta (se pregunta a la ciudadania por su percepcion de la IA), y (2) el ANÁLISIS de los ap</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030</t>
+          <t>https://www.undp.org/es/paraguay/blog/consultas-ciudadanas-sobre-ia-en-paraguay-visiones-diversas-entre-el-campo-y-la-ciudad</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>UY</t>
+          <t>PY</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Consulta Pública y Participación Multiactores: "Niñas, niños, adolescentes, entornos digitales e inteligencia artificial" (Uruguay, 2026)</t>
+          <t>ParaEmpleo</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>NO (lean firme). (1) TEMPORAL: la consulta está ABIERTA hasta el 10/09/2026 y la fase de sistematización/análisis/validación (Fase 3) recién ocurre entre el 10/09 y el 10/10/2026, con informe final el 30/11/2026. A la fecha de evaluación (2026-07-01) la fase de análisis NO se ha ejecutado, por lo qu</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.gub.uy/ministerio-educacion-cultura/comunicacion/noticias/lanzamiento-consulta-publica-sobre-inteligencia-artificial-entornos-digitales</t>
+          <t>https://fairlac.iadb.org/en/paraempleo</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>UY</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Chatbot (Asistente virtual entrenado con IA)</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Excluido 2025</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Atencion ciudadana</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>UY</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Consulta Pública de la Estrategia Nacional de Inteligencia Artificial (IA) de Uruguay 2024–2030,</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Excluido 2025</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>No evidencia de uso de IA</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>UY</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Consulta Pública y Participación Multiactores: "Niñas, niños, adolescentes, entornos digitales e inteligencia artificial" (Uruguay, 2026)</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Descubrimiento</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>NO (lean firme). (1) TEMPORAL: la consulta está ABIERTA hasta el 10/09/2026 y la fase de sistematización/análisis/validación (Fase 3) recién ocurre entre el 10/09 y el 10/10/2026, con informe final el 30/11/2026. A la fecha de evaluación (2026-07-01) la fase de análisis NO se ha ejecutado, por lo qu</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gub.uy/ministerio-educacion-cultura/comunicacion/noticias/lanzamiento-consulta-publica-sobre-inteligencia-artificial-entornos-digitales</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
           <t>VE</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Plan de la Patria 7 Transformaciones (7T) - IA y Big Data en la sistematización de propuestas de la Consulta Popular</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Dudoso</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>NO (resuelto en 2ª pasada, antes DUDA). Hay un proceso participativo claro (consulta/debate nacional para construir el Plan de la Patria 7T, con +63.000 asambleas, 3,4 M de participantes y 34.491 propuestas) cuyo CONTENIDO sí fue recolectado, cargado, sistematizado y agrupado. Pero la 2ª pasada CONF</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>http://www.correodelorinoco.gob.ve/venezuela-impulsa-el-debate-sobre-inteligencia-artificial-bajo-principios-de-soberania-y-etica/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E71"/>
+  <autoFilter ref="A1:E74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7925,7 +7667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8312,7 +8054,7 @@
           <t>José Carlos Vaz, from the USP Public Policy Management course / professor at the University of São Paulo's School of Arts, Sciences and Humanities (EACH) ... coordinates GETIP. (snippet; convocante = universidad USP)</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr"/>
+      <c r="J6" s="11" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>AI could help generate proposals based on knowledge databases and transform them into legally viable drafts / a IA o ajuda a escrever essa proposta. (snippet; rol sobre el contenido del aporte, pero en marco de investigación)</t>
@@ -8354,11 +8096,11 @@
           <t>OPA é o Orçamento Participativo 100% digital do Governo do Estado do Piauí... Após analisar a viabilidade das propostas, o Governo do Estado disponibilizará uma votação por meio da Colab para que qualquer cidadão acima de 16 anos com CPF possa votar no que considera mais importante para o seu município. (Colab)</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr"/>
-      <c r="G7" s="12" t="inlineStr"/>
-      <c r="H7" s="12" t="inlineStr"/>
-      <c r="I7" s="12" t="inlineStr"/>
-      <c r="J7" s="12" t="inlineStr"/>
+      <c r="F7" s="11" t="inlineStr"/>
+      <c r="G7" s="11" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr"/>
+      <c r="I7" s="11" t="inlineStr"/>
+      <c r="J7" s="11" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Todo esse processo é realizado por meio da plataforma Colab Gov... O sistema utiliza tecnologia da AWS, referência mundial em segurança digital. (la IA/tecnología se presenta como soporte operativo, de eficiencia y de seguridad del flujo, no como análisis del contenido de las propuestas → rol de apoyo)</t>
@@ -8995,7 +8737,7 @@
           <t>The platform used an AI tool to keep time and distribute speaking rights equitably, allowing participants to form speaking queues and discuss in small groups with timed agendas. (OCDE 2025) / El Centro de Microdatos de la Universidad de Chile, usando tecnologia basada en Inteligencia Artificial (IA), selecciono esta muestra representativa.</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr"/>
+      <c r="G17" s="11" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Lxs 400: Chile Delibera... es un evento de participacion ciudadana de escala nacional realizado en Chile desde el 9 de diciembre de 2020, con su evento principal a fines de marzo de 2021. (Wikipedia ES) [Evento puntual de una edicion 2020-2021; no se hallaron ediciones posteriores recurrentes].</t>
@@ -9099,42 +8841,57 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Participa Pudahuel — Presupuesto Participativo deliberativo (plataforma Go Vocal/CitizenLab)</t>
+          <t>Participación Ciudadana Proceso Constitucional</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>DUDA(lean NO)</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Municipalidad de la comuna de Pudahuel, Chile (participa.mpudahuel.cl)</t>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>La alcaldía de la comuna de Pudahuel implementó un nuevo modelo de gestión presupuestaria deliberativa y vinculante ... presupuesto municipal 2023 ... más de 1.200 participantes y sobre 150 iniciativas de proyectos</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr"/>
+          <t>Governanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>plataforma de participación activa (participa.mpudahuel.cl)</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr"/>
+          <t>BBDD 2025: Cerrado</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>La alcaldía de la comuna de Pudahuel</t>
-        </is>
-      </c>
-      <c r="J19" s="12" t="inlineStr"/>
-      <c r="K19" s="12" t="inlineStr"/>
+          <t>Secretaría de Participación Ciudadana</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
+        </is>
+      </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://participa.mpudahuel.cl/
-https://go-vocal.com/</t>
+          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
         </is>
       </c>
     </row>
@@ -9146,7 +8903,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Participación Ciudadana Proceso Constitucional</t>
+          <t>Tenemos que hablar de Chile</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -9181,22 +8938,23 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Secretaría de Participación Ciudadana</t>
+          <t>Universidad de Chile y Pontificia Universidad Católica de Chile</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
+          <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
+          <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
+          <t>https://www.tenemosquehablardechile.cl/
+https://static1.squarespace.com/static/630d0dbf05b8104ed4d55d7f/t/67f694b2f91e4f228bb941cb/1744213189210/01.+Primer-InformeTQHDCH.pdf</t>
         </is>
       </c>
     </row>
@@ -9208,7 +8966,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Tenemos que hablar de Chile</t>
+          <t>Un encuentro para la equidad de género en la movilidad en Chile</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -9243,83 +9001,20 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Universidad de Chile y Pontificia Universidad Católica de Chile</t>
+          <t>Universidad Andres Bello</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas</t>
+          <t>Análisis temático de las transcripciones de las mesas</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas</t>
+          <t>Análisis temático de las transcripciones de las mesas</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tenemosquehablardechile.cl/
-https://static1.squarespace.com/static/630d0dbf05b8104ed4d55d7f/t/67f694b2f91e4f228bb941cb/1744213189210/01.+Primer-InformeTQHDCH.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Un encuentro para la equidad de género en la movilidad en Chile</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Governanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>BBDD 2025: Cerrado</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Universidad Andres Bello</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Análisis temático de las transcripciones de las mesas</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Análisis temático de las transcripciones de las mesas</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>https://ipp.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/
 https://noticiasrepositorio.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/
@@ -9327,110 +9022,63 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Viña Decide — Primer Presupuesto Participativo de Viña del Mar (plataforma Go Vocal/CitizenLab)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>DUDA(lean SI)</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Go Vocal ... Viña del Mar, Chile (caso de estudio govocal.com)</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Following devastating wildfires, Go Vocal fueled community-driven recovery by empowering residents to redesign public spaces (caso Viña del Mar)</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Primer Presupuesto Participativo Viña del Mar 2024 (guía alojada en vinadecide.cl)</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Municipalidad de Viña del Mar (Primer Presupuesto Participativo 2024)</t>
-        </is>
-      </c>
-      <c r="J23" s="12" t="inlineStr"/>
-      <c r="K23" s="12" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>https://vinadecide.cl/pages/presupuestoparticipativo
-https://www.govocal.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Chatico</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares, Presupuestos Participativos</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado 2024-2028: NLP y tecnologías semánticas procesaron 147.422 participaciones (10% propuestas libres) para el Plan Distrital de Desarrollo. Citado por</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Plataforma</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Secretaría General de la Alcaldía Mayor de Bogotá</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Interactuar con ciudadanos, responder consultas y plataforma para votar en causas ciudadanas y presupuesto participativo</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>Interactuar con ciudadanos, responder consultas y plataforma para votar en causas ciudadanas y presupuesto participativo</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>https://secretariageneral.gov.co/noticias/chatico-el-agente-virtual-de-servicio-la-ciudadania-supero-los-36-millones-de-conversaciones
 https://bogota.gov.co/mi-ciudad/gestion-publica/distrito-presenta-su-agente-virtual-chatico-que-guia-la-ciudadania
@@ -9438,59 +9086,59 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Citibeats + PNUD Colombia (analítica de datos para la deliberación pública juvenil)</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Data analytics to improve public deliberation in Colombia (UNDP Colombia / El PNUD en Colombia, blog, Bogotá, Colombia).</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Citibeats facilita la comprensión social de la situación actual de Colombia mediante el monitoreo y seguimiento en tiempo real de las opiniones y propuestas expresadas en espacios digitales y presenciales, buscando identificar los principales tópicos de interés de la población.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Citibeats utiliza algoritmos que combinan NLP (Procesamiento de Lenguaje Natural) y ML (Machine Learning), filtrando contenido relevante de distintas fuentes de datos abiertas (Twitter, Facebook, Instagram, foros, blogs, noticias y comentarios de video), clasificando las opiniones e información de los usuarios en categorías y extrayendo conocimiento y patrones de forma automática, en tiempo real.</t>
         </is>
       </c>
-      <c r="G25" s="12" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>El PNUD Colombia está experimentando con Citibeats, una plataforma de inteligencia artificial (IA) ética y responsable. (proyecto descrito como experimentación/piloto del Laboratorio de Aceleración, diciembre 2021).</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>El Programa de las Naciones Unidas para el Desarrollo (PNUD) en Colombia está experimentando con Citibeats... La tecnologia sirve como un habilitador que permite acelerar la comprensión social respecto a los espacios de deliberación pública y las propuestas, necesidades y preocupaciones de la juventud colombiana.</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>El PNUD y aliados estratégicos, como El Avispero, han generado espacios presenciales para contrastar lo que se dice en las conversaciones en línea, donde los jóvenes destacan preocupaciones sobre la corrupción en el país, la necesidad de prevenir la violencia de género y la importancia de promover la educación.</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>El proyecto de comprensión ciudadana analizó 2.129.502 documentos. Las principales categorías de conversación en Colombia giraron en torno a Paz y Justicia, Gobernanza e Inclusión Social.</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>https://www.undp.org/es/colombia/blog/analitica-de-datos-para-mejorar-la-deliberacion-publica-en-colombia
 https://www.undp.org/es/colombia/blog/data-analytics-improve-public-deliberation-colombia
@@ -9501,6 +9149,127 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>ECHO – HáblameD Medellín</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Governanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Implementación, Análisis</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>reconfirmado web (institucional): Reconfirmado: la IA del UNFPA clasifica por ODS las conversaciones ciudadanas captadas en campo (5.000+ personas, 16 comunas).</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>DUDA(lean SI)</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>la herramienta de un resguardo indígena (Zenú, Bajo Sinú, Colombia) para llegar al Congreso (La Silla Vacía)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>a platform for young people in the Zenú community to decide, through digital voting, how they wanted to allocate local budgets</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>The AI summarizes proposals, organizes consensus, and facilitates collective decision-making</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>More than 10,000 users participate in the chatbot at gaitanaia.org, whose discussions feed the community's positions and proposals</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Gaitana IA is a tool created by Carlos Redondo Rincón ... a platform for young people in the Zenú community</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Gaitana is built on the DeepSeek large language model, adapted to the Zenú worldview ... summarizes proposals, organizes consensus</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>artificial intelligence organizes opinions, processes trends and builds consensuses that, if approved, would become legislative initiatives (KienyKe)</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/
+https://www.kienyke.com/</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
@@ -9509,7 +9278,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ECHO – HáblameD Medellín</t>
+          <t>Tenemos que hablar de Colombia</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -9529,12 +9298,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Implementación, Análisis</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>reconfirmado web (institucional): Reconfirmado: la IA del UNFPA clasifica por ODS las conversaciones ciudadanas captadas en campo (5.000+ personas, 16 comunas).</t>
+          <t>BBDD 2025: Cerrado</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -9544,206 +9313,85 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+          <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+          <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+          <t>https://tenemosquehablarcolombia.co/
+https://tenemosquehablarcolombia.co/resultados/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
+          <t xml:space="preserve">PAGA IA </t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>DUDA(lean SI)</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>la herramienta de un resguardo indígena (Zenú, Bajo Sinú, Colombia) para llegar al Congreso (La Silla Vacía)</t>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>a platform for young people in the Zenú community to decide, through digital voting, how they wanted to allocate local budgets</t>
+          <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>The AI summarizes proposals, organizes consensus, and facilitates collective decision-making</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>More than 10,000 users participate in the chatbot at gaitanaia.org, whose discussions feed the community's positions and proposals</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr"/>
+          <t>reconfirmado web (institucional): Reconfirmado: integrada al Tercer Plan de Acción de Estado Abierto 2025-2027; analiza las propuestas ciudadanas y sugiere actividades.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Plataforma</t>
+        </is>
+      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Gaitana IA is a tool created by Carlos Redondo Rincón ... a platform for young people in the Zenú community</t>
+          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Gaitana is built on the DeepSeek large language model, adapted to the Zenú worldview ... summarizes proposals, organizes consensus</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>artificial intelligence organizes opinions, processes trends and builds consensuses that, if approved, would become legislative initiatives (KienyKe)</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/
-https://www.kienyke.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Tenemos que hablar de Colombia</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Governanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>BBDD 2025: Cerrado</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>https://tenemosquehablarcolombia.co/
-https://tenemosquehablarcolombia.co/resultados/</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PAGA IA </t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Referendos e Iniciativas Populares</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>reconfirmado web (institucional): Reconfirmado: integrada al Tercer Plan de Acción de Estado Abierto 2025-2027; analiza las propuestas ciudadanas y sugiere actividades.</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Plataforma</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto
 </t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto
 </t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>https://ia.gobiernoabierto.ec/
 https://ia.gobiernoabierto.ec/
@@ -9751,63 +9399,63 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Guatemala Joven Conversa </t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado: diálogos digitales con IA (DPPA ONU + Fundación Esquipulas); 300+ jóvenes; la IA permite intercambios anónimos y votación de aportes para identifi</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
 https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/
@@ -9815,125 +9463,125 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>HN</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RedPública + iVerify </t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reverificación: plataforma de propuestas ciudadanas con módulo de análisis de tendencias; evidencia de IA central débil, revisar en Fase 2.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Guanajuato hará historia con el primer Programa de Gobierno realizado con IA</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Para integrar la participación ciudadana en este Programa de Gobierno, se realizaron cuatro talleres cubriendo las regiones noreste, norte, centro y sur, con representación de los 46 municipios de Guanajuato.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>El Programa de Gobierno de Guanajuato 2024-2030 es la guía que orienta las acciones del Gobierno de la Gente para lograr un Guanajuato sostenible, equitativo y transparente.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Su diseño incorporó el uso de inteligencia artificial para integrar más de 26 mil voces de distintas regiones y sectores</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>El Programa de Gobierno 2024-2030 hizo historia al ser el primero en realizarse con ayuda de la Inteligencia Artificial (IA), según anunció la Gobernadora Libia Dennise García Muñoz Ledo en el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG).</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía.</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>https://guanajuatointeligente.com/como-hicimos-el-programa/
 https://guanajuatointeligente.com/
@@ -9946,182 +9594,121 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Jalisco - Consulta ¡Armemos un Plan! (Plan Estatal de Desarrollo y Gobernanza 2024-2030)</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>DUDA(lean NO)</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr"/>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>'Armemos un Plan' se llevó a cabo de manera abierta e incluyente del 20 de febrero al 17 de abril por el Gobierno de Jalisco, a través de la Secretaría de Planeación y Participación Ciudadana; la consulta digital recibió 15,899 propuestas ciudadanas.</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Jalisco concluyó la primera etapa de la consulta ciudadana 'Armemos un Plan' con una cifra inédita de 675,484 participaciones, base para desarrollar el Plan Estatal de Desarrollo y Gobernanza 2024-2030.</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Se realizaron 12 foros regionales y la instalación de un Consejo de Planeación Participativa en cada región de Jalisco; se llevaron a cabo 168 mesas regionales, 47 sectoriales y 9 grandes foros temáticos... donde se identificaron y discutieron 1,349 problemáticas planteadas por la ciudadanía. (Metodología participativa/estadística; sin componente de IA.)</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno de Jalisco, a través de la Secretaría de Planeación y Participación Ciudadana (coordinación de Cynthia Cantero Pacheco).</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Las propuestas se construyeron a partir de las opiniones y expresiones de la ciudadanía durante la consulta, agrupando ideas similares y redactándolas de forma clara y ordenada, respetando siempre la intención original de quienes participaron. (Descripción metodológica oficial de armemosunplan.mx/propuestas-ciudadanas, recuperada vía WebSearch que indexa la página; no menciona IA/NLP/algoritmos: describe agrupación editorial manual.)</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>GAP: ninguna fuente atribuye a IA/NLP/minería de texto/clustering el análisis o la agrupación de las 15,899 propuestas; la única descripción del método es 'agrupando ideas similares' de forma manual/editorial.</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>https://armemosunplan.mx/propuestas-ciudadanas/
-https://armemosunplan.mx/wp-content/uploads/2025/10/Armemos-un-Plan-Informe-de-Consulta-COLOR-NNA-v2.4.pdf
-https://plan.jalisco.gob.mx/wp-content/uploads/2025/09/Plan-Estatal-de-Desarrollo-y-Gobernanza-V0.25.pdf
-https://plan.jalisco.gob.mx/documentos-metodologicos/
-https://www.clickgdl.com/noticias/jalisco/concluye-consulta-ciudadana-historica-en-jalisco-para-la-construccion-del-plan-estatal-de-desarrollo-y-gobernanza-2024-2030/
-https://elrespetable.com/2025/05/13/es-jalisco-referente-nacional-e-internacional-en-participacion-ciudadana-con-la-consulta-armemos-un-plan/
-https://lanotadeguadalajara.com/ciencia-y-tecnologia/lanza-el-gobierno-de-jalisco-su-politica-de-inteligencia-artificial-y-gobernanza-de-datos/
-https://ai.jalisco.gob.mx/</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Presupuesto CRECES</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Presupuestos Participativos</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Activo</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Ayundamiento de Hermosilla</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>https://presupuestocreces.hermosillo.gob.mx/</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>La Fundación Panamá Participa lanzó Mansa Idea (www.mansaidea.com), una plataforma basada en inteligencia artificial que recoge miles de propuestas ciudadanas... iniciativa de alcance nacional que se nutre de ideas y propuestas que miles de panameños hicieron durante el desarrollo del Pacto del Bicentenario. (Panamá; fuentes panama24horas.com.pa y laestrella.com.pa)</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea, resultado del Pacto del Bicentenario, ofrece acceso fácil y transparente a más de 175 mil ideas y propuestas generadas por ciudadanos de todo el país. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales. (la IA agrega/organiza/sintetiza el contenido de las propuestas por tema y territorio = Análisis + Traducción Política; el método técnico exacto no se detalla en las fuentes).</t>
         </is>
       </c>
-      <c r="G35" s="12" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>La plataforma fue lanzada el 1 de abril de 2024... constituye una herramienta valiosa de participación ciudadana muy relevante para ciudadanos, candidatos a cargos de elección popular y medios durante la campaña electoral y luego como recurso para el monitoreo del mandato ciudadano. (un despliegue concreto de la plataforma, 2024; sin evidencia de ediciones recurrentes).</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>La Fundación Panamá Participa lanzó Mansa Idea... iniciativa liderada por Paulina Franceschi a través de la Fundación Panamá Participa (sociedad civil). El proceso participativo de origen: 'El 26 de noviembre de 2020, el presidente Laurentino Cortizo Cohen lanzó la iniciativa denominada Pacto del Bicentenario Cerrando Brechas' (gobierno nacional / Concertación Nacional).</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. (la IA procesa el contenido de las propuestas del proceso participativo).</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía. (agregación/síntesis de los aportes ciudadanos = rol sobre el contenido).</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>https://www.panama24horas.com.pa/panama/fundacion-panama-participa-lanza-plataforma-de-propuestas-ciudadanas-mansa-idea/
 https://www.laestrella.com.pa/panama/politica/mansa-idea-una-herramienta-digital-con-propuestas-para-candidatos-YD6746221
@@ -10132,63 +9719,63 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (prensa): VERIFICADO (fuente primaria): el CNE usó IBM Watson Discovery + Studio (ML/NLP) sobre 87.991 documentos de aportes ciudadanos de 847 eventos y 49 espacios de di</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Consejo Nacional de Educación del Perú</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional
 https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080
@@ -10197,59 +9784,59 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Project: National Digital Transformation Strategy | Ministry of Digital Transformation, Trinidad and Tobago (engage.gov.tt/projects/national-digital-transformation-strategy). Ruta interna confirmatoria: engage.gov.tt/projects/e-democracy-govocal-internal (la instancia corre sobre Go Vocal). En 2026: 'Projects | Ministry of Public Administration and Artificial Intelligence' (engage.gov.tt/projects).</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>EngageTT es una plataforma en linea (engage.gov.tt) donde ciudadanos, empresas y partes interesadas pueden recibir actualizaciones en tiempo real sobre iniciativas de transformacion digital y ofrecer retroalimentacion via encuestas y sondeos (polls); el Ministro anima a todos a participar y enviar ideas y comentarios sobre el NDTS, que se disena para evolucionar mediante el compromiso y la colaboracion continuos. Incluye un 'Open Forum' (engage.gov.tt/ideas/open-forum) y 'Input: Submitting Proposals' (engage.gov.tt/ideas/submitting-proposals).</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>The National Strategy for a Digital TT is finalized, and while the Ministry of Digital Transformation is no longer seeking input, they welcome feedback or comments through the citizen engagement digital platform Engage TT. (engage.gov.tt sigue operativo en 2026 bajo MPAAI).</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>The Ministry of Digital Transformation (MDT) officially presented the National Digital Transformation Strategy (NDTS) 2024-2027... launched during a NDTS Symposium in collaboration with the Inter-American Development Bank (IDB) on Wednesday, February 12th 2025. A major highlight... was the introduction of two new digital tools (EngageTT y AskNDTS). (Lanzamiento/anuncio unico en feb-2025; plataforma de uso continuo pero sin &gt;=2 ediciones de proceso participativo documentadas).</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>The Ministry of Digital Transformation (MDT) officially presented the National Digital Transformation Strategy (NDTS) 2024-2027... and introduced the EngageTT website - an online platform where citizens, businesses, and stakeholders can get real-time updates on digital transformation initiatives, and offer feedback via surveys and polls. (Convocante: gobierno nacional / Ministry of Digital Transformation, hoy MPAAI).</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Go Vocal Support Base (AI Analysis): 'Access to this feature depends on your plan. Advanced Sensemaking with auto-insights is available in the Premium plan.' -&gt; la IA/NLP de Go Vocal NO es automatica, depende del plan; y para EngageTT solo se documenta 'feedback via surveys and polls'/Open Forum/ideas, SIN mencion de analisis automatico por IA de los aportes. No se halla evidencia de activacion del NLP sobre el contenido en la instancia TT. 3a PASADA (refuerzo): Oxford Insights, 'The country's AI utilisation for citizens is concentrated in a robust Chatbot programme' (mas 'deployment of large language models for internal development purposes') -&gt; la IA ciudadana de TT es el chatbot, NO el analisis de aportes.</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Sin evidencia de IA aplicada al contenido de los aportes en engage.gov.tt. La unica IA confirmada de cara al ciudadano (AskNDTS/ANANSI) es chatbot de FAQ, excluido del criterio. En 3a pasada, el material de MPAAI 2026 enmarca la IA en el asistente ANANSI y en encuestas de AI-readiness (resultados 'consolidated and reviewed' en talleres), sin mencion de analisis por IA de los aportes del NDTS ni de Go Vocal Sensemaking.</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>https://support.govocal.com/en/articles/8316692-ai-analysis
 https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool
@@ -10271,59 +9858,59 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>UY</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Polis has been used to facilitate discussion and build consensus ... in Uruguay on a national referendum (OCDE 2025, 'Governing with AI')</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists — ran Polis alongside the referendum</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>The algorithm maps participants' responses and clusters opinions, facilitating the identification of positions that are supported by the majority of participants (OCDE 2025)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>16,499 people cast more than 295,000 votes ... The referendum was lost by less than 1%</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>ran Polis alongside the referendum to look for something deeper than "yes or no"</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Polis revealed that even where public safety divided people, surprising points of consensus broke through on other issues — bridges between groups</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/
 https://www.oecd.org/en/publications/governing-with-artificial-intelligence_795de142-en.html</t>
@@ -10331,7 +9918,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L38"/>
+  <autoFilter ref="A1:L35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10350,172 +9937,172 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>GUÍA — Validar los casos y pasar al cálculo (ILIA 2026)</t>
         </is>
       </c>
-      <c r="B1" s="14" t="n"/>
+      <c r="B1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Qué tienes</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
-        <is>
-          <t>Planilla con 6 pestañas (criterio corregido). 37 casos entran/dudosos · 70 excluidos · 107 en total. Tras dedup e-Cidadania: 36 iniciativas.</t>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Planilla con 6 pestañas (criterio corregido). 34 casos entran/dudosos · 73 excluidos · 107 en total. Tras dedup e-Cidadania: 33 iniciativas.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Cómo navegar</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Pestaña 1 = trabajo y cálculo · 2 = qué decidir a mano · 3 = excluidos (referencia) · 4 = evidencia/citas · 5 = esta guía · 6 = metodología CENIA v2.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr"/>
-      <c r="B4" s="14" t="inlineStr"/>
+      <c r="A4" s="14" t="inlineStr"/>
+      <c r="B4" s="13" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>PASO 1 — Confirmar exclusiones (pestaña 2, grupo A)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>4 casos ya FUERA: no son procesos de participación — PE conteo electoral · CO Descongestión (atención) · BR ParticipACT y CR dIAra (civic tech). Solo confirmar.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>PASO 2 — Confirmar rescatados → ENTRA (grupo B)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>7 casos que ENTRAN: MX Presupuesto CRECES · CL LXS 400 · CL Estrategia Gob. Digital · HN RedPública · CL Voz nuevos votantes · CL Jornada UNAB · CO Chatico. Confirmar SI.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>PASO 3 — Casos frontera (RESUELTOS)</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Ya decididos con investigación: ENTRAN TT EngageTT, CO Chatico, BR Colab · SALEN DO CiudadanIA, CO DNP, CR U-Report (+ BR ParticipACT, CR dIAra). Ver casos_frontera_ILIA2026.md. No requiere acción.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>PASO 4 — Resolver DUDAS de campo (grupo E)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>4 casos (Jalisco, Gaitana, Viña Decide, Participa Pudahuel). Abrir la URL y confirmar si es participación con IA en alguna etapa. Marcar SI o NO.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>PASO 5 — Reingresos y dedup (grupos F y G)</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>F: UCampus y CU Código de las Familias (posible reingreso). G: e-Cidadania cuenta como 1; CL Participación Constitucional: 1 SI + 1 NO.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>PASO 6 — Completar datos de cálculo</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Para los que quedan en SI, revisar en la pestaña 1 que estén completos: Tipo de proceso, Etapas, Nivel (0-3), Convocante, Tipo org. Donde 'Nº gaps'&gt;0, abrir la URL y completar.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>PASO 7 — Validar evidencia (pestaña 4)</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Revisar que cada campo crítico tenga cita textual. Celdas ámbar = falta cita → verificar con la fuente antes de dar por bueno.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>PASO 8 — Calcular</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Con la lista final de iniciativas y sus campos completos, correr el motor (Sub1 Uso + Sub2 Desarrollo). Ver config.yaml y src/calc_engine.py.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr"/>
-      <c r="B13" s="14" t="inlineStr"/>
+      <c r="A13" s="14" t="inlineStr"/>
+      <c r="B13" s="13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Regla de elegibilidad (CRITERIO CORREGIDO)</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Lo decisivo es si es REALMENTE un proceso de participación ciudadana (consulta, presupuesto participativo, mini-público, referendo/iniciativa popular, gobernanza colaborativa/deliberación) que usa IA en alguna de las 4 etapas — INCLUIDA la logística en Planificación/Implementación (modera, administra turnos, prepara materiales, organiza). NO se exige que la IA analice el contenido. NO ENTRA: civic tech que no es un proceso participativo (app de reporte/servicio/monitoreo), atención ciudadana, voto/conteo electoral por candidatos, IA como tema, estudio sin despliegue, o duplicado.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Qué alimenta el cálculo (metodología CENIA v2)</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Sub1 (Uso): Tipos de proceso (÷5) · Etapas de uso (÷4) · Continuidad = nivel máximo del país (÷3) · Organización Convocante = 3 sub-componentes (amplitud gubernamental ÷3 + amplitud no gubernamental ÷4 + co-convocatoria por máx. relativo) · Cantidad = nº de iniciativas ELEGIBLES (todas, umbrales fijos). Sub2 (Desarrollo, = 2025): Desarrollador (nacional/internacional × 4 tipos, máx. relativo) · Tipos de IA.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>IMPORTANTE — co-convocatoria</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Anotar TODOS los convocantes de cada iniciativa (no solo el principal): si ≥2 tipos co-convocan, forman una 'combinación' que suma al tercer sub-componente de Organización Convocante.</t>
         </is>
@@ -10542,24 +10129,24 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>METODOLOGÍA FINAL — IA en Participación Ciudadana (CENIA v2 · jun-2026)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Indicador = (Sub-Indicador de Uso + Sub-Indicador de Desarrollo) / 2</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr"/>
-      <c r="B3" s="14" t="inlineStr"/>
-      <c r="C3" s="14" t="inlineStr"/>
-      <c r="D3" s="14" t="inlineStr"/>
+      <c r="A3" s="13" t="inlineStr"/>
+      <c r="B3" s="13" t="inlineStr"/>
+      <c r="C3" s="13" t="inlineStr"/>
+      <c r="D3" s="13" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -10584,280 +10171,280 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Uso de IA
 (promedio simple
 de 5 variables)</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>Tipos de proceso</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>nº de tipos distintos ÷ 5 (máximo absoluto)</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>Tipo de proceso</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n"/>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="A6" s="19" t="n"/>
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>Etapas de uso</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>nº de etapas distintas ÷ 4 (máximo absoluto)</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>Etapas uso IA</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="n"/>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="A7" s="19" t="n"/>
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Continuidad</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>nivel MÁXIMO verificado del país ÷ 3 · un 'anuncio' caduca a los 2 años sin implementación</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>Nivel (0-3)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n"/>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="A8" s="19" t="n"/>
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Organización Convocante</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>promedio de 3 sub-componentes co-iguales (ver detalle abajo)</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Convocante (7-cat)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n"/>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="A9" s="20" t="n"/>
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Cantidad de iniciativas</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>nº de TODAS las iniciativas elegibles del país · umbrales fijos 0→0 · 1-3→25 · 4-6→50 · 7-9→75 · 10+→100</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>1 fila = 1 iniciativa</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Desarrollo de IA
 (idéntico a 2025)</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Desarrollador</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>nacional / internacional × 4 tipos de actor · máximo relativo</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>Tipo desarrollador IA · Origen</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="n"/>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="A11" s="20" t="n"/>
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Tipos de IA</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>nº de sistemas de IA distintos · máximo relativo</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>Tipos/familia IA</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr"/>
-      <c r="B12" s="14" t="inlineStr"/>
-      <c r="C12" s="14" t="inlineStr"/>
-      <c r="D12" s="14" t="inlineStr"/>
+      <c r="A12" s="13" t="inlineStr"/>
+      <c r="B12" s="13" t="inlineStr"/>
+      <c r="C12" s="13" t="inlineStr"/>
+      <c r="D12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>ORGANIZACIÓN CONVOCANTE — 3 sub-componentes co-iguales · valor de la variable = (1 + 2 + 3) / 3</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>1 · Amplitud gubernamental</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>nº de tipos gubernamentales distintos ÷ 3</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>gobierno local · gobierno nacional · otra institución pública</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr"/>
+      <c r="D14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>2 · Amplitud no gubernamental</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>nº de tipos no gubernamentales distintos ÷ 4</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>empresa · universidad · sociedad civil · organización internacional</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr"/>
+      <c r="D15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>3 · Co-convocatoria</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>nº de combinaciones distintas (conjuntos de ≥2 tipos que co-convocan una misma iniciativa) ÷ máximo relativo móvil del ciclo</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>combinaciones DEDUPLICADAS · una co-convocatoria de 4 actores = 1 combinación</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr"/>
+      <c r="D16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr"/>
-      <c r="B17" s="14" t="inlineStr"/>
-      <c r="C17" s="14" t="inlineStr"/>
-      <c r="D17" s="14" t="inlineStr"/>
+      <c r="A17" s="13" t="inlineStr"/>
+      <c r="B17" s="13" t="inlineStr"/>
+      <c r="C17" s="13" t="inlineStr"/>
+      <c r="D17" s="13" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>• ELEGIBILIDAD (criterio corregido): un caso ENTRA si es realmente un proceso de PARTICIPACIÓN CIUDADANA que usa IA en alguna etapa (incl. logística: modera / administra turnos / prepara materiales / organiza). La IA NO necesita analizar el contenido. NO entra civic tech (reporte/servicio/monitoreo), atención ciudadana ni voto/conteo electoral.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr"/>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr"/>
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>• Universidades públicas → cuentan como 'Universidad' (no gubernamental), NO como 'otra institución pública'.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr"/>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr"/>
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>• Anotar TODOS los convocantes de cada iniciativa (no solo el principal): así se detecta la co-convocatoria.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr"/>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr"/>
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>• El máximo relativo de co-convocatoria se recalcula en cada corrida del motor — no se fija a mano.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr"/>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr"/>
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>• 'Cantidad' cuenta las iniciativas elegibles; los duplicados (Cuenta como iniciativa = NO) no se suman.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr"/>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr"/>
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>• El Sub-Indicador de Desarrollo es idéntico al de 2025 (no se modificó).</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr"/>
-      <c r="B24" s="14" t="inlineStr"/>
-      <c r="C24" s="14" t="inlineStr"/>
-      <c r="D24" s="14" t="inlineStr"/>
+      <c r="A24" s="13" t="inlineStr"/>
+      <c r="B24" s="13" t="inlineStr"/>
+      <c r="C24" s="13" t="inlineStr"/>
+      <c r="D24" s="13" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>metodologia_final_CENIA_v2.xlsx · detalle de conformidad en conformidad_metodologia_CENIA.md</t>
         </is>

--- a/data/gates/planilla_ILIA2026_SIMPLE.xlsx
+++ b/data/gates/planilla_ILIA2026_SIMPLE.xlsx
@@ -15,10 +15,10 @@
     <sheet name="6 · Metodología (CENIA v2)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos (entran+dudosos)'!$A$1:$X$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2 · A validar a mano'!$A$1:$G$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 · Excluidos'!$A$1:$E$74</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 · Evidencia y fuentes'!$A$1:$L$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos (entran+dudosos)'!$A$1:$X$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2 · A validar a mano'!$A$1:$G$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 · Excluidos'!$A$1:$E$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 · Evidencia y fuentes'!$A$1:$L$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -582,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X35"/>
+  <dimension ref="A1:X36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3641,12 +3641,12 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CU</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAGA IA </t>
+          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -3666,17 +3666,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Referendos e Iniciativas Populares</t>
+          <t>Participación Digital; Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
@@ -3684,17 +3684,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional; sociedad civil</t>
+          <t>gobierno nacional</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil</t>
+          <t>Privado; Academia; Gobierno</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3714,41 +3714,42 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>NLP; Minería de texto; Recuperación de información; Clasificación automática de documentos</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto. Analiza datos de planes de acción de gobierno abierto de Ecuador y otros países de Hispanoamérica para sugerir actividades e hitos relacionados con temas propuestos por los usuarios</t>
+          <t>Consulta popular legislativa nacional sobre el proyecto del Código de las Familias en Cuba, organizada y supervisada por el Consejo Electoral Nacional (CEN). Se desarrolló entre febrero y abril de 2022 mediante más de 79.000 reuniones en barrios, centros laborales y estudiantiles, con la participación de unos 6.481.200 personas que emitieron opiniones y propuestas sobre el articulado del proyecto de ley. Las propuestas recogidas eran revisadas y clasificadas por juristas en el sistema XISCOP y luego procesadas en el sistema GEMA-CEN, que mediante 'análisis inteligente de los expedientes' agrupaba propuestas similares y determinaba 'propuestas típicas' por párrafo/categoría (se determinaron 5.237 propuestas típicas por Título). XISCOP (UCI) emitía además las estadísticas oficiales. El proceso de consulta cerró en abril de 2022; el Código fue aprobado posteriormente en referendo el 25 de septiembre de 2022.</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
+          <t>Consejo Electoral Nacional (CEN) de Cuba como órgano organizador y supervisor de la consulta popular. El procesamiento informático se apoyó en dos sistemas: XISCOP, desarrollado por la Universidad de las Ciencias Informáticas (UCI), para la entrada, revisión, clasificación y estadísticas oficiales; y GEMA-CEN, basado en el producto GEMA de la empresa estatal Datys, para el 'análisis inteligente' y agrupamiento de las propuestas. La Asamblea Nacional del Poder Popular y la Comisión redactora del Ministerio de Justicia recibieron los resultados.</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V27" s="4" t="n">
-        <v>0</v>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="V27" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>https://ia.gobiernoabierto.ec/
-https://ia.gobiernoabierto.ec/acercade</t>
+          <t>http://www.datys.cu/spa/site/product/15
+https://www.granma.cu/cuba/2022-01-24/herramientas-digitales-seran-claves-durante-la-consulta-popular-del-codigo-de-las-familias-24-01-2022-13-01-18
+https://www.uci.cu/</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>EC-paga-ia</t>
+          <t>CU-consulta-popular-codigo-de-las-familias</t>
         </is>
       </c>
     </row>
@@ -3756,12 +3757,12 @@
       <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guatemala Joven Conversa </t>
+          <t xml:space="preserve">PAGA IA </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -3786,7 +3787,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3799,12 +3800,12 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>organización internacional; sociedad civil</t>
+          <t>gobierno nacional; sociedad civil</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3819,208 +3820,209 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>NLP - Sentiment; NLP - Tópicos</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarrollo y la lucha contra la corrupción.</t>
+          <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto. Analiza datos de planes de acción de gobierno abierto de Ecuador y otros países de Hispanoamérica para sugerir actividades e hitos relacionados con temas propuestos por los usuarios</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
+          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="V28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>https://ia.gobiernoabierto.ec/
+https://ia.gobiernoabierto.ec/acercade</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>EC-paga-ia</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guatemala Joven Conversa </t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>organización internacional; sociedad civil</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Mixto</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>NLP - Sentiment; NLP - Tópicos</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarrollo y la lucha contra la corrupción.</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
         <is>
           <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
 https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/
 https://dppa.un.org/en/using-power-of-ai-to-boost-youth-political-participation-guatemala</t>
         </is>
       </c>
-      <c r="X28" s="2" t="inlineStr">
+      <c r="X29" s="2" t="inlineStr">
         <is>
           <t>GT-guatemala-joven-conversa</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>HN</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RedPública + iVerify </t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>organización internacional; universidad</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno; Academia</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>Internacional, Nacional</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>NLP - Tópicos</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias. Integra iVerify, una herramienta que utiliza aprendizaje automático para detectar y clasificar desinformación electoral antes de su publicación.</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
-        </is>
-      </c>
-      <c r="X29" s="2" t="inlineStr">
-        <is>
-          <t>HN-redpublica-iverify</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Gobernanza Colaborativa; Participación Digital</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4038,228 +4040,228 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
+          <t>organización internacional; universidad</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno; Academia</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>Internacional, Nacional</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>NLP - Tópicos</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias. Integra iVerify, una herramienta que utiliza aprendizaje automático para detectar y clasificar desinformación electoral antes de su publicación.</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>HN-redpublica-iverify</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Gobernanza Colaborativa; Participación Digital</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
           <t>gobierno local</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Gobierno</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>NLP; Otros(no especificado)</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr">
+      <c r="S31" s="2" t="inlineStr">
         <is>
           <t>Elaboración del Programa de Gobierno del Estado de Guanajuato 2024-2030 ('Gobierno de la Gente'), un plan de gobierno construido con participación ciudadana: se recorrió el territorio y se realizaron cuatro talleres regionales (noreste, norte, centro y sur) con representación de los 46 municipios, integrando la voz de más de 26,000 personas mediante talleres y consultas. El contenido fue validado por el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG), conformado por ciudadanía, la Gobernadora, secretarios de cada eje e IPLANEG. Se utilizaron herramientas de inteligencia artificial para procesar y organizar las miles de ideas y propuestas recibidas, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región, transformando el diálogo social en datos para la toma de decisiones que alimentaron los ejes del programa. Adicionalmente existe la asistente virtual 'Esperanza' para consultar el programa ya publicado.</t>
         </is>
       </c>
-      <c r="T30" s="2" t="inlineStr">
+      <c r="T31" s="2" t="inlineStr">
         <is>
           <t>Gobierno del Estado de Guanajuato — Instituto de Planeación, Estadística y Geografía del Estado de Guanajuato (IPLANEG), con validación del COPLADEG. Titular: Gobernadora Libia Dennise García Muñoz Ledo.</t>
         </is>
       </c>
-      <c r="U30" s="2" t="inlineStr">
+      <c r="U31" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="V30" s="5" t="n">
+      <c r="V31" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="W30" s="2" t="inlineStr">
+      <c r="W31" s="2" t="inlineStr">
         <is>
           <t>https://guanajuatointeligente.com/como-hicimos-el-programa/
 https://iplaneg.guanajuato.gob.mx/programagobierno24-30/
 https://iplaneg.guanajuato.gob.mx/wp-content/uploads/03-2.05-Diagnostico-Programa-de-Gobierno-2024-2030-_Diagnostico-Estatal-2025_.pdf</t>
         </is>
       </c>
-      <c r="X30" s="2" t="inlineStr">
+      <c r="X31" s="2" t="inlineStr">
         <is>
           <t>MX-guanajuato-inteligente-2024-2030</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Presupuesto CRECES</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Presupuestos Participativos</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>gobierno local</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>Privado</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>Chatbot - Inespecífico</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>Presupuesto participativo del Ayuntamiento de Hermosillo en México. Utiliza un chatbot que a través de IA simplifica y facilita la votación de los presupuestos participativos</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>Ayundamiento de Hermosilla</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="V31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
-        </is>
-      </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t>MX-presupuesto-creces</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Análisis; Traducción Política</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
@@ -4267,419 +4269,533 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>gobierno local</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>Chatbot - Inespecífico</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>Presupuesto participativo del Ayuntamiento de Hermosillo en México. Utiliza un chatbot que a través de IA simplifica y facilita la votación de los presupuestos participativos</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>Ayundamiento de Hermosilla</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="V32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>MX-presupuesto-creces</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Análisis; Traducción Política</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>sociedad civil; gobierno nacional</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Sociedad Civil</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="P33" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr">
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr">
+      <c r="S33" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea (www.mansaidea.com) es una plataforma digital basada en inteligencia artificial lanzada el 1 de abril de 2024 por la Fundación Panamá Participa (sociedad civil), liderada por Paulina Franceschi. La plataforma organiza y hace navegables más de 175.000 ideas y propuestas ciudadanas generadas durante el Pacto del Bicentenario 'Cerrando Brechas' (proceso participativo nacional convocado por el gobierno de Panamá / Concertación Nacional, presidente Cortizo, 2020-2021), agregando los consensos nacionales y regionales/provinciales por tema en un solo clic. La IA se aplica sobre el CONTENIDO de los aportes ciudadanos (organiza, agrega y sintetiza el corpus de propuestas) para convertirlo en una base de datos navegable. El uso de la IA es un tratamiento PUNTERAL (~2024) de un corpus histórico de un proceso participativo ya cerrado (el Pacto fue 2020-2021), orientado a elevar el nivel de la conversación electoral 2024 y a dotar a candidatos, medios y ciudadanía de una herramienta para alinear planes con las necesidades de la población y monitorear el mandato ciudadano. IMPORTANTE: el proceso participativo original (recolección de aportes) fue convocado por el gobierno; la capa de IA (Mansa Idea) la desarrolla la sociedad civil sobre ese corpus ya recolectado.</t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr">
+      <c r="T33" s="2" t="inlineStr">
         <is>
           <t>Fundación Panamá Participa (sociedad civil, Panamá), iniciativa liderada por Paulina Franceschi. El proceso participativo de origen (Pacto del Bicentenario 'Cerrando Brechas') fue convocado por el Gobierno de Panamá a través del mecanismo de Concertación Nacional para el Desarrollo (presidente Laurentino Cortizo), con apoyo del PNUD.</t>
         </is>
       </c>
-      <c r="U32" s="2" t="inlineStr">
+      <c r="U33" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="V32" s="5" t="n">
+      <c r="V33" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="W32" s="2" t="inlineStr">
+      <c r="W33" s="2" t="inlineStr">
         <is>
           <t>https://mansaidea.com/ (intentar archive.org / cache); buscar 'Mansa Idea metodología inteligencia artificial procesamiento propuestas' y entrevistas técnicas a Paulina Franceschi / Fundación Panamá Participa.
 https://mansaidea.com/ ; buscar 'Mansa Idea 2025' / 'Mansa Idea 2026' / 'Fundación Panamá Participa actividad reciente'.
 https://mansaidea.com/ ; buscar evidencia de actualizaciones periódicas del corpus o nuevas convocatorias.</t>
         </is>
       </c>
-      <c r="X32" s="2" t="inlineStr">
+      <c r="X33" s="2" t="inlineStr">
         <is>
           <t>PA-mansa-idea-pacto-del-bicentenario</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-      <c r="B33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="J33" s="2" t="n">
+      <c r="J34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>otra institución pública</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O33" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr">
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>NLP - Tópicos; NLP - Sentiment</t>
         </is>
       </c>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>Una consulta pública para recoger opiniones sobre el Proyecto Educativo Nacional 2036, utilizando encuestas en línea, talleres y mesas deliberativas.</t>
         </is>
       </c>
-      <c r="T33" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
         <is>
           <t>Consejo Nacional de Educación del Perú</t>
         </is>
       </c>
-      <c r="U33" s="2" t="inlineStr">
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="V33" s="4" t="n">
+      <c r="V34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W33" s="2" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
         <is>
           <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional
 https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080
 https://andina.pe/agencia/noticia-usan-inteligencia-artificial-para-formular-proyecto-educativo-nacional-al-2036-777369.aspx</t>
         </is>
       </c>
-      <c r="X33" s="2" t="inlineStr">
+      <c r="X34" s="2" t="inlineStr">
         <is>
           <t>PE-consulta-ciudadana-sobre-el-proyecto-nac</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>DUDA(lean NO)</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="n">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>gobierno nacional</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>NLP; Resumen automatico; Clasificacion/agrupacion de texto (capacidad de la plataforma sujeta a plan Premium; activacion NO confirmada en TT)</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) es la plataforma de participacion ciudadana del Ministry of Digital Transformation de Trinidad y Tobago (desde mayo 2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), lanzada en el simposio del NDTS el 12 de febrero de 2025 junto al BID (IDB). Se usa como canal de participacion en el proceso de planificacion nacional del National Digital Transformation Strategy (NDTS) 2024-2027, donde ciudadanos, empresas y partes interesadas reciben actualizaciones y aportan retroalimentacion via encuestas, sondeos (polls), un 'Open Forum' de ideas y el envio de propuestas. La instancia corre sobre el software Go Vocal (antes CitizenLab) -confirmado por la ruta interna 'projects/e-democracy-govocal-internal'-. Go Vocal incorpora un modulo de IA/NLP de 'Sensemaking' (analisis y resumen automatico de aportes), pero ese modulo NO viene activo por defecto: segun la documentacion de soporte de Go Vocal, el acceso a la funcion de AI Analysis/Sensemaking DEPENDE DEL PLAN contratado (Advanced Sensemaking con auto-insights esta en el plan Premium). Tras 2a pasada de investigacion (&gt;=14 busquedas/fetches) NO se halla evidencia alguna de que la instancia de Trinidad active ni use esas funciones de IA sobre el CONTENIDO de los aportes; toda la documentacion describe a EngageTT como recolector (surveys, polls, Open Forum, ideas), es decir plataforma usada como formulario sin analisis automatico confirmado. Existe ademas AskNDTS, un chatbot/PWA de IA conversacional para responder preguntas sobre el NDTS (rol de FAQ informativo, EXCLUIDO del criterio).</t>
         </is>
       </c>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="T35" s="2" t="inlineStr">
         <is>
           <t>Ministry of Digital Transformation de Trinidad y Tobago (desde el 23-may-2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), en colaboracion con el Banco Interamericano de Desarrollo (BID/IDB). Plataforma de software: Go Vocal (antes CitizenLab), empresa belga.</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr">
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="V34" s="5" t="n">
+      <c r="V35" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="W34" s="2" t="inlineStr">
+      <c r="W35" s="2" t="inlineStr">
         <is>
           <t>https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
 https://www.govocal.com/plans
 https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool</t>
         </is>
       </c>
-      <c r="X34" s="2" t="inlineStr">
+      <c r="X35" s="2" t="inlineStr">
         <is>
           <t>TT-engagett-plataforma-go-vocal</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
-      <c r="B35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>UY</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>(sin revisar)</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>MEDIA (fuente primaria + OCDE 2025; fetch primario bloqueado por proxy, citas vía repo/WebSearch)</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="J35" s="2" t="n">
+      <c r="J36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>universidad</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Sociedad Civil; Academia</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>Clustering; ML - Inespecífico</t>
         </is>
       </c>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>Referéndum nacional para derogar 135 artículos de la Ley de Urgente Consideración (LUC). Un equipo de la Universidad de la República corrió una conversación Pol.is en paralelo al referéndum del 27/03/2022 (documentado como caso 2021).</t>
         </is>
       </c>
-      <c r="T35" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
         <is>
           <t>Equipo de 13 personas de la Universidad de la República (UdelaR) — ingenieros, comunicadores y científicos de datos; plataforma Pol.is (The Computational Democracy Project)</t>
         </is>
       </c>
-      <c r="U35" s="2" t="inlineStr">
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="V35" s="5" t="n">
+      <c r="V36" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="W35" s="2" t="inlineStr">
+      <c r="W36" s="2" t="inlineStr">
         <is>
           <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/</t>
         </is>
       </c>
-      <c r="X35" s="2" t="inlineStr">
+      <c r="X36" s="2" t="inlineStr">
         <is>
           <t>UY-polis-referendum-luc</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X35"/>
+  <autoFilter ref="A1:X36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4690,7 +4806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5494,149 +5610,73 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>F. Posible reingreso</t>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>G. Dedup (confirmar)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>¿Reingresa? (SI/NO)</t>
+          <t>Confirmar cuenta como 1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>e-Cidadania (Senado Federal)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>El 'matching de ideias' no se cuenta aparte del 'marcado de audiencias' (misma plataforma)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>'Duas ferramentas relacionadas' del mismo portal e-Cidadania (fuente Senado).</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>G. Dedup (confirmar)</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar 1 SI + 1 NO</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma UCampus - participación 2023 (proceso constitucional)</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Verificar si corresponde reingresarlo</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Su referencia lo marca RESCATABLE (confirmar si hubo NLP sobre los aportes del proceso constituyente).</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>https://ingenieria.uchile.cl/noticias/204877/-participacion-ciudadana-proceso-constitucional-sera-por-ucampus
-https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>F. Posible reingreso</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>¿Reingresa? (SI/NO)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>CU</t>
-        </is>
-      </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
+          <t>Participación Ciudadana Proceso Constitucional</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Verificar si corresponde reingresarlo</t>
+          <t>Homónimo duplicado: uno cuenta (SI), el otro NO</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Su referencia lo marca RESCATABLE; mi evidencia (ficha técnica Datys/GEMA = NLP) apoya SI.</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>http://www.datys.cu/spa/site/product/15
-https://www.granma.cu/cuba/2022-01-24/herramientas-digitales-seran-claves-durante-la-consulta-popular-del-codigo-de-las-familias-24-01-2022-13-01-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>G. Dedup (confirmar)</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Confirmar cuenta como 1</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>e-Cidadania (Senado Federal)</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>El 'matching de ideias' no se cuenta aparte del 'marcado de audiencias' (misma plataforma)</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>'Duas ferramentas relacionadas' del mismo portal e-Cidadania (fuente Senado).</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>G. Dedup (confirmar)</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Confirmar 1 SI + 1 NO</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Participación Ciudadana Proceso Constitucional</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Homónimo duplicado: uno cuenta (SI), el otro NO</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
           <t>Ya resuelto en la planilla.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G25"/>
+  <autoFilter ref="A1:G23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5647,7 +5687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6821,27 +6861,27 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>CU</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
+          <t>CiudadanIA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Dudoso</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Dentro de un proceso participativo formal y de gran escala (consulta popular legislativa nacional sobre el Código de las Familias, feb-abr 2022, ~6,5 millones de participantes y cientos de miles de propuestas) se usó IA sobre el CONTENIDO de los aportes ciudadanos: el sistema GEMA-CEN (basado en GEM</t>
+          <t>Solo atención/servicio; la 'participación' es co-diseñar la IA aportando datos, no consulta pública. Sin módulo de participación (verificado). Decisión del equipo.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>http://www.datys.cu/spa/site/product/15</t>
+          <t>https://www.genia.ai/paises-miembros</t>
         </is>
       </c>
     </row>
@@ -6853,22 +6893,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>CiudadanIA</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Solo atención/servicio; la 'participación' es co-diseñar la IA aportando datos, no consulta pública. Sin módulo de participación (verificado). Decisión del equipo.</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.genia.ai/paises-miembros</t>
+          <t>https://www.undp.org/es/guatemala/comunicados-de-prensa/sara-la-nueva-herramienta-de-inteligencia-artificial-para-combatir-la-violencia-de-genero-en-centroamerica</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6920,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>TAÍNA: Gobierno Inteligente</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -6890,66 +6930,66 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Atención ciudadana</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/guatemala/comunicados-de-prensa/sara-la-nueva-herramienta-de-inteligencia-artificial-para-combatir-la-violencia-de-genero-en-centroamerica</t>
+          <t>https://www.diariolibre.com/actualidad/nacional/2023/10/11/gobierno-presenta-estrategia-de-inteligencia-artificial/2489157</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>TAÍNA: Gobierno Inteligente</t>
+          <t>Plataforma de modelos generativos de IA de SEGEPLAN + Red Ciudadana (Guatemala)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Descubrimiento</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>El criterio ELEGIBLE exige que la IA generativa se use para SISTEMATIZAR/CLASIFICAR/RESUMIR el CONTENIDO de los aportes de los diagnosticos participativos (Consejos de Desarrollo COCODES/COMUDES) en los Planes de Desarrollo Municipal (PDM). Toda la evidencia primaria y secundaria (nota SEGEPLAN ?p=1</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.diariolibre.com/actualidad/nacional/2023/10/11/gobierno-presenta-estrategia-de-inteligencia-artificial/2489157</t>
+          <t>https://portal.segeplan.gob.gt/segeplan/?p=14176</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LATAM</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Plataforma de modelos generativos de IA de SEGEPLAN + Red Ciudadana (Guatemala)</t>
+          <t>ANTAI Smart CID (Autoridad Nacional de Transparencia y Acceso a la Información + OS City)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>El criterio ELEGIBLE exige que la IA generativa se use para SISTEMATIZAR/CLASIFICAR/RESUMIR el CONTENIDO de los aportes de los diagnosticos participativos (Consejos de Desarrollo COCODES/COMUDES) en los Planes de Desarrollo Municipal (PDM). Toda la evidencia primaria y secundaria (nota SEGEPLAN ?p=1</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://portal.segeplan.gob.gt/segeplan/?p=14176</t>
+          <t>https://www.caf.com/es/actualidad/noticias/2021/07/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
         </is>
       </c>
     </row>
@@ -6961,7 +7001,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>ANTAI Smart CID (Autoridad Nacional de Transparencia y Acceso a la Información + OS City)</t>
+          <t>Botivist</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -6971,12 +7011,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>No tiene foco en un país específico</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.caf.com/es/actualidad/noticias/2021/07/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
+          <t>https://www.microsoft.com/en-us/research/publication/botivist-calling-volunteers-to-action-using-online-bots/</t>
         </is>
       </c>
     </row>
@@ -6988,7 +7028,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Botivist</t>
+          <t>Chatbot DCI (Denuncia Ciudadana Idónea)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -6998,12 +7038,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>No tiene foco en un país específico</t>
+          <t>No evidencia de uso de IA</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/research/publication/botivist-calling-volunteers-to-action-using-online-bots/</t>
+          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci-1</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7055,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Chatbot DCI (Denuncia Ciudadana Idónea)</t>
+          <t>Citibeats: Covid-19 (“Percepciones ciudadanas COVID-19”)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -7025,12 +7065,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA</t>
+          <t>Análisis de redes sociales, no es participación</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci-1</t>
+          <t>https://forbescentroamerica.com/2021/04/28/civiclytics-el-big-data-apoya-la-recuperacion-economica</t>
         </is>
       </c>
     </row>
@@ -7042,7 +7082,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Citibeats: Covid-19 (“Percepciones ciudadanas COVID-19”)</t>
+          <t>Ushahidi "AI for Good"</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -7052,24 +7092,24 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Análisis de redes sociales, no es participación</t>
+          <t>No se evidencia el uso de IA en los proyectos de participación listados para Latam</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://forbescentroamerica.com/2021/04/28/civiclytics-el-big-data-apoya-la-recuperacion-economica</t>
+          <t>https://www.ushahidi.com/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Ushahidi "AI for Good"</t>
+          <t>AMIMgo</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -7079,12 +7119,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>No se evidencia el uso de IA en los proyectos de participación listados para Latam</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.ushahidi.com/</t>
+          <t>https://amim.mx/noticias/detalle/estrena-amim-chatbot-para-la-atencion-ciudadana</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7136,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>AMIMgo</t>
+          <t>ATIC</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -7106,12 +7146,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://amim.mx/noticias/detalle/estrena-amim-chatbot-para-la-atencion-ciudadana</t>
+          <t>https://oem.com.mx/la-prensa/metropoli/info-cdmx-implementa-atic-una-herramienta-con-ia-que-facilita-el-acceso-a-la-informacion-13081722</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7163,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>ATIC</t>
+          <t>ChatBot “Claudia"</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -7133,12 +7173,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No es participación</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://oem.com.mx/la-prensa/metropoli/info-cdmx-implementa-atic-una-herramienta-con-ia-que-facilita-el-acceso-a-la-informacion-13081722</t>
+          <t>https://mexicocomovamos.mx/animal-politico/2024/08/chatbot-claudia-una-herramienta-de-participacion-ciudadana/</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7190,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>ChatBot “Claudia"</t>
+          <t>Chatbot "Inés"</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -7160,12 +7200,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>No es participación</t>
+          <t>No es participación, es informativo</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://mexicocomovamos.mx/animal-politico/2024/08/chatbot-claudia-una-herramienta-de-participacion-ciudadana/</t>
+          <t>https://centralelectoral.ine.mx/2024/04/17/nueva-version-del-chatbot-del-ine-en-whatsapp-permitira-verificar-informacion-sobre-elecciones-2024/</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7217,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Chatbot "Inés"</t>
+          <t>Chatbot Sam Petrino</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -7187,12 +7227,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>No es participación, es informativo</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://centralelectoral.ine.mx/2024/04/17/nueva-version-del-chatbot-del-ine-en-whatsapp-permitira-verificar-informacion-sobre-elecciones-2024/</t>
+          <t>https://www.civica.digital/historias/chatbot-sam-petrino</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7244,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Sam Petrino</t>
+          <t>Chatbot Victoria</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -7219,7 +7259,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.civica.digital/historias/chatbot-sam-petrino</t>
+          <t>https://adip.cdmx.gob.mx/comunicacion/nota/la-adip-y-el-gobierno-de-la-ciudad-presentan-victoria-el-robot-que-colaborara-en-la-atencion-de-la-ciudadania</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7271,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Victoria</t>
+          <t>INAOE (Conacyt) – Laboratorio de Tecnologías del Lenguaje</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -7241,12 +7281,12 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://adip.cdmx.gob.mx/comunicacion/nota/la-adip-y-el-gobierno-de-la-ciudad-presentan-victoria-el-robot-que-colaborara-en-la-atencion-de-la-ciudadania</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
     </row>
@@ -7258,22 +7298,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>INAOE (Conacyt) – Laboratorio de Tecnologías del Lenguaje</t>
+          <t>Jalisco - Consulta ¡Armemos un Plan! (Plan Estatal de Desarrollo y Gobernanza 2024-2030)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Proceso participativo real y masivo (675.484 participaciones; 15.899 propuestas), pero NO hay evidencia de uso de IA para analizar/agrupar/clasificar el contenido de las propuestas (usa_IA_en_proceso 'no'). Sin uso de IA → NO. Decisión del equipo.</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
+          <t>https://armemosunplan.mx/propuestas-ciudadanas/</t>
         </is>
       </c>
     </row>
@@ -7285,22 +7325,22 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Jalisco - Consulta ¡Armemos un Plan! (Plan Estatal de Desarrollo y Gobernanza 2024-2030)</t>
+          <t>Movimex</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Proceso participativo real y masivo (675.484 participaciones; 15.899 propuestas), pero NO hay evidencia de uso de IA para analizar/agrupar/clasificar el contenido de las propuestas (usa_IA_en_proceso 'no'). Sin uso de IA → NO. Decisión del equipo.</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://armemosunplan.mx/propuestas-ciudadanas/</t>
+          <t>https://animalpolitico.com/estados/chatbot-movimex-tramites-denuncias-edomex</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7352,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Movimex</t>
+          <t>Sistema *0311 Locatel</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -7322,12 +7362,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Atención ciudadana</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://animalpolitico.com/estados/chatbot-movimex-tramites-denuncias-edomex</t>
+          <t>https://research.latinxinai.org/papers/naacl/2022/pdf/paper_01.pdf</t>
         </is>
       </c>
     </row>
@@ -7339,22 +7379,22 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Sistema *0311 Locatel</t>
+          <t>Sufragio seguro</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Baseline 2025</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>EXCLUSIÓN FIRME (recodificación 2026): Exclusión FIRME (recodificación 2026): integridad/proceso electoral, no contenido</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://research.latinxinai.org/papers/naacl/2022/pdf/paper_01.pdf</t>
+          <t>https://algoritmoscide.org/proyectos/sufragio-seguro/</t>
         </is>
       </c>
     </row>
@@ -7366,34 +7406,34 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Sufragio seguro</t>
+          <t>Violetta</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Baseline 2025</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>EXCLUSIÓN FIRME (recodificación 2026): Exclusión FIRME (recodificación 2026): integridad/proceso electoral, no contenido</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://algoritmoscide.org/proyectos/sufragio-seguro/</t>
+          <t>https://holasoyvioletta.com/acerca-de/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Violetta</t>
+          <t>Dr. ROSA y Dr. NICO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -7403,24 +7443,24 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://holasoyvioletta.com/acerca-de/</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Dr. ROSA y Dr. NICO</t>
+          <t>JNE WhatsApp Chatbot</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -7435,7 +7475,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
+          <t>https://portal.jne.gob.pe/Portal/Pagina/Nota/12783</t>
         </is>
       </c>
     </row>
@@ -7447,49 +7487,49 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>JNE WhatsApp Chatbot</t>
+          <t>Sistema de cómputo con IA para las Elecciones Generales 2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Conteo electoral (OCR de actas): votación política, no participación.</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://portal.jne.gob.pe/Portal/Pagina/Nota/12783</t>
+          <t>https://andina.pe/agencia/noticia-onpe-utilizara-un-nuevo-sistema-computo-resultados-incorporara-ia-1021072.aspx</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PY</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Sistema de cómputo con IA para las Elecciones Generales 2026</t>
+          <t>Consultas ciudadanas sobre IA en Paraguay - PNUD Accelerator Lab (AccLab) + Columbia SIPA + MITIC / insumo del diagnóstico AILA (Atlas de IA)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Descubrimiento</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Conteo electoral (OCR de actas): votación política, no participación.</t>
+          <t>El criterio ELEGIBLE exige que dentro de un proceso participativo convocado se use IA (NLP/ML/clustering/sentimiento) SOBRE EL CONTENIDO de los aportes. Aquí ocurre lo contrario: (1) la IA es el TEMA de la consulta (se pregunta a la ciudadania por su percepcion de la IA), y (2) el ANÁLISIS de los ap</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-onpe-utilizara-un-nuevo-sistema-computo-resultados-incorporara-ia-1021072.aspx</t>
+          <t>https://www.undp.org/es/paraguay/blog/consultas-ciudadanas-sobre-ia-en-paraguay-visiones-diversas-entre-el-campo-y-la-ciudad</t>
         </is>
       </c>
     </row>
@@ -7501,34 +7541,34 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Consultas ciudadanas sobre IA en Paraguay - PNUD Accelerator Lab (AccLab) + Columbia SIPA + MITIC / insumo del diagnóstico AILA (Atlas de IA)</t>
+          <t>ParaEmpleo</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>El criterio ELEGIBLE exige que dentro de un proceso participativo convocado se use IA (NLP/ML/clustering/sentimiento) SOBRE EL CONTENIDO de los aportes. Aquí ocurre lo contrario: (1) la IA es el TEMA de la consulta (se pregunta a la ciudadania por su percepcion de la IA), y (2) el ANÁLISIS de los ap</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/paraguay/blog/consultas-ciudadanas-sobre-ia-en-paraguay-visiones-diversas-entre-el-campo-y-la-ciudad</t>
+          <t>https://fairlac.iadb.org/en/paraempleo</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>PY</t>
+          <t>UY</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>ParaEmpleo</t>
+          <t>Chatbot (Asistente virtual entrenado con IA)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -7538,12 +7578,12 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/en/paraempleo</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7595,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Chatbot (Asistente virtual entrenado con IA)</t>
+          <t>Consulta Pública de la Estrategia Nacional de Inteligencia Artificial (IA) de Uruguay 2024–2030,</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -7565,12 +7605,12 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No evidencia de uso de IA</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
+          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030</t>
         </is>
       </c>
     </row>
@@ -7582,81 +7622,54 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Consulta Pública de la Estrategia Nacional de Inteligencia Artificial (IA) de Uruguay 2024–2030,</t>
+          <t>Consulta Pública y Participación Multiactores: "Niñas, niños, adolescentes, entornos digitales e inteligencia artificial" (Uruguay, 2026)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Descubrimiento</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA</t>
+          <t>NO (lean firme). (1) TEMPORAL: la consulta está ABIERTA hasta el 10/09/2026 y la fase de sistematización/análisis/validación (Fase 3) recién ocurre entre el 10/09 y el 10/10/2026, con informe final el 30/11/2026. A la fecha de evaluación (2026-07-01) la fase de análisis NO se ha ejecutado, por lo qu</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030</t>
+          <t>https://www.gub.uy/ministerio-educacion-cultura/comunicacion/noticias/lanzamiento-consulta-publica-sobre-inteligencia-artificial-entornos-digitales</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>UY</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Consulta Pública y Participación Multiactores: "Niñas, niños, adolescentes, entornos digitales e inteligencia artificial" (Uruguay, 2026)</t>
+          <t>Plan de la Patria 7 Transformaciones (7T) - IA y Big Data en la sistematización de propuestas de la Consulta Popular</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Dudoso</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>NO (lean firme). (1) TEMPORAL: la consulta está ABIERTA hasta el 10/09/2026 y la fase de sistematización/análisis/validación (Fase 3) recién ocurre entre el 10/09 y el 10/10/2026, con informe final el 30/11/2026. A la fecha de evaluación (2026-07-01) la fase de análisis NO se ha ejecutado, por lo qu</t>
+          <t>NO (resuelto en 2ª pasada, antes DUDA). Hay un proceso participativo claro (consulta/debate nacional para construir el Plan de la Patria 7T, con +63.000 asambleas, 3,4 M de participantes y 34.491 propuestas) cuyo CONTENIDO sí fue recolectado, cargado, sistematizado y agrupado. Pero la 2ª pasada CONF</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.gub.uy/ministerio-educacion-cultura/comunicacion/noticias/lanzamiento-consulta-publica-sobre-inteligencia-artificial-entornos-digitales</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Plan de la Patria 7 Transformaciones (7T) - IA y Big Data en la sistematización de propuestas de la Consulta Popular</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Dudoso</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>NO (resuelto en 2ª pasada, antes DUDA). Hay un proceso participativo claro (consulta/debate nacional para construir el Plan de la Patria 7T, con +63.000 asambleas, 3,4 M de participantes y 34.491 propuestas) cuyo CONTENIDO sí fue recolectado, cargado, sistematizado y agrupado. Pero la 2ª pasada CONF</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
           <t>http://www.correodelorinoco.gob.ve/venezuela-impulsa-el-debate-sobre-inteligencia-artificial-bajo-principios-de-soberania-y-etica/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E74"/>
+  <autoFilter ref="A1:E73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7667,7 +7680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9336,62 +9349,130 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>CU</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Para agilizar la recogida y el procesamiento de los criterios, la Universidad de las Ciencias Informáticas (UCI) y Datys diseñaron dos sistemas informáticos de gestión (XISCOP y GEMA-CEN) [proceso de consulta popular del Código de las Familias en Cuba].</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>consulta popular del proyecto del Código de las Familias (...) la Universidad de las Ciencias Informáticas (UCI) y Datys diseñaron dos sistemas informáticos de gestión (XISCOP y GEMA-CEN)</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>luego se sube a GEMA-CEN (también operado por especialistas) que, a través del análisis inteligente de los expedientes, organiza las propuestas y agrupa las similares, facilitando el trabajo y evitando errores. GEMA-CEN permite determinar las propuestas típicas para un párrafo en cada una de las categorías establecidas</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Más de seis millones 481 mil personas participaron en las reuniones (...) la consulta popular del proyecto del Código de las Familias (...) convocada entre febrero y abril [de 2022]; del total de propuestas procesadas se determinaron 5 237 propuestas típicas por Título</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>del total de propuestas procesadas se determinaron 5 237 propuestas típicas por Título, conformadas a partir de la asociación de propuestas idénticas y de aquellas con redacción diferente pero referidas al mismo criterio u opinión</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>La consulta popular (...) fue organizada y supervisada por el Consejo Electoral Nacional (CEN) [órgano del Estado cubano]; los resultados se entregaron al Parlamento (Asamblea Nacional) y a su Comisión redactora</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>se sube a GEMA-CEN (...) que, a través del análisis inteligente de los expedientes, organiza las propuestas y agrupa las similares (...) permite determinar las propuestas típicas para un párrafo en cada una de las categorías establecidas</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>GEMA es una herramienta para el análisis de información contenida en grandes volúmenes de archivos de diferentes formatos e idiomas, con funcionalidades orientadas a la recuperación y clasificación de información (...) complementando los resultados mediante técnicas modernas de recuperación de información para obtener archivos similares, eliminar resultados no relevantes y agrupar documentos comunes</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>http://www.datys.cu/spa/site/product/15
+https://www.granma.cu/cuba/2022-01-24/herramientas-digitales-seran-claves-durante-la-consulta-popular-del-codigo-de-las-familias-24-01-2022-13-01-18
+https://www.espirituano.gob.cu/noticias/7716-como-sera-el-proceso-de-consulta-popular-del-nuevo-codigo-de-las-familias
+http://www.cubadebate.cu/noticias/2021/12/19/como-sera-el-proceso-de-consulta-popular-del-nuevo-codigo-de-las-familias/
+http://www.cubadebate.cu/noticias/2022/05/14/consulta-popular-del-proyecto-de-codigo-de-las-familias-61-96-por-ciento-de-opiniones-estuvieron-a-favor/
+https://es.wikipedia.org/wiki/C%C3%B3digo_de_las_Familias_de_Cuba
+https://oncubanews.com/cuba/softwares-cubanos-seran-utilizados-en-el-proceso-de-consulta-popular-sobre-el-codigo-de-las-familias/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>EC</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PAGA IA </t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado: integrada al Tercer Plan de Acción de Estado Abierto 2025-2027; analiza las propuestas ciudadanas y sugiere actividades.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Plataforma</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto
 </t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto
 </t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>https://ia.gobiernoabierto.ec/
 https://ia.gobiernoabierto.ec/
@@ -9399,63 +9480,63 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Guatemala Joven Conversa </t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado: diálogos digitales con IA (DPPA ONU + Fundación Esquipulas); 300+ jóvenes; la IA permite intercambios anónimos y votación de aportes para identifi</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
 https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/
@@ -9463,125 +9544,125 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>HN</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RedPública + iVerify </t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Referendos e Iniciativas Populares</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>reconfirmado web (institucional): Reverificación: plataforma de propuestas ciudadanas con módulo de análisis de tendencias; evidencia de IA central débil, revisar en Fase 2.</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
-        </is>
-      </c>
-    </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RedPública + iVerify </t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Referendos e Iniciativas Populares</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>reconfirmado web (institucional): Reverificación: plataforma de propuestas ciudadanas con módulo de análisis de tendencias; evidencia de IA central débil, revisar en Fase 2.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Guanajuato hará historia con el primer Programa de Gobierno realizado con IA</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Para integrar la participación ciudadana en este Programa de Gobierno, se realizaron cuatro talleres cubriendo las regiones noreste, norte, centro y sur, con representación de los 46 municipios de Guanajuato.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>El Programa de Gobierno de Guanajuato 2024-2030 es la guía que orienta las acciones del Gobierno de la Gente para lograr un Guanajuato sostenible, equitativo y transparente.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Su diseño incorporó el uso de inteligencia artificial para integrar más de 26 mil voces de distintas regiones y sectores</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>El Programa de Gobierno 2024-2030 hizo historia al ser el primero en realizarse con ayuda de la Inteligencia Artificial (IA), según anunció la Gobernadora Libia Dennise García Muñoz Ledo en el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG).</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía.</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>https://guanajuatointeligente.com/como-hicimos-el-programa/
 https://guanajuatointeligente.com/
@@ -9594,121 +9675,121 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Presupuesto CRECES</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Presupuestos Participativos</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>BBDD 2025: Activo</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Ayundamiento de Hermosilla</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
-        </is>
-      </c>
-    </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Presupuesto CRECES</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Presupuestos Participativos</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>BBDD 2025: Activo</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Ayundamiento de Hermosilla</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>La Fundación Panamá Participa lanzó Mansa Idea (www.mansaidea.com), una plataforma basada en inteligencia artificial que recoge miles de propuestas ciudadanas... iniciativa de alcance nacional que se nutre de ideas y propuestas que miles de panameños hicieron durante el desarrollo del Pacto del Bicentenario. (Panamá; fuentes panama24horas.com.pa y laestrella.com.pa)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea, resultado del Pacto del Bicentenario, ofrece acceso fácil y transparente a más de 175 mil ideas y propuestas generadas por ciudadanos de todo el país. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales. (la IA agrega/organiza/sintetiza el contenido de las propuestas por tema y territorio = Análisis + Traducción Política; el método técnico exacto no se detalla en las fuentes).</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>La plataforma fue lanzada el 1 de abril de 2024... constituye una herramienta valiosa de participación ciudadana muy relevante para ciudadanos, candidatos a cargos de elección popular y medios durante la campaña electoral y luego como recurso para el monitoreo del mandato ciudadano. (un despliegue concreto de la plataforma, 2024; sin evidencia de ediciones recurrentes).</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>La Fundación Panamá Participa lanzó Mansa Idea... iniciativa liderada por Paulina Franceschi a través de la Fundación Panamá Participa (sociedad civil). El proceso participativo de origen: 'El 26 de noviembre de 2020, el presidente Laurentino Cortizo Cohen lanzó la iniciativa denominada Pacto del Bicentenario Cerrando Brechas' (gobierno nacional / Concertación Nacional).</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. (la IA procesa el contenido de las propuestas del proceso participativo).</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía. (agregación/síntesis de los aportes ciudadanos = rol sobre el contenido).</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>https://www.panama24horas.com.pa/panama/fundacion-panama-participa-lanza-plataforma-de-propuestas-ciudadanas-mansa-idea/
 https://www.laestrella.com.pa/panama/politica/mansa-idea-una-herramienta-digital-con-propuestas-para-candidatos-YD6746221
@@ -9719,63 +9800,63 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (prensa): VERIFICADO (fuente primaria): el CNE usó IBM Watson Discovery + Studio (ML/NLP) sobre 87.991 documentos de aportes ciudadanos de 847 eventos y 49 espacios de di</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Consejo Nacional de Educación del Perú</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional
 https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080
@@ -9784,59 +9865,59 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Project: National Digital Transformation Strategy | Ministry of Digital Transformation, Trinidad and Tobago (engage.gov.tt/projects/national-digital-transformation-strategy). Ruta interna confirmatoria: engage.gov.tt/projects/e-democracy-govocal-internal (la instancia corre sobre Go Vocal). En 2026: 'Projects | Ministry of Public Administration and Artificial Intelligence' (engage.gov.tt/projects).</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>EngageTT es una plataforma en linea (engage.gov.tt) donde ciudadanos, empresas y partes interesadas pueden recibir actualizaciones en tiempo real sobre iniciativas de transformacion digital y ofrecer retroalimentacion via encuestas y sondeos (polls); el Ministro anima a todos a participar y enviar ideas y comentarios sobre el NDTS, que se disena para evolucionar mediante el compromiso y la colaboracion continuos. Incluye un 'Open Forum' (engage.gov.tt/ideas/open-forum) y 'Input: Submitting Proposals' (engage.gov.tt/ideas/submitting-proposals).</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>The National Strategy for a Digital TT is finalized, and while the Ministry of Digital Transformation is no longer seeking input, they welcome feedback or comments through the citizen engagement digital platform Engage TT. (engage.gov.tt sigue operativo en 2026 bajo MPAAI).</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>The Ministry of Digital Transformation (MDT) officially presented the National Digital Transformation Strategy (NDTS) 2024-2027... launched during a NDTS Symposium in collaboration with the Inter-American Development Bank (IDB) on Wednesday, February 12th 2025. A major highlight... was the introduction of two new digital tools (EngageTT y AskNDTS). (Lanzamiento/anuncio unico en feb-2025; plataforma de uso continuo pero sin &gt;=2 ediciones de proceso participativo documentadas).</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>The Ministry of Digital Transformation (MDT) officially presented the National Digital Transformation Strategy (NDTS) 2024-2027... and introduced the EngageTT website - an online platform where citizens, businesses, and stakeholders can get real-time updates on digital transformation initiatives, and offer feedback via surveys and polls. (Convocante: gobierno nacional / Ministry of Digital Transformation, hoy MPAAI).</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Go Vocal Support Base (AI Analysis): 'Access to this feature depends on your plan. Advanced Sensemaking with auto-insights is available in the Premium plan.' -&gt; la IA/NLP de Go Vocal NO es automatica, depende del plan; y para EngageTT solo se documenta 'feedback via surveys and polls'/Open Forum/ideas, SIN mencion de analisis automatico por IA de los aportes. No se halla evidencia de activacion del NLP sobre el contenido en la instancia TT. 3a PASADA (refuerzo): Oxford Insights, 'The country's AI utilisation for citizens is concentrated in a robust Chatbot programme' (mas 'deployment of large language models for internal development purposes') -&gt; la IA ciudadana de TT es el chatbot, NO el analisis de aportes.</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Sin evidencia de IA aplicada al contenido de los aportes en engage.gov.tt. La unica IA confirmada de cara al ciudadano (AskNDTS/ANANSI) es chatbot de FAQ, excluido del criterio. En 3a pasada, el material de MPAAI 2026 enmarca la IA en el asistente ANANSI y en encuestas de AI-readiness (resultados 'consolidated and reviewed' en talleres), sin mencion de analisis por IA de los aportes del NDTS ni de Go Vocal Sensemaking.</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>https://support.govocal.com/en/articles/8316692-ai-analysis
 https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool
@@ -9858,59 +9939,59 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>UY</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Polis has been used to facilitate discussion and build consensus ... in Uruguay on a national referendum (OCDE 2025, 'Governing with AI')</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists — ran Polis alongside the referendum</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>The algorithm maps participants' responses and clusters opinions, facilitating the identification of positions that are supported by the majority of participants (OCDE 2025)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>16,499 people cast more than 295,000 votes ... The referendum was lost by less than 1%</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="H36" s="11" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>ran Polis alongside the referendum to look for something deeper than "yes or no"</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>Polis revealed that even where public safety divided people, surprising points of consensus broke through on other issues — bridges between groups</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/
 https://www.oecd.org/en/publications/governing-with-artificial-intelligence_795de142-en.html</t>
@@ -9918,7 +9999,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L35"/>
+  <autoFilter ref="A1:L36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9952,7 +10033,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>Planilla con 6 pestañas (criterio corregido). 34 casos entran/dudosos · 73 excluidos · 107 en total. Tras dedup e-Cidadania: 33 iniciativas.</t>
+          <t>Planilla con 6 pestañas (criterio corregido). 35 casos entran/dudosos · 72 excluidos · 107 en total. Tras dedup e-Cidadania: 34 iniciativas.</t>
         </is>
       </c>
     </row>

--- a/data/gates/planilla_ILIA2026_SIMPLE.xlsx
+++ b/data/gates/planilla_ILIA2026_SIMPLE.xlsx
@@ -800,7 +800,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -924,7 +924,11 @@
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Voz a Texto; NLP</t>
+        </is>
+      </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
@@ -1383,7 +1387,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -1938,7 +1942,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>otra institución pública</t>
+          <t>gobierno nacional</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1978,7 +1982,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>Biblioteca del Congreso Nacional</t>
+          <t>Gobierno de Chile (Presidencia/SEGPRES) — convocante del Proceso Constituyente Abierto; la Biblioteca del Congreso Nacional sistematiza y archiva los resultados (convenio con Senado, Cámara y SEGPRES).</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -2309,7 +2313,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2777,7 +2781,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -3093,7 +3097,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Referendos e Iniciativas Populares; Presupuestos Participativos</t>
+          <t>Presupuestos Participativos; Participación Digital</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -3146,8 +3150,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atención automatizada mediante procesamiento de lenguaje natural, análisis de datos y algoritmos de inteligencia artificial para responder consultas ciudadanas sobre más de 400 temas de interés.
-</t>
+          <t>Agente virtual de Bogotá (Secretaría General) con módulos de PARTICIPACIÓN además de atención: votación de Causas Ciudadanas y de los Presupuestos Participativos (240.000+ votos desde 2022) y recepción de más de 147.000 aportes ciudadanos para la construcción del Plan Distrital de Desarrollo 'Bogotá Camina Segura' 2024-2027. Renovado con IA generativa (2026); atiende por WhatsApp/Telegram/webchat.</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -3589,7 +3592,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3907,7 +3910,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Implementación; Análisis</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
@@ -3935,7 +3938,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4605,7 +4608,11 @@
           <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="n">
         <v>1</v>
       </c>
@@ -4626,7 +4633,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>no-claro</t>
+          <t>apoyo</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4641,7 +4648,7 @@
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>NLP; Resumen automatico; Clasificacion/agrupacion de texto (capacidad de la plataforma sujeta a plan Premium; activacion NO confirmada en TT)</t>
+          <t>Chatbot - Inespecífico</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
@@ -4747,7 +4754,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil; Academia</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">

--- a/data/gates/planilla_ILIA2026_SIMPLE.xlsx
+++ b/data/gates/planilla_ILIA2026_SIMPLE.xlsx
@@ -15,10 +15,10 @@
     <sheet name="6 · Metodología (CENIA v2)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos (entran+dudosos)'!$A$1:$X$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2 · A validar a mano'!$A$1:$G$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 · Excluidos'!$A$1:$E$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 · Evidencia y fuentes'!$A$1:$L$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos (entran+dudosos)'!$A$1:$X$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2 · A validar a mano'!$A$1:$G$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 · Excluidos'!$A$1:$E$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 · Evidencia y fuentes'!$A$1:$L$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -582,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X36"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Cátedra Brasil / Co:Lab USP - IA generativa en presupuesto participativo (SP)</t>
+          <t>OPA Piauí - Orçamento Participativo Digital (Colab + AWS)</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1242,16 +1242,16 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>universidad</t>
+          <t>gobierno local</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>contenido</t>
+          <t>apoyo</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1274,44 +1274,40 @@
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>LLM / IA generativa (NLP)</t>
-        </is>
-      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no-claro</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>Investigación académica (Co:Lab USP / Cátedra Brasil-Alemania, GETIP) sobre el uso de IA generativa para apoyar a la ciudadanía a redactar y estructurar propuestas en procesos de participación, tomando como referencia el orçamento participativo de São Paulo. Descrito como 'pesquisas em andamento' / proyecto de investigación-prototipo, no como una herramienta oficial desplegada en el proceso real (que opera vía la plataforma Participe+/Participe Mais de la Prefeitura, sin IA generativa confirmada).</t>
+          <t>OPA (Orçamento Participativo Digital) es el presupuesto participativo 100% digital del Gobierno del Estado de Piauí (Brasil), creado en 2023 y coordinado por la Secretaria do Planejamento (SEPLAN) con apoyo de la Secretaria de Relações Sociais (Seres). Se ejecuta sobre la plataforma Colab Gov (de la govtech Colab) con infraestructura AWS. El ciclo incluye cadastramento de propuestas por entidades comunitarias/asociaciones, una fase de 'análise técnica' (verificación de documentación, viabilidad de ejecución, claridad de la descripción, adecuación al área temática y no duplicación) y una votación popular abierta a la ciudadanía. En la edición 2026-2027, según el material de Colab, 'a análise ganhou agilidade com o uso de inteligência artificial, que reduziu em 40% o tempo de processamento das propostas', con economía de R$ 1,75 millón y 99,98% de disponibilidad del sistema. La señal disponible vincula la IA al procesamiento/agilización del flujo, a la seguridad de la infraestructura (filtrado de conexiones inseguras vía AWS CloudFront), a un chatbot/capacitación (CapacitIA) y a un 'Observatório do OPA' de transparencia; la 'análise técnica' de viabilidad se describe de forma reiterada como tarea conducida por equipos técnicos a través de la plataforma. NO hay evidencia de que la IA clasifique, agrupe (clustering) o sintetice el CONTENIDO temático/semántico de las propuestas en el OPA.</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>Co:Lab / Colaboratório de Desenvolvimento e Participação (EACH-USP) y GETIP - Grupo de Estudos em Tecnologia e Inovação na Gestão Pública; investigador José Carlos Vaz (titular da Cátedra CAPES Brasil-Alemanha na Universidade de Münster); coautora Fernanda Campagnucci.</t>
+          <t>Governo do Estado do Piauí - Secretaria do Planejamento (SEPLAN), con apoyo de la Secretaria de Relações Sociais (Seres). Socio tecnológico: GovTech Colab (plataforma Colab Gov); infraestructura: AWS (Amazon Web Services).</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="V6" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>https://participemais.prefeitura.sp.gov.br/budgets
-https://colab.each.usp.br/blog/2025/03/28/a-ia-generativa-e-o-futuro-da-participacao-cidada-pesquisas-em-andamento/
-https://scope.uni-muenster.de/wp-content/uploads/2025/01/PT-BR-Policy-Brief-AI_Jan2025.pdf</t>
+          <t>https://sia.pi.gov.br/projetos/opa/
+https://tiinside.com.br/21/10/2025/em-parceria-com-a-aws-colab-lanca-ia-que-constroi-fluxos-de-governo-em-segundos/
+https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>BR-catedra-brasil-co-lab-usp-ia-generativa</t>
+          <t>BR-opa-piaui-presupuesto-participativo-digi</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1320,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>OPA Piauí - Orçamento Participativo Digital (Colab + AWS)</t>
+          <t>Plan Plurianual de la ciudad de Natal</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1332,9 +1328,9 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1344,21 +1340,21 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Presupuestos Participativos; Participación Digital</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Implementación; Análisis</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1377,53 +1373,55 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>apoyo</t>
+          <t>contenido</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Gobierno; Privado</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr"/>
+          <t>Nacional, Internacional</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>LLM; NLP</t>
+        </is>
+      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>no-claro</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>OPA (Orçamento Participativo Digital) es el presupuesto participativo 100% digital del Gobierno del Estado de Piauí (Brasil), creado en 2023 y coordinado por la Secretaria do Planejamento (SEPLAN) con apoyo de la Secretaria de Relações Sociais (Seres). Se ejecuta sobre la plataforma Colab Gov (de la govtech Colab) con infraestructura AWS. El ciclo incluye cadastramento de propuestas por entidades comunitarias/asociaciones, una fase de 'análise técnica' (verificación de documentación, viabilidad de ejecución, claridad de la descripción, adecuación al área temática y no duplicación) y una votación popular abierta a la ciudadanía. En la edición 2026-2027, según el material de Colab, 'a análise ganhou agilidade com o uso de inteligência artificial, que reduziu em 40% o tempo de processamento das propostas', con economía de R$ 1,75 millón y 99,98% de disponibilidad del sistema. La señal disponible vincula la IA al procesamiento/agilización del flujo, a la seguridad de la infraestructura (filtrado de conexiones inseguras vía AWS CloudFront), a un chatbot/capacitación (CapacitIA) y a un 'Observatório do OPA' de transparencia; la 'análise técnica' de viabilidad se describe de forma reiterada como tarea conducida por equipos técnicos a través de la plataforma. NO hay evidencia de que la IA clasifique, agrupe (clustering) o sintetice el CONTENIDO temático/semántico de las propuestas en el OPA.</t>
+          <t>Recolección de información a través de tres preguntas habilitadas por WhatsApp para diseñar el Plan Plurianual de la ciudad 2026-2029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>Governo do Estado do Piauí - Secretaria do Planejamento (SEPLAN), con apoyo de la Secretaria de Relações Sociais (Seres). Socio tecnológico: GovTech Colab (plataforma Colab Gov); infraestructura: AWS (Amazon Web Services).</t>
+          <t>Prefeitura Municipal de Natal, a través de la Secretaría Municipal de Planeamiento (SEMPLA)</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V7" s="5" t="n">
-        <v>7</v>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>https://sia.pi.gov.br/projetos/opa/
-https://tiinside.com.br/21/10/2025/em-parceria-com-a-aws-colab-lanca-ia-que-constroi-fluxos-de-governo-em-segundos/
-https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/</t>
+          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>BR-opa-piaui-presupuesto-participativo-digi</t>
+          <t>BR-plan-plurianual-de-la-ciudad-de-natal</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1434,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Plan Plurianual de la ciudad de Natal</t>
+          <t>Portal e-Cidadania: Marcado automático de respuestas ciudadanas en videos de audiencias públicas</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1466,7 +1464,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Traducción Política</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
@@ -1479,7 +1477,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>gobierno local</t>
+          <t>gobierno nacional</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1494,17 +1492,17 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Gobierno; Privado</t>
+          <t>Gobierno</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Nacional, Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>LLM; NLP</t>
+          <t>Voz a Texto; LLM; NLP</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -1514,12 +1512,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>Recolección de información a través de tres preguntas habilitadas por WhatsApp para diseñar el Plan Plurianual de la ciudad 2026-2029</t>
+          <t>Implementación de IA para identificar y marcar en los videos de eventos las respuestas dadas a preguntas ciudadanas, incluso cuando estas no fueron respondidas directamente durante las audiencias.</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>Prefeitura Municipal de Natal, a través de la Secretaría Municipal de Planeamiento (SEMPLA)</t>
+          <t>Senado Federal de Brasil</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1527,17 +1525,17 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="V8" s="4" t="n">
-        <v>0</v>
+      <c r="V8" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
+          <t>https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>BR-plan-plurianual-de-la-ciudad-de-natal</t>
+          <t>BR-portal-e-cidadania-marcado-automatico-de</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1548,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Portal e-Cidadania: Marcado automático de respuestas ciudadanas en videos de audiencias públicas</t>
+          <t>São Paulo - Programa de Metas / Participe Mais (Gemini)</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1558,9 +1556,9 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1570,17 +1568,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+          <t>MEDIA-ALTA</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Traducción Política</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
@@ -1588,12 +1586,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional</t>
+          <t>gobierno local</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1608,7 +1606,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Sociedad Civil; Gobierno</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1618,7 +1616,7 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Voz a Texto; LLM; NLP</t>
+          <t>LLM generativa; NLP; Clasificación de texto</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -1628,12 +1626,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>Implementación de IA para identificar y marcar en los videos de eventos las respuestas dadas a preguntas ciudadanas, incluso cuando estas no fueron respondidas directamente durante las audiencias.</t>
+          <t>Consulta pública del Programa de Metas 2025-2028 / Plano Plurianual (PPA) 2026-2029 / Planos de Ação das Subprefeituras (PAS) 2026-2029 de la Prefeitura de São Paulo, realizada en el portal Participe Mais (Participe+), plataforma de participación social de la Prefeitura construida sobre el software libre Decidim (basado en CONSUL/Decidim de Madrid-Barcelona). La consulta estuvo abierta del 7/04/2025 al 11/05/2025; el ciclo participativo incluyó 36 audiencias públicas híbridas en la ciudad (abril-mayo 2025) y recibió 6.368 propostas y más de 31.000 interacciones ciudadanas (sugerencias, apoyos, propuestas y críticas). Sobre ese material, en mayo de 2025 Carolina Borges -Agente de Governo Aberto de la Prefeitura- desarrolló una herramienta (Python + Pandas + Google Gemini) que clasifica las propostas en categorías, las ordena por asunto y cantidad de apoyos y genera relatórios y painéis visuales (ranking de temas más recurrentes y participación por distrito y subprefeitura), 'facilitando a divulgação das propostas à população'. La herramienta y su metodología se presentaron en la oficina 'Análise de Dados com Inteligência Artificial na Gestão Pública: Programa de Metas' de la Escola do Parlamento de la Câmara Municipal de São Paulo (15/12/2025), realizada en parceria con el Programa Agentes de Governo Aberto da Prefeitura.</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>Senado Federal de Brasil</t>
+          <t>Proceso participativo (Programa de Metas / PPA / PAS): Prefeitura de São Paulo (Secretaria Municipal de Planejamento / Casa Civil / Coordenadoria de Governo Aberto, portal Participe Mais). Herramienta de IA: desarrollada por Carolina Borges, Agente de Governo Aberto de São Paulo (formación en Ciência da Computação y posgrado en Gestão e Controle Social de Políticas Públicas por la Escola de Contas do TCM-SP; experiencia profesional, académica y voluntaria), presentada en la oficina de la Escola do Parlamento da Câmara Municipal de São Paulo en parceria con el Programa Agentes de Governo Aberto. No se confirmó que la Prefeitura adoptara esta herramienta como su pipeline oficial de análisis del proceso.</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1642,21 +1640,26 @@
         </is>
       </c>
       <c r="V9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias</t>
+          <t>https://gestaourbana.prefeitura.sp.gov.br/wp-content/uploads/2025/10/Relatorio_Oficinas_Participativas.pdf
+https://gestaourbana.prefeitura.sp.gov.br/planos-de-acao-das-subprefeituras/</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>BR-portal-e-cidadania-marcado-automatico-de</t>
+          <t>BR-sao-paulo-programa-de-metas-participe-ma</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>➜ NO contar (duplicado)</t>
+        </is>
+      </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>BR</t>
@@ -1664,7 +1667,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>São Paulo - Programa de Metas / Participe Mais (Gemini)</t>
+          <t>e-Cidadania Senado - IA matching de ideas legislativas</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1672,29 +1675,29 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>NO (duplicado)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>MEDIA-ALTA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
+          <t>Participación Digital; Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Análisis; Traducción Política</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
@@ -1702,12 +1705,12 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>gobierno local</t>
+          <t>gobierno nacional</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1722,7 +1725,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil; Gobierno</t>
+          <t>Gobierno</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,22 +1735,22 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>LLM generativa; NLP; Clasificación de texto</t>
+          <t>NLP; Búsqueda semántica</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no-claro</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>Consulta pública del Programa de Metas 2025-2028 / Plano Plurianual (PPA) 2026-2029 / Planos de Ação das Subprefeituras (PAS) 2026-2029 de la Prefeitura de São Paulo, realizada en el portal Participe Mais (Participe+), plataforma de participación social de la Prefeitura construida sobre el software libre Decidim (basado en CONSUL/Decidim de Madrid-Barcelona). La consulta estuvo abierta del 7/04/2025 al 11/05/2025; el ciclo participativo incluyó 36 audiencias públicas híbridas en la ciudad (abril-mayo 2025) y recibió 6.368 propostas y más de 31.000 interacciones ciudadanas (sugerencias, apoyos, propuestas y críticas). Sobre ese material, en mayo de 2025 Carolina Borges -Agente de Governo Aberto de la Prefeitura- desarrolló una herramienta (Python + Pandas + Google Gemini) que clasifica las propostas en categorías, las ordena por asunto y cantidad de apoyos y genera relatórios y painéis visuales (ranking de temas más recurrentes y participación por distrito y subprefeitura), 'facilitando a divulgação das propostas à população'. La herramienta y su metodología se presentaron en la oficina 'Análise de Dados com Inteligência Artificial na Gestão Pública: Programa de Metas' de la Escola do Parlamento de la Câmara Municipal de São Paulo (15/12/2025), realizada en parceria con el Programa Agentes de Governo Aberto da Prefeitura.</t>
+          <t>Portal e-Cidadania del Senado Federal de Brasil, módulo 'Ideia Legislativa', donde la población envía sugerencias para crear o mejorar leyes. Tradicionalmente una idea debía reunir 20.000 apoyos en 4 meses para ser formalizada como Sugestão Legislativa y analizada por la Comissão de Direitos Humanos e Legislação Participativa (CDH). A fines de 2025 / enero 2026 el Senado desplegó una herramienta de inteligencia artificial (búsqueda semántica) sobre el banco de ideias legislativas (145.993 ideias a enero 2026) que, a pedido de la Consultoria Legislativa cuando un senador prepara un proyecto, busca y selecciona las ideas ciudadanas temáticamente compatibles para incorporarlas y citarlas en la justificación del proyecto de ley, sin exigir el mínimo de apoyos.</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>Proceso participativo (Programa de Metas / PPA / PAS): Prefeitura de São Paulo (Secretaria Municipal de Planejamento / Casa Civil / Coordenadoria de Governo Aberto, portal Participe Mais). Herramienta de IA: desarrollada por Carolina Borges, Agente de Governo Aberto de São Paulo (formación en Ciência da Computação y posgrado en Gestão e Controle Social de Políticas Públicas por la Escola de Contas do TCM-SP; experiencia profesional, académica y voluntaria), presentada en la oficina de la Escola do Parlamento da Câmara Municipal de São Paulo en parceria con el Programa Agentes de Governo Aberto. No se confirmó que la Prefeitura adoptara esta herramienta como su pipeline oficial de análisis del proceso.</t>
+          <t>Senado Federal do Brasil - Consultoria Legislativa en conjunto con el Programa e-Cidadania (Secretaria de Transparência / Coordenação do e-Cidadania). Herramienta desarrollada por el servidor Alisson Bruno (coordenador do e-Cidadania) en el marco del Desafio de Inovação do Senado.</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1756,137 +1759,134 @@
         </is>
       </c>
       <c r="V10" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>https://gestaourbana.prefeitura.sp.gov.br/wp-content/uploads/2025/10/Relatorio_Oficinas_Participativas.pdf
-https://gestaourbana.prefeitura.sp.gov.br/planos-de-acao-das-subprefeituras/</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="inlineStr">
-        <is>
-          <t>BR-sao-paulo-programa-de-metas-participe-ma</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>➜ NO contar (duplicado)</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>e-Cidadania Senado - IA matching de ideas legislativas</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>NO (duplicado)</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Participación Digital; Referendos e Iniciativas Populares</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Análisis; Traducción Política</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>gobierno nacional</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>NLP; Búsqueda semántica</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>no-claro</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>Portal e-Cidadania del Senado Federal de Brasil, módulo 'Ideia Legislativa', donde la población envía sugerencias para crear o mejorar leyes. Tradicionalmente una idea debía reunir 20.000 apoyos en 4 meses para ser formalizada como Sugestão Legislativa y analizada por la Comissão de Direitos Humanos e Legislação Participativa (CDH). A fines de 2025 / enero 2026 el Senado desplegó una herramienta de inteligencia artificial (búsqueda semántica) sobre el banco de ideias legislativas (145.993 ideias a enero 2026) que, a pedido de la Consultoria Legislativa cuando un senador prepara un proyecto, busca y selecciona las ideas ciudadanas temáticamente compatibles para incorporarlas y citarlas en la justificación del proyecto de ley, sin exigir el mínimo de apoyos.</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>Senado Federal do Brasil - Consultoria Legislativa en conjunto con el Programa e-Cidadania (Secretaria de Transparência / Coordenação do e-Cidadania). Herramienta desarrollada por el servidor Alisson Bruno (coordenador do e-Cidadania) en el marco del Desafio de Inovação do Senado.</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="V11" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial
 https://www12.senado.leg.br/radio/1/noticia/2026/01/15/ia-vai-aproximar-ideias-legislativas-do-e-cidadania-e-projetos-de-senadores
 https://www.poder360.com.br/poder-congresso/ia-do-senado-usa-sugestoes-enviadas-por-cidadaos-em-projetos-de-lei/</t>
         </is>
       </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>BR-e-cidadania-senado-ia-matching-de-ideas</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Cabildos 2016</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>gobierno nacional</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>NLP - Tópicos</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>Análisis de los cabildos del proceso constitucional en 2016</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno de Chile (Presidencia/SEGPRES) — convocante del Proceso Constituyente Abierto; la Biblioteca del Congreso Nacional sistematiza y archiva los resultados (convenio con Senado, Cámara y SEGPRES).</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bcn.cl/procesoconstituyente/cabildos2016/
+https://aclanthology.org/W17-5101/
+https://journals.plos.org/plosone/article?id=10.1371%2Fjournal.pone.0267443</t>
+        </is>
+      </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>BR-e-cidadania-senado-ia-matching-de-ideas</t>
+          <t>CL-cabildos-2016</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Cabildos 2016</t>
+          <t>El Chile que Queremos (ECQQ) - MinCiencia</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>Gobierno</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos</t>
+          <t>NLP; Clasificación de texto; Modelado de tópicos (LDA); Redes neuronales recurrentes (RNN); Random Forest; Clasificación de emociones; Machine Learning</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
@@ -1977,157 +1977,156 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>Análisis de los cabildos del proceso constitucional en 2016</t>
+          <t>Iniciativa gubernamental de diálogos ciudadanos y escucha social presentada por el Gobierno de Chile el 22 de noviembre de 2019, en el marco del Acuerdo por la Justicia Social y el Acuerdo por una Nueva Constitución tras el estallido social. Entre noviembre de 2019 y marzo de 2020, la ciudadanía pudo participar mediante diálogos grupales (cabildos) o consultas individuales en el sitio www.chilequequeremos.cl, registrando sus necesidades y propuestas para complementar futuras políticas públicas. El proceso fue un esfuerzo conjunto de los Ministerios de Desarrollo Social y Familia, de Ciencia/Tecnología/Conocimiento e Innovación (MinCiencia), de Agricultura, la SEGEGOB y la División de Gobierno Digital. El Ministerio de Ciencia fue responsable de SISTEMATIZAR los aportes ciudadanos usando ciencia de datos / IA: el repositorio público MinCiencia/ECQQ contiene el código que clasifica las contribuciones (texto libre de los aportes) mediante redes neuronales recurrentes (RNN) y árboles de decisión (Random Forest), y sistematiza emociones y necesidades mediante análisis de tópicos (NLP/LDA) sobre el contenido de diálogos y consultas individuales.</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>Gobierno de Chile (Presidencia/SEGPRES) — convocante del Proceso Constituyente Abierto; la Biblioteca del Congreso Nacional sistematiza y archiva los resultados (convenio con Senado, Cámara y SEGPRES).</t>
+          <t>Gobierno de Chile - proceso conjunto liderado por el Ministerio de Desarrollo Social y Familia; sistematización de los aportes con ciencia de datos/IA a cargo del Ministerio de Ciencia, Tecnología, Conocimiento e Innovación (MinCiencia). Participaron también Ministerio de Agricultura, SEGEGOB y División de Gobierno Digital.</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>0</v>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="V12" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bcn.cl/procesoconstituyente/cabildos2016/
-https://aclanthology.org/W17-5101/
-https://journals.plos.org/plosone/article?id=10.1371%2Fjournal.pone.0267443</t>
-        </is>
-      </c>
-      <c r="X12" s="2" t="inlineStr">
-        <is>
-          <t>CL-cabildos-2016</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>El Chile que Queremos (ECQQ) - MinCiencia</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>gobierno nacional</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>NLP; Clasificación de texto; Modelado de tópicos (LDA); Redes neuronales recurrentes (RNN); Random Forest; Clasificación de emociones; Machine Learning</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>Iniciativa gubernamental de diálogos ciudadanos y escucha social presentada por el Gobierno de Chile el 22 de noviembre de 2019, en el marco del Acuerdo por la Justicia Social y el Acuerdo por una Nueva Constitución tras el estallido social. Entre noviembre de 2019 y marzo de 2020, la ciudadanía pudo participar mediante diálogos grupales (cabildos) o consultas individuales en el sitio www.chilequequeremos.cl, registrando sus necesidades y propuestas para complementar futuras políticas públicas. El proceso fue un esfuerzo conjunto de los Ministerios de Desarrollo Social y Familia, de Ciencia/Tecnología/Conocimiento e Innovación (MinCiencia), de Agricultura, la SEGEGOB y la División de Gobierno Digital. El Ministerio de Ciencia fue responsable de SISTEMATIZAR los aportes ciudadanos usando ciencia de datos / IA: el repositorio público MinCiencia/ECQQ contiene el código que clasifica las contribuciones (texto libre de los aportes) mediante redes neuronales recurrentes (RNN) y árboles de decisión (Random Forest), y sistematiza emociones y necesidades mediante análisis de tópicos (NLP/LDA) sobre el contenido de diálogos y consultas individuales.</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno de Chile - proceso conjunto liderado por el Ministerio de Desarrollo Social y Familia; sistematización de los aportes con ciencia de datos/IA a cargo del Ministerio de Ciencia, Tecnología, Conocimiento e Innovación (MinCiencia). Participaron también Ministerio de Agricultura, SEGEGOB y División de Gobierno Digital.</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="V13" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>https://github.com/MinCiencia/ECQQ/activity
 https://www.chilequequeremos.cl
 https://minciencia.gob.cl/noticias/</t>
         </is>
       </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>CL-el-chile-que-queremos-ecqq-minciencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>gobierno nacional</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>NLP - Tópicos</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>Uso de IA para analizar datos cualitativos en consulta ciudadana.</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>Secretaría de Gobierno Digital</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030
+https://participacion.digital.gob.cl/folders/consultas-ciudadanas</t>
+        </is>
+      </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>CL-el-chile-que-queremos-ecqq-minciencia</t>
+          <t>CL-estrategia-de-gobierno-digital-informe-p</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>CL</t>
@@ -2135,7 +2134,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
+          <t>Estudio dIAlogos - Percepciones de Futuro</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2165,7 +2164,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación; Análisis</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
@@ -2178,12 +2177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional</t>
+          <t>sociedad civil; empresa</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2203,7 +2202,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos</t>
+          <t>NLP</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
@@ -2213,17 +2212,17 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>Uso de IA para analizar datos cualitativos en consulta ciudadana.</t>
+          <t>Estudio que utilizó distintas herramientas de IA para conocer las percepciones de futuro de la población chilena</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>Secretaría de Gobierno Digital</t>
+          <t>Fundación Encuentros del Futuro y Merlín Research</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="V14" s="4" t="n">
@@ -2231,18 +2230,22 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030
-https://participacion.digital.gob.cl/folders/consultas-ciudadanas</t>
+          <t>https://estudiodialogos.cl/
+https://fairlac.iadb.org/en/dialogos-study-perceptions-future</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>CL-estrategia-de-gobierno-digital-informe-p</t>
+          <t>CL-estudio-dialogos-percepciones-de-futuro</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
+        </is>
+      </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>CL</t>
@@ -2250,7 +2253,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Estudio dIAlogos - Percepciones de Futuro</t>
+          <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -2280,7 +2283,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
@@ -2293,12 +2296,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>sociedad civil; empresa</t>
+          <t>universidad</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2318,7 +2321,7 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>NLP</t>
+          <t>NLP - Tópicos</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -2328,17 +2331,17 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>Estudio que utilizó distintas herramientas de IA para conocer las percepciones de futuro de la población chilena</t>
+          <t xml:space="preserve">Jornadas de diálogo de la comunidad académica y otos stakeholders. </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>Fundación Encuentros del Futuro y Merlín Research</t>
+          <t>Universidad Andres Bello</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="V15" s="4" t="n">
@@ -2346,13 +2349,13 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>https://estudiodialogos.cl/
-https://fairlac.iadb.org/en/dialogos-study-perceptions-future</t>
+          <t>https://ipp.unab.cl/
+https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>CL-estudio-dialogos-percepciones-de-futuro</t>
+          <t>CL-jornada-de-escucha-lanzamiento-instituto</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2372,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
+          <t>LXS 400 - Chile Delibera</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2377,9 +2380,9 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2389,17 +2392,17 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Mini públicos</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación; Planificación</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
@@ -2412,32 +2415,32 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>universidad</t>
+          <t>gobierno nacional; universidad; sociedad civil</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>contenido</t>
+          <t>apoyo</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos</t>
+          <t>Moderación/facilitación automatizada; Sistema de reglas/temporización; Muestreo estadístico asistido por IA</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
@@ -2447,160 +2450,156 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jornadas de diálogo de la comunidad académica y otos stakeholders. </t>
+          <t>Encuesta deliberativa nacional (Deliberative Poll, modelo de James S. Fishkin) convocada por el Senado de Chile (Comisión Desafíos del Futuro) junto a la Fundación Tribu, el Centro para la Democracia Deliberativa de la Universidad de Stanford, la Universidad de Chile, la Asociación Chilena de Municipalidades (AChM) y el Servicio de Registro Civil. Un mini-público de ~400-514 ciudadanos seleccionados aleatoriamente y representativos del país deliberó de forma online (vía Zoom y la Stanford Online Deliberation Platform) los días 5, 6 y 7 de marzo de 2021 sobre reformas a pensiones y salud, en grupos pequeños y sesiones plenarias, de cara al debate constitucional. El proceso comenzó en diciembre de 2020 con la selección de la muestra y la entrega de material informativo equilibrado (argumentos a favor y en contra). La plataforma online de Stanford incorporó un moderador automatizado (IA) que controlaba los tiempos y distribuía equitativamente los turnos de palabra (colas de habla, temporizador, sistema de señal para determinar quién hablaba a continuación); en paralelo, el Centro de Microdatos de la U. de Chile usó tecnología basada en IA para seleccionar la muestra representativa.</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>Universidad Andres Bello</t>
+          <t>Senado de Chile (Comisión Desafíos del Futuro, Ciencia, Tecnología e Innovación) y Fundación Tribu, con la Universidad de Stanford (Center for Deliberative Democracy / Deliberative Democracy Lab), la Universidad de Chile (Centro de Microdatos), la Asociación Chilena de Municipalidades (AChM) y el Servicio de Registro Civil e Identificación.</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>0</v>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="V16" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>https://ipp.unab.cl/
-https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
-        </is>
-      </c>
-      <c r="X16" s="2" t="inlineStr">
-        <is>
-          <t>CL-jornada-de-escucha-lanzamiento-instituto</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>LXS 400 - Chile Delibera</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Mini públicos</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Implementación; Planificación</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>gobierno nacional; universidad; sociedad civil</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>Mixto</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>apoyo</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>Academia</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>Moderación/facilitación automatizada; Sistema de reglas/temporización; Muestreo estadístico asistido por IA</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>Encuesta deliberativa nacional (Deliberative Poll, modelo de James S. Fishkin) convocada por el Senado de Chile (Comisión Desafíos del Futuro) junto a la Fundación Tribu, el Centro para la Democracia Deliberativa de la Universidad de Stanford, la Universidad de Chile, la Asociación Chilena de Municipalidades (AChM) y el Servicio de Registro Civil. Un mini-público de ~400-514 ciudadanos seleccionados aleatoriamente y representativos del país deliberó de forma online (vía Zoom y la Stanford Online Deliberation Platform) los días 5, 6 y 7 de marzo de 2021 sobre reformas a pensiones y salud, en grupos pequeños y sesiones plenarias, de cara al debate constitucional. El proceso comenzó en diciembre de 2020 con la selección de la muestra y la entrega de material informativo equilibrado (argumentos a favor y en contra). La plataforma online de Stanford incorporó un moderador automatizado (IA) que controlaba los tiempos y distribuía equitativamente los turnos de palabra (colas de habla, temporizador, sistema de señal para determinar quién hablaba a continuación); en paralelo, el Centro de Microdatos de la U. de Chile usó tecnología basada en IA para seleccionar la muestra representativa.</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>Senado de Chile (Comisión Desafíos del Futuro, Ciencia, Tecnología e Innovación) y Fundación Tribu, con la Universidad de Stanford (Center for Deliberative Democracy / Deliberative Democracy Lab), la Universidad de Chile (Centro de Microdatos), la Asociación Chilena de Municipalidades (AChM) y el Servicio de Registro Civil e Identificación.</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="V17" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
         <is>
           <t>https://es.wikipedia.org/wiki/Lxs_400:_Chile_Delibera
 https://www.lxs400.cl/noticias/
 https://www.senado.cl/comunicaciones/noticias/chile-delibera-lxs-400-un-fin-de-semana-de-democracia-deliberativa-online</t>
         </is>
       </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>CL-lxs-400-chile-delibera</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>La voz de los nuevos votantes</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Implementación; Análisis</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>universidad</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>NLP - Tópicos</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>Análisis de Lenguaje Natural para los audios transcritos de encuesta realizada en persona.</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>Universidad Andres Bello</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf
+https://ipp.unab.cl/publicacion/la-voz-de-los-nuevos-votantes-san-bernardo/</t>
+        </is>
+      </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>CL-lxs-400-chile-delibera</t>
+          <t>CL-la-voz-de-los-nuevos-votantes</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>CL</t>
@@ -2608,7 +2607,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>La voz de los nuevos votantes</t>
+          <t>Participación Ciudadana Proceso Constitucional</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2638,7 +2637,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
@@ -2651,12 +2650,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>universidad</t>
+          <t>gobierno nacional</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2666,7 +2665,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2686,12 +2685,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>Análisis de Lenguaje Natural para los audios transcritos de encuesta realizada en persona.</t>
+          <t>Análisis de los resultados obtenidos de los Diálogos Ciudadanos Autoconvocados dentro del proceso constitucional</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>Universidad Andres Bello</t>
+          <t>Secretaría de Participación Ciudadana</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2704,13 +2703,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf
-https://ipp.unab.cl/publicacion/la-voz-de-los-nuevos-votantes-san-bernardo/</t>
+          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>CL-la-voz-de-los-nuevos-votantes</t>
+          <t>CL-participacion-ciudadana-proceso-constitu</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2721,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Participación Ciudadana Proceso Constitucional</t>
+          <t>Tenemos que hablar de Chile</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2733,7 +2731,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SI*</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2766,12 +2764,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional</t>
+          <t>universidad</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2801,17 +2799,17 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>Análisis de los resultados obtenidos de los Diálogos Ciudadanos Autoconvocados dentro del proceso constitucional</t>
+          <t>Iniciativa de diálogo y participación llevada a cabo por la UCH y PUC en el contexto de manifestaciones sociales</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>Secretaría de Participación Ciudadana</t>
+          <t>Universidad de Chile y Pontificia Universidad Católica de Chile</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="V19" s="4" t="n">
@@ -2819,12 +2817,13 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
+          <t>https://www.tenemosquehablardechile.cl/
+https://static1.squarespace.com/static/630d0dbf05b8104ed4d55d7f/t/67f694b2f91e4f228bb941cb/1744213189210/01.+Primer-InformeTQHDCH.pdf</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>CL-participacion-ciudadana-proceso-constitu</t>
+          <t>CL-tenemos-que-hablar-de-chile</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2836,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Tenemos que hablar de Chile</t>
+          <t>Un encuentro para la equidad de género en la movilidad en Chile</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2847,7 +2846,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>SI*</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2885,7 +2884,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2895,7 +2894,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2915,272 +2914,275 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>Iniciativa de diálogo y participación llevada a cabo por la UCH y PUC en el contexto de manifestaciones sociales</t>
+          <t>Espacio participativo para levantar opiniones y propuestas de autoridades, miembros de la sociedad civil y académicos sobre la movilidad con perspectiva de género en Chile.</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>Universidad de Chile y Pontificia Universidad Católica de Chile</t>
+          <t>Universidad Andres Bello</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="V20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tenemosquehablardechile.cl/
-https://static1.squarespace.com/static/630d0dbf05b8104ed4d55d7f/t/67f694b2f91e4f228bb941cb/1744213189210/01.+Primer-InformeTQHDCH.pdf</t>
-        </is>
-      </c>
-      <c r="X20" s="2" t="inlineStr">
-        <is>
-          <t>CL-tenemos-que-hablar-de-chile</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Un encuentro para la equidad de género en la movilidad en Chile</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>universidad</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>Privado</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>Privado</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>NLP - Tópicos</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>Espacio participativo para levantar opiniones y propuestas de autoridades, miembros de la sociedad civil y académicos sobre la movilidad con perspectiva de género en Chile.</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>Universidad Andres Bello</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>https://ipp.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/
 https://noticiasrepositorio.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/
 https://public.tableau.com/app/profile/ivania.yovanovic/viz/UnencuentroparalaequidaddegneroenlamovilidadenChile-CIUDHAD/CIUDHADTransporteyGnero</t>
         </is>
       </c>
-      <c r="X21" s="2" t="inlineStr">
+      <c r="X20" s="2" t="inlineStr">
         <is>
           <t>CL-un-encuentro-para-la-equidad-de-genero-e</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Chatico</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Presupuestos Participativos; Participación Digital</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="J21" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>gobierno local</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Privado; Gobierno</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>NLP; LLM</t>
         </is>
       </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>Agente virtual de Bogotá (Secretaría General) con módulos de PARTICIPACIÓN además de atención: votación de Causas Ciudadanas y de los Presupuestos Participativos (240.000+ votos desde 2022) y recepción de más de 147.000 aportes ciudadanos para la construcción del Plan Distrital de Desarrollo 'Bogotá Camina Segura' 2024-2027. Renovado con IA generativa (2026); atiende por WhatsApp/Telegram/webchat.</t>
         </is>
       </c>
-      <c r="T22" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
         <is>
           <t>Secretaría General de la Alcaldía Mayor de Bogotá</t>
         </is>
       </c>
-      <c r="U22" s="2" t="inlineStr">
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="V22" s="4" t="n">
+      <c r="V21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W22" s="2" t="inlineStr">
+      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>https://secretariageneral.gov.co/noticias/chatico-el-agente-virtual-de-servicio-la-ciudadania-supero-los-36-millones-de-conversaciones
 https://bogota.gov.co/mi-ciudad/gestion-publica/distrito-presenta-su-agente-virtual-chatico-que-guia-la-ciudadania
 https://bogota.gov.co/mi-ciudad/participacion-y-cultura-ciudadana/plan-desarrollo-bogota-camina-segura-tuvo-147-mil-aportes-ciudadanos</t>
         </is>
       </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>CO-chatico</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>ECHO – HáblameD Medellín</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Implementación; Análisis</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>organización internacional; gobierno local</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Mixto</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>Voz a Texto; NLP; LLM</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>IA que capta voz ciudadana en debates guiados y clasifica cada enunciado en metas ODS, generando visualizaciones para la planificación territorial</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+        </is>
+      </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>CO-chatico</t>
+          <t>CO-echo-hablamed-medellin</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
+        </is>
+      </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>CO</t>
@@ -3188,17 +3190,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Citibeats + PNUD Colombia (analítica de datos para la deliberación pública juvenil)</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>(sin revisar)</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>DUDA(lean SI)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3208,17 +3210,17 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>MEDIA (múltiples fuentes de prensa independientes; sin verificación técnica del método; cobertura crítica)</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital</t>
+          <t>Presupuestos Participativos; Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Análisis; Traducción Política</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
@@ -3226,19 +3228,15 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>organización internacional</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>Mixto</t>
-        </is>
-      </c>
+          <t>sociedad civil</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
@@ -3246,52 +3244,52 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>NLP; Machine Learning; Clasificación de texto; Análisis de sentimiento; Clustering temático</t>
+          <t>LLM; NLP</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>Iniciativa del Laboratorio de Aceleración del PNUD Colombia que, en el contexto del paro nacional de 2021, usó la plataforma de IA Citibeats para monitorear y agrupar en tiempo real las opiniones y propuestas de la juventud colombiana sobre la coyuntura del país, con el fin de 'mejorar la deliberación pública'. La IA filtra y clasifica contenido de fuentes abiertas (Twitter, Facebook, Instagram, foros, blogs, noticias y comentarios de video). En paralelo, el PNUD y aliados como El Avispero generaron espacios presenciales para contrastar lo dicho en las conversaciones en línea; no hay evidencia de que Citibeats procesara los aportes de un proceso participativo formal convocado (consulta, cabildo o deliberación con inputs estructurados), sino principalmente social listening de medios digitales.</t>
+          <t>Plataforma participativa donde jóvenes del resguardo Zenú deciden por votación digital la asignación de presupuestos locales del cabildo y debaten proyectos de ley / proponen iniciativas ciudadanas colectivas.</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>PNUD Colombia - Laboratorio de Aceleración (Accelerator Lab), con la plataforma de IA Citibeats (empresa, España)</t>
+          <t>Resguardo indígena Zenú (Reparo Torrente, Bajo Sinú); creador Carlos Redondo Rincón</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="V23" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/colombia/blog/analitica-de-datos-para-mejorar-la-deliberacion-publica-en-colombia
-https://www.undp.org/es/colombia/laboratorio-aceleracion
-https://www.undp.org/es/colombia/blog/data-analytics-improve-public-deliberation-colombia</t>
+          <t>https://cerosetenta.uniandes.edu.co/
+https://gaitanaia.org/
+https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>CO-citibeats-pnud-colombia-deliberacion-pub</t>
+          <t>CO-gaitana-ia-resguardo-zenu</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3302,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>ECHO – HáblameD Medellín</t>
+          <t>Tenemos que hablar de Colombia</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3324,7 +3322,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3334,7 +3332,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
@@ -3347,7 +3345,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>organización internacional; gobierno local</t>
+          <t>universidad; empresa; sociedad civil</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3362,37 +3360,37 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>Voz a Texto; NLP; LLM</t>
+          <t>NLP - Tópicos; NLP - Sentiment</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>IA que capta voz ciudadana en debates guiados y clasifica cada enunciado en metas ODS, generando visualizaciones para la planificación territorial</t>
+          <t>Plataforma colaborativa de diálogo e incidencia ciudadana para la conversación entre diversos actores de la sociedad colombiana, surgido a partir de eventos de manifestaciones sociales.</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="V24" s="4" t="n">
@@ -3400,39 +3398,36 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+          <t>https://tenemosquehablarcolombia.co/
+https://tenemosquehablarcolombia.co/resultados/</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>CO-echo-hablamed-medellin</t>
+          <t>CO-tenemos-que-hablar-de-colombia</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>CU</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>(sin revisar)</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>DUDA(lean SI)</t>
+          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3442,17 +3437,17 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (múltiples fuentes de prensa independientes; sin verificación técnica del método; cobertura crítica)</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Presupuestos Participativos; Gobernanza Colaborativa</t>
+          <t>Participación Digital; Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Análisis; Traducción Política</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
@@ -3460,15 +3455,19 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>sociedad civil</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>gobierno nacional</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
@@ -3476,7 +3475,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil</t>
+          <t>Privado; Academia; Gobierno</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3486,42 +3485,42 @@
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>LLM; NLP</t>
+          <t>NLP; Minería de texto; Recuperación de información; Clasificación automática de documentos</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>Plataforma participativa donde jóvenes del resguardo Zenú deciden por votación digital la asignación de presupuestos locales del cabildo y debaten proyectos de ley / proponen iniciativas ciudadanas colectivas.</t>
+          <t>Consulta popular legislativa nacional sobre el proyecto del Código de las Familias en Cuba, organizada y supervisada por el Consejo Electoral Nacional (CEN). Se desarrolló entre febrero y abril de 2022 mediante más de 79.000 reuniones en barrios, centros laborales y estudiantiles, con la participación de unos 6.481.200 personas que emitieron opiniones y propuestas sobre el articulado del proyecto de ley. Las propuestas recogidas eran revisadas y clasificadas por juristas en el sistema XISCOP y luego procesadas en el sistema GEMA-CEN, que mediante 'análisis inteligente de los expedientes' agrupaba propuestas similares y determinaba 'propuestas típicas' por párrafo/categoría (se determinaron 5.237 propuestas típicas por Título). XISCOP (UCI) emitía además las estadísticas oficiales. El proceso de consulta cerró en abril de 2022; el Código fue aprobado posteriormente en referendo el 25 de septiembre de 2022.</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>Resguardo indígena Zenú (Reparo Torrente, Bajo Sinú); creador Carlos Redondo Rincón</t>
+          <t>Consejo Electoral Nacional (CEN) de Cuba como órgano organizador y supervisor de la consulta popular. El procesamiento informático se apoyó en dos sistemas: XISCOP, desarrollado por la Universidad de las Ciencias Informáticas (UCI), para la entrada, revisión, clasificación y estadísticas oficiales; y GEMA-CEN, basado en el producto GEMA de la empresa estatal Datys, para el 'análisis inteligente' y agrupamiento de las propuestas. La Asamblea Nacional del Poder Popular y la Comisión redactora del Ministerio de Justicia recibieron los resultados.</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="V25" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>https://cerosetenta.uniandes.edu.co/
-https://gaitanaia.org/
-https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/</t>
+          <t>http://www.datys.cu/spa/site/product/15
+https://www.granma.cu/cuba/2022-01-24/herramientas-digitales-seran-claves-durante-la-consulta-popular-del-codigo-de-las-familias-24-01-2022-13-01-18
+https://www.uci.cu/</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>CO-gaitana-ia-resguardo-zenu</t>
+          <t>CU-consulta-popular-codigo-de-las-familias</t>
         </is>
       </c>
     </row>
@@ -3529,12 +3528,12 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Tenemos que hablar de Colombia</t>
+          <t xml:space="preserve">PAGA IA </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -3554,17 +3553,17 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
@@ -3572,12 +3571,12 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>universidad; empresa; sociedad civil</t>
+          <t>gobierno nacional; sociedad civil</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3592,7 +3591,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3602,27 +3601,27 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos; NLP - Sentiment</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>Plataforma colaborativa de diálogo e incidencia ciudadana para la conversación entre diversos actores de la sociedad colombiana, surgido a partir de eventos de manifestaciones sociales.</t>
+          <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto. Analiza datos de planes de acción de gobierno abierto de Ecuador y otros países de Hispanoamérica para sugerir actividades e hitos relacionados con temas propuestos por los usuarios</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
+          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="V26" s="4" t="n">
@@ -3630,13 +3629,13 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>https://tenemosquehablarcolombia.co/
-https://tenemosquehablarcolombia.co/resultados/</t>
+          <t>https://ia.gobiernoabierto.ec/
+https://ia.gobiernoabierto.ec/acercade</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>CO-tenemos-que-hablar-de-colombia</t>
+          <t>EC-paga-ia</t>
         </is>
       </c>
     </row>
@@ -3644,12 +3643,12 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CU</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
+          <t xml:space="preserve">Guatemala Joven Conversa </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -3669,17 +3668,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital; Referendos e Iniciativas Populares</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación; Análisis</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
@@ -3692,12 +3691,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional</t>
+          <t>organización internacional; sociedad civil</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3707,17 +3706,17 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Privado; Academia; Gobierno</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>NLP; Minería de texto; Recuperación de información; Clasificación automática de documentos</t>
+          <t>NLP - Sentiment; NLP - Tópicos</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
@@ -3727,45 +3726,49 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>Consulta popular legislativa nacional sobre el proyecto del Código de las Familias en Cuba, organizada y supervisada por el Consejo Electoral Nacional (CEN). Se desarrolló entre febrero y abril de 2022 mediante más de 79.000 reuniones en barrios, centros laborales y estudiantiles, con la participación de unos 6.481.200 personas que emitieron opiniones y propuestas sobre el articulado del proyecto de ley. Las propuestas recogidas eran revisadas y clasificadas por juristas en el sistema XISCOP y luego procesadas en el sistema GEMA-CEN, que mediante 'análisis inteligente de los expedientes' agrupaba propuestas similares y determinaba 'propuestas típicas' por párrafo/categoría (se determinaron 5.237 propuestas típicas por Título). XISCOP (UCI) emitía además las estadísticas oficiales. El proceso de consulta cerró en abril de 2022; el Código fue aprobado posteriormente en referendo el 25 de septiembre de 2022.</t>
+          <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarrollo y la lucha contra la corrupción.</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>Consejo Electoral Nacional (CEN) de Cuba como órgano organizador y supervisor de la consulta popular. El procesamiento informático se apoyó en dos sistemas: XISCOP, desarrollado por la Universidad de las Ciencias Informáticas (UCI), para la entrada, revisión, clasificación y estadísticas oficiales; y GEMA-CEN, basado en el producto GEMA de la empresa estatal Datys, para el 'análisis inteligente' y agrupamiento de las propuestas. La Asamblea Nacional del Poder Popular y la Comisión redactora del Ministerio de Justicia recibieron los resultados.</t>
+          <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="V27" s="5" t="n">
-        <v>4</v>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>http://www.datys.cu/spa/site/product/15
-https://www.granma.cu/cuba/2022-01-24/herramientas-digitales-seran-claves-durante-la-consulta-popular-del-codigo-de-las-familias-24-01-2022-13-01-18
-https://www.uci.cu/</t>
+          <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
+https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/
+https://dppa.un.org/en/using-power-of-ai-to-boost-youth-political-participation-guatemala</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>CU-consulta-popular-codigo-de-las-familias</t>
+          <t>GT-guatemala-joven-conversa</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
+        </is>
+      </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAGA IA </t>
+          <t xml:space="preserve">RedPública + iVerify </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -3795,7 +3798,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
@@ -3803,17 +3806,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional; sociedad civil</t>
+          <t>organización internacional; universidad</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3823,32 +3826,32 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil</t>
+          <t>Gobierno; Academia</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Internacional, Nacional</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>NLP - Tópicos</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto. Analiza datos de planes de acción de gobierno abierto de Ecuador y otros países de Hispanoamérica para sugerir actividades e hitos relacionados con temas propuestos por los usuarios</t>
+          <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias. Integra iVerify, una herramienta que utiliza aprendizaje automático para detectar y clasificar desinformación electoral antes de su publicación.</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
+          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3861,13 +3864,12 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>https://ia.gobiernoabierto.ec/
-https://ia.gobiernoabierto.ec/acercade</t>
+          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>EC-paga-ia</t>
+          <t>HN-redpublica-iverify</t>
         </is>
       </c>
     </row>
@@ -3875,12 +3877,12 @@
       <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guatemala Joven Conversa </t>
+          <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -3900,17 +3902,17 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Gobernanza Colaborativa; Participación Digital</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
@@ -3923,12 +3925,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>organización internacional; sociedad civil</t>
+          <t>gobierno local</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3938,32 +3940,32 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Gobierno</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>NLP - Sentiment; NLP - Tópicos</t>
+          <t>NLP; Otros(no especificado)</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>no-claro</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarrollo y la lucha contra la corrupción.</t>
+          <t>Elaboración del Programa de Gobierno del Estado de Guanajuato 2024-2030 ('Gobierno de la Gente'), un plan de gobierno construido con participación ciudadana: se recorrió el territorio y se realizaron cuatro talleres regionales (noreste, norte, centro y sur) con representación de los 46 municipios, integrando la voz de más de 26,000 personas mediante talleres y consultas. El contenido fue validado por el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG), conformado por ciudadanía, la Gobernadora, secretarios de cada eje e IPLANEG. Se utilizaron herramientas de inteligencia artificial para procesar y organizar las miles de ideas y propuestas recibidas, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región, transformando el diálogo social en datos para la toma de decisiones que alimentaron los ejes del programa. Adicionalmente existe la asistente virtual 'Esperanza' para consultar el programa ya publicado.</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
+          <t>Gobierno del Estado de Guanajuato — Instituto de Planeación, Estadística y Geografía del Estado de Guanajuato (IPLANEG), con validación del COPLADEG. Titular: Gobernadora Libia Dennise García Muñoz Ledo.</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3971,19 +3973,19 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="V29" s="4" t="n">
-        <v>0</v>
+      <c r="V29" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
-https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/
-https://dppa.un.org/en/using-power-of-ai-to-boost-youth-political-participation-guatemala</t>
+          <t>https://guanajuatointeligente.com/como-hicimos-el-programa/
+https://iplaneg.guanajuato.gob.mx/programagobierno24-30/
+https://iplaneg.guanajuato.gob.mx/wp-content/uploads/03-2.05-Diagnostico-Programa-de-Gobierno-2024-2030-_Diagnostico-Estatal-2025_.pdf</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>GT-guatemala-joven-conversa</t>
+          <t>MX-guanajuato-inteligente-2024-2030</t>
         </is>
       </c>
     </row>
@@ -3995,12 +3997,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RedPública + iVerify </t>
+          <t>Presupuesto CRECES</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4020,17 +4022,17 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Referendos e Iniciativas Populares</t>
+          <t>Presupuestos Participativos</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
@@ -4043,7 +4045,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>organización internacional; universidad</t>
+          <t>gobierno local</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -4058,17 +4060,17 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Gobierno; Academia</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Internacional, Nacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos</t>
+          <t>Chatbot - Inespecífico</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
@@ -4078,30 +4080,30 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias. Integra iVerify, una herramienta que utiliza aprendizaje automático para detectar y clasificar desinformación electoral antes de su publicación.</t>
+          <t>Presupuesto participativo del Ayuntamiento de Hermosillo en México. Utiliza un chatbot que a través de IA simplifica y facilita la votación de los presupuestos participativos</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
+          <t>Ayundamiento de Hermosilla</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>0</v>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="V30" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
+          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>HN-redpublica-iverify</t>
+          <t>MX-presupuesto-creces</t>
         </is>
       </c>
     </row>
@@ -4109,12 +4111,12 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
+          <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4134,17 +4136,17 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa; Participación Digital</t>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Análisis; Traducción Política</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
@@ -4152,17 +4154,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>gobierno local</t>
+          <t>sociedad civil; gobierno nacional</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4172,7 +4174,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4180,11 +4182,7 @@
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>NLP; Otros(no especificado)</t>
-        </is>
-      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
       <c r="R31" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
@@ -4192,12 +4190,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>Elaboración del Programa de Gobierno del Estado de Guanajuato 2024-2030 ('Gobierno de la Gente'), un plan de gobierno construido con participación ciudadana: se recorrió el territorio y se realizaron cuatro talleres regionales (noreste, norte, centro y sur) con representación de los 46 municipios, integrando la voz de más de 26,000 personas mediante talleres y consultas. El contenido fue validado por el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG), conformado por ciudadanía, la Gobernadora, secretarios de cada eje e IPLANEG. Se utilizaron herramientas de inteligencia artificial para procesar y organizar las miles de ideas y propuestas recibidas, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región, transformando el diálogo social en datos para la toma de decisiones que alimentaron los ejes del programa. Adicionalmente existe la asistente virtual 'Esperanza' para consultar el programa ya publicado.</t>
+          <t>Mansa Idea (www.mansaidea.com) es una plataforma digital basada en inteligencia artificial lanzada el 1 de abril de 2024 por la Fundación Panamá Participa (sociedad civil), liderada por Paulina Franceschi. La plataforma organiza y hace navegables más de 175.000 ideas y propuestas ciudadanas generadas durante el Pacto del Bicentenario 'Cerrando Brechas' (proceso participativo nacional convocado por el gobierno de Panamá / Concertación Nacional, presidente Cortizo, 2020-2021), agregando los consensos nacionales y regionales/provinciales por tema en un solo clic. La IA se aplica sobre el CONTENIDO de los aportes ciudadanos (organiza, agrega y sintetiza el corpus de propuestas) para convertirlo en una base de datos navegable. El uso de la IA es un tratamiento PUNTERAL (~2024) de un corpus histórico de un proceso participativo ya cerrado (el Pacto fue 2020-2021), orientado a elevar el nivel de la conversación electoral 2024 y a dotar a candidatos, medios y ciudadanía de una herramienta para alinear planes con las necesidades de la población y monitorear el mandato ciudadano. IMPORTANTE: el proceso participativo original (recolección de aportes) fue convocado por el gobierno; la capa de IA (Mansa Idea) la desarrolla la sociedad civil sobre ese corpus ya recolectado.</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>Gobierno del Estado de Guanajuato — Instituto de Planeación, Estadística y Geografía del Estado de Guanajuato (IPLANEG), con validación del COPLADEG. Titular: Gobernadora Libia Dennise García Muñoz Ledo.</t>
+          <t>Fundación Panamá Participa (sociedad civil, Panamá), iniciativa liderada por Paulina Franceschi. El proceso participativo de origen (Pacto del Bicentenario 'Cerrando Brechas') fue convocado por el Gobierno de Panamá a través del mecanismo de Concertación Nacional para el Desarrollo (presidente Laurentino Cortizo), con apoyo del PNUD.</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -4206,248 +4204,254 @@
         </is>
       </c>
       <c r="V31" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>https://guanajuatointeligente.com/como-hicimos-el-programa/
-https://iplaneg.guanajuato.gob.mx/programagobierno24-30/
-https://iplaneg.guanajuato.gob.mx/wp-content/uploads/03-2.05-Diagnostico-Programa-de-Gobierno-2024-2030-_Diagnostico-Estatal-2025_.pdf</t>
-        </is>
-      </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t>MX-guanajuato-inteligente-2024-2030</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Presupuesto CRECES</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Presupuestos Participativos</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>gobierno local</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>Privado</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>Chatbot - Inespecífico</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>Presupuesto participativo del Ayuntamiento de Hermosillo en México. Utiliza un chatbot que a través de IA simplifica y facilita la votación de los presupuestos participativos</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>Ayundamiento de Hermosilla</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="V32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
-        </is>
-      </c>
-      <c r="X32" s="2" t="inlineStr">
-        <is>
-          <t>MX-presupuesto-creces</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Análisis; Traducción Política</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>sociedad civil; gobierno nacional</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>Privado</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>Sociedad Civil</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>no-claro</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>Mansa Idea (www.mansaidea.com) es una plataforma digital basada en inteligencia artificial lanzada el 1 de abril de 2024 por la Fundación Panamá Participa (sociedad civil), liderada por Paulina Franceschi. La plataforma organiza y hace navegables más de 175.000 ideas y propuestas ciudadanas generadas durante el Pacto del Bicentenario 'Cerrando Brechas' (proceso participativo nacional convocado por el gobierno de Panamá / Concertación Nacional, presidente Cortizo, 2020-2021), agregando los consensos nacionales y regionales/provinciales por tema en un solo clic. La IA se aplica sobre el CONTENIDO de los aportes ciudadanos (organiza, agrega y sintetiza el corpus de propuestas) para convertirlo en una base de datos navegable. El uso de la IA es un tratamiento PUNTERAL (~2024) de un corpus histórico de un proceso participativo ya cerrado (el Pacto fue 2020-2021), orientado a elevar el nivel de la conversación electoral 2024 y a dotar a candidatos, medios y ciudadanía de una herramienta para alinear planes con las necesidades de la población y monitorear el mandato ciudadano. IMPORTANTE: el proceso participativo original (recolección de aportes) fue convocado por el gobierno; la capa de IA (Mansa Idea) la desarrolla la sociedad civil sobre ese corpus ya recolectado.</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>Fundación Panamá Participa (sociedad civil, Panamá), iniciativa liderada por Paulina Franceschi. El proceso participativo de origen (Pacto del Bicentenario 'Cerrando Brechas') fue convocado por el Gobierno de Panamá a través del mecanismo de Concertación Nacional para el Desarrollo (presidente Laurentino Cortizo), con apoyo del PNUD.</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="V33" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="W33" s="2" t="inlineStr">
         <is>
           <t>https://mansaidea.com/ (intentar archive.org / cache); buscar 'Mansa Idea metodología inteligencia artificial procesamiento propuestas' y entrevistas técnicas a Paulina Franceschi / Fundación Panamá Participa.
 https://mansaidea.com/ ; buscar 'Mansa Idea 2025' / 'Mansa Idea 2026' / 'Fundación Panamá Participa actividad reciente'.
 https://mansaidea.com/ ; buscar evidencia de actualizaciones periódicas del corpus o nuevas convocatorias.</t>
         </is>
       </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>PA-mansa-idea-pacto-del-bicentenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>otra institución pública</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>NLP - Tópicos; NLP - Sentiment</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>Una consulta pública para recoger opiniones sobre el Proyecto Educativo Nacional 2036, utilizando encuestas en línea, talleres y mesas deliberativas.</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>Consejo Nacional de Educación del Perú</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional
+https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080
+https://andina.pe/agencia/noticia-usan-inteligencia-artificial-para-formular-proyecto-educativo-nacional-al-2036-777369.aspx</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>PE-consulta-ciudadana-sobre-el-proyecto-nac</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>DUDA(lean NO)</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Plataforma</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>gobierno nacional</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>apoyo</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>Chatbot - Inespecífico</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>no-claro</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>EngageTT (engage.gov.tt) es la plataforma de participacion ciudadana del Ministry of Digital Transformation de Trinidad y Tobago (desde mayo 2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), lanzada en el simposio del NDTS el 12 de febrero de 2025 junto al BID (IDB). Se usa como canal de participacion en el proceso de planificacion nacional del National Digital Transformation Strategy (NDTS) 2024-2027, donde ciudadanos, empresas y partes interesadas reciben actualizaciones y aportan retroalimentacion via encuestas, sondeos (polls), un 'Open Forum' de ideas y el envio de propuestas. La instancia corre sobre el software Go Vocal (antes CitizenLab) -confirmado por la ruta interna 'projects/e-democracy-govocal-internal'-. Go Vocal incorpora un modulo de IA/NLP de 'Sensemaking' (analisis y resumen automatico de aportes), pero ese modulo NO viene activo por defecto: segun la documentacion de soporte de Go Vocal, el acceso a la funcion de AI Analysis/Sensemaking DEPENDE DEL PLAN contratado (Advanced Sensemaking con auto-insights esta en el plan Premium). Tras 2a pasada de investigacion (&gt;=14 busquedas/fetches) NO se halla evidencia alguna de que la instancia de Trinidad active ni use esas funciones de IA sobre el CONTENIDO de los aportes; toda la documentacion describe a EngageTT como recolector (surveys, polls, Open Forum, ideas), es decir plataforma usada como formulario sin analisis automatico confirmado. Existe ademas AskNDTS, un chatbot/PWA de IA conversacional para responder preguntas sobre el NDTS (rol de FAQ informativo, EXCLUIDO del criterio).</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Digital Transformation de Trinidad y Tobago (desde el 23-may-2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), en colaboracion con el Banco Interamericano de Desarrollo (BID/IDB). Plataforma de software: Go Vocal (antes CitizenLab), empresa belga.</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="V33" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
+https://www.govocal.com/plans
+https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool</t>
+        </is>
+      </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>PA-mansa-idea-pacto-del-bicentenario</t>
+          <t>TT-engagett-plataforma-go-vocal</t>
         </is>
       </c>
     </row>
@@ -4455,24 +4459,24 @@
       <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>UY</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
+          <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>(sin revisar)</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
           <t>sí</t>
@@ -4480,12 +4484,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+          <t>MEDIA (fuente primaria + OCDE 2025; fetch primario bloqueado por proxy, citas vía repo/WebSearch)</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4503,7 +4507,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>otra institución pública</t>
+          <t>universidad</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -4518,7 +4522,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4528,7 +4532,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos; NLP - Sentiment</t>
+          <t>Clustering; ML - Inespecífico</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
@@ -4538,271 +4542,35 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Una consulta pública para recoger opiniones sobre el Proyecto Educativo Nacional 2036, utilizando encuestas en línea, talleres y mesas deliberativas.</t>
+          <t>Referéndum nacional para derogar 135 artículos de la Ley de Urgente Consideración (LUC). Un equipo de la Universidad de la República corrió una conversación Pol.is en paralelo al referéndum del 27/03/2022 (documentado como caso 2021).</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>Consejo Nacional de Educación del Perú</t>
+          <t>Equipo de 13 personas de la Universidad de la República (UdelaR) — ingenieros, comunicadores y científicos de datos; plataforma Pol.is (The Computational Democracy Project)</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>0</v>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="V34" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional
-https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080
-https://andina.pe/agencia/noticia-usan-inteligencia-artificial-para-formular-proyecto-educativo-nacional-al-2036-777369.aspx</t>
+          <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>PE-consulta-ciudadana-sobre-el-proyecto-nac</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>DUDA(lean NO)</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>gobierno nacional</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>apoyo</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>Privado</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>Chatbot - Inespecífico</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>no-claro</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>EngageTT (engage.gov.tt) es la plataforma de participacion ciudadana del Ministry of Digital Transformation de Trinidad y Tobago (desde mayo 2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), lanzada en el simposio del NDTS el 12 de febrero de 2025 junto al BID (IDB). Se usa como canal de participacion en el proceso de planificacion nacional del National Digital Transformation Strategy (NDTS) 2024-2027, donde ciudadanos, empresas y partes interesadas reciben actualizaciones y aportan retroalimentacion via encuestas, sondeos (polls), un 'Open Forum' de ideas y el envio de propuestas. La instancia corre sobre el software Go Vocal (antes CitizenLab) -confirmado por la ruta interna 'projects/e-democracy-govocal-internal'-. Go Vocal incorpora un modulo de IA/NLP de 'Sensemaking' (analisis y resumen automatico de aportes), pero ese modulo NO viene activo por defecto: segun la documentacion de soporte de Go Vocal, el acceso a la funcion de AI Analysis/Sensemaking DEPENDE DEL PLAN contratado (Advanced Sensemaking con auto-insights esta en el plan Premium). Tras 2a pasada de investigacion (&gt;=14 busquedas/fetches) NO se halla evidencia alguna de que la instancia de Trinidad active ni use esas funciones de IA sobre el CONTENIDO de los aportes; toda la documentacion describe a EngageTT como recolector (surveys, polls, Open Forum, ideas), es decir plataforma usada como formulario sin analisis automatico confirmado. Existe ademas AskNDTS, un chatbot/PWA de IA conversacional para responder preguntas sobre el NDTS (rol de FAQ informativo, EXCLUIDO del criterio).</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>Ministry of Digital Transformation de Trinidad y Tobago (desde el 23-may-2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), en colaboracion con el Banco Interamericano de Desarrollo (BID/IDB). Plataforma de software: Go Vocal (antes CitizenLab), empresa belga.</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="V35" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
-https://www.govocal.com/plans
-https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool</t>
-        </is>
-      </c>
-      <c r="X35" s="2" t="inlineStr">
-        <is>
-          <t>TT-engagett-plataforma-go-vocal</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr"/>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>UY</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>(sin revisar)</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA (fuente primaria + OCDE 2025; fetch primario bloqueado por proxy, citas vía repo/WebSearch)</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Referendos e Iniciativas Populares</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>universidad</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>Sociedad Civil</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>Clustering; ML - Inespecífico</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>Referéndum nacional para derogar 135 artículos de la Ley de Urgente Consideración (LUC). Un equipo de la Universidad de la República corrió una conversación Pol.is en paralelo al referéndum del 27/03/2022 (documentado como caso 2021).</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>Equipo de 13 personas de la Universidad de la República (UdelaR) — ingenieros, comunicadores y científicos de datos; plataforma Pol.is (The Computational Democracy Project)</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="V36" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/</t>
-        </is>
-      </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
           <t>UY-polis-referendum-luc</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X36"/>
+  <autoFilter ref="A1:X34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4813,7 +4581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5240,450 +5008,526 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>A. Excluir (criterio corregido)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar NO (ya fuera del conteo)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Cátedra Brasil / Co:Lab USP - IA generativa en presupuesto participativo (SP)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>No es un proceso de participación (o sin IA verificada) → excluido</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Investigación académica en curso ('pesquisas em andamento') sobre IA generativa para participación: sin despliegue con ciudadanos ni proceso propio (verificado). Estudio sin despliegue → NO. Decisión del equipo.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://participemais.prefeitura.sp.gov.br/budgets
+https://colab.each.usp.br/blog/2025/03/28/a-ia-generativa-e-o-futuro-da-participacao-cidada-pesquisas-em-andamento/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>A. Excluir (criterio corregido)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Confirmar NO (ya fuera del conteo)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Citibeats + PNUD Colombia (analítica de datos para la deliberación pública juvenil)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>No es un proceso de participación (o sin IA verificada) → excluido</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Escucha social de redes abiertas (Twitter/Facebook) durante el paro de 2021: no hay proceso participativo convocado (verificado). Misma regla que U-Report (solo opinión) → NO. Decisión del equipo.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/es/colombia/blog/analitica-de-datos-para-mejorar-la-deliberacion-publica-en-colombia
+https://www.undp.org/es/colombia/laboratorio-aceleracion</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Presupuesto CRECES</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Presupuesto participativo (Hermosillo); la IA (chatbot) facilita la votación (Implementación).</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://presupuestocreces.hermosillo.gob.mx/</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>LXS 400 - Chile Delibera</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Mini-público del Senado; la IA modera y administra los turnos de palabra (Implementación/Planificación).</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://es.wikipedia.org/wiki/Lxs_400:_Chile_Delibera
 https://www.lxs400.cl/noticias/</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Consulta ciudadana; la IA analiza los aportes (Análisis).</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030
 https://participacion.digital.gob.cl/folders/consultas-ciudadanas</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>HN</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RedPública + iVerify </t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Plataforma de propuestas de ley ciudadanas (participación legislativa).</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>La voz de los nuevos votantes</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Consulta a nuevos votantes con NLP — proceso ejecutado por el equipo (confirmado).</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf
 https://ipp.unab.cl/publicacion/la-voz-de-los-nuevos-votantes-san-bernardo/</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Jornada de escucha / diálogo — proceso ejecutado por el equipo (confirmado).</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://ipp.unab.cl/
 https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Chatico</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Tiene módulos de participación (aportes al Plan de Desarrollo de Bogotá) — confirmado por el equipo.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://secretariageneral.gov.co/noticias/chatico-el-agente-virtual-de-servicio-la-ciudadania-supero-los-36-millones-de-conversaciones
 https://bogota.gov.co/mi-ciudad/gestion-publica/distrito-presenta-su-agente-virtual-chatico-que-guia-la-ciudadania</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Colab</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Permite sugerir ideas y votar en decisiones municipales (módulos de participación) — confirmado por el equipo.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.colab.com.br/sou-cidadao/</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Caso borde: el chatbot AskNDTS (IA) informa/apoya la implementación del proceso NDTS y el módulo Go Vocal Sensemaking está planeado (existe). → ENTRA como apoyo a la implementación. Decisión del equipo.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
 https://www.govocal.com/plans</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>B. Rescatado → ENTRA</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Confirmar SI</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Sí es participación; la IA aporta en alguna etapa (incl. logística) → ENTRA</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Un LLM (DeepSeek) resume, organiza y construye CONSENSOS sobre el contenido de los aportes en un proceso participativo real (cabildo Zenú). Procesa el contenido → ENTRA. Decisión del equipo.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://cerosetenta.uniandes.edu.co/
 https://gaitanaia.org/</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>G. Dedup (confirmar)</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Confirmar cuenta como 1</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>e-Cidadania (Senado Federal)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>El 'matching de ideias' no se cuenta aparte del 'marcado de audiencias' (misma plataforma)</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>'Duas ferramentas relacionadas' del mismo portal e-Cidadania (fuente Senado).</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>G. Dedup (confirmar)</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Confirmar 1 SI + 1 NO</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Participación Ciudadana Proceso Constitucional</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Homónimo duplicado: uno cuenta (SI), el otro NO</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Ya resuelto en la planilla.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G23"/>
+  <autoFilter ref="A1:G25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5694,7 +5538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5928,22 +5772,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>De ciudadano a senador: la inteligencia artificial y la reinvención de la elaboración legislativa en Brasil”</t>
+          <t>Cátedra Brasil / Co:Lab USP - IA generativa en presupuesto participativo (SP)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Propuesta, pero no hay datos sobre que se vaya a ejecutar</t>
+          <t>Investigación académica en curso ('pesquisas em andamento') sobre IA generativa para participación: sin despliegue con ciudadanos ni proceso propio (verificado). Estudio sin despliegue → NO. Decisión del equipo.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://rebootdemocracy.ai/blog/ai-lawmaking-brazil-senate</t>
+          <t>https://colab.each.usp.br/blog/2025/03/28/a-ia-generativa-e-o-futuro-da-participacao-cidada-pesquisas-em-andamento/</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5799,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Fala.BR</t>
+          <t>De ciudadano a senador: la inteligencia artificial y la reinvención de la elaboración legislativa en Brasil”</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -5965,12 +5809,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Propuesta, pero no hay datos sobre que se vaya a ejecutar</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://falabr.cgu.gov.br/</t>
+          <t>https://rebootdemocracy.ai/blog/ai-lawmaking-brazil-senate</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5826,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Jaque</t>
+          <t>Fala.BR</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -5997,7 +5841,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
+          <t>https://falabr.cgu.gov.br/</t>
         </is>
       </c>
     </row>
@@ -6009,7 +5853,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Mudamos</t>
+          <t>Jaque</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -6019,12 +5863,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>No se identifica uso de IA</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.mudamos.org/</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
     </row>
@@ -6036,22 +5880,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ParticipACT Brasil</t>
+          <t>Mudamos</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Civic tech de reporte urbano (app para reportar problemas): no es un proceso participativo.</t>
+          <t>No se identifica uso de IA</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://site.participact.com.br/</t>
+          <t>https://www.mudamos.org/</t>
         </is>
       </c>
     </row>
@@ -6063,22 +5907,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Participa+ Brasil</t>
+          <t>ParticipACT Brasil</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>No se identifica uso de IA</t>
+          <t>Civic tech de reporte urbano (app para reportar problemas): no es un proceso participativo.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.br/participamaisbrasil/pagina-inicial</t>
+          <t>https://site.participact.com.br/</t>
         </is>
       </c>
     </row>
@@ -6090,22 +5934,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Participe+ (ParticipeMais) - app estudiantil UnB-MDS de IA sobre contenidos de Brasil Participativo</t>
+          <t>Participa+ Brasil</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>NO ENTRA. Aunque tecnicamente la IA SI procesa el CONTENIDO de los aportes (agrupa por temas via HDBSCAN y clasifica en eixos por similitud semantica, ademas de resumir con LLM), el candidato incumple una condicion NECESARIA del criterio de inclusion ('SI solo si caso distinto, DESPLEGADO OFICIALMEN</t>
+          <t>No se identifica uso de IA</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/unb-mds/ParticipeMais</t>
+          <t>https://www.gov.br/participamaisbrasil/pagina-inicial</t>
         </is>
       </c>
     </row>
@@ -6117,7 +5961,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Projeto Lumina - análise de sentimentos das propostas de Brasil Participativo (projeto estudantil UnB-MDS)</t>
+          <t>Participe+ (ParticipeMais) - app estudiantil UnB-MDS de IA sobre contenidos de Brasil Participativo</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -6127,12 +5971,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>NO ENTRA. Aunque la IA sí actúa sobre el CONTENIDO de aportes ciudadanos (análisis de sentimiento positivo/negativo/neutro de las propuestas y comentarios de Brasil Participativo, rol_IA=contenido), falla el requisito de DESPLIEGUE OFICIAL: Projeto Lumina es un EJERCICIO ACADÉMICO de la disciplina '</t>
+          <t>NO ENTRA. Aunque tecnicamente la IA SI procesa el CONTENIDO de los aportes (agrupa por temas via HDBSCAN y clasifica en eixos por similitud semantica, ademas de resumir con LLM), el candidato incumple una condicion NECESARIA del criterio de inclusion ('SI solo si caso distinto, DESPLEGADO OFICIALMEN</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/unb-mds/2024-2-Lumina</t>
+          <t>https://github.com/unb-mds/ParticipeMais</t>
         </is>
       </c>
     </row>
@@ -6144,22 +5988,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Querido Diário</t>
+          <t>Projeto Lumina - análise de sentimentos das propostas de Brasil Participativo (projeto estudantil UnB-MDS)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Descubrimiento</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>NO ENTRA. Aunque la IA sí actúa sobre el CONTENIDO de aportes ciudadanos (análisis de sentimiento positivo/negativo/neutro de las propuestas y comentarios de Brasil Participativo, rol_IA=contenido), falla el requisito de DESPLIEGUE OFICIAL: Projeto Lumina es un EJERCICIO ACADÉMICO de la disciplina '</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://ok.org.br/projetos/querido-diario/</t>
+          <t>https://github.com/unb-mds/2024-2-Lumina</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6015,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Robô ALICE (CGU)</t>
+          <t>Querido Diário</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -6186,7 +6030,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://oecd-opsi.org/innovations/robot-alice-bid-contract-and-notice-analyser/</t>
+          <t>https://ok.org.br/projetos/querido-diario/</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6042,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Serenata.ai</t>
+          <t>Robô ALICE (CGU)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -6208,12 +6052,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>No es participación Ciudadana</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://serenata.ai/</t>
+          <t>https://oecd-opsi.org/innovations/robot-alice-bid-contract-and-notice-analyser/</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6069,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Tira-Dúvidas TSE</t>
+          <t>Serenata.ai</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -6235,24 +6079,24 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No es participación Ciudadana</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.tse.jus.br/comunicacao/noticias/2022/Setembro/tira-duvidas-do-tse-no-whatsapp-ganha-ferramenta-inedita-de-checagem-de-fatos-para-as-eleicoes-2022-402542</t>
+          <t>https://serenata.ai/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Caminar</t>
+          <t>Tira-Dúvidas TSE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -6262,12 +6106,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>De acuerdo a la descripción, solo permitiría a los ciudadanos consultar</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://parlamericas.org/uploads/documents/Presentation-OPNStaffMeeting-ProyectoCAMINARChile_MiguelLanderos-sp.pdf</t>
+          <t>https://www.tse.jus.br/comunicacao/noticias/2022/Setembro/tira-duvidas-do-tse-no-whatsapp-ganha-ferramenta-inedita-de-checagem-de-fatos-para-as-eleicoes-2022-402542</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6123,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Modelo de inferencia de posturas en Twitter (referéndum)</t>
+          <t>Caminar</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -6289,12 +6133,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Es un estudio</t>
+          <t>De acuerdo a la descripción, solo permitiría a los ciudadanos consultar</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.15532</t>
+          <t>https://parlamericas.org/uploads/documents/Presentation-OPNStaffMeeting-ProyectoCAMINARChile_MiguelLanderos-sp.pdf</t>
         </is>
       </c>
     </row>
@@ -6306,22 +6150,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Participa Pudahuel — Presupuesto Participativo deliberativo (plataforma Go Vocal/CitizenLab)</t>
+          <t>Modelo de inferencia de posturas en Twitter (referéndum)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Presupuesto participativo real, pero solo se confirma que la plataforma (Go Vocal) tiene el módulo de IA/NLP de fábrica; NO hay traza de que Pudahuel lo activara sobre los aportes (usa_IA_en_proceso 'no-claro', sin evidencia). Sin uso de IA verificado → NO. Decisión del equipo.</t>
+          <t>Es un estudio</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://participa.mpudahuel.cl/</t>
+          <t>https://arxiv.org/abs/2303.15532</t>
         </is>
       </c>
     </row>
@@ -6333,22 +6177,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Participación Ciudadana Proceso Constitucional</t>
+          <t>Participa Pudahuel — Presupuesto Participativo deliberativo (plataforma Go Vocal/CitizenLab)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Baseline 2025</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Aplica a los dos casos homónimos (autoconvocados y audiencias)</t>
+          <t>Presupuesto participativo real, pero solo se confirma que la plataforma (Go Vocal) tiene el módulo de IA/NLP de fábrica; NO hay traza de que Pudahuel lo activara sobre los aportes (usa_IA_en_proceso 'no-claro', sin evidencia). Sin uso de IA verificado → NO. Decisión del equipo.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
+          <t>https://participa.mpudahuel.cl/</t>
         </is>
       </c>
     </row>
@@ -6360,22 +6204,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Plataforma UCampus - participación 2023 (proceso constitucional)</t>
+          <t>Participación Ciudadana Proceso Constitucional</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Excluido (revisar)</t>
+          <t>Baseline 2025</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>MANTENER EXCLUIDO. Existe un proceso participativo ELEGIBLE (Proceso Constitucional 2023, mecanismos de participación ciudadana con ~280 mil personas, convocado por el Estado de Chile), y UCampus (Universidad de Chile) fue el operador técnico de dos de los cuatro mecanismos (Audiencias Públicas e In</t>
+          <t>Aplica a los dos casos homónimos (autoconvocados y audiencias)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://ucampus.cl/ucampus-es-la-plataforma-digital-del-proceso-constitucional-2023/</t>
+          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
         </is>
       </c>
     </row>
@@ -6387,22 +6231,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Senador Virtual / CrowdLaw (GobLab UAI + IMFD)</t>
+          <t>Plataforma UCampus - participación 2023 (proceso constitucional)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Dudoso</t>
+          <t>Excluido (revisar)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2a PASADA (resuelve DUDA -&gt; NO). La plataforma Senador Virtual / Congreso Virtual es un proceso participativo digital del Congreso de Chile (gobierno nacional) plenamente activo y consolidado (&gt;16 anios, &gt;130.000 participantes), pero la plataforma en si NO usa IA sobre el contenido de los aportes y </t>
+          <t>MANTENER EXCLUIDO. Existe un proceso participativo ELEGIBLE (Proceso Constitucional 2023, mecanismos de participación ciudadana con ~280 mil personas, convocado por el Estado de Chile), y UCampus (Universidad de Chile) fue el operador técnico de dos de los cuatro mecanismos (Audiencias Públicas e In</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://goblab.uai.cl/en/16-years-of-crowdlaw-in-the-chilean-parliament/</t>
+          <t>https://ucampus.cl/ucampus-es-la-plataforma-digital-del-proceso-constitucional-2023/</t>
         </is>
       </c>
     </row>
@@ -6414,49 +6258,49 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Viña Decide — Primer Presupuesto Participativo de Viña del Mar (plataforma Go Vocal/CitizenLab)</t>
+          <t>Senador Virtual / CrowdLaw (GobLab UAI + IMFD)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Dudoso</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Presupuesto participativo real sobre plataforma Go Vocal, pero no se encontró en el informe ejecutivo ninguna traza de uso de IA sobre los aportes (usa_IA_en_proceso 'no-claro', sin evidencia). Sin uso de IA verificado → NO. Decisión del equipo.</t>
+          <t xml:space="preserve">2a PASADA (resuelve DUDA -&gt; NO). La plataforma Senador Virtual / Congreso Virtual es un proceso participativo digital del Congreso de Chile (gobierno nacional) plenamente activo y consolidado (&gt;16 anios, &gt;130.000 participantes), pero la plataforma en si NO usa IA sobre el contenido de los aportes y </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://vinadecide.cl/pages/presupuestoparticipativo</t>
+          <t>https://goblab.uai.cl/en/16-years-of-crowdlaw-in-the-chilean-parliament/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Asamblea Ciudadana Itinerante del Concejo de Bogotá</t>
+          <t>Viña Decide — Primer Presupuesto Participativo de Viña del Mar (plataforma Go Vocal/CitizenLab)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Excluido (revisar)</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>El proceso es elegible en su forma (mini-publico deliberativo recurrente convocado por gobierno local: Concejo de Bogota via DemoLab; 3 ediciones 2020/2021/2023). Sin embargo, NO se encontro evidencia de uso de inteligencia artificial sobre el CONTENIDO de los aportes ciudadanos dentro del proceso p</t>
+          <t>Presupuesto participativo real sobre plataforma Go Vocal, pero no se encontró en el informe ejecutivo ninguna traza de uso de IA sobre los aportes (usa_IA_en_proceso 'no-claro', sin evidencia). Sin uso de IA verificado → NO. Decisión del equipo.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://concejodebogota.gov.co/llega-al-concejo-de-bogota-la-tercera-asamblea-ciudadana-que-busca/cbogota/2023-05-23/084537.php</t>
+          <t>https://vinadecide.cl/pages/presupuestoparticipativo</t>
         </is>
       </c>
     </row>
@@ -6468,22 +6312,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Atlántico – Plan de Ordenamiento Departamental (POD) 2025-2050 / plataforma LITA</t>
+          <t>Asamblea Ciudadana Itinerante del Concejo de Bogotá</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido (revisar)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>NO ELEGIBLE. Dentro de un proceso participativo real (POD con mesas/talleres subregionales), la IA (plataforma LITA / base de datos con IA) cumple funciones de ALMACENAMIENTO, PROCESAMIENTO y ESTRUCTURACIÓN de información técnica territorial y CRUCE de datos técnicos/geoespaciales de punta para actu</t>
+          <t>El proceso es elegible en su forma (mini-publico deliberativo recurrente convocado por gobierno local: Concejo de Bogota via DemoLab; 3 ediciones 2020/2021/2023). Sin embargo, NO se encontro evidencia de uso de inteligencia artificial sobre el CONTENIDO de los aportes ciudadanos dentro del proceso p</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.atlantico.gov.co/index.php/noticias/prensa-planeacion/27250-plan-de-ordenamiento-departamental-toma-forma-en-el-atlantico</t>
+          <t>https://concejodebogota.gov.co/llega-al-concejo-de-bogota-la-tercera-asamblea-ciudadana-que-busca/cbogota/2023-05-23/084537.php</t>
         </is>
       </c>
     </row>
@@ -6495,22 +6339,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Chatbot ALBA</t>
+          <t>Atlántico – Plan de Ordenamiento Departamental (POD) 2025-2050 / plataforma LITA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Descubrimiento</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>NO ELEGIBLE. Dentro de un proceso participativo real (POD con mesas/talleres subregionales), la IA (plataforma LITA / base de datos con IA) cumple funciones de ALMACENAMIENTO, PROCESAMIENTO y ESTRUCTURACIÓN de información técnica territorial y CRUCE de datos técnicos/geoespaciales de punta para actu</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://barranquilla.gov.co/chatbot</t>
+          <t>https://www.atlantico.gov.co/index.php/noticias/prensa-planeacion/27250-plan-de-ordenamiento-departamental-toma-forma-en-el-atlantico</t>
         </is>
       </c>
     </row>
@@ -6522,7 +6366,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Rama Judicial</t>
+          <t>Chatbot ALBA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -6537,7 +6381,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.ramajudicial.gov.co/web/centro-de-documentacion-judicial/nuevo-chatbot</t>
+          <t>https://barranquilla.gov.co/chatbot</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6393,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Rebecca</t>
+          <t>Chatbot Rama Judicial</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -6559,12 +6403,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Atención ciudadana</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://bogota.gov.co/mi-ciudad/habitat/bogota-tiene-chatbot-renobo-que-utiliza-inteligencia-artificial</t>
+          <t>https://www.ramajudicial.gov.co/web/centro-de-documentacion-judicial/nuevo-chatbot</t>
         </is>
       </c>
     </row>
@@ -6576,22 +6420,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>DNP - Diálogos Regionales Vinculantes (PND 2022-2026)</t>
+          <t>Chatbot Rebecca</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Participación real, pero el análisis fue manual/cualitativo; solo text-analytics ligero (nubes de palabras + tabulación), sin NLP sobre el contenido (verificado). Decisión del equipo.</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://dialogosregionales.dnp.gov.co/</t>
+          <t>https://bogota.gov.co/mi-ciudad/habitat/bogota-tiene-chatbot-renobo-que-utiliza-inteligencia-artificial</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6447,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Descongestión de solicitudes diarias del programa Ingreso Solidario</t>
+          <t>Citibeats + PNUD Colombia (analítica de datos para la deliberación pública juvenil)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -6613,12 +6457,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana (triage de 10.000 correos/día): servicio, no participación.</t>
+          <t>Escucha social de redes abiertas (Twitter/Facebook) durante el paro de 2021: no hay proceso participativo convocado (verificado). Misma regla que U-Report (solo opinión) → NO. Decisión del equipo.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/inteligencia-artificial-la-herramienta-que-descongestiono-10-000-solicitudes-diarias-de-ingreso-solidario/</t>
+          <t>https://www.undp.org/es/colombia/blog/analitica-de-datos-para-mejorar-la-deliberacion-publica-en-colombia</t>
         </is>
       </c>
     </row>
@@ -6630,22 +6474,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>IA para participación en el POT de Bogotá (Control Visible / Auditoría General)</t>
+          <t>DNP - Diálogos Regionales Vinculantes (PND 2022-2026)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Dudoso</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>NO ENTRA. El criterio de elegibilidad exige que dentro de un proceso participativo se DESPLIEGUE IA real (institucional) sobre el CONTENIDO de los aportes ciudadanos. El caso documentado es un ARTÍCULO ACADÉMICO (Fundación Universitaria del Área Andina, Maestría en Innovación; publicado en la revist</t>
+          <t>Participación real, pero el análisis fue manual/cualitativo; solo text-analytics ligero (nubes de palabras + tabulación), sin NLP sobre el contenido (verificado). Decisión del equipo.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://controlvisible.auditoria.gov.co/index.php/rcf/article/view/63</t>
+          <t>https://dialogosregionales.dnp.gov.co/</t>
         </is>
       </c>
     </row>
@@ -6657,22 +6501,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ISIDataInsights / Reto de Ciudad 'Datos con Historia' (SDP Bogotá)</t>
+          <t>Descongestión de solicitudes diarias del programa Ingreso Solidario</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>DUDA con inclinación NO (REAFIRMADA en 3ª pasada con búsqueda amplia, jul-2026). Por un lado, la herramienta ISIDataInsights está diseñada para operar sobre el CONTENIDO de información cualitativa de planeación, incluyendo explícitamente 'los aportes ciudadanos' (procesar, validar consistencia, apli</t>
+          <t>Atención ciudadana (triage de 10.000 correos/día): servicio, no participación.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.sdp.gov.co/noticias/bogota-cuenta-herramienta-innovadora-abordar-los-problemas-urbanos-aporte-de-la-ciudadania</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/inteligencia-artificial-la-herramienta-que-descongestiono-10-000-solicitudes-diarias-de-ingreso-solidario/</t>
         </is>
       </c>
     </row>
@@ -6684,22 +6528,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Mini-Public del diálogo social de la Procuraduría</t>
+          <t>IA para participación en el POT de Bogotá (Control Visible / Auditoría General)</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Excluido (revisar)</t>
+          <t>Dudoso</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se MANTIENE EXCLUIDO (entra=NO), confirmando el motivo de exclusión de 2025 ('No se encontró información sobre el uso de la IA en la implementación de los Mini Publics'). El proceso es ELEGIBLE por su naturaleza (mini-público / diálogo social deliberativo convocado por la Procuraduría General de la </t>
+          <t>NO ENTRA. El criterio de elegibilidad exige que dentro de un proceso participativo se DESPLIEGUE IA real (institucional) sobre el CONTENIDO de los aportes ciudadanos. El caso documentado es un ARTÍCULO ACADÉMICO (Fundación Universitaria del Área Andina, Maestría en Innovación; publicado en la revist</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://ideemos.org/mini-public-del-dialogo-social-de-la-procuraduria/</t>
+          <t>https://controlvisible.auditoria.gov.co/index.php/rcf/article/view/63</t>
         </is>
       </c>
     </row>
@@ -6711,22 +6555,22 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Pa' que veás (Cali)</t>
+          <t>ISIDataInsights / Reto de Ciudad 'Datos con Historia' (SDP Bogotá)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Excluido (revisar)</t>
+          <t>Nuevo</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se revisa por su analogia con dIAra (bots que recopilan quejas ciudadanas y predicen riesgos en obras). Sin embargo, NO se encontro evidencia de uso de inteligencia artificial sobre el CONTENIDO de los aportes/quejas ciudadanas dentro de un proceso participativo. 'Pa' que veas' es, en su nucleo, un </t>
+          <t>DUDA con inclinación NO (REAFIRMADA en 3ª pasada con búsqueda amplia, jul-2026). Por un lado, la herramienta ISIDataInsights está diseñada para operar sobre el CONTENIDO de información cualitativa de planeación, incluyendo explícitamente 'los aportes ciudadanos' (procesar, validar consistencia, apli</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.iadb.org/en/news/city-cali-launches-platform-monitoring-public-investment-idb-support</t>
+          <t>https://www.sdp.gov.co/noticias/bogota-cuenta-herramienta-innovadora-abordar-los-problemas-urbanos-aporte-de-la-ciudadania</t>
         </is>
       </c>
     </row>
@@ -6738,22 +6582,22 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Plataforma Urna de Cristal</t>
+          <t>Mini-Public del diálogo social de la Procuraduría</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (revisar)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA</t>
+          <t xml:space="preserve">Se MANTIENE EXCLUIDO (entra=NO), confirmando el motivo de exclusión de 2025 ('No se encontró información sobre el uso de la IA en la implementación de los Mini Publics'). El proceso es ELEGIBLE por su naturaleza (mini-público / diálogo social deliberativo convocado por la Procuraduría General de la </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://projects.itforchange.net/mavc/wp-content/uploads/2017/09/Voice-or-Chatter_Case-Study_Colombia_August-2017.pdf</t>
+          <t>https://ideemos.org/mini-public-del-dialogo-social-de-la-procuraduria/</t>
         </is>
       </c>
     </row>
@@ -6765,22 +6609,22 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SISBÉN IV</t>
+          <t>Pa' que veás (Cali)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (revisar)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t xml:space="preserve">Se revisa por su analogia con dIAra (bots que recopilan quejas ciudadanas y predicen riesgos en obras). Sin embargo, NO se encontro evidencia de uso de inteligencia artificial sobre el CONTENIDO de los aportes/quejas ciudadanas dentro de un proceso participativo. 'Pa' que veas' es, en su nucleo, un </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/sisben</t>
+          <t>https://www.iadb.org/en/news/city-cali-launches-platform-monitoring-public-investment-idb-support</t>
         </is>
       </c>
     </row>
@@ -6792,88 +6636,88 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>iLabs - Laboratorios de Inteligencia Colectiva (Ideemos)</t>
+          <t>Plataforma Urna de Cristal</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Excluido (revisar)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>MANTENER EXCLUIDO. La regla de reingreso exige evidencia de IA aplicada al CONTENIDO de los aportes ciudadanos dentro de un proceso participativo. La fuente primaria (página iLabs de Ideemos y su PDF) describe 'Inteligencia Artificial' y 'Machine Learning' SOLO como parte de un listado de técnicas c</t>
+          <t>No evidencia de uso de IA</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://ideemos.org/ilabs-laboratorios-de-inteligencia-colectiva/</t>
+          <t>https://projects.itforchange.net/mavc/wp-content/uploads/2017/09/Voice-or-Chatter_Case-Study_Colombia_August-2017.pdf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>U-Report Costa Rica – chatbot juvenil</t>
+          <t>SISBÉN IV</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>UNICEF lo define como 'encuestas de opinión' (panel de sondeo/percepción juvenil anónimo: clima, salud mental, educación); sin proceso participativo estructurado con incidencia concreta (verificado). Solo opinión → fuera. Decisión del equipo.</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://costarica.ureport.in/</t>
+          <t>https://fairlac.iadb.org/sisben</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>dIAra</t>
+          <t>iLabs - Laboratorios de Inteligencia Colectiva (Ideemos)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido (revisar)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Civic tech de fiscalización de obras (control social vía app): no es un proceso participativo.</t>
+          <t>MANTENER EXCLUIDO. La regla de reingreso exige evidencia de IA aplicada al CONTENIDO de los aportes ciudadanos dentro de un proceso participativo. La fuente primaria (página iLabs de Ideemos y su PDF) describe 'Inteligencia Artificial' y 'Machine Learning' SOLO como parte de un listado de técnicas c</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.opengovpartnership.org/the-open-gov-challenge/costa-rica-artificial-intelligence-alerts-citizen-control-public-infrastructure/</t>
+          <t>https://ideemos.org/ilabs-laboratorios-de-inteligencia-colectiva/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CiudadanIA</t>
+          <t>U-Report Costa Rica – chatbot juvenil</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -6883,39 +6727,39 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Solo atención/servicio; la 'participación' es co-diseñar la IA aportando datos, no consulta pública. Sin módulo de participación (verificado). Decisión del equipo.</t>
+          <t>UNICEF lo define como 'encuestas de opinión' (panel de sondeo/percepción juvenil anónimo: clima, salud mental, educación); sin proceso participativo estructurado con incidencia concreta (verificado). Solo opinión → fuera. Decisión del equipo.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.genia.ai/paises-miembros</t>
+          <t>https://costarica.ureport.in/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>dIAra</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Civic tech de fiscalización de obras (control social vía app): no es un proceso participativo.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/guatemala/comunicados-de-prensa/sara-la-nueva-herramienta-de-inteligencia-artificial-para-combatir-la-violencia-de-genero-en-centroamerica</t>
+          <t>https://www.opengovpartnership.org/the-open-gov-challenge/costa-rica-artificial-intelligence-alerts-citizen-control-public-infrastructure/</t>
         </is>
       </c>
     </row>
@@ -6927,61 +6771,61 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>TAÍNA: Gobierno Inteligente</t>
+          <t>CiudadanIA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>Solo atención/servicio; la 'participación' es co-diseñar la IA aportando datos, no consulta pública. Sin módulo de participación (verificado). Decisión del equipo.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.diariolibre.com/actualidad/nacional/2023/10/11/gobierno-presenta-estrategia-de-inteligencia-artificial/2489157</t>
+          <t>https://www.genia.ai/paises-miembros</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Plataforma de modelos generativos de IA de SEGEPLAN + Red Ciudadana (Guatemala)</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>El criterio ELEGIBLE exige que la IA generativa se use para SISTEMATIZAR/CLASIFICAR/RESUMIR el CONTENIDO de los aportes de los diagnosticos participativos (Consejos de Desarrollo COCODES/COMUDES) en los Planes de Desarrollo Municipal (PDM). Toda la evidencia primaria y secundaria (nota SEGEPLAN ?p=1</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://portal.segeplan.gob.gt/segeplan/?p=14176</t>
+          <t>https://www.undp.org/es/guatemala/comunicados-de-prensa/sara-la-nueva-herramienta-de-inteligencia-artificial-para-combatir-la-violencia-de-genero-en-centroamerica</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LATAM</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ANTAI Smart CID (Autoridad Nacional de Transparencia y Acceso a la Información + OS City)</t>
+          <t>TAÍNA: Gobierno Inteligente</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -6991,39 +6835,39 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Atención ciudadana</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.caf.com/es/actualidad/noticias/2021/07/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
+          <t>https://www.diariolibre.com/actualidad/nacional/2023/10/11/gobierno-presenta-estrategia-de-inteligencia-artificial/2489157</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LATAM</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Botivist</t>
+          <t>Plataforma de modelos generativos de IA de SEGEPLAN + Red Ciudadana (Guatemala)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Descubrimiento</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>No tiene foco en un país específico</t>
+          <t>El criterio ELEGIBLE exige que la IA generativa se use para SISTEMATIZAR/CLASIFICAR/RESUMIR el CONTENIDO de los aportes de los diagnosticos participativos (Consejos de Desarrollo COCODES/COMUDES) en los Planes de Desarrollo Municipal (PDM). Toda la evidencia primaria y secundaria (nota SEGEPLAN ?p=1</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/research/publication/botivist-calling-volunteers-to-action-using-online-bots/</t>
+          <t>https://portal.segeplan.gob.gt/segeplan/?p=14176</t>
         </is>
       </c>
     </row>
@@ -7035,7 +6879,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Chatbot DCI (Denuncia Ciudadana Idónea)</t>
+          <t>ANTAI Smart CID (Autoridad Nacional de Transparencia y Acceso a la Información + OS City)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -7045,12 +6889,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci-1</t>
+          <t>https://www.caf.com/es/actualidad/noticias/2021/07/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
         </is>
       </c>
     </row>
@@ -7062,7 +6906,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Citibeats: Covid-19 (“Percepciones ciudadanas COVID-19”)</t>
+          <t>Botivist</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -7072,12 +6916,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Análisis de redes sociales, no es participación</t>
+          <t>No tiene foco en un país específico</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://forbescentroamerica.com/2021/04/28/civiclytics-el-big-data-apoya-la-recuperacion-economica</t>
+          <t>https://www.microsoft.com/en-us/research/publication/botivist-calling-volunteers-to-action-using-online-bots/</t>
         </is>
       </c>
     </row>
@@ -7089,7 +6933,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Ushahidi "AI for Good"</t>
+          <t>Chatbot DCI (Denuncia Ciudadana Idónea)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -7099,24 +6943,24 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>No se evidencia el uso de IA en los proyectos de participación listados para Latam</t>
+          <t>No evidencia de uso de IA</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.ushahidi.com/</t>
+          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci-1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>LATAM</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>AMIMgo</t>
+          <t>Citibeats: Covid-19 (“Percepciones ciudadanas COVID-19”)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -7126,24 +6970,24 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Análisis de redes sociales, no es participación</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://amim.mx/noticias/detalle/estrena-amim-chatbot-para-la-atencion-ciudadana</t>
+          <t>https://forbescentroamerica.com/2021/04/28/civiclytics-el-big-data-apoya-la-recuperacion-economica</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>LATAM</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>ATIC</t>
+          <t>Ushahidi "AI for Good"</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -7153,12 +6997,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No se evidencia el uso de IA en los proyectos de participación listados para Latam</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://oem.com.mx/la-prensa/metropoli/info-cdmx-implementa-atic-una-herramienta-con-ia-que-facilita-el-acceso-a-la-informacion-13081722</t>
+          <t>https://www.ushahidi.com/</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7014,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>ChatBot “Claudia"</t>
+          <t>AMIMgo</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -7180,12 +7024,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>No es participación</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://mexicocomovamos.mx/animal-politico/2024/08/chatbot-claudia-una-herramienta-de-participacion-ciudadana/</t>
+          <t>https://amim.mx/noticias/detalle/estrena-amim-chatbot-para-la-atencion-ciudadana</t>
         </is>
       </c>
     </row>
@@ -7197,7 +7041,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Chatbot "Inés"</t>
+          <t>ATIC</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -7207,12 +7051,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>No es participación, es informativo</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://centralelectoral.ine.mx/2024/04/17/nueva-version-del-chatbot-del-ine-en-whatsapp-permitira-verificar-informacion-sobre-elecciones-2024/</t>
+          <t>https://oem.com.mx/la-prensa/metropoli/info-cdmx-implementa-atic-una-herramienta-con-ia-que-facilita-el-acceso-a-la-informacion-13081722</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7068,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Sam Petrino</t>
+          <t>ChatBot “Claudia"</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -7234,12 +7078,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No es participación</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.civica.digital/historias/chatbot-sam-petrino</t>
+          <t>https://mexicocomovamos.mx/animal-politico/2024/08/chatbot-claudia-una-herramienta-de-participacion-ciudadana/</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7095,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Victoria</t>
+          <t>Chatbot "Inés"</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -7261,12 +7105,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>No es participación, es informativo</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://adip.cdmx.gob.mx/comunicacion/nota/la-adip-y-el-gobierno-de-la-ciudad-presentan-victoria-el-robot-que-colaborara-en-la-atencion-de-la-ciudadania</t>
+          <t>https://centralelectoral.ine.mx/2024/04/17/nueva-version-del-chatbot-del-ine-en-whatsapp-permitira-verificar-informacion-sobre-elecciones-2024/</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7122,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>INAOE (Conacyt) – Laboratorio de Tecnologías del Lenguaje</t>
+          <t>Chatbot Sam Petrino</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -7288,12 +7132,12 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
+          <t>https://www.civica.digital/historias/chatbot-sam-petrino</t>
         </is>
       </c>
     </row>
@@ -7305,22 +7149,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Jalisco - Consulta ¡Armemos un Plan! (Plan Estatal de Desarrollo y Gobernanza 2024-2030)</t>
+          <t>Chatbot Victoria</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Proceso participativo real y masivo (675.484 participaciones; 15.899 propuestas), pero NO hay evidencia de uso de IA para analizar/agrupar/clasificar el contenido de las propuestas (usa_IA_en_proceso 'no'). Sin uso de IA → NO. Decisión del equipo.</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://armemosunplan.mx/propuestas-ciudadanas/</t>
+          <t>https://adip.cdmx.gob.mx/comunicacion/nota/la-adip-y-el-gobierno-de-la-ciudad-presentan-victoria-el-robot-que-colaborara-en-la-atencion-de-la-ciudadania</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7176,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Movimex</t>
+          <t>INAOE (Conacyt) – Laboratorio de Tecnologías del Lenguaje</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -7347,7 +7191,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://animalpolitico.com/estados/chatbot-movimex-tramites-denuncias-edomex</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
     </row>
@@ -7359,22 +7203,22 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Sistema *0311 Locatel</t>
+          <t>Jalisco - Consulta ¡Armemos un Plan! (Plan Estatal de Desarrollo y Gobernanza 2024-2030)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana</t>
+          <t>Proceso participativo real y masivo (675.484 participaciones; 15.899 propuestas), pero NO hay evidencia de uso de IA para analizar/agrupar/clasificar el contenido de las propuestas (usa_IA_en_proceso 'no'). Sin uso de IA → NO. Decisión del equipo.</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://research.latinxinai.org/papers/naacl/2022/pdf/paper_01.pdf</t>
+          <t>https://armemosunplan.mx/propuestas-ciudadanas/</t>
         </is>
       </c>
     </row>
@@ -7386,22 +7230,22 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Sufragio seguro</t>
+          <t>Movimex</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Baseline 2025</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>EXCLUSIÓN FIRME (recodificación 2026): Exclusión FIRME (recodificación 2026): integridad/proceso electoral, no contenido</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://algoritmoscide.org/proyectos/sufragio-seguro/</t>
+          <t>https://animalpolitico.com/estados/chatbot-movimex-tramites-denuncias-edomex</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7257,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Violetta</t>
+          <t>Sistema *0311 Locatel</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -7423,51 +7267,51 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>Atención ciudadana</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://holasoyvioletta.com/acerca-de/</t>
+          <t>https://research.latinxinai.org/papers/naacl/2022/pdf/paper_01.pdf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Dr. ROSA y Dr. NICO</t>
+          <t>Sufragio seguro</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Baseline 2025</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>EXCLUSIÓN FIRME (recodificación 2026): Exclusión FIRME (recodificación 2026): integridad/proceso electoral, no contenido</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
+          <t>https://algoritmoscide.org/proyectos/sufragio-seguro/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>JNE WhatsApp Chatbot</t>
+          <t>Violetta</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -7477,132 +7321,132 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://portal.jne.gob.pe/Portal/Pagina/Nota/12783</t>
+          <t>https://holasoyvioletta.com/acerca-de/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Sistema de cómputo con IA para las Elecciones Generales 2026</t>
+          <t>Dr. ROSA y Dr. NICO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Excluido (criterio corregido)</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Conteo electoral (OCR de actas): votación política, no participación.</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-onpe-utilizara-un-nuevo-sistema-computo-resultados-incorporara-ia-1021072.aspx</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>PY</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Consultas ciudadanas sobre IA en Paraguay - PNUD Accelerator Lab (AccLab) + Columbia SIPA + MITIC / insumo del diagnóstico AILA (Atlas de IA)</t>
+          <t>JNE WhatsApp Chatbot</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>El criterio ELEGIBLE exige que dentro de un proceso participativo convocado se use IA (NLP/ML/clustering/sentimiento) SOBRE EL CONTENIDO de los aportes. Aquí ocurre lo contrario: (1) la IA es el TEMA de la consulta (se pregunta a la ciudadania por su percepcion de la IA), y (2) el ANÁLISIS de los ap</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/paraguay/blog/consultas-ciudadanas-sobre-ia-en-paraguay-visiones-diversas-entre-el-campo-y-la-ciudad</t>
+          <t>https://portal.jne.gob.pe/Portal/Pagina/Nota/12783</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>PY</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>ParaEmpleo</t>
+          <t>Sistema de cómputo con IA para las Elecciones Generales 2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Excluido (criterio corregido)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana</t>
+          <t>Conteo electoral (OCR de actas): votación política, no participación.</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/en/paraempleo</t>
+          <t>https://andina.pe/agencia/noticia-onpe-utilizara-un-nuevo-sistema-computo-resultados-incorporara-ia-1021072.aspx</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>UY</t>
+          <t>PY</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Chatbot (Asistente virtual entrenado con IA)</t>
+          <t>Consultas ciudadanas sobre IA en Paraguay - PNUD Accelerator Lab (AccLab) + Columbia SIPA + MITIC / insumo del diagnóstico AILA (Atlas de IA)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Excluido 2025</t>
+          <t>Descubrimiento</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana</t>
+          <t>El criterio ELEGIBLE exige que dentro de un proceso participativo convocado se use IA (NLP/ML/clustering/sentimiento) SOBRE EL CONTENIDO de los aportes. Aquí ocurre lo contrario: (1) la IA es el TEMA de la consulta (se pregunta a la ciudadania por su percepcion de la IA), y (2) el ANÁLISIS de los ap</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
+          <t>https://www.undp.org/es/paraguay/blog/consultas-ciudadanas-sobre-ia-en-paraguay-visiones-diversas-entre-el-campo-y-la-ciudad</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>UY</t>
+          <t>PY</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Consulta Pública de la Estrategia Nacional de Inteligencia Artificial (IA) de Uruguay 2024–2030,</t>
+          <t>ParaEmpleo</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -7612,12 +7456,12 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA</t>
+          <t>No es participación ciudadana</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030</t>
+          <t>https://fairlac.iadb.org/en/paraempleo</t>
         </is>
       </c>
     </row>
@@ -7629,54 +7473,108 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Consulta Pública y Participación Multiactores: "Niñas, niños, adolescentes, entornos digitales e inteligencia artificial" (Uruguay, 2026)</t>
+          <t>Chatbot (Asistente virtual entrenado con IA)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Descubrimiento</t>
+          <t>Excluido 2025</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>NO (lean firme). (1) TEMPORAL: la consulta está ABIERTA hasta el 10/09/2026 y la fase de sistematización/análisis/validación (Fase 3) recién ocurre entre el 10/09 y el 10/10/2026, con informe final el 30/11/2026. A la fecha de evaluación (2026-07-01) la fase de análisis NO se ha ejecutado, por lo qu</t>
+          <t>Atencion ciudadana</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.gub.uy/ministerio-educacion-cultura/comunicacion/noticias/lanzamiento-consulta-publica-sobre-inteligencia-artificial-entornos-digitales</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>UY</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Consulta Pública de la Estrategia Nacional de Inteligencia Artificial (IA) de Uruguay 2024–2030,</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Excluido 2025</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>No evidencia de uso de IA</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>UY</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Consulta Pública y Participación Multiactores: "Niñas, niños, adolescentes, entornos digitales e inteligencia artificial" (Uruguay, 2026)</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Descubrimiento</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>NO (lean firme). (1) TEMPORAL: la consulta está ABIERTA hasta el 10/09/2026 y la fase de sistematización/análisis/validación (Fase 3) recién ocurre entre el 10/09 y el 10/10/2026, con informe final el 30/11/2026. A la fecha de evaluación (2026-07-01) la fase de análisis NO se ha ejecutado, por lo qu</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gub.uy/ministerio-educacion-cultura/comunicacion/noticias/lanzamiento-consulta-publica-sobre-inteligencia-artificial-entornos-digitales</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
           <t>VE</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Plan de la Patria 7 Transformaciones (7T) - IA y Big Data en la sistematización de propuestas de la Consulta Popular</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>Dudoso</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>NO (resuelto en 2ª pasada, antes DUDA). Hay un proceso participativo claro (consulta/debate nacional para construir el Plan de la Patria 7T, con +63.000 asambleas, 3,4 M de participantes y 34.491 propuestas) cuyo CONTENIDO sí fue recolectado, cargado, sistematizado y agrupado. Pero la 2ª pasada CONF</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>http://www.correodelorinoco.gob.ve/venezuela-impulsa-el-debate-sobre-inteligencia-artificial-bajo-principios-de-soberania-y-etica/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E73"/>
+  <autoFilter ref="A1:E75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7687,7 +7585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8036,7 +7934,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Cátedra Brasil / Co:Lab USP - IA generativa en presupuesto participativo (SP)</t>
+          <t>OPA Piauí - Orçamento Participativo Digital (Colab + AWS)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -8046,87 +7944,25 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Co:Lab / Colaboratório de Desenvolvimento e Participação (COLAB-USP) opera na USP Leste (EACH-USP), São Paulo, Brasil. (Localización institucional confirmada por colab.each.usp.br; no cita textual exacta recuperable por bloqueo 403 de la página.)</t>
+          <t>OPA é o Orçamento Participativo 100% digital do Governo do Estado do Piauí, em parceria com a Colab. (Colab, 'OPA, Colab e a participação digital no Piauí')</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>No projeto da Cátedra Brasil, há o orçamento participativo da cidade em que cidadãos podem dar sugestões sobre o orçamento público com auxílio da inteligência artificial. (snippet de búsqueda sobre jornal.usp.br / Cátedra Brasil)</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>um cidadão pode propor uma rede de ciclovias na zona leste de São Paulo e a IA o ajuda a escrever essa proposta, fazendo perguntas sobre seus objetivos. (snippet de búsqueda; describe el apoyo de IA en la fase de generación/redacción de la propuesta)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>A IA Generativa e o Futuro da Participação Cidadã: Pesquisas em Andamento (título del post Co:Lab, 2025-03-28; 'pesquisas em andamento' = investigación en curso)</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Co:Lab USP has a research project titled 'A IA Generativa e o Futuro da Participação Cidadã: Pesquisas em Andamento' ... updated as of March 28, 2025. (snippet; encuadra como proyecto de investigación, sin ediciones recurrentes ni despliegue)</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>José Carlos Vaz, from the USP Public Policy Management course / professor at the University of São Paulo's School of Arts, Sciences and Humanities (EACH) ... coordinates GETIP. (snippet; convocante = universidad USP)</t>
-        </is>
-      </c>
+          <t>OPA é o Orçamento Participativo 100% digital do Governo do Estado do Piauí... Após analisar a viabilidade das propostas, o Governo do Estado disponibilizará uma votação por meio da Colab para que qualquer cidadão acima de 16 anos com CPF possa votar no que considera mais importante para o seu município. (Colab)</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr"/>
+      <c r="G6" s="11" t="inlineStr"/>
+      <c r="H6" s="11" t="inlineStr"/>
+      <c r="I6" s="11" t="inlineStr"/>
       <c r="J6" s="11" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>AI could help generate proposals based on knowledge databases and transform them into legally viable drafts / a IA o ajuda a escrever essa proposta. (snippet; rol sobre el contenido del aporte, pero en marco de investigación)</t>
+          <t>Todo esse processo é realizado por meio da plataforma Colab Gov... O sistema utiliza tecnologia da AWS, referência mundial em segurança digital. (la IA/tecnología se presenta como soporte operativo, de eficiencia y de seguridad del flujo, no como análisis del contenido de las propuestas → rol de apoyo)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>https://colab.each.usp.br/blog/2025/03/28/a-ia-generativa-e-o-futuro-da-participacao-cidada-pesquisas-em-andamento/
-https://jornal.usp.br/radio-usp/ia-tem-potencial-para-ampliar-participacao-politica-online-e-auxiliar-gestores-em-decisoes/
-https://scope.uni-muenster.de/wp-content/uploads/2025/01/PT-BR-Policy-Brief-AI_Jan2025.pdf
-https://colab.each.usp.br/projetos-em-andamento-2/
-https://participemais.prefeitura.sp.gov.br/budgets</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>OPA Piauí - Orçamento Participativo Digital (Colab + AWS)</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>OPA é o Orçamento Participativo 100% digital do Governo do Estado do Piauí, em parceria com a Colab. (Colab, 'OPA, Colab e a participação digital no Piauí')</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>OPA é o Orçamento Participativo 100% digital do Governo do Estado do Piauí... Após analisar a viabilidade das propostas, o Governo do Estado disponibilizará uma votação por meio da Colab para que qualquer cidadão acima de 16 anos com CPF possa votar no que considera mais importante para o seu município. (Colab)</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr"/>
-      <c r="G7" s="11" t="inlineStr"/>
-      <c r="H7" s="11" t="inlineStr"/>
-      <c r="I7" s="11" t="inlineStr"/>
-      <c r="J7" s="11" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Todo esse processo é realizado por meio da plataforma Colab Gov... O sistema utiliza tecnologia da AWS, referência mundial em segurança digital. (la IA/tecnología se presenta como soporte operativo, de eficiencia y de seguridad del flujo, no como análisis del contenido de las propuestas → rol de apoyo)</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/
 https://sia.pi.gov.br/projetos/opa/
@@ -8140,6 +7976,68 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Plan Plurianual de la ciudad de Natal</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Governanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Implementación, Análisis</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>reconfirmado web (institucional): Reconfirmado: modelos de lenguaje identifican el tema de cada mensaje ciudadano por WhatsApp; nueva edición PPA 2026-2029 'Plano Natal Pra Frente'.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Plataforma</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Prefeitura Municipal de Natal, a través de la Secretaría Municipal de Planeamiento (SEMPLA)</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
@@ -8148,7 +8046,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Plan Plurianual de la ciudad de Natal</t>
+          <t>Portal e-Cidadania: Marcado automático de respuestas ciudadanas en videos de audiencias públicas</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -8168,12 +8066,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Implementación, Análisis</t>
+          <t>Traducción Política</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>reconfirmado web (institucional): Reconfirmado: modelos de lenguaje identifican el tema de cada mensaje ciudadano por WhatsApp; nueva edición PPA 2026-2029 'Plano Natal Pra Frente'.</t>
+          <t>reconfirmado web (institucional): Reconfirmado 2025: la IA analiza transcripciones de 1.800+ audiencias y marca 2.700+ preguntas ciudadanas como respondidas.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -8183,22 +8081,23 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Prefeitura Municipal de Natal, a través de la Secretaría Municipal de Planeamiento (SEMPLA)</t>
+          <t>Senado Federal de Brasil</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas</t>
+          <t>Identificar y marcar momentos en los videos donde las preguntas ciudadanas fueron respondidas, ya sea directa o indirectamente.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas</t>
+          <t>Identificar y marcar momentos en los videos donde las preguntas ciudadanas fueron respondidas, ya sea directa o indirectamente.</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
+          <t>https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias
+https://ipen-network.org/spotlight-on-public-engagement-practice-brazil/</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8109,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Portal e-Cidadania: Marcado automático de respuestas ciudadanas en videos de audiencias públicas</t>
+          <t>São Paulo - Programa de Metas / Participe Mais (Gemini)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -8220,108 +8119,45 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+          <t>Programa de Metas 2025-2028, PPA e PAS 2026-2029 - portal Participe Mais da Prefeitura de São Paulo (participemais.prefeitura.sp.gov.br/legislation/processes/323).</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Governanza Colaborativa</t>
+          <t>as sugestões enviadas pela população para o PPA (Plano Plurianual) 2026-2029, durante a consulta pública do Programa de Metas no portal Participe Mais, que é a plataforma de participação social da Prefeitura</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Traducción Política</t>
+          <t>Em maio de 2025, foi elaborada uma ferramenta que classifica as propostas para o Programa de Metas em categorias e as ordena por assunto e quantidade de apoios, facilitando a divulgação das propostas. (...) exibição dos relatórios e painéis visuais gerados pela análise destacam: ranking dos temas mais recorrentes; participação em cada distrito e subprefeitura</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>reconfirmado web (institucional): Reconfirmado 2025: la IA analiza transcripciones de 1.800+ audiencias y marca 2.700+ preguntas ciudadanas como respondidas.</t>
+          <t>Após o Ciclo Participativo, com 36 audiências públicas híbridas pela cidade (abril e maio), recebimento de 6.368 propostas e mais de 31 mil interações dos cidadãos (...) através do site de consultas públicas da Prefeitura - ParticipeMais, a gestão incorporou seis metas a mais à versão inicial de 126</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Continuidad (BBDD 2025): Plataforma</t>
+          <t>Em maio de 2025, foi elaborada uma ferramenta que classifica as propostas para o Programa de Metas em categorias e as ordena por assunto e quantidade de apoios (...) No desenvolvimento da ferramenta foram utilizados conhecimentos em dados abertos, inteligência artificial e gestão pública.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Senado Federal de Brasil</t>
+          <t>através do site de consultas públicas da Prefeitura - ParticipeMais, a gestão incorporou seis metas a mais à versão inicial de 126</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Identificar y marcar momentos en los videos donde las preguntas ciudadanas fueron respondidas, ya sea directa o indirectamente.</t>
+          <t>A metodologia demonstra a solução com exposição de trechos de código e explicação das tecnologias utilizadas: Python, Pandas, Google Gemini. (...) desafios reais encontrados, como o alto volume de dados, otimização do tempo de análise e ajustes necessários nos comandos para a Inteligência Artificial</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Identificar y marcar momentos en los videos donde las preguntas ciudadanas fueron respondidas, ya sea directa o indirectamente.</t>
+          <t>uma ferramenta que classifica as propostas para o Programa de Metas em categorias e as ordena por assunto e quantidade de apoios</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias
-https://ipen-network.org/spotlight-on-public-engagement-practice-brazil/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>São Paulo - Programa de Metas / Participe Mais (Gemini)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Programa de Metas 2025-2028, PPA e PAS 2026-2029 - portal Participe Mais da Prefeitura de São Paulo (participemais.prefeitura.sp.gov.br/legislation/processes/323).</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>as sugestões enviadas pela população para o PPA (Plano Plurianual) 2026-2029, durante a consulta pública do Programa de Metas no portal Participe Mais, que é a plataforma de participação social da Prefeitura</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Em maio de 2025, foi elaborada uma ferramenta que classifica as propostas para o Programa de Metas em categorias e as ordena por assunto e quantidade de apoios, facilitando a divulgação das propostas. (...) exibição dos relatórios e painéis visuais gerados pela análise destacam: ranking dos temas mais recorrentes; participação em cada distrito e subprefeitura</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Após o Ciclo Participativo, com 36 audiências públicas híbridas pela cidade (abril e maio), recebimento de 6.368 propostas e mais de 31 mil interações dos cidadãos (...) através do site de consultas públicas da Prefeitura - ParticipeMais, a gestão incorporou seis metas a mais à versão inicial de 126</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Em maio de 2025, foi elaborada uma ferramenta que classifica as propostas para o Programa de Metas em categorias e as ordena por assunto e quantidade de apoios (...) No desenvolvimento da ferramenta foram utilizados conhecimentos em dados abertos, inteligência artificial e gestão pública.</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>através do site de consultas públicas da Prefeitura - ParticipeMais, a gestão incorporou seis metas a mais à versão inicial de 126</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>A metodologia demonstra a solução com exposição de trechos de código e explicação das tecnologias utilizadas: Python, Pandas, Google Gemini. (...) desafios reais encontrados, como o alto volume de dados, otimização do tempo de análise e ajustes necessários nos comandos para a Inteligência Artificial</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>uma ferramenta que classifica as propostas para o Programa de Metas em categorias e as ordena por assunto e quantidade de apoios</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>https://www.saopaulo.sp.leg.br/escoladoparlamento/cursos/em-andamento/oficina-analise-de-dados-com-inteligencia-artificial-na-gestao-publica-programa-de-metas/
 https://www.saopaulo.sp.leg.br/escoladoparlamento/cursos/cursos-anteriores/cursos-realizados-em-2025/oficina-analise-de-dados-com-inteligencia-artificial-na-gestao-publica-programa-de-metas/
@@ -8337,63 +8173,63 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>e-Cidadania Senado - IA matching de ideas legislativas</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Cidadãos ajudam a escrever projetos de lei com ferramenta de inteligência artificial — Senado Notícias (Senado Federal, Brasil), 16/01/2026.</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>uma nova ferramenta de inteligência artificial criada pelo Senado permite que ideias enviadas ao portal e-Cidadania influenciem projetos de lei — mesmo quando não atingem o número mínimo de apoios antes exigido</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Com o uso da inteligência artificial, é feita uma busca no banco de ideias legislativas e, então, são selecionadas aquelas que são compatíveis com a proposta em questão. As ideias selecionadas podem ser incorporadas ao projeto e citadas em sua justificação</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>IA vai aproximar ideias legislativas do e-Cidadania a projetos de senadores — Rádio Senado, 15/01/2026 (matéria de divulgação da ferramenta em uso no início de 2026)</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>O primeiro resultado já veio: uma sugestão enviada por Cândida Magalhães, de São Paulo, que pedia atendimento psicológico gratuito para filhos de mulheres vítimas de violência doméstica, foi identificada pela ferramenta e incorporada a um projeto de lei: o PL 6.125/2025</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>uma nova ferramenta de inteligência artificial criada pelo Senado</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Quando um senador pede ajuda à Consultoria Legislativa para elaborar um projeto, a equipe de consultores solicita ao e-Cidadania uma lista de sugestões feitas pelos cidadãos. Com o uso da inteligência artificial, é feita uma busca no banco de ideias legislativas</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Com o uso da inteligência artificial, é feita uma busca no banco de ideias legislativas e, então, são selecionadas aquelas que são compatíveis com a proposta em questão</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial
 https://www.poder360.com.br/poder-congresso/ia-do-senado-usa-sugestoes-enviadas-por-cidadaos-em-projetos-de-lei/
@@ -8405,63 +8241,63 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Cabildos 2016</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (academico): Evidencia académica del NLP sobre los cabildos 2016: argument mining sobre 240.468 argumentos (ACL 2017, UChile/DCC) y Structural Topic Modeling (PLOS One 2022)</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Biblioteca del Congreso Nacional</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Clasificación y análisis de texto para identificar conceptos clave</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Clasificación y análisis de texto para identificar conceptos clave</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>https://www.bcn.cl/procesoconstituyente/cabildos2016/
 https://aclanthology.org/W17-5101/
@@ -8469,63 +8305,63 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>El Chile que Queremos (ECQQ) - MinCiencia</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>El Chile que Queremos cierra etapa de diálogos con más de 130 mil participantes en las 345 comunas del país (titular de noticia del Ministerio de Desarrollo Social y Familia - Gobierno de Chile).</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>El Gobierno presentó la iniciativa el viernes 22 de noviembre de 2019. La participación fue posible hasta el 31 de marzo a través de diálogos ciudadanos o consultas individuales en www.chilequequeremos.cl (gob.cl).</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Este repositorio contiene los procedimientos para realizar la clasificación de las contribuciones con redes neuronales (README del repositorio MinCiencia/ECQQ, carpeta contributions_rnn).</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>130.810 personas participaron en los Diálogos Ciudadanos impulsados por El Chile Que Queremos, desde noviembre de 2019 hasta marzo de 2020. La decisión de concluir anticipadamente los diálogos ciudadanos fue parte de las medidas del gobierno para frenar la propagación del COVID-19, aunque la plataforma permaneció abierta hasta el 31 de marzo de 2020.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>130.810 personas participaron en los Diálogos Ciudadanos impulsados por El Chile Que Queremos, desde noviembre de 2019 hasta marzo de 2020 (proceso único, una sola edición).</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>El Gobierno presentó 'El Chile que Queremos', iniciativa de diálogos y escucha social para avanzar en nuevas propuestas para el país. La iniciativa fue un esfuerzo conjunto entre los Ministerios de Desarrollo Social y Familia, de Ciencia, Tecnología, Conocimiento e Innovación, de Agricultura, la Secretaría General de Gobierno y la División de Gobierno Digital (gob.cl / desarrollosocialyfamilia.gob.cl).</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>La información recibida de la ciudadanía es sistematizada por el Ministerio de Ciencias, siendo la ciencia de datos una herramienta clave para este amplio y participativo ejercicio de escucha. / clasificación de las contribuciones con árboles de decisión (README MinCiencia/ECQQ).</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Grouping Emotions.ipynb que sirve para sistematizar las Emociones / Analisis de Topicos - Necesidades.ipynb que sirve para sistematizar tanto las necesidades personales como las del país (README MinCiencia/ECQQ).</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>https://github.com/MinCiencia/ECQQ
 https://www.desarrollosocialyfamilia.gob.cl/noticias/el-chile-que-queremos-cierra-etapa-de-dialogos-con-mas-de-130-mil-participantes-en-las-345-comunas-d
@@ -8537,6 +8373,69 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Governanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>BBDD 2025: Cerrado</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Secretaría de Gobierno Digital</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Identificar patrones, sintetizar las principales críticas y estructurar las conclusiones de manera clara y coherente de datos cualitativos en encuesta de consulta ciudadana</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Identificar patrones, sintetizar las principales críticas y estructurar las conclusiones de manera clara y coherente de datos cualitativos en encuesta de consulta ciudadana</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030
+https://participacion.digital.gob.cl/folders/consultas-ciudadanas</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -8545,7 +8444,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
+          <t>Estudio dIAlogos - Percepciones de Futuro</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -8565,7 +8464,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación, Análisis</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8580,23 +8479,23 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Secretaría de Gobierno Digital</t>
+          <t>Fundación Encuentros del Futuro y Merlín Research</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Identificar patrones, sintetizar las principales críticas y estructurar las conclusiones de manera clara y coherente de datos cualitativos en encuesta de consulta ciudadana</t>
+          <t>Realización de entrevistas y codificación de respuestas</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Identificar patrones, sintetizar las principales críticas y estructurar las conclusiones de manera clara y coherente de datos cualitativos en encuesta de consulta ciudadana</t>
+          <t>Realización de entrevistas y codificación de respuestas</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030
-https://participacion.digital.gob.cl/folders/consultas-ciudadanas</t>
+          <t>https://estudiodialogos.cl/
+https://fairlac.iadb.org/en/dialogos-study-perceptions-future</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8507,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Estudio dIAlogos - Percepciones de Futuro</t>
+          <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -8628,7 +8527,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Implementación, Análisis</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8643,23 +8542,23 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Fundación Encuentros del Futuro y Merlín Research</t>
+          <t>Universidad Andres Bello</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Realización de entrevistas y codificación de respuestas</t>
+          <t>Identificar tópicos y organizarlos demográficamente para generar visualizaciones</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Realización de entrevistas y codificación de respuestas</t>
+          <t>Identificar tópicos y organizarlos demográficamente para generar visualizaciones</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://estudiodialogos.cl/
-https://fairlac.iadb.org/en/dialogos-study-perceptions-future</t>
+          <t>https://ipp.unab.cl/
+https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
         </is>
       </c>
     </row>
@@ -8671,7 +8570,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
+          <t>LXS 400 - Chile Delibera</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -8681,104 +8580,41 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+          <t>In 2020, the Senate of Chile partnered with the Stanford Center for Deliberative Democracy to involve citizens in the online deliberative process 'LXS 400 - Chile Delibera' performed through the Stanford Online Deliberation Platform. (OCDE 2025, 'AI in civic participation and open government')</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Governanza Colaborativa</t>
+          <t>Over 500 citizens representative of the Chilean society discussed in small groups and deliberated in plenary sessions on health and pension reforms. (OCDE 2025) / Entre el 5 y el 7 de marzo, 400 personas seleccionadas a traves de una metodologia aleatoria y representativas de todo Chile se reunieron para deliberar sobre dos de los temas publicos mas importantes para el pais: pensiones y salud.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>BBDD 2025: Cerrado</t>
-        </is>
-      </c>
+          <t>The platform used an AI tool to keep time and distribute speaking rights equitably, allowing participants to form speaking queues and discuss in small groups with timed agendas. (OCDE 2025) / El Centro de Microdatos de la Universidad de Chile, usando tecnologia basada en Inteligencia Artificial (IA), selecciono esta muestra representativa.</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
+          <t>Lxs 400: Chile Delibera... es un evento de participacion ciudadana de escala nacional realizado en Chile desde el 9 de diciembre de 2020, con su evento principal a fines de marzo de 2021. (Wikipedia ES) [Evento puntual de una edicion 2020-2021; no se hallaron ediciones posteriores recurrentes].</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Universidad Andres Bello</t>
+          <t>La iniciativa fue impulsada por la Fundacion Tribu; el Senado a traves de la Comision de Desafios del Futuro; la Asociacion Chilena de Municipalidades; la Universidad de Chile; y el Centro para la Democracia Deliberativa de la Universidad de Stanford.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Identificar tópicos y organizarlos demográficamente para generar visualizaciones</t>
+          <t>The platform used an AI tool to keep time and distribute speaking rights equitably... (OCDE 2025) [confirma que SI se uso IA dentro del proceso, en rol de facilitacion/logistica].</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Identificar tópicos y organizarlos demográficamente para generar visualizaciones</t>
+          <t>The platform used an AI tool to keep time and distribute speaking rights equitably, allowing participants to form speaking queues and discuss in small groups with timed agendas. (OCDE 2025) / An automated moderator controls perspective elicitation, with an automated cue system to determine which participant to elicit a perspective from next and an automated timer to determine how long each participant has to state their perspective. (descripcion de la Stanford Online Deliberation Platform)</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>https://ipp.unab.cl/
-https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>LXS 400 - Chile Delibera</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>In 2020, the Senate of Chile partnered with the Stanford Center for Deliberative Democracy to involve citizens in the online deliberative process 'LXS 400 - Chile Delibera' performed through the Stanford Online Deliberation Platform. (OCDE 2025, 'AI in civic participation and open government')</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Over 500 citizens representative of the Chilean society discussed in small groups and deliberated in plenary sessions on health and pension reforms. (OCDE 2025) / Entre el 5 y el 7 de marzo, 400 personas seleccionadas a traves de una metodologia aleatoria y representativas de todo Chile se reunieron para deliberar sobre dos de los temas publicos mas importantes para el pais: pensiones y salud.</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>The platform used an AI tool to keep time and distribute speaking rights equitably, allowing participants to form speaking queues and discuss in small groups with timed agendas. (OCDE 2025) / El Centro de Microdatos de la Universidad de Chile, usando tecnologia basada en Inteligencia Artificial (IA), selecciono esta muestra representativa.</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Lxs 400: Chile Delibera... es un evento de participacion ciudadana de escala nacional realizado en Chile desde el 9 de diciembre de 2020, con su evento principal a fines de marzo de 2021. (Wikipedia ES) [Evento puntual de una edicion 2020-2021; no se hallaron ediciones posteriores recurrentes].</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>La iniciativa fue impulsada por la Fundacion Tribu; el Senado a traves de la Comision de Desafios del Futuro; la Asociacion Chilena de Municipalidades; la Universidad de Chile; y el Centro para la Democracia Deliberativa de la Universidad de Stanford.</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>The platform used an AI tool to keep time and distribute speaking rights equitably... (OCDE 2025) [confirma que SI se uso IA dentro del proceso, en rol de facilitacion/logistica].</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>The platform used an AI tool to keep time and distribute speaking rights equitably, allowing participants to form speaking queues and discuss in small groups with timed agendas. (OCDE 2025) / An automated moderator controls perspective elicitation, with an automated cue system to determine which participant to elicit a perspective from next and an automated timer to determine how long each participant has to state their perspective. (descripcion de la Stanford Online Deliberation Platform)</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>https://www.oecd.org/en/publications/2025/06/governing-with-artificial-intelligence_398fa287/full-report/ai-in-civic-participation-and-open-government_51227ce7.html
 https://deliberation.stanford.edu/news/lxs-400-national-deliberative-poll-chile
@@ -8790,6 +8626,69 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>La voz de los nuevos votantes</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Governanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Implementación, Análisis</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>BBDD 2025: Cerrado</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Universidad Andres Bello</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Análisis de transcripciones para identificación de temas y palabras clave.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Análisis de transcripciones para identificación de temas y palabras clave.</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf
+https://ipp.unab.cl/publicacion/la-voz-de-los-nuevos-votantes-san-bernardo/</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
@@ -8798,7 +8697,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>La voz de los nuevos votantes</t>
+          <t>Participación Ciudadana Proceso Constitucional</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -8818,7 +8717,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Implementación, Análisis</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8833,23 +8732,22 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Universidad Andres Bello</t>
+          <t>Secretaría de Participación Ciudadana</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Análisis de transcripciones para identificación de temas y palabras clave.</t>
+          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Análisis de transcripciones para identificación de temas y palabras clave.</t>
+          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf
-https://ipp.unab.cl/publicacion/la-voz-de-los-nuevos-votantes-san-bernardo/</t>
+          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
         </is>
       </c>
     </row>
@@ -8861,7 +8759,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Participación Ciudadana Proceso Constitucional</t>
+          <t>Tenemos que hablar de Chile</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -8896,22 +8794,23 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Secretaría de Participación Ciudadana</t>
+          <t>Universidad de Chile y Pontificia Universidad Católica de Chile</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
+          <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
+          <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
+          <t>https://www.tenemosquehablardechile.cl/
+https://static1.squarespace.com/static/630d0dbf05b8104ed4d55d7f/t/67f694b2f91e4f228bb941cb/1744213189210/01.+Primer-InformeTQHDCH.pdf</t>
         </is>
       </c>
     </row>
@@ -8923,7 +8822,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Tenemos que hablar de Chile</t>
+          <t>Un encuentro para la equidad de género en la movilidad en Chile</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -8958,83 +8857,20 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Universidad de Chile y Pontificia Universidad Católica de Chile</t>
+          <t>Universidad Andres Bello</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas</t>
+          <t>Análisis temático de las transcripciones de las mesas</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas</t>
+          <t>Análisis temático de las transcripciones de las mesas</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tenemosquehablardechile.cl/
-https://static1.squarespace.com/static/630d0dbf05b8104ed4d55d7f/t/67f694b2f91e4f228bb941cb/1744213189210/01.+Primer-InformeTQHDCH.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Un encuentro para la equidad de género en la movilidad en Chile</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Governanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>BBDD 2025: Cerrado</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Universidad Andres Bello</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>Análisis temático de las transcripciones de las mesas</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Análisis temático de las transcripciones de las mesas</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>https://ipp.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/
 https://noticiasrepositorio.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/
@@ -9042,63 +8878,63 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Chatico</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares, Presupuestos Participativos</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado 2024-2028: NLP y tecnologías semánticas procesaron 147.422 participaciones (10% propuestas libres) para el Plan Distrital de Desarrollo. Citado por</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Plataforma</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Secretaría General de la Alcaldía Mayor de Bogotá</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Interactuar con ciudadanos, responder consultas y plataforma para votar en causas ciudadanas y presupuesto participativo</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>Interactuar con ciudadanos, responder consultas y plataforma para votar en causas ciudadanas y presupuesto participativo</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>https://secretariageneral.gov.co/noticias/chatico-el-agente-virtual-de-servicio-la-ciudadania-supero-los-36-millones-de-conversaciones
 https://bogota.gov.co/mi-ciudad/gestion-publica/distrito-presenta-su-agente-virtual-chatico-que-guia-la-ciudadania
@@ -9106,6 +8942,68 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ECHO – HáblameD Medellín</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Governanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Implementación, Análisis</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>reconfirmado web (institucional): Reconfirmado: la IA del UNFPA clasifica por ODS las conversaciones ciudadanas captadas en campo (5.000+ personas, 16 comunas).</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+        </is>
+      </c>
+    </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
@@ -9114,58 +9012,54 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Citibeats + PNUD Colombia (analítica de datos para la deliberación pública juvenil)</t>
+          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>DUDA(lean SI)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Data analytics to improve public deliberation in Colombia (UNDP Colombia / El PNUD en Colombia, blog, Bogotá, Colombia).</t>
+          <t>la herramienta de un resguardo indígena (Zenú, Bajo Sinú, Colombia) para llegar al Congreso (La Silla Vacía)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Citibeats facilita la comprensión social de la situación actual de Colombia mediante el monitoreo y seguimiento en tiempo real de las opiniones y propuestas expresadas en espacios digitales y presenciales, buscando identificar los principales tópicos de interés de la población.</t>
+          <t>a platform for young people in the Zenú community to decide, through digital voting, how they wanted to allocate local budgets</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Citibeats utiliza algoritmos que combinan NLP (Procesamiento de Lenguaje Natural) y ML (Machine Learning), filtrando contenido relevante de distintas fuentes de datos abiertas (Twitter, Facebook, Instagram, foros, blogs, noticias y comentarios de video), clasificando las opiniones e información de los usuarios en categorías y extrayendo conocimiento y patrones de forma automática, en tiempo real.</t>
-        </is>
-      </c>
-      <c r="G23" s="11" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>El PNUD Colombia está experimentando con Citibeats, una plataforma de inteligencia artificial (IA) ética y responsable. (proyecto descrito como experimentación/piloto del Laboratorio de Aceleración, diciembre 2021).</t>
-        </is>
-      </c>
+          <t>The AI summarizes proposals, organizes consensus, and facilitates collective decision-making</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>More than 10,000 users participate in the chatbot at gaitanaia.org, whose discussions feed the community's positions and proposals</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>El Programa de las Naciones Unidas para el Desarrollo (PNUD) en Colombia está experimentando con Citibeats... La tecnologia sirve como un habilitador que permite acelerar la comprensión social respecto a los espacios de deliberación pública y las propuestas, necesidades y preocupaciones de la juventud colombiana.</t>
+          <t>Gaitana IA is a tool created by Carlos Redondo Rincón ... a platform for young people in the Zenú community</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>El PNUD y aliados estratégicos, como El Avispero, han generado espacios presenciales para contrastar lo que se dice en las conversaciones en línea, donde los jóvenes destacan preocupaciones sobre la corrupción en el país, la necesidad de prevenir la violencia de género y la importancia de promover la educación.</t>
+          <t>Gaitana is built on the DeepSeek large language model, adapted to the Zenú worldview ... summarizes proposals, organizes consensus</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>El proyecto de comprensión ciudadana analizó 2.129.502 documentos. Las principales categorías de conversación en Colombia giraron en torno a Paz y Justicia, Gobernanza e Inclusión Social.</t>
+          <t>artificial intelligence organizes opinions, processes trends and builds consensuses that, if approved, would become legislative initiatives (KienyKe)</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/colombia/blog/analitica-de-datos-para-mejorar-la-deliberacion-publica-en-colombia
-https://www.undp.org/es/colombia/blog/data-analytics-improve-public-deliberation-colombia
-https://www.co.undp.org/content/colombia/es/home/Blog/2021/diciembre/data-analytics-to-improve-public-deliberation-in-colombia.html
-https://www.undp.org/es/colombia/press-releases/universidades-p%C3%BAblicas-y-privadas-la-iglesia-cat%C3%B3lica-en-bogot%C3%A1-y-el-pnud-habilitan-una-plataforma-presencial-y-virtual-para
-https://blogthinkbig.com/citibeats-datos-objetivos-en-tiempo-real-para-un-impacto-social-positivo
-https://www.linkedin.com/posts/matteo-mezzanotte-67412817_latam-colombian-undp-activity-6879002241148170241-oxKI</t>
+          <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/
+https://www.kienyke.com/</t>
         </is>
       </c>
     </row>
@@ -9177,7 +9071,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ECHO – HáblameD Medellín</t>
+          <t>Tenemos que hablar de Colombia</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -9197,12 +9091,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Implementación, Análisis</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>reconfirmado web (institucional): Reconfirmado: la IA del UNFPA clasifica por ODS las conversaciones ciudadanas captadas en campo (5.000+ personas, 16 comunas).</t>
+          <t>BBDD 2025: Cerrado</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -9212,204 +9106,83 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+          <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+          <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+          <t>https://tenemosquehablarcolombia.co/
+https://tenemosquehablarcolombia.co/resultados/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>CU</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
+          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>DUDA(lean SI)</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>la herramienta de un resguardo indígena (Zenú, Bajo Sinú, Colombia) para llegar al Congreso (La Silla Vacía)</t>
+          <t>Para agilizar la recogida y el procesamiento de los criterios, la Universidad de las Ciencias Informáticas (UCI) y Datys diseñaron dos sistemas informáticos de gestión (XISCOP y GEMA-CEN) [proceso de consulta popular del Código de las Familias en Cuba].</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>a platform for young people in the Zenú community to decide, through digital voting, how they wanted to allocate local budgets</t>
+          <t>consulta popular del proyecto del Código de las Familias (...) la Universidad de las Ciencias Informáticas (UCI) y Datys diseñaron dos sistemas informáticos de gestión (XISCOP y GEMA-CEN)</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>The AI summarizes proposals, organizes consensus, and facilitates collective decision-making</t>
+          <t>luego se sube a GEMA-CEN (también operado por especialistas) que, a través del análisis inteligente de los expedientes, organiza las propuestas y agrupa las similares, facilitando el trabajo y evitando errores. GEMA-CEN permite determinar las propuestas típicas para un párrafo en cada una de las categorías establecidas</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>More than 10,000 users participate in the chatbot at gaitanaia.org, whose discussions feed the community's positions and proposals</t>
-        </is>
-      </c>
-      <c r="H25" s="11" t="inlineStr"/>
+          <t>Más de seis millones 481 mil personas participaron en las reuniones (...) la consulta popular del proyecto del Código de las Familias (...) convocada entre febrero y abril [de 2022]; del total de propuestas procesadas se determinaron 5 237 propuestas típicas por Título</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>del total de propuestas procesadas se determinaron 5 237 propuestas típicas por Título, conformadas a partir de la asociación de propuestas idénticas y de aquellas con redacción diferente pero referidas al mismo criterio u opinión</t>
+        </is>
+      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Gaitana IA is a tool created by Carlos Redondo Rincón ... a platform for young people in the Zenú community</t>
+          <t>La consulta popular (...) fue organizada y supervisada por el Consejo Electoral Nacional (CEN) [órgano del Estado cubano]; los resultados se entregaron al Parlamento (Asamblea Nacional) y a su Comisión redactora</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Gaitana is built on the DeepSeek large language model, adapted to the Zenú worldview ... summarizes proposals, organizes consensus</t>
+          <t>se sube a GEMA-CEN (...) que, a través del análisis inteligente de los expedientes, organiza las propuestas y agrupa las similares (...) permite determinar las propuestas típicas para un párrafo en cada una de las categorías establecidas</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>artificial intelligence organizes opinions, processes trends and builds consensuses that, if approved, would become legislative initiatives (KienyKe)</t>
+          <t>GEMA es una herramienta para el análisis de información contenida en grandes volúmenes de archivos de diferentes formatos e idiomas, con funcionalidades orientadas a la recuperación y clasificación de información (...) complementando los resultados mediante técnicas modernas de recuperación de información para obtener archivos similares, eliminar resultados no relevantes y agrupar documentos comunes</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/
-https://www.kienyke.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Tenemos que hablar de Colombia</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Governanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>BBDD 2025: Cerrado</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>https://tenemosquehablarcolombia.co/
-https://tenemosquehablarcolombia.co/resultados/</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CU</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Para agilizar la recogida y el procesamiento de los criterios, la Universidad de las Ciencias Informáticas (UCI) y Datys diseñaron dos sistemas informáticos de gestión (XISCOP y GEMA-CEN) [proceso de consulta popular del Código de las Familias en Cuba].</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>consulta popular del proyecto del Código de las Familias (...) la Universidad de las Ciencias Informáticas (UCI) y Datys diseñaron dos sistemas informáticos de gestión (XISCOP y GEMA-CEN)</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>luego se sube a GEMA-CEN (también operado por especialistas) que, a través del análisis inteligente de los expedientes, organiza las propuestas y agrupa las similares, facilitando el trabajo y evitando errores. GEMA-CEN permite determinar las propuestas típicas para un párrafo en cada una de las categorías establecidas</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Más de seis millones 481 mil personas participaron en las reuniones (...) la consulta popular del proyecto del Código de las Familias (...) convocada entre febrero y abril [de 2022]; del total de propuestas procesadas se determinaron 5 237 propuestas típicas por Título</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>del total de propuestas procesadas se determinaron 5 237 propuestas típicas por Título, conformadas a partir de la asociación de propuestas idénticas y de aquellas con redacción diferente pero referidas al mismo criterio u opinión</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>La consulta popular (...) fue organizada y supervisada por el Consejo Electoral Nacional (CEN) [órgano del Estado cubano]; los resultados se entregaron al Parlamento (Asamblea Nacional) y a su Comisión redactora</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>se sube a GEMA-CEN (...) que, a través del análisis inteligente de los expedientes, organiza las propuestas y agrupa las similares (...) permite determinar las propuestas típicas para un párrafo en cada una de las categorías establecidas</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>GEMA es una herramienta para el análisis de información contenida en grandes volúmenes de archivos de diferentes formatos e idiomas, con funcionalidades orientadas a la recuperación y clasificación de información (...) complementando los resultados mediante técnicas modernas de recuperación de información para obtener archivos similares, eliminar resultados no relevantes y agrupar documentos comunes</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>http://www.datys.cu/spa/site/product/15
 https://www.granma.cu/cuba/2022-01-24/herramientas-digitales-seran-claves-durante-la-consulta-popular-del-codigo-de-las-familias-24-01-2022-13-01-18
@@ -9421,65 +9194,65 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>EC</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PAGA IA </t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado: integrada al Tercer Plan de Acción de Estado Abierto 2025-2027; analiza las propuestas ciudadanas y sugiere actividades.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Plataforma</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto
 </t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto
 </t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>https://ia.gobiernoabierto.ec/
 https://ia.gobiernoabierto.ec/
@@ -9487,63 +9260,63 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Guatemala Joven Conversa </t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado: diálogos digitales con IA (DPPA ONU + Fundación Esquipulas); 300+ jóvenes; la IA permite intercambios anónimos y votación de aportes para identifi</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
 https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/
@@ -9551,125 +9324,125 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>HN</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RedPública + iVerify </t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reverificación: plataforma de propuestas ciudadanas con módulo de análisis de tendencias; evidencia de IA central débil, revisar en Fase 2.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Guanajuato hará historia con el primer Programa de Gobierno realizado con IA</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Para integrar la participación ciudadana en este Programa de Gobierno, se realizaron cuatro talleres cubriendo las regiones noreste, norte, centro y sur, con representación de los 46 municipios de Guanajuato.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>El Programa de Gobierno de Guanajuato 2024-2030 es la guía que orienta las acciones del Gobierno de la Gente para lograr un Guanajuato sostenible, equitativo y transparente.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Su diseño incorporó el uso de inteligencia artificial para integrar más de 26 mil voces de distintas regiones y sectores</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>El Programa de Gobierno 2024-2030 hizo historia al ser el primero en realizarse con ayuda de la Inteligencia Artificial (IA), según anunció la Gobernadora Libia Dennise García Muñoz Ledo en el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG).</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía.</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>https://guanajuatointeligente.com/como-hicimos-el-programa/
 https://guanajuatointeligente.com/
@@ -9682,121 +9455,121 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Presupuesto CRECES</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Presupuestos Participativos</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Activo</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Ayundamiento de Hermosilla</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>https://presupuestocreces.hermosillo.gob.mx/</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>La Fundación Panamá Participa lanzó Mansa Idea (www.mansaidea.com), una plataforma basada en inteligencia artificial que recoge miles de propuestas ciudadanas... iniciativa de alcance nacional que se nutre de ideas y propuestas que miles de panameños hicieron durante el desarrollo del Pacto del Bicentenario. (Panamá; fuentes panama24horas.com.pa y laestrella.com.pa)</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea, resultado del Pacto del Bicentenario, ofrece acceso fácil y transparente a más de 175 mil ideas y propuestas generadas por ciudadanos de todo el país. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales. (la IA agrega/organiza/sintetiza el contenido de las propuestas por tema y territorio = Análisis + Traducción Política; el método técnico exacto no se detalla en las fuentes).</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>La plataforma fue lanzada el 1 de abril de 2024... constituye una herramienta valiosa de participación ciudadana muy relevante para ciudadanos, candidatos a cargos de elección popular y medios durante la campaña electoral y luego como recurso para el monitoreo del mandato ciudadano. (un despliegue concreto de la plataforma, 2024; sin evidencia de ediciones recurrentes).</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>La Fundación Panamá Participa lanzó Mansa Idea... iniciativa liderada por Paulina Franceschi a través de la Fundación Panamá Participa (sociedad civil). El proceso participativo de origen: 'El 26 de noviembre de 2020, el presidente Laurentino Cortizo Cohen lanzó la iniciativa denominada Pacto del Bicentenario Cerrando Brechas' (gobierno nacional / Concertación Nacional).</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. (la IA procesa el contenido de las propuestas del proceso participativo).</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía. (agregación/síntesis de los aportes ciudadanos = rol sobre el contenido).</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>https://www.panama24horas.com.pa/panama/fundacion-panama-participa-lanza-plataforma-de-propuestas-ciudadanas-mansa-idea/
 https://www.laestrella.com.pa/panama/politica/mansa-idea-una-herramienta-digital-con-propuestas-para-candidatos-YD6746221
@@ -9807,63 +9580,63 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (prensa): VERIFICADO (fuente primaria): el CNE usó IBM Watson Discovery + Studio (ML/NLP) sobre 87.991 documentos de aportes ciudadanos de 847 eventos y 49 espacios de di</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>Consejo Nacional de Educación del Perú</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional
 https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080
@@ -9872,59 +9645,59 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Project: National Digital Transformation Strategy | Ministry of Digital Transformation, Trinidad and Tobago (engage.gov.tt/projects/national-digital-transformation-strategy). Ruta interna confirmatoria: engage.gov.tt/projects/e-democracy-govocal-internal (la instancia corre sobre Go Vocal). En 2026: 'Projects | Ministry of Public Administration and Artificial Intelligence' (engage.gov.tt/projects).</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>EngageTT es una plataforma en linea (engage.gov.tt) donde ciudadanos, empresas y partes interesadas pueden recibir actualizaciones en tiempo real sobre iniciativas de transformacion digital y ofrecer retroalimentacion via encuestas y sondeos (polls); el Ministro anima a todos a participar y enviar ideas y comentarios sobre el NDTS, que se disena para evolucionar mediante el compromiso y la colaboracion continuos. Incluye un 'Open Forum' (engage.gov.tt/ideas/open-forum) y 'Input: Submitting Proposals' (engage.gov.tt/ideas/submitting-proposals).</t>
         </is>
       </c>
-      <c r="F35" s="11" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>The National Strategy for a Digital TT is finalized, and while the Ministry of Digital Transformation is no longer seeking input, they welcome feedback or comments through the citizen engagement digital platform Engage TT. (engage.gov.tt sigue operativo en 2026 bajo MPAAI).</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>The Ministry of Digital Transformation (MDT) officially presented the National Digital Transformation Strategy (NDTS) 2024-2027... launched during a NDTS Symposium in collaboration with the Inter-American Development Bank (IDB) on Wednesday, February 12th 2025. A major highlight... was the introduction of two new digital tools (EngageTT y AskNDTS). (Lanzamiento/anuncio unico en feb-2025; plataforma de uso continuo pero sin &gt;=2 ediciones de proceso participativo documentadas).</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>The Ministry of Digital Transformation (MDT) officially presented the National Digital Transformation Strategy (NDTS) 2024-2027... and introduced the EngageTT website - an online platform where citizens, businesses, and stakeholders can get real-time updates on digital transformation initiatives, and offer feedback via surveys and polls. (Convocante: gobierno nacional / Ministry of Digital Transformation, hoy MPAAI).</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Go Vocal Support Base (AI Analysis): 'Access to this feature depends on your plan. Advanced Sensemaking with auto-insights is available in the Premium plan.' -&gt; la IA/NLP de Go Vocal NO es automatica, depende del plan; y para EngageTT solo se documenta 'feedback via surveys and polls'/Open Forum/ideas, SIN mencion de analisis automatico por IA de los aportes. No se halla evidencia de activacion del NLP sobre el contenido en la instancia TT. 3a PASADA (refuerzo): Oxford Insights, 'The country's AI utilisation for citizens is concentrated in a robust Chatbot programme' (mas 'deployment of large language models for internal development purposes') -&gt; la IA ciudadana de TT es el chatbot, NO el analisis de aportes.</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Sin evidencia de IA aplicada al contenido de los aportes en engage.gov.tt. La unica IA confirmada de cara al ciudadano (AskNDTS/ANANSI) es chatbot de FAQ, excluido del criterio. En 3a pasada, el material de MPAAI 2026 enmarca la IA en el asistente ANANSI y en encuestas de AI-readiness (resultados 'consolidated and reviewed' en talleres), sin mencion de analisis por IA de los aportes del NDTS ni de Go Vocal Sensemaking.</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>https://support.govocal.com/en/articles/8316692-ai-analysis
 https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool
@@ -9946,59 +9719,59 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>UY</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Polis has been used to facilitate discussion and build consensus ... in Uruguay on a national referendum (OCDE 2025, 'Governing with AI')</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists — ran Polis alongside the referendum</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>The algorithm maps participants' responses and clusters opinions, facilitating the identification of positions that are supported by the majority of participants (OCDE 2025)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>16,499 people cast more than 295,000 votes ... The referendum was lost by less than 1%</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="H34" s="11" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>ran Polis alongside the referendum to look for something deeper than "yes or no"</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Polis revealed that even where public safety divided people, surprising points of consensus broke through on other issues — bridges between groups</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/
 https://www.oecd.org/en/publications/governing-with-artificial-intelligence_795de142-en.html</t>
@@ -10006,7 +9779,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L36"/>
+  <autoFilter ref="A1:L34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10040,7 +9813,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>Planilla con 6 pestañas (criterio corregido). 35 casos entran/dudosos · 72 excluidos · 107 en total. Tras dedup e-Cidadania: 34 iniciativas.</t>
+          <t>Planilla con 6 pestañas (criterio corregido). 33 casos entran/dudosos · 74 excluidos · 107 en total. Tras dedup e-Cidadania: 32 iniciativas.</t>
         </is>
       </c>
     </row>

--- a/data/gates/planilla_ILIA2026_SIMPLE.xlsx
+++ b/data/gates/planilla_ILIA2026_SIMPLE.xlsx
@@ -1459,12 +1459,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Gobernanza Colaborativa; Participación Digital; Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Traducción Política</t>
+          <t>Traducción Política; Análisis</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Voz a Texto; LLM; NLP</t>
+          <t>Voz a Texto; LLM; NLP; Búsqueda semántica</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">

--- a/data/gates/planilla_ILIA2026_SIMPLE.xlsx
+++ b/data/gates/planilla_ILIA2026_SIMPLE.xlsx
@@ -15,10 +15,10 @@
     <sheet name="6 · Metodología (CENIA v2)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos (entran+dudosos)'!$A$1:$X$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos (entran+dudosos)'!$A$1:$X$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2 · A validar a mano'!$A$1:$G$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 · Excluidos'!$A$1:$E$75</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 · Evidencia y fuentes'!$A$1:$L$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 · Evidencia y fuentes'!$A$1:$L$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -582,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X34"/>
+  <dimension ref="A1:X35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1208,220 +1208,221 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>Meta Community Forum on Generative AI — cohorte Brasil (Deliberative Polling, Stanford)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>ALTA (plataforma, moderador automatizado, fechas, cohorte BR y hallazgos BR confirmados con citas verbatim de Stanford/BIT); pendiente solo N de Brasil e idioma, y el pipeline de análisis (posible upgrade a 'contenido')</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Mini públicos</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>empresa; universidad</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>apoyo</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Moderación/facilitación automatizada; Sistema de reglas/temporización</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>no-claro</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>Foro comunitario deliberativo (Deliberative Polling®) sobre principios para los chatbots de IA generativa, realizado el 28-29 de octubre de 2023 en la Stanford Online Deliberation Platform con 1.545 participantes de muestras científicas de Brasil, Alemania, España y EE.UU. Formato: grupos pequeños de 8-12 personas (166 grupos, con grupo de control por país), panel de expertos en plenario, cuadernillo informativo (~50 págs.) y 44 preguntas de opinión pre/post. Los resultados (publicados abr-2024) incluyen hallazgos específicos de Brasil (p. ej., fuerte oposición a relaciones románticas humano-chatbot; énfasis en perspectivas locales en las fuentes de la IA). Meta declaró que los resultados 'ayudaron a dar forma a algunas de las decisiones más fundamentales' del diseño de sus productos de IA generativa.</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>Meta (convocante/financista) + Stanford Deliberative Democracy Lab (diseño y ejecución del Deliberative Polling®) + Behavioural Insights Team (entrega y recomendaciones)</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>https://cddrl.fsi.stanford.edu/publication/meta-community-forum-results-analysis
+https://transparency.meta.com/governance/community-forums/2023-community-forum-on-generative-AI/</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>BR-meta-community-forum-genai</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>OPA Piauí - Orçamento Participativo Digital (Colab + AWS)</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Presupuestos Participativos; Participación Digital</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>gobierno local</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>apoyo</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>OPA (Orçamento Participativo Digital) es el presupuesto participativo 100% digital del Gobierno del Estado de Piauí (Brasil), creado en 2023 y coordinado por la Secretaria do Planejamento (SEPLAN) con apoyo de la Secretaria de Relações Sociais (Seres). Se ejecuta sobre la plataforma Colab Gov (de la govtech Colab) con infraestructura AWS. El ciclo incluye cadastramento de propuestas por entidades comunitarias/asociaciones, una fase de 'análise técnica' (verificación de documentación, viabilidad de ejecución, claridad de la descripción, adecuación al área temática y no duplicación) y una votación popular abierta a la ciudadanía. En la edición 2026-2027, según el material de Colab, 'a análise ganhou agilidade com o uso de inteligência artificial, que reduziu em 40% o tempo de processamento das propostas', con economía de R$ 1,75 millón y 99,98% de disponibilidad del sistema. La señal disponible vincula la IA al procesamiento/agilización del flujo, a la seguridad de la infraestructura (filtrado de conexiones inseguras vía AWS CloudFront), a un chatbot/capacitación (CapacitIA) y a un 'Observatório do OPA' de transparencia; la 'análise técnica' de viabilidad se describe de forma reiterada como tarea conducida por equipos técnicos a través de la plataforma. NO hay evidencia de que la IA clasifique, agrupe (clustering) o sintetice el CONTENIDO temático/semántico de las propuestas en el OPA.</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>Governo do Estado do Piauí - Secretaria do Planejamento (SEPLAN), con apoyo de la Secretaria de Relações Sociais (Seres). Socio tecnológico: GovTech Colab (plataforma Colab Gov); infraestructura: AWS (Amazon Web Services).</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V6" s="5" t="n">
+      <c r="V7" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="W6" s="2" t="inlineStr">
+      <c r="W7" s="2" t="inlineStr">
         <is>
           <t>https://sia.pi.gov.br/projetos/opa/
 https://tiinside.com.br/21/10/2025/em-parceria-com-a-aws-colab-lanca-ia-que-constroi-fluxos-de-governo-em-segundos/
 https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/</t>
         </is>
       </c>
-      <c r="X6" s="2" t="inlineStr">
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>BR-opa-piaui-presupuesto-participativo-digi</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Plan Plurianual de la ciudad de Natal</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Implementación; Análisis</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>gobierno local</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno; Privado</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>Nacional, Internacional</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>LLM; NLP</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>Recolección de información a través de tres preguntas habilitadas por WhatsApp para diseñar el Plan Plurianual de la ciudad 2026-2029</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>Prefeitura Municipal de Natal, a través de la Secretaría Municipal de Planeamiento (SEMPLA)</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
-        </is>
-      </c>
-      <c r="X7" s="2" t="inlineStr">
-        <is>
-          <t>BR-plan-plurianual-de-la-ciudad-de-natal</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1435,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Portal e-Cidadania: Marcado automático de respuestas ciudadanas en videos de audiencias públicas</t>
+          <t>Plan Plurianual de la ciudad de Natal</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1459,12 +1460,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa; Participación Digital; Referendos e Iniciativas Populares</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Traducción Política; Análisis</t>
+          <t>Implementación; Análisis</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
@@ -1477,7 +1478,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional</t>
+          <t>gobierno local</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1492,17 +1493,17 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Gobierno; Privado</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Nacional, Internacional</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Voz a Texto; LLM; NLP; Búsqueda semántica</t>
+          <t>LLM; NLP</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -1512,12 +1513,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>Implementación de IA para identificar y marcar en los videos de eventos las respuestas dadas a preguntas ciudadanas, incluso cuando estas no fueron respondidas directamente durante las audiencias.</t>
+          <t>Recolección de información a través de tres preguntas habilitadas por WhatsApp para diseñar el Plan Plurianual de la ciudad 2026-2029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>Senado Federal de Brasil</t>
+          <t>Prefeitura Municipal de Natal, a través de la Secretaría Municipal de Planeamiento (SEMPLA)</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1525,17 +1526,17 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="V8" s="5" t="n">
-        <v>1</v>
+      <c r="V8" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias</t>
+          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>BR-portal-e-cidadania-marcado-automatico-de</t>
+          <t>BR-plan-plurianual-de-la-ciudad-de-natal</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1549,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>São Paulo - Programa de Metas / Participe Mais (Gemini)</t>
+          <t>Portal e-Cidadania: Marcado automático de respuestas ciudadanas en videos de audiencias públicas</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1556,9 +1557,9 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1568,17 +1569,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>MEDIA-ALTA</t>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
+          <t>Gobernanza Colaborativa; Participación Digital; Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Traducción Política; Análisis</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
@@ -1586,1129 +1587,1129 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
+          <t>Plataforma</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>gobierno nacional</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Voz a Texto; LLM; NLP; Búsqueda semántica</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>Implementación de IA para identificar y marcar en los videos de eventos las respuestas dadas a preguntas ciudadanas, incluso cuando estas no fueron respondidas directamente durante las audiencias.</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>Senado Federal de Brasil</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="V9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>BR-portal-e-cidadania-marcado-automatico-de</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo - Programa de Metas / Participe Mais (Gemini)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>MEDIA-ALTA</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>gobierno local</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>Sociedad Civil; Gobierno</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>LLM generativa; NLP; Clasificación de texto</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>Consulta pública del Programa de Metas 2025-2028 / Plano Plurianual (PPA) 2026-2029 / Planos de Ação das Subprefeituras (PAS) 2026-2029 de la Prefeitura de São Paulo, realizada en el portal Participe Mais (Participe+), plataforma de participación social de la Prefeitura construida sobre el software libre Decidim (basado en CONSUL/Decidim de Madrid-Barcelona). La consulta estuvo abierta del 7/04/2025 al 11/05/2025; el ciclo participativo incluyó 36 audiencias públicas híbridas en la ciudad (abril-mayo 2025) y recibió 6.368 propostas y más de 31.000 interacciones ciudadanas (sugerencias, apoyos, propuestas y críticas). Sobre ese material, en mayo de 2025 Carolina Borges -Agente de Governo Aberto de la Prefeitura- desarrolló una herramienta (Python + Pandas + Google Gemini) que clasifica las propostas en categorías, las ordena por asunto y cantidad de apoyos y genera relatórios y painéis visuales (ranking de temas más recurrentes y participación por distrito y subprefeitura), 'facilitando a divulgação das propostas à população'. La herramienta y su metodología se presentaron en la oficina 'Análise de Dados com Inteligência Artificial na Gestão Pública: Programa de Metas' de la Escola do Parlamento de la Câmara Municipal de São Paulo (15/12/2025), realizada en parceria con el Programa Agentes de Governo Aberto da Prefeitura.</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>Proceso participativo (Programa de Metas / PPA / PAS): Prefeitura de São Paulo (Secretaria Municipal de Planejamento / Casa Civil / Coordenadoria de Governo Aberto, portal Participe Mais). Herramienta de IA: desarrollada por Carolina Borges, Agente de Governo Aberto de São Paulo (formación en Ciência da Computação y posgrado en Gestão e Controle Social de Políticas Públicas por la Escola de Contas do TCM-SP; experiencia profesional, académica y voluntaria), presentada en la oficina de la Escola do Parlamento da Câmara Municipal de São Paulo en parceria con el Programa Agentes de Governo Aberto. No se confirmó que la Prefeitura adoptara esta herramienta como su pipeline oficial de análisis del proceso.</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="V9" s="5" t="n">
+      <c r="V10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="W9" s="2" t="inlineStr">
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>https://gestaourbana.prefeitura.sp.gov.br/wp-content/uploads/2025/10/Relatorio_Oficinas_Participativas.pdf
 https://gestaourbana.prefeitura.sp.gov.br/planos-de-acao-das-subprefeituras/</t>
         </is>
       </c>
-      <c r="X9" s="2" t="inlineStr">
+      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>BR-sao-paulo-programa-de-metas-participe-ma</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>➜ NO contar (duplicado)</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>e-Cidadania Senado - IA matching de ideas legislativas</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>NO (duplicado)</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Participación Digital; Referendos e Iniciativas Populares</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Análisis; Traducción Política</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>gobierno nacional</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Gobierno</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>NLP; Búsqueda semántica</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>Portal e-Cidadania del Senado Federal de Brasil, módulo 'Ideia Legislativa', donde la población envía sugerencias para crear o mejorar leyes. Tradicionalmente una idea debía reunir 20.000 apoyos en 4 meses para ser formalizada como Sugestão Legislativa y analizada por la Comissão de Direitos Humanos e Legislação Participativa (CDH). A fines de 2025 / enero 2026 el Senado desplegó una herramienta de inteligencia artificial (búsqueda semántica) sobre el banco de ideias legislativas (145.993 ideias a enero 2026) que, a pedido de la Consultoria Legislativa cuando un senador prepara un proyecto, busca y selecciona las ideas ciudadanas temáticamente compatibles para incorporarlas y citarlas en la justificación del proyecto de ley, sin exigir el mínimo de apoyos.</t>
         </is>
       </c>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
         <is>
           <t>Senado Federal do Brasil - Consultoria Legislativa en conjunto con el Programa e-Cidadania (Secretaria de Transparência / Coordenação do e-Cidadania). Herramienta desarrollada por el servidor Alisson Bruno (coordenador do e-Cidadania) en el marco del Desafio de Inovação do Senado.</t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr">
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="V10" s="5" t="n">
+      <c r="V11" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="W10" s="2" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial
 https://www12.senado.leg.br/radio/1/noticia/2026/01/15/ia-vai-aproximar-ideias-legislativas-do-e-cidadania-e-projetos-de-senadores
 https://www.poder360.com.br/poder-congresso/ia-do-senado-usa-sugestoes-enviadas-por-cidadaos-em-projetos-de-lei/</t>
         </is>
       </c>
-      <c r="X10" s="2" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr">
         <is>
           <t>BR-e-cidadania-senado-ia-matching-de-ideas</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Cabildos 2016</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="J12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>gobierno nacional</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Academia</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>NLP - Tópicos</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>Análisis de los cabildos del proceso constitucional en 2016</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>Gobierno de Chile (Presidencia/SEGPRES) — convocante del Proceso Constituyente Abierto; la Biblioteca del Congreso Nacional sistematiza y archiva los resultados (convenio con Senado, Cámara y SEGPRES).</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="V11" s="4" t="n">
+      <c r="V12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W11" s="2" t="inlineStr">
+      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>https://www.bcn.cl/procesoconstituyente/cabildos2016/
 https://aclanthology.org/W17-5101/
 https://journals.plos.org/plosone/article?id=10.1371%2Fjournal.pone.0267443</t>
         </is>
       </c>
-      <c r="X11" s="2" t="inlineStr">
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>CL-cabildos-2016</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>El Chile que Queremos (ECQQ) - MinCiencia</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="J13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>gobierno nacional</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Gobierno</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>NLP; Clasificación de texto; Modelado de tópicos (LDA); Redes neuronales recurrentes (RNN); Random Forest; Clasificación de emociones; Machine Learning</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>Iniciativa gubernamental de diálogos ciudadanos y escucha social presentada por el Gobierno de Chile el 22 de noviembre de 2019, en el marco del Acuerdo por la Justicia Social y el Acuerdo por una Nueva Constitución tras el estallido social. Entre noviembre de 2019 y marzo de 2020, la ciudadanía pudo participar mediante diálogos grupales (cabildos) o consultas individuales en el sitio www.chilequequeremos.cl, registrando sus necesidades y propuestas para complementar futuras políticas públicas. El proceso fue un esfuerzo conjunto de los Ministerios de Desarrollo Social y Familia, de Ciencia/Tecnología/Conocimiento e Innovación (MinCiencia), de Agricultura, la SEGEGOB y la División de Gobierno Digital. El Ministerio de Ciencia fue responsable de SISTEMATIZAR los aportes ciudadanos usando ciencia de datos / IA: el repositorio público MinCiencia/ECQQ contiene el código que clasifica las contribuciones (texto libre de los aportes) mediante redes neuronales recurrentes (RNN) y árboles de decisión (Random Forest), y sistematiza emociones y necesidades mediante análisis de tópicos (NLP/LDA) sobre el contenido de diálogos y consultas individuales.</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>Gobierno de Chile - proceso conjunto liderado por el Ministerio de Desarrollo Social y Familia; sistematización de los aportes con ciencia de datos/IA a cargo del Ministerio de Ciencia, Tecnología, Conocimiento e Innovación (MinCiencia). Participaron también Ministerio de Agricultura, SEGEGOB y División de Gobierno Digital.</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="V12" s="5" t="n">
+      <c r="V13" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="W12" s="2" t="inlineStr">
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>https://github.com/MinCiencia/ECQQ/activity
 https://www.chilequequeremos.cl
 https://minciencia.gob.cl/noticias/</t>
         </is>
       </c>
-      <c r="X12" s="2" t="inlineStr">
+      <c r="X13" s="2" t="inlineStr">
         <is>
           <t>CL-el-chile-que-queremos-ecqq-minciencia</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>gobierno nacional</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>NLP - Tópicos</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>Uso de IA para analizar datos cualitativos en consulta ciudadana.</t>
         </is>
       </c>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>Secretaría de Gobierno Digital</t>
         </is>
       </c>
-      <c r="U13" s="2" t="inlineStr">
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="V13" s="4" t="n">
+      <c r="V14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W13" s="2" t="inlineStr">
+      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030
 https://participacion.digital.gob.cl/folders/consultas-ciudadanas</t>
         </is>
       </c>
-      <c r="X13" s="2" t="inlineStr">
+      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>CL-estrategia-de-gobierno-digital-informe-p</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Estudio dIAlogos - Percepciones de Futuro</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Implementación; Análisis</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>sociedad civil; empresa</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>Mixto</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>NLP</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>Estudio que utilizó distintas herramientas de IA para conocer las percepciones de futuro de la población chilena</t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
         <is>
           <t>Fundación Encuentros del Futuro y Merlín Research</t>
         </is>
       </c>
-      <c r="U14" s="2" t="inlineStr">
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="V14" s="4" t="n">
+      <c r="V15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W14" s="2" t="inlineStr">
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>https://estudiodialogos.cl/
 https://fairlac.iadb.org/en/dialogos-study-perceptions-future</t>
         </is>
       </c>
-      <c r="X14" s="2" t="inlineStr">
+      <c r="X15" s="2" t="inlineStr">
         <is>
           <t>CL-estudio-dialogos-percepciones-de-futuro</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>universidad</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>NLP - Tópicos</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornadas de diálogo de la comunidad académica y otos stakeholders. </t>
         </is>
       </c>
-      <c r="T15" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
         <is>
           <t>Universidad Andres Bello</t>
         </is>
       </c>
-      <c r="U15" s="2" t="inlineStr">
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="V15" s="4" t="n">
+      <c r="V16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W15" s="2" t="inlineStr">
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>https://ipp.unab.cl/
 https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
         </is>
       </c>
-      <c r="X15" s="2" t="inlineStr">
+      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>CL-jornada-de-escucha-lanzamiento-instituto</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>LXS 400 - Chile Delibera</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Mini públicos</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>Implementación; Planificación</t>
         </is>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J17" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>gobierno nacional; universidad; sociedad civil</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>Mixto</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>apoyo</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Academia</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>Moderación/facilitación automatizada; Sistema de reglas/temporización; Muestreo estadístico asistido por IA</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>Encuesta deliberativa nacional (Deliberative Poll, modelo de James S. Fishkin) convocada por el Senado de Chile (Comisión Desafíos del Futuro) junto a la Fundación Tribu, el Centro para la Democracia Deliberativa de la Universidad de Stanford, la Universidad de Chile, la Asociación Chilena de Municipalidades (AChM) y el Servicio de Registro Civil. Un mini-público de ~400-514 ciudadanos seleccionados aleatoriamente y representativos del país deliberó de forma online (vía Zoom y la Stanford Online Deliberation Platform) los días 5, 6 y 7 de marzo de 2021 sobre reformas a pensiones y salud, en grupos pequeños y sesiones plenarias, de cara al debate constitucional. El proceso comenzó en diciembre de 2020 con la selección de la muestra y la entrega de material informativo equilibrado (argumentos a favor y en contra). La plataforma online de Stanford incorporó un moderador automatizado (IA) que controlaba los tiempos y distribuía equitativamente los turnos de palabra (colas de habla, temporizador, sistema de señal para determinar quién hablaba a continuación); en paralelo, el Centro de Microdatos de la U. de Chile usó tecnología basada en IA para seleccionar la muestra representativa.</t>
         </is>
       </c>
-      <c r="T16" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
         <is>
           <t>Senado de Chile (Comisión Desafíos del Futuro, Ciencia, Tecnología e Innovación) y Fundación Tribu, con la Universidad de Stanford (Center for Deliberative Democracy / Deliberative Democracy Lab), la Universidad de Chile (Centro de Microdatos), la Asociación Chilena de Municipalidades (AChM) y el Servicio de Registro Civil e Identificación.</t>
         </is>
       </c>
-      <c r="U16" s="2" t="inlineStr">
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="V16" s="5" t="n">
+      <c r="V17" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="W16" s="2" t="inlineStr">
+      <c r="W17" s="2" t="inlineStr">
         <is>
           <t>https://es.wikipedia.org/wiki/Lxs_400:_Chile_Delibera
 https://www.lxs400.cl/noticias/
 https://www.senado.cl/comunicaciones/noticias/chile-delibera-lxs-400-un-fin-de-semana-de-democracia-deliberativa-online</t>
         </is>
       </c>
-      <c r="X16" s="2" t="inlineStr">
+      <c r="X17" s="2" t="inlineStr">
         <is>
           <t>CL-lxs-400-chile-delibera</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>La voz de los nuevos votantes</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Implementación; Análisis</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="J18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>universidad</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>NLP - Tópicos</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>Análisis de Lenguaje Natural para los audios transcritos de encuesta realizada en persona.</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
         <is>
           <t>Universidad Andres Bello</t>
         </is>
       </c>
-      <c r="U17" s="2" t="inlineStr">
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V17" s="4" t="n">
+      <c r="V18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf
 https://ipp.unab.cl/publicacion/la-voz-de-los-nuevos-votantes-san-bernardo/</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
         <is>
           <t>CL-la-voz-de-los-nuevos-votantes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Participación Ciudadana Proceso Constitucional</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>gobierno nacional</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Academia</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>NLP - Tópicos</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>Análisis de los resultados obtenidos de los Diálogos Ciudadanos Autoconvocados dentro del proceso constitucional</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>Secretaría de Participación Ciudadana</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
-        </is>
-      </c>
-      <c r="X18" s="2" t="inlineStr">
-        <is>
-          <t>CL-participacion-ciudadana-proceso-constitu</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2722,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Tenemos que hablar de Chile</t>
+          <t>Participación Ciudadana Proceso Constitucional</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2731,7 +2732,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>SI*</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2764,12 +2765,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>universidad</t>
+          <t>gobierno nacional</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2799,17 +2800,17 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>Iniciativa de diálogo y participación llevada a cabo por la UCH y PUC en el contexto de manifestaciones sociales</t>
+          <t>Análisis de los resultados obtenidos de los Diálogos Ciudadanos Autoconvocados dentro del proceso constitucional</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>Universidad de Chile y Pontificia Universidad Católica de Chile</t>
+          <t>Secretaría de Participación Ciudadana</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="V19" s="4" t="n">
@@ -2817,13 +2818,12 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>https://www.tenemosquehablardechile.cl/
-https://static1.squarespace.com/static/630d0dbf05b8104ed4d55d7f/t/67f694b2f91e4f228bb941cb/1744213189210/01.+Primer-InformeTQHDCH.pdf</t>
+          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>CL-tenemos-que-hablar-de-chile</t>
+          <t>CL-participacion-ciudadana-proceso-constitu</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Un encuentro para la equidad de género en la movilidad en Chile</t>
+          <t>Tenemos que hablar de Chile</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SI*</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2914,313 +2914,310 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>Espacio participativo para levantar opiniones y propuestas de autoridades, miembros de la sociedad civil y académicos sobre la movilidad con perspectiva de género en Chile.</t>
+          <t>Iniciativa de diálogo y participación llevada a cabo por la UCH y PUC en el contexto de manifestaciones sociales</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>Universidad Andres Bello</t>
+          <t>Universidad de Chile y Pontificia Universidad Católica de Chile</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="V20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tenemosquehablardechile.cl/
+https://static1.squarespace.com/static/630d0dbf05b8104ed4d55d7f/t/67f694b2f91e4f228bb941cb/1744213189210/01.+Primer-InformeTQHDCH.pdf</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>CL-tenemos-que-hablar-de-chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Un encuentro para la equidad de género en la movilidad en Chile</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>universidad</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>NLP - Tópicos</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>Espacio participativo para levantar opiniones y propuestas de autoridades, miembros de la sociedad civil y académicos sobre la movilidad con perspectiva de género en Chile.</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>Universidad Andres Bello</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>https://ipp.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/
 https://noticiasrepositorio.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/
 https://public.tableau.com/app/profile/ivania.yovanovic/viz/UnencuentroparalaequidaddegneroenlamovilidadenChile-CIUDHAD/CIUDHADTransporteyGnero</t>
         </is>
       </c>
-      <c r="X20" s="2" t="inlineStr">
+      <c r="X21" s="2" t="inlineStr">
         <is>
           <t>CL-un-encuentro-para-la-equidad-de-genero-e</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Chatico</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Presupuestos Participativos; Participación Digital</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="J22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>gobierno local</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Privado; Gobierno</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>NLP; LLM</t>
         </is>
       </c>
-      <c r="R21" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>Agente virtual de Bogotá (Secretaría General) con módulos de PARTICIPACIÓN además de atención: votación de Causas Ciudadanas y de los Presupuestos Participativos (240.000+ votos desde 2022) y recepción de más de 147.000 aportes ciudadanos para la construcción del Plan Distrital de Desarrollo 'Bogotá Camina Segura' 2024-2027. Renovado con IA generativa (2026); atiende por WhatsApp/Telegram/webchat.</t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
         <is>
           <t>Secretaría General de la Alcaldía Mayor de Bogotá</t>
         </is>
       </c>
-      <c r="U21" s="2" t="inlineStr">
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="V21" s="4" t="n">
+      <c r="V22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W21" s="2" t="inlineStr">
+      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>https://secretariageneral.gov.co/noticias/chatico-el-agente-virtual-de-servicio-la-ciudadania-supero-los-36-millones-de-conversaciones
 https://bogota.gov.co/mi-ciudad/gestion-publica/distrito-presenta-su-agente-virtual-chatico-que-guia-la-ciudadania
 https://bogota.gov.co/mi-ciudad/participacion-y-cultura-ciudadana/plan-desarrollo-bogota-camina-segura-tuvo-147-mil-aportes-ciudadanos</t>
         </is>
       </c>
-      <c r="X21" s="2" t="inlineStr">
+      <c r="X22" s="2" t="inlineStr">
         <is>
           <t>CO-chatico</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>ECHO – HáblameD Medellín</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Implementación; Análisis</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>organización internacional; gobierno local</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>Mixto</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>Voz a Texto; NLP; LLM</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>IA que capta voz ciudadana en debates guiados y clasifica cada enunciado en metas ODS, generando visualizaciones para la planificación territorial</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
-        </is>
-      </c>
-      <c r="X22" s="2" t="inlineStr">
-        <is>
-          <t>CO-echo-hablamed-medellin</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>(sin revisar)</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>DUDA(lean SI)</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA (múltiples fuentes de prensa independientes; sin verificación técnica del método; cobertura crítica)</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Presupuestos Participativos; Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Análisis; Traducción Política</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
@@ -3228,183 +3225,186 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>organización internacional; gobierno local</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Mixto</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>Voz a Texto; NLP; LLM</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>IA que capta voz ciudadana en debates guiados y clasifica cada enunciado en metas ODS, generando visualizaciones para la planificación territorial</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>CO-echo-hablamed-medellin</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>(sin revisar)</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>DUDA(lean SI)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>MEDIA (múltiples fuentes de prensa independientes; sin verificación técnica del método; cobertura crítica)</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Presupuestos Participativos; Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Análisis; Traducción Política</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>sociedad civil</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Sociedad Civil</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>LLM; NLP</t>
         </is>
       </c>
-      <c r="R23" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>Plataforma participativa donde jóvenes del resguardo Zenú deciden por votación digital la asignación de presupuestos locales del cabildo y debaten proyectos de ley / proponen iniciativas ciudadanas colectivas.</t>
         </is>
       </c>
-      <c r="T23" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
         <is>
           <t>Resguardo indígena Zenú (Reparo Torrente, Bajo Sinú); creador Carlos Redondo Rincón</t>
         </is>
       </c>
-      <c r="U23" s="2" t="inlineStr">
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="V23" s="5" t="n">
+      <c r="V24" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="W23" s="2" t="inlineStr">
+      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>https://cerosetenta.uniandes.edu.co/
 https://gaitanaia.org/
 https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/</t>
         </is>
       </c>
-      <c r="X23" s="2" t="inlineStr">
+      <c r="X24" s="2" t="inlineStr">
         <is>
           <t>CO-gaitana-ia-resguardo-zenu</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Tenemos que hablar de Colombia</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>universidad; empresa; sociedad civil</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>Mixto</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>Academia</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>NLP - Tópicos; NLP - Sentiment</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma colaborativa de diálogo e incidencia ciudadana para la conversación entre diversos actores de la sociedad colombiana, surgido a partir de eventos de manifestaciones sociales.</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>https://tenemosquehablarcolombia.co/
-https://tenemosquehablarcolombia.co/resultados/</t>
-        </is>
-      </c>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t>CO-tenemos-que-hablar-de-colombia</t>
         </is>
       </c>
     </row>
@@ -3412,12 +3412,12 @@
       <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CU</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
+          <t>Tenemos que hablar de Colombia</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital; Referendos e Iniciativas Populares</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3460,182 +3460,182 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
+          <t>universidad; empresa; sociedad civil</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Mixto</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>NLP - Tópicos; NLP - Sentiment</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>Plataforma colaborativa de diálogo e incidencia ciudadana para la conversación entre diversos actores de la sociedad colombiana, surgido a partir de eventos de manifestaciones sociales.</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>https://tenemosquehablarcolombia.co/
+https://tenemosquehablarcolombia.co/resultados/</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>CO-tenemos-que-hablar-de-colombia</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>CU</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Participación Digital; Referendos e Iniciativas Populares</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t>gobierno nacional</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Privado; Academia; Gobierno</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>NLP; Minería de texto; Recuperación de información; Clasificación automática de documentos</t>
         </is>
       </c>
-      <c r="R25" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>Consulta popular legislativa nacional sobre el proyecto del Código de las Familias en Cuba, organizada y supervisada por el Consejo Electoral Nacional (CEN). Se desarrolló entre febrero y abril de 2022 mediante más de 79.000 reuniones en barrios, centros laborales y estudiantiles, con la participación de unos 6.481.200 personas que emitieron opiniones y propuestas sobre el articulado del proyecto de ley. Las propuestas recogidas eran revisadas y clasificadas por juristas en el sistema XISCOP y luego procesadas en el sistema GEMA-CEN, que mediante 'análisis inteligente de los expedientes' agrupaba propuestas similares y determinaba 'propuestas típicas' por párrafo/categoría (se determinaron 5.237 propuestas típicas por Título). XISCOP (UCI) emitía además las estadísticas oficiales. El proceso de consulta cerró en abril de 2022; el Código fue aprobado posteriormente en referendo el 25 de septiembre de 2022.</t>
         </is>
       </c>
-      <c r="T25" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
         <is>
           <t>Consejo Electoral Nacional (CEN) de Cuba como órgano organizador y supervisor de la consulta popular. El procesamiento informático se apoyó en dos sistemas: XISCOP, desarrollado por la Universidad de las Ciencias Informáticas (UCI), para la entrada, revisión, clasificación y estadísticas oficiales; y GEMA-CEN, basado en el producto GEMA de la empresa estatal Datys, para el 'análisis inteligente' y agrupamiento de las propuestas. La Asamblea Nacional del Poder Popular y la Comisión redactora del Ministerio de Justicia recibieron los resultados.</t>
         </is>
       </c>
-      <c r="U25" s="2" t="inlineStr">
+      <c r="U26" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="V25" s="5" t="n">
+      <c r="V26" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="W25" s="2" t="inlineStr">
+      <c r="W26" s="2" t="inlineStr">
         <is>
           <t>http://www.datys.cu/spa/site/product/15
 https://www.granma.cu/cuba/2022-01-24/herramientas-digitales-seran-claves-durante-la-consulta-popular-del-codigo-de-las-familias-24-01-2022-13-01-18
 https://www.uci.cu/</t>
         </is>
       </c>
-      <c r="X25" s="2" t="inlineStr">
+      <c r="X26" s="2" t="inlineStr">
         <is>
           <t>CU-consulta-popular-codigo-de-las-familias</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PAGA IA </t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Referendos e Iniciativas Populares</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>gobierno nacional; sociedad civil</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>Mixto</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>Sociedad Civil</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto. Analiza datos de planes de acción de gobierno abierto de Ecuador y otros países de Hispanoamérica para sugerir actividades e hitos relacionados con temas propuestos por los usuarios</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>https://ia.gobiernoabierto.ec/
-https://ia.gobiernoabierto.ec/acercade</t>
-        </is>
-      </c>
-      <c r="X26" s="2" t="inlineStr">
-        <is>
-          <t>EC-paga-ia</t>
         </is>
       </c>
     </row>
@@ -3643,12 +3643,12 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guatemala Joven Conversa </t>
+          <t xml:space="preserve">PAGA IA </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>organización internacional; sociedad civil</t>
+          <t>gobierno nacional; sociedad civil</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3706,208 +3706,209 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>NLP - Sentiment; NLP - Tópicos</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarrollo y la lucha contra la corrupción.</t>
+          <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto. Analiza datos de planes de acción de gobierno abierto de Ecuador y otros países de Hispanoamérica para sugerir actividades e hitos relacionados con temas propuestos por los usuarios</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
+          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="V27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>https://ia.gobiernoabierto.ec/
+https://ia.gobiernoabierto.ec/acercade</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>EC-paga-ia</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guatemala Joven Conversa </t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Implementación; Análisis</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>organización internacional; sociedad civil</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Mixto</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>NLP - Sentiment; NLP - Tópicos</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarrollo y la lucha contra la corrupción.</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
 https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/
 https://dppa.un.org/en/using-power-of-ai-to-boost-youth-political-participation-guatemala</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
         <is>
           <t>GT-guatemala-joven-conversa</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>HN</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RedPública + iVerify </t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>organización internacional; universidad</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno; Academia</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>Internacional, Nacional</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>NLP - Tópicos</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias. Integra iVerify, una herramienta que utiliza aprendizaje automático para detectar y clasificar desinformación electoral antes de su publicación.</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
-        </is>
-      </c>
-      <c r="X28" s="2" t="inlineStr">
-        <is>
-          <t>HN-redpublica-iverify</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Gobernanza Colaborativa; Participación Digital</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3925,228 +3926,228 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
+          <t>organización internacional; universidad</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>Gobierno; Academia</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>Internacional, Nacional</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>NLP - Tópicos</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias. Integra iVerify, una herramienta que utiliza aprendizaje automático para detectar y clasificar desinformación electoral antes de su publicación.</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>HN-redpublica-iverify</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Gobernanza Colaborativa; Participación Digital</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
           <t>gobierno local</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Gobierno</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>NLP; Otros(no especificado)</t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>Elaboración del Programa de Gobierno del Estado de Guanajuato 2024-2030 ('Gobierno de la Gente'), un plan de gobierno construido con participación ciudadana: se recorrió el territorio y se realizaron cuatro talleres regionales (noreste, norte, centro y sur) con representación de los 46 municipios, integrando la voz de más de 26,000 personas mediante talleres y consultas. El contenido fue validado por el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG), conformado por ciudadanía, la Gobernadora, secretarios de cada eje e IPLANEG. Se utilizaron herramientas de inteligencia artificial para procesar y organizar las miles de ideas y propuestas recibidas, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región, transformando el diálogo social en datos para la toma de decisiones que alimentaron los ejes del programa. Adicionalmente existe la asistente virtual 'Esperanza' para consultar el programa ya publicado.</t>
         </is>
       </c>
-      <c r="T29" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
         <is>
           <t>Gobierno del Estado de Guanajuato — Instituto de Planeación, Estadística y Geografía del Estado de Guanajuato (IPLANEG), con validación del COPLADEG. Titular: Gobernadora Libia Dennise García Muñoz Ledo.</t>
         </is>
       </c>
-      <c r="U29" s="2" t="inlineStr">
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="V29" s="5" t="n">
+      <c r="V30" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="W29" s="2" t="inlineStr">
+      <c r="W30" s="2" t="inlineStr">
         <is>
           <t>https://guanajuatointeligente.com/como-hicimos-el-programa/
 https://iplaneg.guanajuato.gob.mx/programagobierno24-30/
 https://iplaneg.guanajuato.gob.mx/wp-content/uploads/03-2.05-Diagnostico-Programa-de-Gobierno-2024-2030-_Diagnostico-Estatal-2025_.pdf</t>
         </is>
       </c>
-      <c r="X29" s="2" t="inlineStr">
+      <c r="X30" s="2" t="inlineStr">
         <is>
           <t>MX-guanajuato-inteligente-2024-2030</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Presupuesto CRECES</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Presupuestos Participativos</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>gobierno local</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>Privado</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>Chatbot - Inespecífico</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>Presupuesto participativo del Ayuntamiento de Hermosillo en México. Utiliza un chatbot que a través de IA simplifica y facilita la votación de los presupuestos participativos</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>Ayundamiento de Hermosilla</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="V30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
-        </is>
-      </c>
-      <c r="X30" s="2" t="inlineStr">
-        <is>
-          <t>MX-presupuesto-creces</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Análisis; Traducción Política</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
@@ -4154,423 +4155,537 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
+          <t>Uso único</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>gobierno local</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>Chatbot - Inespecífico</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>Presupuesto participativo del Ayuntamiento de Hermosillo en México. Utiliza un chatbot que a través de IA simplifica y facilita la votación de los presupuestos participativos</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>Ayundamiento de Hermosilla</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="V31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>MX-presupuesto-creces</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Análisis; Traducción Política</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>sociedad civil; gobierno nacional</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Sociedad Civil</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea (www.mansaidea.com) es una plataforma digital basada en inteligencia artificial lanzada el 1 de abril de 2024 por la Fundación Panamá Participa (sociedad civil), liderada por Paulina Franceschi. La plataforma organiza y hace navegables más de 175.000 ideas y propuestas ciudadanas generadas durante el Pacto del Bicentenario 'Cerrando Brechas' (proceso participativo nacional convocado por el gobierno de Panamá / Concertación Nacional, presidente Cortizo, 2020-2021), agregando los consensos nacionales y regionales/provinciales por tema en un solo clic. La IA se aplica sobre el CONTENIDO de los aportes ciudadanos (organiza, agrega y sintetiza el corpus de propuestas) para convertirlo en una base de datos navegable. El uso de la IA es un tratamiento PUNTERAL (~2024) de un corpus histórico de un proceso participativo ya cerrado (el Pacto fue 2020-2021), orientado a elevar el nivel de la conversación electoral 2024 y a dotar a candidatos, medios y ciudadanía de una herramienta para alinear planes con las necesidades de la población y monitorear el mandato ciudadano. IMPORTANTE: el proceso participativo original (recolección de aportes) fue convocado por el gobierno; la capa de IA (Mansa Idea) la desarrolla la sociedad civil sobre ese corpus ya recolectado.</t>
         </is>
       </c>
-      <c r="T31" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
         <is>
           <t>Fundación Panamá Participa (sociedad civil, Panamá), iniciativa liderada por Paulina Franceschi. El proceso participativo de origen (Pacto del Bicentenario 'Cerrando Brechas') fue convocado por el Gobierno de Panamá a través del mecanismo de Concertación Nacional para el Desarrollo (presidente Laurentino Cortizo), con apoyo del PNUD.</t>
         </is>
       </c>
-      <c r="U31" s="2" t="inlineStr">
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="V31" s="5" t="n">
+      <c r="V32" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>https://mansaidea.com/ (intentar archive.org / cache); buscar 'Mansa Idea metodología inteligencia artificial procesamiento propuestas' y entrevistas técnicas a Paulina Franceschi / Fundación Panamá Participa.
 https://mansaidea.com/ ; buscar 'Mansa Idea 2025' / 'Mansa Idea 2026' / 'Fundación Panamá Participa actividad reciente'.
 https://mansaidea.com/ ; buscar evidencia de actualizaciones periódicas del corpus o nuevas convocatorias.</t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
         <is>
           <t>PA-mansa-idea-pacto-del-bicentenario</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="J32" s="2" t="n">
+      <c r="J33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>otra institución pública</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="P33" s="2" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
+      <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>NLP - Tópicos; NLP - Sentiment</t>
         </is>
       </c>
-      <c r="R32" s="2" t="inlineStr">
+      <c r="R33" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr">
+      <c r="S33" s="2" t="inlineStr">
         <is>
           <t>Una consulta pública para recoger opiniones sobre el Proyecto Educativo Nacional 2036, utilizando encuestas en línea, talleres y mesas deliberativas.</t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr">
+      <c r="T33" s="2" t="inlineStr">
         <is>
           <t>Consejo Nacional de Educación del Perú</t>
         </is>
       </c>
-      <c r="U32" s="2" t="inlineStr">
+      <c r="U33" s="2" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="V32" s="4" t="n">
+      <c r="V33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W32" s="2" t="inlineStr">
+      <c r="W33" s="2" t="inlineStr">
         <is>
           <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional
 https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080
 https://andina.pe/agencia/noticia-usan-inteligencia-artificial-para-formular-proyecto-educativo-nacional-al-2036-777369.aspx</t>
         </is>
       </c>
-      <c r="X32" s="2" t="inlineStr">
+      <c r="X33" s="2" t="inlineStr">
         <is>
           <t>PE-consulta-ciudadana-sobre-el-proyecto-nac</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>➜ RESCATADO → ENTRA (criterio corregido)</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>DUDA(lean NO)</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="J33" s="2" t="n">
+      <c r="J34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>gobierno nacional</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>apoyo</t>
         </is>
       </c>
-      <c r="O33" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr">
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>Chatbot - Inespecífico</t>
         </is>
       </c>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) es la plataforma de participacion ciudadana del Ministry of Digital Transformation de Trinidad y Tobago (desde mayo 2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), lanzada en el simposio del NDTS el 12 de febrero de 2025 junto al BID (IDB). Se usa como canal de participacion en el proceso de planificacion nacional del National Digital Transformation Strategy (NDTS) 2024-2027, donde ciudadanos, empresas y partes interesadas reciben actualizaciones y aportan retroalimentacion via encuestas, sondeos (polls), un 'Open Forum' de ideas y el envio de propuestas. La instancia corre sobre el software Go Vocal (antes CitizenLab) -confirmado por la ruta interna 'projects/e-democracy-govocal-internal'-. Go Vocal incorpora un modulo de IA/NLP de 'Sensemaking' (analisis y resumen automatico de aportes), pero ese modulo NO viene activo por defecto: segun la documentacion de soporte de Go Vocal, el acceso a la funcion de AI Analysis/Sensemaking DEPENDE DEL PLAN contratado (Advanced Sensemaking con auto-insights esta en el plan Premium). Tras 2a pasada de investigacion (&gt;=14 busquedas/fetches) NO se halla evidencia alguna de que la instancia de Trinidad active ni use esas funciones de IA sobre el CONTENIDO de los aportes; toda la documentacion describe a EngageTT como recolector (surveys, polls, Open Forum, ideas), es decir plataforma usada como formulario sin analisis automatico confirmado. Existe ademas AskNDTS, un chatbot/PWA de IA conversacional para responder preguntas sobre el NDTS (rol de FAQ informativo, EXCLUIDO del criterio).</t>
         </is>
       </c>
-      <c r="T33" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
         <is>
           <t>Ministry of Digital Transformation de Trinidad y Tobago (desde el 23-may-2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), en colaboracion con el Banco Interamericano de Desarrollo (BID/IDB). Plataforma de software: Go Vocal (antes CitizenLab), empresa belga.</t>
         </is>
       </c>
-      <c r="U33" s="2" t="inlineStr">
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="V33" s="5" t="n">
+      <c r="V34" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="W33" s="2" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
         <is>
           <t>https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan
 https://www.govocal.com/plans
 https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool</t>
         </is>
       </c>
-      <c r="X33" s="2" t="inlineStr">
+      <c r="X34" s="2" t="inlineStr">
         <is>
           <t>TT-engagett-plataforma-go-vocal</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr"/>
-      <c r="B34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>UY</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>(sin revisar)</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>MEDIA (fuente primaria + OCDE 2025; fetch primario bloqueado por proxy, citas vía repo/WebSearch)</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="J34" s="2" t="n">
+      <c r="J35" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>universidad</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Sociedad Civil</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>Clustering; ML - Inespecífico</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
         <is>
           <t>Referéndum nacional para derogar 135 artículos de la Ley de Urgente Consideración (LUC). Un equipo de la Universidad de la República corrió una conversación Pol.is en paralelo al referéndum del 27/03/2022 (documentado como caso 2021).</t>
         </is>
       </c>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="T35" s="2" t="inlineStr">
         <is>
           <t>Equipo de 13 personas de la Universidad de la República (UdelaR) — ingenieros, comunicadores y científicos de datos; plataforma Pol.is (The Computational Democracy Project)</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr">
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="V34" s="5" t="n">
+      <c r="V35" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="W34" s="2" t="inlineStr">
+      <c r="W35" s="2" t="inlineStr">
         <is>
           <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/</t>
         </is>
       </c>
-      <c r="X34" s="2" t="inlineStr">
+      <c r="X35" s="2" t="inlineStr">
         <is>
           <t>UY-polis-referendum-luc</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X34"/>
+  <autoFilter ref="A1:X35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7585,7 +7700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7934,35 +8049,100 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>Meta Community Forum on Generative AI — cohorte Brasil (Deliberative Polling, Stanford)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>scientific samples from Brazil, Germany, Spain, and the United States (deliberation.stanford.edu/meta-community-forum-generative-ai-results)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>On October 28-29, 2023, participants from these countries gathered on the Stanford Online Deliberation Platform... to consider future directions for the development of AI chatbots (deliberation.stanford.edu)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Moderación automatizada de la deliberación en grupos pequeños = apoyo a la IMPLEMENTACIÓN (verbatim del moderador, informe Stanford DDL/FSI)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Deliberación 28-29 oct 2023; '2023 Results Announced' (abr-2024) — proceso concluido (deliberation.stanford.edu)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Uso único: foro de oct-2023; el foro 2024 de 'AI Agents' NO incluyó a Brasil (deliberation.stanford.edu / FSI)</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Foro de Meta diseñado y ejecutado por el Stanford Deliberative Democracy Lab; BIT 'designed and delivered' foros 'on Meta's behalf' (transparency.meta.com; bi.team)</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>the small group discussion sessions were conducted using the Stanford Online Deliberation Platform, developed by the Deliberative Democracy Lab and the Stanford Crowdsourcing Democracy Team, with participants each assigned to rooms of 8-12 people (bi.team/blogs/metas-community-forum-on-ai — socio ejecutor)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>[La plataforma] moderated the video based discussions, controlled the queue for talking, nudged those who had not volunteered to talk, intervened if there was incivility, and moved the group through the agenda... 'the AI-assisted featured moderator' (informe Stanford DDL/FSI, PDF oficial leído íntegro)</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>https://deliberation.stanford.edu/meta-community-forum-generative-ai-results
+https://transparency.meta.com/governance/community-forums/2023-community-forum-on-generative-AI/
+https://about.fb.com/news/2024/04/leading-the-way-in-governance-innovation-with-community-forums-on-ai/
+https://cddrl.fsi.stanford.edu/publication/meta-community-forum-results-analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>OPA Piauí - Orçamento Participativo Digital (Colab + AWS)</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>OPA é o Orçamento Participativo 100% digital do Governo do Estado do Piauí, em parceria com a Colab. (Colab, 'OPA, Colab e a participação digital no Piauí')</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>OPA é o Orçamento Participativo 100% digital do Governo do Estado do Piauí... Após analisar a viabilidade das propostas, o Governo do Estado disponibilizará uma votação por meio da Colab para que qualquer cidadão acima de 16 anos com CPF possa votar no que considera mais importante para o seu município. (Colab)</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr"/>
-      <c r="G6" s="11" t="inlineStr"/>
-      <c r="H6" s="11" t="inlineStr"/>
-      <c r="I6" s="11" t="inlineStr"/>
-      <c r="J6" s="11" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr"/>
+      <c r="G7" s="11" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr"/>
+      <c r="I7" s="11" t="inlineStr"/>
+      <c r="J7" s="11" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Todo esse processo é realizado por meio da plataforma Colab Gov... O sistema utiliza tecnologia da AWS, referência mundial em segurança digital. (la IA/tecnología se presenta como soporte operativo, de eficiencia y de seguridad del flujo, no como análisis del contenido de las propuestas → rol de apoyo)</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/
 https://sia.pi.gov.br/projetos/opa/
@@ -7976,68 +8156,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Plan Plurianual de la ciudad de Natal</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Governanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Implementación, Análisis</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>reconfirmado web (institucional): Reconfirmado: modelos de lenguaje identifican el tema de cada mensaje ciudadano por WhatsApp; nueva edición PPA 2026-2029 'Plano Natal Pra Frente'.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Plataforma</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Prefeitura Municipal de Natal, a través de la Secretaría Municipal de Planeamiento (SEMPLA)</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
@@ -8046,118 +8164,180 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>Plan Plurianual de la ciudad de Natal</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Governanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Implementación, Análisis</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>reconfirmado web (institucional): Reconfirmado: modelos de lenguaje identifican el tema de cada mensaje ciudadano por WhatsApp; nueva edición PPA 2026-2029 'Plano Natal Pra Frente'.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Plataforma</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Prefeitura Municipal de Natal, a través de la Secretaría Municipal de Planeamiento (SEMPLA)</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>Portal e-Cidadania: Marcado automático de respuestas ciudadanas en videos de audiencias públicas</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Traducción Política</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado 2025: la IA analiza transcripciones de 1.800+ audiencias y marca 2.700+ preguntas ciudadanas como respondidas.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Plataforma</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Senado Federal de Brasil</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Identificar y marcar momentos en los videos donde las preguntas ciudadanas fueron respondidas, ya sea directa o indirectamente.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Identificar y marcar momentos en los videos donde las preguntas ciudadanas fueron respondidas, ya sea directa o indirectamente.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias
 https://ipen-network.org/spotlight-on-public-engagement-practice-brazil/</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>São Paulo - Programa de Metas / Participe Mais (Gemini)</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Programa de Metas 2025-2028, PPA e PAS 2026-2029 - portal Participe Mais da Prefeitura de São Paulo (participemais.prefeitura.sp.gov.br/legislation/processes/323).</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>as sugestões enviadas pela população para o PPA (Plano Plurianual) 2026-2029, durante a consulta pública do Programa de Metas no portal Participe Mais, que é a plataforma de participação social da Prefeitura</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Em maio de 2025, foi elaborada uma ferramenta que classifica as propostas para o Programa de Metas em categorias e as ordena por assunto e quantidade de apoios, facilitando a divulgação das propostas. (...) exibição dos relatórios e painéis visuais gerados pela análise destacam: ranking dos temas mais recorrentes; participação em cada distrito e subprefeitura</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Após o Ciclo Participativo, com 36 audiências públicas híbridas pela cidade (abril e maio), recebimento de 6.368 propostas e mais de 31 mil interações dos cidadãos (...) através do site de consultas públicas da Prefeitura - ParticipeMais, a gestão incorporou seis metas a mais à versão inicial de 126</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Em maio de 2025, foi elaborada uma ferramenta que classifica as propostas para o Programa de Metas em categorias e as ordena por assunto e quantidade de apoios (...) No desenvolvimento da ferramenta foram utilizados conhecimentos em dados abertos, inteligência artificial e gestão pública.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>através do site de consultas públicas da Prefeitura - ParticipeMais, a gestão incorporou seis metas a mais à versão inicial de 126</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>A metodologia demonstra a solução com exposição de trechos de código e explicação das tecnologias utilizadas: Python, Pandas, Google Gemini. (...) desafios reais encontrados, como o alto volume de dados, otimização do tempo de análise e ajustes necessários nos comandos para a Inteligência Artificial</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>uma ferramenta que classifica as propostas para o Programa de Metas em categorias e as ordena por assunto e quantidade de apoios</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>https://www.saopaulo.sp.leg.br/escoladoparlamento/cursos/em-andamento/oficina-analise-de-dados-com-inteligencia-artificial-na-gestao-publica-programa-de-metas/
 https://www.saopaulo.sp.leg.br/escoladoparlamento/cursos/cursos-anteriores/cursos-realizados-em-2025/oficina-analise-de-dados-com-inteligencia-artificial-na-gestao-publica-programa-de-metas/
@@ -8173,63 +8353,63 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>e-Cidadania Senado - IA matching de ideas legislativas</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Cidadãos ajudam a escrever projetos de lei com ferramenta de inteligência artificial — Senado Notícias (Senado Federal, Brasil), 16/01/2026.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>uma nova ferramenta de inteligência artificial criada pelo Senado permite que ideias enviadas ao portal e-Cidadania influenciem projetos de lei — mesmo quando não atingem o número mínimo de apoios antes exigido</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Com o uso da inteligência artificial, é feita uma busca no banco de ideias legislativas e, então, são selecionadas aquelas que são compatíveis com a proposta em questão. As ideias selecionadas podem ser incorporadas ao projeto e citadas em sua justificação</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>IA vai aproximar ideias legislativas do e-Cidadania a projetos de senadores — Rádio Senado, 15/01/2026 (matéria de divulgação da ferramenta em uso no início de 2026)</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>O primeiro resultado já veio: uma sugestão enviada por Cândida Magalhães, de São Paulo, que pedia atendimento psicológico gratuito para filhos de mulheres vítimas de violência doméstica, foi identificada pela ferramenta e incorporada a um projeto de lei: o PL 6.125/2025</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>uma nova ferramenta de inteligência artificial criada pelo Senado</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Quando um senador pede ajuda à Consultoria Legislativa para elaborar um projeto, a equipe de consultores solicita ao e-Cidadania uma lista de sugestões feitas pelos cidadãos. Com o uso da inteligência artificial, é feita uma busca no banco de ideias legislativas</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Com o uso da inteligência artificial, é feita uma busca no banco de ideias legislativas e, então, são selecionadas aquelas que são compatíveis com a proposta em questão</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial
 https://www.poder360.com.br/poder-congresso/ia-do-senado-usa-sugestoes-enviadas-por-cidadaos-em-projetos-de-lei/
@@ -8241,63 +8421,63 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Cabildos 2016</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (academico): Evidencia académica del NLP sobre los cabildos 2016: argument mining sobre 240.468 argumentos (ACL 2017, UChile/DCC) y Structural Topic Modeling (PLOS One 2022)</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Biblioteca del Congreso Nacional</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Clasificación y análisis de texto para identificar conceptos clave</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Clasificación y análisis de texto para identificar conceptos clave</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>https://www.bcn.cl/procesoconstituyente/cabildos2016/
 https://aclanthology.org/W17-5101/
@@ -8305,63 +8485,63 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>El Chile que Queremos (ECQQ) - MinCiencia</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>El Chile que Queremos cierra etapa de diálogos con más de 130 mil participantes en las 345 comunas del país (titular de noticia del Ministerio de Desarrollo Social y Familia - Gobierno de Chile).</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>El Gobierno presentó la iniciativa el viernes 22 de noviembre de 2019. La participación fue posible hasta el 31 de marzo a través de diálogos ciudadanos o consultas individuales en www.chilequequeremos.cl (gob.cl).</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Este repositorio contiene los procedimientos para realizar la clasificación de las contribuciones con redes neuronales (README del repositorio MinCiencia/ECQQ, carpeta contributions_rnn).</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>130.810 personas participaron en los Diálogos Ciudadanos impulsados por El Chile Que Queremos, desde noviembre de 2019 hasta marzo de 2020. La decisión de concluir anticipadamente los diálogos ciudadanos fue parte de las medidas del gobierno para frenar la propagación del COVID-19, aunque la plataforma permaneció abierta hasta el 31 de marzo de 2020.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>130.810 personas participaron en los Diálogos Ciudadanos impulsados por El Chile Que Queremos, desde noviembre de 2019 hasta marzo de 2020 (proceso único, una sola edición).</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>El Gobierno presentó 'El Chile que Queremos', iniciativa de diálogos y escucha social para avanzar en nuevas propuestas para el país. La iniciativa fue un esfuerzo conjunto entre los Ministerios de Desarrollo Social y Familia, de Ciencia, Tecnología, Conocimiento e Innovación, de Agricultura, la Secretaría General de Gobierno y la División de Gobierno Digital (gob.cl / desarrollosocialyfamilia.gob.cl).</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>La información recibida de la ciudadanía es sistematizada por el Ministerio de Ciencias, siendo la ciencia de datos una herramienta clave para este amplio y participativo ejercicio de escucha. / clasificación de las contribuciones con árboles de decisión (README MinCiencia/ECQQ).</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>Grouping Emotions.ipynb que sirve para sistematizar las Emociones / Analisis de Topicos - Necesidades.ipynb que sirve para sistematizar tanto las necesidades personales como las del país (README MinCiencia/ECQQ).</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>https://github.com/MinCiencia/ECQQ
 https://www.desarrollosocialyfamilia.gob.cl/noticias/el-chile-que-queremos-cierra-etapa-de-dialogos-con-mas-de-130-mil-participantes-en-las-345-comunas-d
@@ -8373,248 +8553,248 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Cerrado</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Secretaría de Gobierno Digital</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Identificar patrones, sintetizar las principales críticas y estructurar las conclusiones de manera clara y coherente de datos cualitativos en encuesta de consulta ciudadana</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Identificar patrones, sintetizar las principales críticas y estructurar las conclusiones de manera clara y coherente de datos cualitativos en encuesta de consulta ciudadana</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030
 https://participacion.digital.gob.cl/folders/consultas-ciudadanas</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Estudio dIAlogos - Percepciones de Futuro</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Implementación, Análisis</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Cerrado</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Fundación Encuentros del Futuro y Merlín Research</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Realización de entrevistas y codificación de respuestas</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>Realización de entrevistas y codificación de respuestas</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>https://estudiodialogos.cl/
 https://fairlac.iadb.org/en/dialogos-study-perceptions-future</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Cerrado</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Universidad Andres Bello</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Identificar tópicos y organizarlos demográficamente para generar visualizaciones</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>Identificar tópicos y organizarlos demográficamente para generar visualizaciones</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>https://ipp.unab.cl/
 https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>LXS 400 - Chile Delibera</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>In 2020, the Senate of Chile partnered with the Stanford Center for Deliberative Democracy to involve citizens in the online deliberative process 'LXS 400 - Chile Delibera' performed through the Stanford Online Deliberation Platform. (OCDE 2025, 'AI in civic participation and open government')</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Over 500 citizens representative of the Chilean society discussed in small groups and deliberated in plenary sessions on health and pension reforms. (OCDE 2025) / Entre el 5 y el 7 de marzo, 400 personas seleccionadas a traves de una metodologia aleatoria y representativas de todo Chile se reunieron para deliberar sobre dos de los temas publicos mas importantes para el pais: pensiones y salud.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>The platform used an AI tool to keep time and distribute speaking rights equitably, allowing participants to form speaking queues and discuss in small groups with timed agendas. (OCDE 2025) / El Centro de Microdatos de la Universidad de Chile, usando tecnologia basada en Inteligencia Artificial (IA), selecciono esta muestra representativa.</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Lxs 400: Chile Delibera... es un evento de participacion ciudadana de escala nacional realizado en Chile desde el 9 de diciembre de 2020, con su evento principal a fines de marzo de 2021. (Wikipedia ES) [Evento puntual de una edicion 2020-2021; no se hallaron ediciones posteriores recurrentes].</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>La iniciativa fue impulsada por la Fundacion Tribu; el Senado a traves de la Comision de Desafios del Futuro; la Asociacion Chilena de Municipalidades; la Universidad de Chile; y el Centro para la Democracia Deliberativa de la Universidad de Stanford.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>The platform used an AI tool to keep time and distribute speaking rights equitably... (OCDE 2025) [confirma que SI se uso IA dentro del proceso, en rol de facilitacion/logistica].</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>The platform used an AI tool to keep time and distribute speaking rights equitably, allowing participants to form speaking queues and discuss in small groups with timed agendas. (OCDE 2025) / An automated moderator controls perspective elicitation, with an automated cue system to determine which participant to elicit a perspective from next and an automated timer to determine how long each participant has to state their perspective. (descripcion de la Stanford Online Deliberation Platform)</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>https://www.oecd.org/en/publications/2025/06/governing-with-artificial-intelligence_398fa287/full-report/ai-in-civic-participation-and-open-government_51227ce7.html
 https://deliberation.stanford.edu/news/lxs-400-national-deliberative-poll-chile
@@ -8626,131 +8806,69 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>La voz de los nuevos votantes</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Implementación, Análisis</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Cerrado</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Universidad Andres Bello</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Análisis de transcripciones para identificación de temas y palabras clave.</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Análisis de transcripciones para identificación de temas y palabras clave.</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf
 https://ipp.unab.cl/publicacion/la-voz-de-los-nuevos-votantes-san-bernardo/</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Participación Ciudadana Proceso Constitucional</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Governanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>BBDD 2025: Cerrado</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Secretaría de Participación Ciudadana</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
-        </is>
-      </c>
-    </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -8759,118 +8877,180 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>Participación Ciudadana Proceso Constitucional</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Governanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>BBDD 2025: Cerrado</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Secretaría de Participación Ciudadana</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>Tenemos que hablar de Chile</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Cerrado</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Universidad de Chile y Pontificia Universidad Católica de Chile</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>https://www.tenemosquehablardechile.cl/
 https://static1.squarespace.com/static/630d0dbf05b8104ed4d55d7f/t/67f694b2f91e4f228bb941cb/1744213189210/01.+Primer-InformeTQHDCH.pdf</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Un encuentro para la equidad de género en la movilidad en Chile</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Cerrado</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Universidad Andres Bello</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Análisis temático de las transcripciones de las mesas</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>Análisis temático de las transcripciones de las mesas</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>https://ipp.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/
 https://noticiasrepositorio.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/
@@ -8878,63 +9058,63 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Chatico</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares, Presupuestos Participativos</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado 2024-2028: NLP y tecnologías semánticas procesaron 147.422 participaciones (10% propuestas libres) para el Plan Distrital de Desarrollo. Citado por</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Plataforma</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Secretaría General de la Alcaldía Mayor de Bogotá</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Interactuar con ciudadanos, responder consultas y plataforma para votar en causas ciudadanas y presupuesto participativo</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>Interactuar con ciudadanos, responder consultas y plataforma para votar en causas ciudadanas y presupuesto participativo</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>https://secretariageneral.gov.co/noticias/chatico-el-agente-virtual-de-servicio-la-ciudadania-supero-los-36-millones-de-conversaciones
 https://bogota.gov.co/mi-ciudad/gestion-publica/distrito-presenta-su-agente-virtual-chatico-que-guia-la-ciudadania
@@ -8942,68 +9122,6 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>ECHO – HáblameD Medellín</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Governanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Implementación, Análisis</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>reconfirmado web (institucional): Reconfirmado: la IA del UNFPA clasifica por ODS las conversaciones ciudadanas captadas en campo (5.000+ personas, 16 comunas).</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
-        </is>
-      </c>
-    </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
@@ -9012,177 +9130,239 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
+          <t>ECHO – HáblameD Medellín</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Governanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Implementación, Análisis</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>reconfirmado web (institucional): Reconfirmado: la IA del UNFPA clasifica por ODS las conversaciones ciudadanas captadas en campo (5.000+ personas, 16 comunas).</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>DUDA(lean SI)</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>la herramienta de un resguardo indígena (Zenú, Bajo Sinú, Colombia) para llegar al Congreso (La Silla Vacía)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>a platform for young people in the Zenú community to decide, through digital voting, how they wanted to allocate local budgets</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>The AI summarizes proposals, organizes consensus, and facilitates collective decision-making</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>More than 10,000 users participate in the chatbot at gaitanaia.org, whose discussions feed the community's positions and proposals</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Gaitana IA is a tool created by Carlos Redondo Rincón ... a platform for young people in the Zenú community</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Gaitana is built on the DeepSeek large language model, adapted to the Zenú worldview ... summarizes proposals, organizes consensus</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>artificial intelligence organizes opinions, processes trends and builds consensuses that, if approved, would become legislative initiatives (KienyKe)</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/
 https://www.kienyke.com/</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Tenemos que hablar de Colombia</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Cerrado</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>https://tenemosquehablarcolombia.co/
 https://tenemosquehablarcolombia.co/resultados/</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>CU</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Para agilizar la recogida y el procesamiento de los criterios, la Universidad de las Ciencias Informáticas (UCI) y Datys diseñaron dos sistemas informáticos de gestión (XISCOP y GEMA-CEN) [proceso de consulta popular del Código de las Familias en Cuba].</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>consulta popular del proyecto del Código de las Familias (...) la Universidad de las Ciencias Informáticas (UCI) y Datys diseñaron dos sistemas informáticos de gestión (XISCOP y GEMA-CEN)</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>luego se sube a GEMA-CEN (también operado por especialistas) que, a través del análisis inteligente de los expedientes, organiza las propuestas y agrupa las similares, facilitando el trabajo y evitando errores. GEMA-CEN permite determinar las propuestas típicas para un párrafo en cada una de las categorías establecidas</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Más de seis millones 481 mil personas participaron en las reuniones (...) la consulta popular del proyecto del Código de las Familias (...) convocada entre febrero y abril [de 2022]; del total de propuestas procesadas se determinaron 5 237 propuestas típicas por Título</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>del total de propuestas procesadas se determinaron 5 237 propuestas típicas por Título, conformadas a partir de la asociación de propuestas idénticas y de aquellas con redacción diferente pero referidas al mismo criterio u opinión</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>La consulta popular (...) fue organizada y supervisada por el Consejo Electoral Nacional (CEN) [órgano del Estado cubano]; los resultados se entregaron al Parlamento (Asamblea Nacional) y a su Comisión redactora</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>se sube a GEMA-CEN (...) que, a través del análisis inteligente de los expedientes, organiza las propuestas y agrupa las similares (...) permite determinar las propuestas típicas para un párrafo en cada una de las categorías establecidas</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>GEMA es una herramienta para el análisis de información contenida en grandes volúmenes de archivos de diferentes formatos e idiomas, con funcionalidades orientadas a la recuperación y clasificación de información (...) complementando los resultados mediante técnicas modernas de recuperación de información para obtener archivos similares, eliminar resultados no relevantes y agrupar documentos comunes</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>http://www.datys.cu/spa/site/product/15
 https://www.granma.cu/cuba/2022-01-24/herramientas-digitales-seran-claves-durante-la-consulta-popular-del-codigo-de-las-familias-24-01-2022-13-01-18
@@ -9194,65 +9374,65 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>EC</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PAGA IA </t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado: integrada al Tercer Plan de Acción de Estado Abierto 2025-2027; analiza las propuestas ciudadanas y sugiere actividades.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Plataforma</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto
 </t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto
 </t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>https://ia.gobiernoabierto.ec/
 https://ia.gobiernoabierto.ec/
@@ -9260,63 +9440,63 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Guatemala Joven Conversa </t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado: diálogos digitales con IA (DPPA ONU + Fundación Esquipulas); 300+ jóvenes; la IA permite intercambios anónimos y votación de aportes para identifi</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
 https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/
@@ -9324,125 +9504,125 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>HN</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RedPública + iVerify </t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Referendos e Iniciativas Populares</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>reconfirmado web (institucional): Reverificación: plataforma de propuestas ciudadanas con módulo de análisis de tendencias; evidencia de IA central débil, revisar en Fase 2.</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RedPública + iVerify </t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Referendos e Iniciativas Populares</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>reconfirmado web (institucional): Reverificación: plataforma de propuestas ciudadanas con módulo de análisis de tendencias; evidencia de IA central débil, revisar en Fase 2.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Guanajuato hará historia con el primer Programa de Gobierno realizado con IA</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Para integrar la participación ciudadana en este Programa de Gobierno, se realizaron cuatro talleres cubriendo las regiones noreste, norte, centro y sur, con representación de los 46 municipios de Guanajuato.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>El Programa de Gobierno de Guanajuato 2024-2030 es la guía que orienta las acciones del Gobierno de la Gente para lograr un Guanajuato sostenible, equitativo y transparente.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Su diseño incorporó el uso de inteligencia artificial para integrar más de 26 mil voces de distintas regiones y sectores</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>El Programa de Gobierno 2024-2030 hizo historia al ser el primero en realizarse con ayuda de la Inteligencia Artificial (IA), según anunció la Gobernadora Libia Dennise García Muñoz Ledo en el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG).</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía.</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>https://guanajuatointeligente.com/como-hicimos-el-programa/
 https://guanajuatointeligente.com/
@@ -9455,121 +9635,121 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Presupuesto CRECES</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Presupuestos Participativos</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>BBDD 2025: Activo</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Ayundamiento de Hermosilla</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
-        </is>
-      </c>
-    </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Presupuesto CRECES</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Presupuestos Participativos</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>BBDD 2025: Activo</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Ayundamiento de Hermosilla</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>La Fundación Panamá Participa lanzó Mansa Idea (www.mansaidea.com), una plataforma basada en inteligencia artificial que recoge miles de propuestas ciudadanas... iniciativa de alcance nacional que se nutre de ideas y propuestas que miles de panameños hicieron durante el desarrollo del Pacto del Bicentenario. (Panamá; fuentes panama24horas.com.pa y laestrella.com.pa)</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea, resultado del Pacto del Bicentenario, ofrece acceso fácil y transparente a más de 175 mil ideas y propuestas generadas por ciudadanos de todo el país. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales. (la IA agrega/organiza/sintetiza el contenido de las propuestas por tema y territorio = Análisis + Traducción Política; el método técnico exacto no se detalla en las fuentes).</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>La plataforma fue lanzada el 1 de abril de 2024... constituye una herramienta valiosa de participación ciudadana muy relevante para ciudadanos, candidatos a cargos de elección popular y medios durante la campaña electoral y luego como recurso para el monitoreo del mandato ciudadano. (un despliegue concreto de la plataforma, 2024; sin evidencia de ediciones recurrentes).</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>La Fundación Panamá Participa lanzó Mansa Idea... iniciativa liderada por Paulina Franceschi a través de la Fundación Panamá Participa (sociedad civil). El proceso participativo de origen: 'El 26 de noviembre de 2020, el presidente Laurentino Cortizo Cohen lanzó la iniciativa denominada Pacto del Bicentenario Cerrando Brechas' (gobierno nacional / Concertación Nacional).</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. (la IA procesa el contenido de las propuestas del proceso participativo).</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía. (agregación/síntesis de los aportes ciudadanos = rol sobre el contenido).</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>https://www.panama24horas.com.pa/panama/fundacion-panama-participa-lanza-plataforma-de-propuestas-ciudadanas-mansa-idea/
 https://www.laestrella.com.pa/panama/politica/mansa-idea-una-herramienta-digital-con-propuestas-para-candidatos-YD6746221
@@ -9580,63 +9760,63 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (prensa): VERIFICADO (fuente primaria): el CNE usó IBM Watson Discovery + Studio (ML/NLP) sobre 87.991 documentos de aportes ciudadanos de 847 eventos y 49 espacios de di</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Consejo Nacional de Educación del Perú</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional
 https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080
@@ -9645,59 +9825,59 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Project: National Digital Transformation Strategy | Ministry of Digital Transformation, Trinidad and Tobago (engage.gov.tt/projects/national-digital-transformation-strategy). Ruta interna confirmatoria: engage.gov.tt/projects/e-democracy-govocal-internal (la instancia corre sobre Go Vocal). En 2026: 'Projects | Ministry of Public Administration and Artificial Intelligence' (engage.gov.tt/projects).</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>EngageTT es una plataforma en linea (engage.gov.tt) donde ciudadanos, empresas y partes interesadas pueden recibir actualizaciones en tiempo real sobre iniciativas de transformacion digital y ofrecer retroalimentacion via encuestas y sondeos (polls); el Ministro anima a todos a participar y enviar ideas y comentarios sobre el NDTS, que se disena para evolucionar mediante el compromiso y la colaboracion continuos. Incluye un 'Open Forum' (engage.gov.tt/ideas/open-forum) y 'Input: Submitting Proposals' (engage.gov.tt/ideas/submitting-proposals).</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>The National Strategy for a Digital TT is finalized, and while the Ministry of Digital Transformation is no longer seeking input, they welcome feedback or comments through the citizen engagement digital platform Engage TT. (engage.gov.tt sigue operativo en 2026 bajo MPAAI).</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>The Ministry of Digital Transformation (MDT) officially presented the National Digital Transformation Strategy (NDTS) 2024-2027... launched during a NDTS Symposium in collaboration with the Inter-American Development Bank (IDB) on Wednesday, February 12th 2025. A major highlight... was the introduction of two new digital tools (EngageTT y AskNDTS). (Lanzamiento/anuncio unico en feb-2025; plataforma de uso continuo pero sin &gt;=2 ediciones de proceso participativo documentadas).</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>The Ministry of Digital Transformation (MDT) officially presented the National Digital Transformation Strategy (NDTS) 2024-2027... and introduced the EngageTT website - an online platform where citizens, businesses, and stakeholders can get real-time updates on digital transformation initiatives, and offer feedback via surveys and polls. (Convocante: gobierno nacional / Ministry of Digital Transformation, hoy MPAAI).</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Go Vocal Support Base (AI Analysis): 'Access to this feature depends on your plan. Advanced Sensemaking with auto-insights is available in the Premium plan.' -&gt; la IA/NLP de Go Vocal NO es automatica, depende del plan; y para EngageTT solo se documenta 'feedback via surveys and polls'/Open Forum/ideas, SIN mencion de analisis automatico por IA de los aportes. No se halla evidencia de activacion del NLP sobre el contenido en la instancia TT. 3a PASADA (refuerzo): Oxford Insights, 'The country's AI utilisation for citizens is concentrated in a robust Chatbot programme' (mas 'deployment of large language models for internal development purposes') -&gt; la IA ciudadana de TT es el chatbot, NO el analisis de aportes.</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Sin evidencia de IA aplicada al contenido de los aportes en engage.gov.tt. La unica IA confirmada de cara al ciudadano (AskNDTS/ANANSI) es chatbot de FAQ, excluido del criterio. En 3a pasada, el material de MPAAI 2026 enmarca la IA en el asistente ANANSI y en encuestas de AI-readiness (resultados 'consolidated and reviewed' en talleres), sin mencion de analisis por IA de los aportes del NDTS ni de Go Vocal Sensemaking.</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>https://support.govocal.com/en/articles/8316692-ai-analysis
 https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool
@@ -9719,59 +9899,59 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>UY</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Polis has been used to facilitate discussion and build consensus ... in Uruguay on a national referendum (OCDE 2025, 'Governing with AI')</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists — ran Polis alongside the referendum</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>The algorithm maps participants' responses and clusters opinions, facilitating the identification of positions that are supported by the majority of participants (OCDE 2025)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>16,499 people cast more than 295,000 votes ... The referendum was lost by less than 1%</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>ran Polis alongside the referendum to look for something deeper than "yes or no"</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Polis revealed that even where public safety divided people, surprising points of consensus broke through on other issues — bridges between groups</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/
 https://www.oecd.org/en/publications/governing-with-artificial-intelligence_795de142-en.html</t>
@@ -9779,7 +9959,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L34"/>
+  <autoFilter ref="A1:L35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9813,7 +9993,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>Planilla con 6 pestañas (criterio corregido). 33 casos entran/dudosos · 74 excluidos · 107 en total. Tras dedup e-Cidadania: 32 iniciativas.</t>
+          <t>Planilla con 6 pestañas (criterio corregido). 34 casos entran/dudosos · 74 excluidos · 107 en total. Tras dedup e-Cidadania: 33 iniciativas.</t>
         </is>
       </c>
     </row>
